--- a/BACKEND/EjemplosExcels/file-AF.xlsx
+++ b/BACKEND/EjemplosExcels/file-AF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVS-System\BACKEND\EjemplosExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F550E0-362F-49DA-B60B-842EF3ED287B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46DE0A7-6025-4E25-824E-87FADEAD095B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -678,7 +678,7 @@
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -711,7 +711,7 @@
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -744,7 +744,7 @@
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -779,7 +779,7 @@
         <v>33</v>
       </c>
       <c r="K5" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -814,7 +814,7 @@
         <v>33</v>
       </c>
       <c r="K6" s="11">
-        <v>99</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -847,7 +847,7 @@
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/BACKEND/EjemplosExcels/file-AF.xlsx
+++ b/BACKEND/EjemplosExcels/file-AF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVS-System\BACKEND\EjemplosExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46DE0A7-6025-4E25-824E-87FADEAD095B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE425A1-A60D-4F95-95FA-40A13263A53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>Apellido y nombre</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>DNI - 49062828</t>
+  </si>
+  <si>
+    <t>1ro</t>
   </si>
 </sst>
 </file>
@@ -677,8 +680,8 @@
         <v>16</v>
       </c>
       <c r="J2" s="10"/>
-      <c r="K2" s="11">
-        <v>33</v>
+      <c r="K2" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -710,8 +713,8 @@
         <v>16</v>
       </c>
       <c r="J3" s="10"/>
-      <c r="K3" s="11">
-        <v>33</v>
+      <c r="K3" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -743,8 +746,8 @@
         <v>28</v>
       </c>
       <c r="J4" s="10"/>
-      <c r="K4" s="11">
-        <v>33</v>
+      <c r="K4" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -778,8 +781,8 @@
       <c r="J5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="11">
-        <v>33</v>
+      <c r="K5" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -813,8 +816,8 @@
       <c r="J6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="11">
-        <v>33</v>
+      <c r="K6" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -846,8 +849,8 @@
         <v>16</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="11">
-        <v>33</v>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/BACKEND/EjemplosExcels/file-AF.xlsx
+++ b/BACKEND/EjemplosExcels/file-AF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVS-System\BACKEND\EjemplosExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D46DE0A7-6025-4E25-824E-87FADEAD095B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F550E0-362F-49DA-B60B-842EF3ED287B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -678,7 +678,7 @@
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -711,7 +711,7 @@
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -744,7 +744,7 @@
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -779,7 +779,7 @@
         <v>33</v>
       </c>
       <c r="K5" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -814,7 +814,7 @@
         <v>33</v>
       </c>
       <c r="K6" s="11">
-        <v>33</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -847,7 +847,7 @@
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/BACKEND/EjemplosExcels/file-AF.xlsx
+++ b/BACKEND/EjemplosExcels/file-AF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVS-System\BACKEND\EjemplosExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F550E0-362F-49DA-B60B-842EF3ED287B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE425A1-A60D-4F95-95FA-40A13263A53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>Apellido y nombre</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>DNI - 49062828</t>
+  </si>
+  <si>
+    <t>1ro</t>
   </si>
 </sst>
 </file>
@@ -677,8 +680,8 @@
         <v>16</v>
       </c>
       <c r="J2" s="10"/>
-      <c r="K2" s="11">
-        <v>32</v>
+      <c r="K2" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -710,8 +713,8 @@
         <v>16</v>
       </c>
       <c r="J3" s="10"/>
-      <c r="K3" s="11">
-        <v>32</v>
+      <c r="K3" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -743,8 +746,8 @@
         <v>28</v>
       </c>
       <c r="J4" s="10"/>
-      <c r="K4" s="11">
-        <v>32</v>
+      <c r="K4" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -778,8 +781,8 @@
       <c r="J5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="11">
-        <v>32</v>
+      <c r="K5" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -813,8 +816,8 @@
       <c r="J6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="11">
-        <v>99</v>
+      <c r="K6" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -846,8 +849,8 @@
         <v>16</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="11">
-        <v>32</v>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/BACKEND/EjemplosExcels/file-AF.xlsx
+++ b/BACKEND/EjemplosExcels/file-AF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVS-System\BACKEND\EjemplosExcels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVE-System\BACKEND\EjemplosExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE425A1-A60D-4F95-95FA-40A13263A53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAD23E2-3633-4462-B1CF-6DAC58F6E851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
   <si>
     <t>Apellido y nombre</t>
   </si>
@@ -177,12 +177,15 @@
   <si>
     <t>1ro</t>
   </si>
+  <si>
+    <t>DNI - 94177248</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +208,18 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -226,7 +241,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -264,11 +279,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -304,16 +332,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,7 +421,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:K7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:K8">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Apellido y nombre"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Documento"/>
@@ -854,17 +895,35 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="11"/>
+      <c r="A8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="17">
+        <v>2023</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="20"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
@@ -874,7 +933,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="16"/>
+      <c r="H9" s="13"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
@@ -887,7 +946,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
-      <c r="H10" s="16"/>
+      <c r="H10" s="13"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -900,7 +959,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="11"/>
-      <c r="H11" s="16"/>
+      <c r="H11" s="13"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -913,20 +972,20 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="16"/>
+      <c r="H12" s="13"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
-      <c r="B13" s="9"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="16"/>
+      <c r="H13" s="13"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
@@ -939,7 +998,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="16"/>
+      <c r="H14" s="13"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -952,7 +1011,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="11"/>
-      <c r="H15" s="16"/>
+      <c r="H15" s="13"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -965,7 +1024,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="16"/>
+      <c r="H16" s="13"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
@@ -978,7 +1037,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="16"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -991,7 +1050,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="16"/>
+      <c r="H18" s="13"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -1004,7 +1063,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="16"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
@@ -1017,7 +1076,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="11"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -1030,7 +1089,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="16"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
@@ -1043,7 +1102,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="11"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="13"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -1056,7 +1115,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="11"/>
-      <c r="H23" s="16"/>
+      <c r="H23" s="13"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -1069,7 +1128,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="11"/>
-      <c r="H24" s="16"/>
+      <c r="H24" s="13"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -1082,7 +1141,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="11"/>
-      <c r="H25" s="16"/>
+      <c r="H25" s="13"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -1095,7 +1154,7 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="11"/>
-      <c r="H26" s="16"/>
+      <c r="H26" s="13"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -1108,7 +1167,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="11"/>
-      <c r="H27" s="16"/>
+      <c r="H27" s="13"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -1121,7 +1180,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="11"/>
-      <c r="H28" s="16"/>
+      <c r="H28" s="13"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -1134,7 +1193,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="11"/>
-      <c r="H29" s="16"/>
+      <c r="H29" s="13"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
@@ -1147,7 +1206,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="11"/>
-      <c r="H30" s="16"/>
+      <c r="H30" s="13"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -1160,7 +1219,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="11"/>
-      <c r="H31" s="16"/>
+      <c r="H31" s="13"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
@@ -1173,7 +1232,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="11"/>
-      <c r="H32" s="16"/>
+      <c r="H32" s="13"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -1186,7 +1245,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="11"/>
-      <c r="H33" s="16"/>
+      <c r="H33" s="13"/>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
@@ -1199,7 +1258,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="11"/>
-      <c r="H34" s="16"/>
+      <c r="H34" s="13"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -1212,7 +1271,7 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="11"/>
-      <c r="H35" s="16"/>
+      <c r="H35" s="13"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -1225,7 +1284,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="11"/>
-      <c r="H36" s="16"/>
+      <c r="H36" s="13"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -1238,7 +1297,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="11"/>
-      <c r="H37" s="16"/>
+      <c r="H37" s="13"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
@@ -1251,7 +1310,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="11"/>
-      <c r="H38" s="16"/>
+      <c r="H38" s="13"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -1264,7 +1323,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="11"/>
-      <c r="H39" s="16"/>
+      <c r="H39" s="13"/>
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
@@ -1277,7 +1336,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="11"/>
-      <c r="H40" s="16"/>
+      <c r="H40" s="13"/>
       <c r="I40" s="11"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -1290,7 +1349,7 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="11"/>
-      <c r="H41" s="16"/>
+      <c r="H41" s="13"/>
       <c r="I41" s="11"/>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
@@ -1303,7 +1362,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="11"/>
-      <c r="H42" s="16"/>
+      <c r="H42" s="13"/>
       <c r="I42" s="11"/>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
@@ -1316,7 +1375,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="11"/>
-      <c r="H43" s="16"/>
+      <c r="H43" s="13"/>
       <c r="I43" s="11"/>
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
@@ -1329,7 +1388,7 @@
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="11"/>
-      <c r="H44" s="16"/>
+      <c r="H44" s="13"/>
       <c r="I44" s="11"/>
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
@@ -1342,7 +1401,7 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="11"/>
-      <c r="H45" s="16"/>
+      <c r="H45" s="13"/>
       <c r="I45" s="11"/>
       <c r="J45" s="11"/>
       <c r="K45" s="11"/>
@@ -1355,7 +1414,7 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="11"/>
-      <c r="H46" s="16"/>
+      <c r="H46" s="13"/>
       <c r="I46" s="11"/>
       <c r="J46" s="11"/>
       <c r="K46" s="11"/>
@@ -1368,7 +1427,7 @@
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="11"/>
-      <c r="H47" s="16"/>
+      <c r="H47" s="13"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
@@ -1381,7 +1440,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="11"/>
-      <c r="H48" s="16"/>
+      <c r="H48" s="13"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
       <c r="K48" s="11"/>
@@ -1394,7 +1453,7 @@
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="11"/>
-      <c r="H49" s="16"/>
+      <c r="H49" s="13"/>
       <c r="I49" s="11"/>
       <c r="J49" s="11"/>
       <c r="K49" s="11"/>
@@ -1407,7 +1466,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="11"/>
-      <c r="H50" s="16"/>
+      <c r="H50" s="13"/>
       <c r="I50" s="11"/>
       <c r="J50" s="11"/>
       <c r="K50" s="11"/>
@@ -1420,7 +1479,7 @@
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="11"/>
-      <c r="H51" s="16"/>
+      <c r="H51" s="13"/>
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
       <c r="K51" s="11"/>
@@ -1433,7 +1492,7 @@
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="11"/>
-      <c r="H52" s="16"/>
+      <c r="H52" s="13"/>
       <c r="I52" s="11"/>
       <c r="J52" s="11"/>
       <c r="K52" s="11"/>
@@ -1446,7 +1505,7 @@
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="11"/>
-      <c r="H53" s="16"/>
+      <c r="H53" s="13"/>
       <c r="I53" s="11"/>
       <c r="J53" s="11"/>
       <c r="K53" s="11"/>
@@ -1459,7 +1518,7 @@
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="11"/>
-      <c r="H54" s="16"/>
+      <c r="H54" s="13"/>
       <c r="I54" s="11"/>
       <c r="J54" s="11"/>
       <c r="K54" s="11"/>
@@ -1472,7 +1531,7 @@
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="11"/>
-      <c r="H55" s="16"/>
+      <c r="H55" s="13"/>
       <c r="I55" s="11"/>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
@@ -1485,7 +1544,7 @@
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="11"/>
-      <c r="H56" s="16"/>
+      <c r="H56" s="13"/>
       <c r="I56" s="11"/>
       <c r="J56" s="11"/>
       <c r="K56" s="11"/>
@@ -1498,7 +1557,7 @@
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="11"/>
-      <c r="H57" s="16"/>
+      <c r="H57" s="13"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
@@ -1511,7 +1570,7 @@
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="11"/>
-      <c r="H58" s="16"/>
+      <c r="H58" s="13"/>
       <c r="I58" s="11"/>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
@@ -1524,7 +1583,7 @@
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
       <c r="G59" s="11"/>
-      <c r="H59" s="16"/>
+      <c r="H59" s="13"/>
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
@@ -1537,7 +1596,7 @@
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="11"/>
-      <c r="H60" s="16"/>
+      <c r="H60" s="13"/>
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
@@ -1550,7 +1609,7 @@
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
       <c r="G61" s="11"/>
-      <c r="H61" s="16"/>
+      <c r="H61" s="13"/>
       <c r="I61" s="11"/>
       <c r="J61" s="11"/>
       <c r="K61" s="11"/>
@@ -1563,7 +1622,7 @@
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
       <c r="G62" s="11"/>
-      <c r="H62" s="16"/>
+      <c r="H62" s="13"/>
       <c r="I62" s="11"/>
       <c r="J62" s="11"/>
       <c r="K62" s="11"/>
@@ -1576,7 +1635,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="11"/>
-      <c r="H63" s="16"/>
+      <c r="H63" s="13"/>
       <c r="I63" s="11"/>
       <c r="J63" s="11"/>
       <c r="K63" s="11"/>
@@ -1589,7 +1648,7 @@
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="11"/>
-      <c r="H64" s="16"/>
+      <c r="H64" s="13"/>
       <c r="I64" s="11"/>
       <c r="J64" s="11"/>
       <c r="K64" s="11"/>
@@ -1602,7 +1661,7 @@
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
       <c r="G65" s="11"/>
-      <c r="H65" s="16"/>
+      <c r="H65" s="13"/>
       <c r="I65" s="11"/>
       <c r="J65" s="11"/>
       <c r="K65" s="11"/>
@@ -1615,7 +1674,7 @@
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
       <c r="G66" s="11"/>
-      <c r="H66" s="16"/>
+      <c r="H66" s="13"/>
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
       <c r="K66" s="11"/>
@@ -1628,7 +1687,7 @@
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
       <c r="G67" s="11"/>
-      <c r="H67" s="16"/>
+      <c r="H67" s="13"/>
       <c r="I67" s="11"/>
       <c r="J67" s="11"/>
       <c r="K67" s="11"/>
@@ -1641,7 +1700,7 @@
       <c r="E68" s="9"/>
       <c r="F68" s="9"/>
       <c r="G68" s="11"/>
-      <c r="H68" s="16"/>
+      <c r="H68" s="13"/>
       <c r="I68" s="11"/>
       <c r="J68" s="11"/>
       <c r="K68" s="11"/>
@@ -1654,7 +1713,7 @@
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
       <c r="G69" s="11"/>
-      <c r="H69" s="16"/>
+      <c r="H69" s="13"/>
       <c r="I69" s="11"/>
       <c r="J69" s="11"/>
       <c r="K69" s="11"/>
@@ -1667,7 +1726,7 @@
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
       <c r="G70" s="11"/>
-      <c r="H70" s="16"/>
+      <c r="H70" s="13"/>
       <c r="I70" s="11"/>
       <c r="J70" s="11"/>
       <c r="K70" s="11"/>
@@ -1680,7 +1739,7 @@
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
       <c r="G71" s="11"/>
-      <c r="H71" s="16"/>
+      <c r="H71" s="13"/>
       <c r="I71" s="11"/>
       <c r="J71" s="11"/>
       <c r="K71" s="11"/>
@@ -1693,7 +1752,7 @@
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
       <c r="G72" s="11"/>
-      <c r="H72" s="16"/>
+      <c r="H72" s="13"/>
       <c r="I72" s="11"/>
       <c r="J72" s="11"/>
       <c r="K72" s="11"/>
@@ -1706,7 +1765,7 @@
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
       <c r="G73" s="11"/>
-      <c r="H73" s="16"/>
+      <c r="H73" s="13"/>
       <c r="I73" s="11"/>
       <c r="J73" s="11"/>
       <c r="K73" s="11"/>
@@ -1719,7 +1778,7 @@
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
       <c r="G74" s="11"/>
-      <c r="H74" s="16"/>
+      <c r="H74" s="13"/>
       <c r="I74" s="11"/>
       <c r="J74" s="11"/>
       <c r="K74" s="11"/>
@@ -1732,7 +1791,7 @@
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
       <c r="G75" s="11"/>
-      <c r="H75" s="16"/>
+      <c r="H75" s="13"/>
       <c r="I75" s="11"/>
       <c r="J75" s="11"/>
       <c r="K75" s="11"/>
@@ -1745,7 +1804,7 @@
       <c r="E76" s="9"/>
       <c r="F76" s="9"/>
       <c r="G76" s="11"/>
-      <c r="H76" s="16"/>
+      <c r="H76" s="13"/>
       <c r="I76" s="11"/>
       <c r="J76" s="11"/>
       <c r="K76" s="11"/>
@@ -1758,7 +1817,7 @@
       <c r="E77" s="9"/>
       <c r="F77" s="9"/>
       <c r="G77" s="11"/>
-      <c r="H77" s="16"/>
+      <c r="H77" s="13"/>
       <c r="I77" s="11"/>
       <c r="J77" s="11"/>
       <c r="K77" s="11"/>
@@ -1771,7 +1830,7 @@
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
       <c r="G78" s="11"/>
-      <c r="H78" s="16"/>
+      <c r="H78" s="13"/>
       <c r="I78" s="11"/>
       <c r="J78" s="11"/>
       <c r="K78" s="11"/>
@@ -1784,7 +1843,7 @@
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
       <c r="G79" s="11"/>
-      <c r="H79" s="16"/>
+      <c r="H79" s="13"/>
       <c r="I79" s="11"/>
       <c r="J79" s="11"/>
       <c r="K79" s="11"/>
@@ -1797,7 +1856,7 @@
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
       <c r="G80" s="11"/>
-      <c r="H80" s="16"/>
+      <c r="H80" s="13"/>
       <c r="I80" s="11"/>
       <c r="J80" s="11"/>
       <c r="K80" s="11"/>
@@ -1810,7 +1869,7 @@
       <c r="E81" s="9"/>
       <c r="F81" s="9"/>
       <c r="G81" s="11"/>
-      <c r="H81" s="16"/>
+      <c r="H81" s="13"/>
       <c r="I81" s="11"/>
       <c r="J81" s="11"/>
       <c r="K81" s="11"/>
@@ -1823,7 +1882,7 @@
       <c r="E82" s="9"/>
       <c r="F82" s="9"/>
       <c r="G82" s="11"/>
-      <c r="H82" s="16"/>
+      <c r="H82" s="13"/>
       <c r="I82" s="11"/>
       <c r="J82" s="11"/>
       <c r="K82" s="11"/>
@@ -1836,7 +1895,7 @@
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
       <c r="G83" s="11"/>
-      <c r="H83" s="16"/>
+      <c r="H83" s="13"/>
       <c r="I83" s="11"/>
       <c r="J83" s="11"/>
       <c r="K83" s="11"/>
@@ -1849,7 +1908,7 @@
       <c r="E84" s="9"/>
       <c r="F84" s="9"/>
       <c r="G84" s="11"/>
-      <c r="H84" s="16"/>
+      <c r="H84" s="13"/>
       <c r="I84" s="11"/>
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
@@ -1862,7 +1921,7 @@
       <c r="E85" s="9"/>
       <c r="F85" s="9"/>
       <c r="G85" s="11"/>
-      <c r="H85" s="16"/>
+      <c r="H85" s="13"/>
       <c r="I85" s="11"/>
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
@@ -1875,7 +1934,7 @@
       <c r="E86" s="9"/>
       <c r="F86" s="9"/>
       <c r="G86" s="11"/>
-      <c r="H86" s="16"/>
+      <c r="H86" s="13"/>
       <c r="I86" s="11"/>
       <c r="J86" s="11"/>
       <c r="K86" s="11"/>
@@ -1888,7 +1947,7 @@
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
       <c r="G87" s="11"/>
-      <c r="H87" s="16"/>
+      <c r="H87" s="13"/>
       <c r="I87" s="11"/>
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
@@ -1901,7 +1960,7 @@
       <c r="E88" s="9"/>
       <c r="F88" s="9"/>
       <c r="G88" s="11"/>
-      <c r="H88" s="16"/>
+      <c r="H88" s="13"/>
       <c r="I88" s="11"/>
       <c r="J88" s="11"/>
       <c r="K88" s="11"/>
@@ -1914,7 +1973,7 @@
       <c r="E89" s="9"/>
       <c r="F89" s="9"/>
       <c r="G89" s="11"/>
-      <c r="H89" s="16"/>
+      <c r="H89" s="13"/>
       <c r="I89" s="11"/>
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
@@ -1927,7 +1986,7 @@
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
       <c r="G90" s="11"/>
-      <c r="H90" s="16"/>
+      <c r="H90" s="13"/>
       <c r="I90" s="11"/>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
@@ -1940,7 +1999,7 @@
       <c r="E91" s="9"/>
       <c r="F91" s="9"/>
       <c r="G91" s="11"/>
-      <c r="H91" s="16"/>
+      <c r="H91" s="13"/>
       <c r="I91" s="11"/>
       <c r="J91" s="11"/>
       <c r="K91" s="11"/>
@@ -1953,7 +2012,7 @@
       <c r="E92" s="9"/>
       <c r="F92" s="9"/>
       <c r="G92" s="11"/>
-      <c r="H92" s="16"/>
+      <c r="H92" s="13"/>
       <c r="I92" s="11"/>
       <c r="J92" s="11"/>
       <c r="K92" s="11"/>
@@ -1966,7 +2025,7 @@
       <c r="E93" s="9"/>
       <c r="F93" s="9"/>
       <c r="G93" s="11"/>
-      <c r="H93" s="16"/>
+      <c r="H93" s="13"/>
       <c r="I93" s="11"/>
       <c r="J93" s="11"/>
       <c r="K93" s="11"/>
@@ -1979,7 +2038,7 @@
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
       <c r="G94" s="11"/>
-      <c r="H94" s="16"/>
+      <c r="H94" s="13"/>
       <c r="I94" s="11"/>
       <c r="J94" s="11"/>
       <c r="K94" s="11"/>
@@ -1992,7 +2051,7 @@
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
       <c r="G95" s="11"/>
-      <c r="H95" s="16"/>
+      <c r="H95" s="13"/>
       <c r="I95" s="11"/>
       <c r="J95" s="11"/>
       <c r="K95" s="11"/>
@@ -2005,7 +2064,7 @@
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
       <c r="G96" s="11"/>
-      <c r="H96" s="16"/>
+      <c r="H96" s="13"/>
       <c r="I96" s="11"/>
       <c r="J96" s="11"/>
       <c r="K96" s="11"/>
@@ -2018,7 +2077,7 @@
       <c r="E97" s="9"/>
       <c r="F97" s="9"/>
       <c r="G97" s="11"/>
-      <c r="H97" s="16"/>
+      <c r="H97" s="13"/>
       <c r="I97" s="11"/>
       <c r="J97" s="11"/>
       <c r="K97" s="11"/>
@@ -2031,7 +2090,7 @@
       <c r="E98" s="9"/>
       <c r="F98" s="9"/>
       <c r="G98" s="11"/>
-      <c r="H98" s="16"/>
+      <c r="H98" s="13"/>
       <c r="I98" s="11"/>
       <c r="J98" s="11"/>
       <c r="K98" s="11"/>
@@ -2044,7 +2103,7 @@
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
       <c r="G99" s="11"/>
-      <c r="H99" s="16"/>
+      <c r="H99" s="13"/>
       <c r="I99" s="11"/>
       <c r="J99" s="11"/>
       <c r="K99" s="11"/>
@@ -2057,7 +2116,7 @@
       <c r="E100" s="9"/>
       <c r="F100" s="9"/>
       <c r="G100" s="11"/>
-      <c r="H100" s="16"/>
+      <c r="H100" s="13"/>
       <c r="I100" s="11"/>
       <c r="J100" s="11"/>
       <c r="K100" s="11"/>
@@ -2070,7 +2129,7 @@
       <c r="E101" s="9"/>
       <c r="F101" s="9"/>
       <c r="G101" s="11"/>
-      <c r="H101" s="16"/>
+      <c r="H101" s="13"/>
       <c r="I101" s="11"/>
       <c r="J101" s="11"/>
       <c r="K101" s="11"/>
@@ -2083,7 +2142,7 @@
       <c r="E102" s="9"/>
       <c r="F102" s="9"/>
       <c r="G102" s="11"/>
-      <c r="H102" s="16"/>
+      <c r="H102" s="13"/>
       <c r="I102" s="11"/>
       <c r="J102" s="11"/>
       <c r="K102" s="11"/>
@@ -2096,7 +2155,7 @@
       <c r="E103" s="9"/>
       <c r="F103" s="9"/>
       <c r="G103" s="11"/>
-      <c r="H103" s="16"/>
+      <c r="H103" s="13"/>
       <c r="I103" s="11"/>
       <c r="J103" s="11"/>
       <c r="K103" s="11"/>
@@ -2109,7 +2168,7 @@
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
       <c r="G104" s="11"/>
-      <c r="H104" s="16"/>
+      <c r="H104" s="13"/>
       <c r="I104" s="11"/>
       <c r="J104" s="11"/>
       <c r="K104" s="11"/>
@@ -2122,7 +2181,7 @@
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
       <c r="G105" s="11"/>
-      <c r="H105" s="16"/>
+      <c r="H105" s="13"/>
       <c r="I105" s="11"/>
       <c r="J105" s="11"/>
       <c r="K105" s="11"/>
@@ -2135,7 +2194,7 @@
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
       <c r="G106" s="11"/>
-      <c r="H106" s="16"/>
+      <c r="H106" s="13"/>
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
@@ -2148,7 +2207,7 @@
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
       <c r="G107" s="11"/>
-      <c r="H107" s="16"/>
+      <c r="H107" s="13"/>
       <c r="I107" s="11"/>
       <c r="J107" s="11"/>
       <c r="K107" s="11"/>
@@ -2161,7 +2220,7 @@
       <c r="E108" s="9"/>
       <c r="F108" s="9"/>
       <c r="G108" s="11"/>
-      <c r="H108" s="16"/>
+      <c r="H108" s="13"/>
       <c r="I108" s="11"/>
       <c r="J108" s="11"/>
       <c r="K108" s="11"/>
@@ -2174,7 +2233,7 @@
       <c r="E109" s="9"/>
       <c r="F109" s="9"/>
       <c r="G109" s="11"/>
-      <c r="H109" s="16"/>
+      <c r="H109" s="13"/>
       <c r="I109" s="11"/>
       <c r="J109" s="11"/>
       <c r="K109" s="11"/>
@@ -2187,7 +2246,7 @@
       <c r="E110" s="9"/>
       <c r="F110" s="9"/>
       <c r="G110" s="11"/>
-      <c r="H110" s="16"/>
+      <c r="H110" s="13"/>
       <c r="I110" s="11"/>
       <c r="J110" s="11"/>
       <c r="K110" s="11"/>
@@ -2200,7 +2259,7 @@
       <c r="E111" s="9"/>
       <c r="F111" s="9"/>
       <c r="G111" s="11"/>
-      <c r="H111" s="16"/>
+      <c r="H111" s="13"/>
       <c r="I111" s="11"/>
       <c r="J111" s="11"/>
       <c r="K111" s="11"/>
@@ -2213,7 +2272,7 @@
       <c r="E112" s="9"/>
       <c r="F112" s="9"/>
       <c r="G112" s="11"/>
-      <c r="H112" s="16"/>
+      <c r="H112" s="13"/>
       <c r="I112" s="11"/>
       <c r="J112" s="11"/>
       <c r="K112" s="11"/>
@@ -2226,7 +2285,7 @@
       <c r="E113" s="9"/>
       <c r="F113" s="9"/>
       <c r="G113" s="11"/>
-      <c r="H113" s="16"/>
+      <c r="H113" s="13"/>
       <c r="I113" s="11"/>
       <c r="J113" s="11"/>
       <c r="K113" s="11"/>
@@ -2239,7 +2298,7 @@
       <c r="E114" s="9"/>
       <c r="F114" s="9"/>
       <c r="G114" s="11"/>
-      <c r="H114" s="16"/>
+      <c r="H114" s="13"/>
       <c r="I114" s="11"/>
       <c r="J114" s="11"/>
       <c r="K114" s="11"/>
@@ -2252,7 +2311,7 @@
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
       <c r="G115" s="11"/>
-      <c r="H115" s="16"/>
+      <c r="H115" s="13"/>
       <c r="I115" s="11"/>
       <c r="J115" s="11"/>
       <c r="K115" s="11"/>
@@ -2265,7 +2324,7 @@
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
       <c r="G116" s="11"/>
-      <c r="H116" s="16"/>
+      <c r="H116" s="13"/>
       <c r="I116" s="11"/>
       <c r="J116" s="11"/>
       <c r="K116" s="11"/>
@@ -2278,7 +2337,7 @@
       <c r="E117" s="9"/>
       <c r="F117" s="9"/>
       <c r="G117" s="11"/>
-      <c r="H117" s="16"/>
+      <c r="H117" s="13"/>
       <c r="I117" s="11"/>
       <c r="J117" s="11"/>
       <c r="K117" s="11"/>
@@ -2291,7 +2350,7 @@
       <c r="E118" s="9"/>
       <c r="F118" s="9"/>
       <c r="G118" s="11"/>
-      <c r="H118" s="16"/>
+      <c r="H118" s="13"/>
       <c r="I118" s="11"/>
       <c r="J118" s="11"/>
       <c r="K118" s="11"/>
@@ -2304,7 +2363,7 @@
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
       <c r="G119" s="11"/>
-      <c r="H119" s="16"/>
+      <c r="H119" s="13"/>
       <c r="I119" s="11"/>
       <c r="J119" s="11"/>
       <c r="K119" s="11"/>
@@ -2317,7 +2376,7 @@
       <c r="E120" s="9"/>
       <c r="F120" s="9"/>
       <c r="G120" s="11"/>
-      <c r="H120" s="16"/>
+      <c r="H120" s="13"/>
       <c r="I120" s="11"/>
       <c r="J120" s="11"/>
       <c r="K120" s="11"/>
@@ -2330,7 +2389,7 @@
       <c r="E121" s="9"/>
       <c r="F121" s="9"/>
       <c r="G121" s="11"/>
-      <c r="H121" s="16"/>
+      <c r="H121" s="13"/>
       <c r="I121" s="11"/>
       <c r="J121" s="11"/>
       <c r="K121" s="11"/>
@@ -2343,7 +2402,7 @@
       <c r="E122" s="9"/>
       <c r="F122" s="9"/>
       <c r="G122" s="11"/>
-      <c r="H122" s="16"/>
+      <c r="H122" s="13"/>
       <c r="I122" s="11"/>
       <c r="J122" s="11"/>
       <c r="K122" s="11"/>
@@ -2356,7 +2415,7 @@
       <c r="E123" s="9"/>
       <c r="F123" s="9"/>
       <c r="G123" s="11"/>
-      <c r="H123" s="16"/>
+      <c r="H123" s="13"/>
       <c r="I123" s="11"/>
       <c r="J123" s="11"/>
       <c r="K123" s="11"/>
@@ -2369,7 +2428,7 @@
       <c r="E124" s="9"/>
       <c r="F124" s="9"/>
       <c r="G124" s="11"/>
-      <c r="H124" s="16"/>
+      <c r="H124" s="13"/>
       <c r="I124" s="11"/>
       <c r="J124" s="11"/>
       <c r="K124" s="11"/>
@@ -2382,7 +2441,7 @@
       <c r="E125" s="9"/>
       <c r="F125" s="9"/>
       <c r="G125" s="11"/>
-      <c r="H125" s="16"/>
+      <c r="H125" s="13"/>
       <c r="I125" s="11"/>
       <c r="J125" s="11"/>
       <c r="K125" s="11"/>
@@ -2395,7 +2454,7 @@
       <c r="E126" s="9"/>
       <c r="F126" s="9"/>
       <c r="G126" s="11"/>
-      <c r="H126" s="16"/>
+      <c r="H126" s="13"/>
       <c r="I126" s="11"/>
       <c r="J126" s="11"/>
       <c r="K126" s="11"/>
@@ -2408,7 +2467,7 @@
       <c r="E127" s="9"/>
       <c r="F127" s="9"/>
       <c r="G127" s="11"/>
-      <c r="H127" s="16"/>
+      <c r="H127" s="13"/>
       <c r="I127" s="11"/>
       <c r="J127" s="11"/>
       <c r="K127" s="11"/>
@@ -2421,7 +2480,7 @@
       <c r="E128" s="9"/>
       <c r="F128" s="9"/>
       <c r="G128" s="11"/>
-      <c r="H128" s="16"/>
+      <c r="H128" s="13"/>
       <c r="I128" s="11"/>
       <c r="J128" s="11"/>
       <c r="K128" s="11"/>
@@ -2434,7 +2493,7 @@
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
       <c r="G129" s="11"/>
-      <c r="H129" s="16"/>
+      <c r="H129" s="13"/>
       <c r="I129" s="11"/>
       <c r="J129" s="11"/>
       <c r="K129" s="11"/>
@@ -2447,7 +2506,7 @@
       <c r="E130" s="9"/>
       <c r="F130" s="9"/>
       <c r="G130" s="11"/>
-      <c r="H130" s="16"/>
+      <c r="H130" s="13"/>
       <c r="I130" s="11"/>
       <c r="J130" s="11"/>
       <c r="K130" s="11"/>
@@ -2460,7 +2519,7 @@
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
       <c r="G131" s="11"/>
-      <c r="H131" s="16"/>
+      <c r="H131" s="13"/>
       <c r="I131" s="11"/>
       <c r="J131" s="11"/>
       <c r="K131" s="11"/>
@@ -2473,7 +2532,7 @@
       <c r="E132" s="9"/>
       <c r="F132" s="9"/>
       <c r="G132" s="11"/>
-      <c r="H132" s="16"/>
+      <c r="H132" s="13"/>
       <c r="I132" s="11"/>
       <c r="J132" s="11"/>
       <c r="K132" s="11"/>
@@ -2486,7 +2545,7 @@
       <c r="E133" s="9"/>
       <c r="F133" s="9"/>
       <c r="G133" s="11"/>
-      <c r="H133" s="16"/>
+      <c r="H133" s="13"/>
       <c r="I133" s="11"/>
       <c r="J133" s="11"/>
       <c r="K133" s="11"/>
@@ -2499,7 +2558,7 @@
       <c r="E134" s="9"/>
       <c r="F134" s="9"/>
       <c r="G134" s="11"/>
-      <c r="H134" s="16"/>
+      <c r="H134" s="13"/>
       <c r="I134" s="11"/>
       <c r="J134" s="11"/>
       <c r="K134" s="11"/>
@@ -2512,7 +2571,7 @@
       <c r="E135" s="9"/>
       <c r="F135" s="9"/>
       <c r="G135" s="11"/>
-      <c r="H135" s="16"/>
+      <c r="H135" s="13"/>
       <c r="I135" s="11"/>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
@@ -2525,7 +2584,7 @@
       <c r="E136" s="9"/>
       <c r="F136" s="9"/>
       <c r="G136" s="11"/>
-      <c r="H136" s="16"/>
+      <c r="H136" s="13"/>
       <c r="I136" s="11"/>
       <c r="J136" s="11"/>
       <c r="K136" s="11"/>
@@ -2538,7 +2597,7 @@
       <c r="E137" s="9"/>
       <c r="F137" s="9"/>
       <c r="G137" s="11"/>
-      <c r="H137" s="16"/>
+      <c r="H137" s="13"/>
       <c r="I137" s="11"/>
       <c r="J137" s="11"/>
       <c r="K137" s="11"/>
@@ -2551,7 +2610,7 @@
       <c r="E138" s="9"/>
       <c r="F138" s="9"/>
       <c r="G138" s="11"/>
-      <c r="H138" s="16"/>
+      <c r="H138" s="13"/>
       <c r="I138" s="11"/>
       <c r="J138" s="11"/>
       <c r="K138" s="11"/>
@@ -2564,7 +2623,7 @@
       <c r="E139" s="9"/>
       <c r="F139" s="9"/>
       <c r="G139" s="11"/>
-      <c r="H139" s="16"/>
+      <c r="H139" s="13"/>
       <c r="I139" s="11"/>
       <c r="J139" s="11"/>
       <c r="K139" s="11"/>
@@ -2577,7 +2636,7 @@
       <c r="E140" s="9"/>
       <c r="F140" s="9"/>
       <c r="G140" s="11"/>
-      <c r="H140" s="16"/>
+      <c r="H140" s="13"/>
       <c r="I140" s="11"/>
       <c r="J140" s="11"/>
       <c r="K140" s="11"/>
@@ -2590,7 +2649,7 @@
       <c r="E141" s="9"/>
       <c r="F141" s="9"/>
       <c r="G141" s="11"/>
-      <c r="H141" s="16"/>
+      <c r="H141" s="13"/>
       <c r="I141" s="11"/>
       <c r="J141" s="11"/>
       <c r="K141" s="11"/>
@@ -2603,7 +2662,7 @@
       <c r="E142" s="9"/>
       <c r="F142" s="9"/>
       <c r="G142" s="11"/>
-      <c r="H142" s="16"/>
+      <c r="H142" s="13"/>
       <c r="I142" s="11"/>
       <c r="J142" s="11"/>
       <c r="K142" s="11"/>
@@ -2616,7 +2675,7 @@
       <c r="E143" s="9"/>
       <c r="F143" s="9"/>
       <c r="G143" s="11"/>
-      <c r="H143" s="16"/>
+      <c r="H143" s="13"/>
       <c r="I143" s="11"/>
       <c r="J143" s="11"/>
       <c r="K143" s="11"/>
@@ -2629,7 +2688,7 @@
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
       <c r="G144" s="11"/>
-      <c r="H144" s="16"/>
+      <c r="H144" s="13"/>
       <c r="I144" s="11"/>
       <c r="J144" s="11"/>
       <c r="K144" s="11"/>
@@ -2642,7 +2701,7 @@
       <c r="E145" s="9"/>
       <c r="F145" s="9"/>
       <c r="G145" s="11"/>
-      <c r="H145" s="16"/>
+      <c r="H145" s="13"/>
       <c r="I145" s="11"/>
       <c r="J145" s="11"/>
       <c r="K145" s="11"/>
@@ -2655,7 +2714,7 @@
       <c r="E146" s="9"/>
       <c r="F146" s="9"/>
       <c r="G146" s="11"/>
-      <c r="H146" s="16"/>
+      <c r="H146" s="13"/>
       <c r="I146" s="11"/>
       <c r="J146" s="11"/>
       <c r="K146" s="11"/>
@@ -2668,7 +2727,7 @@
       <c r="E147" s="9"/>
       <c r="F147" s="9"/>
       <c r="G147" s="11"/>
-      <c r="H147" s="16"/>
+      <c r="H147" s="13"/>
       <c r="I147" s="11"/>
       <c r="J147" s="11"/>
       <c r="K147" s="11"/>
@@ -2681,7 +2740,7 @@
       <c r="E148" s="9"/>
       <c r="F148" s="9"/>
       <c r="G148" s="11"/>
-      <c r="H148" s="16"/>
+      <c r="H148" s="13"/>
       <c r="I148" s="11"/>
       <c r="J148" s="11"/>
       <c r="K148" s="11"/>
@@ -2694,7 +2753,7 @@
       <c r="E149" s="9"/>
       <c r="F149" s="9"/>
       <c r="G149" s="11"/>
-      <c r="H149" s="16"/>
+      <c r="H149" s="13"/>
       <c r="I149" s="11"/>
       <c r="J149" s="11"/>
       <c r="K149" s="11"/>
@@ -2707,7 +2766,7 @@
       <c r="E150" s="9"/>
       <c r="F150" s="9"/>
       <c r="G150" s="11"/>
-      <c r="H150" s="16"/>
+      <c r="H150" s="13"/>
       <c r="I150" s="11"/>
       <c r="J150" s="11"/>
       <c r="K150" s="11"/>
@@ -2720,7 +2779,7 @@
       <c r="E151" s="9"/>
       <c r="F151" s="9"/>
       <c r="G151" s="11"/>
-      <c r="H151" s="16"/>
+      <c r="H151" s="13"/>
       <c r="I151" s="11"/>
       <c r="J151" s="11"/>
       <c r="K151" s="11"/>
@@ -2733,7 +2792,7 @@
       <c r="E152" s="9"/>
       <c r="F152" s="9"/>
       <c r="G152" s="11"/>
-      <c r="H152" s="16"/>
+      <c r="H152" s="13"/>
       <c r="I152" s="11"/>
       <c r="J152" s="11"/>
       <c r="K152" s="11"/>
@@ -2746,7 +2805,7 @@
       <c r="E153" s="9"/>
       <c r="F153" s="9"/>
       <c r="G153" s="11"/>
-      <c r="H153" s="16"/>
+      <c r="H153" s="13"/>
       <c r="I153" s="11"/>
       <c r="J153" s="11"/>
       <c r="K153" s="11"/>
@@ -2759,7 +2818,7 @@
       <c r="E154" s="9"/>
       <c r="F154" s="9"/>
       <c r="G154" s="11"/>
-      <c r="H154" s="16"/>
+      <c r="H154" s="13"/>
       <c r="I154" s="11"/>
       <c r="J154" s="11"/>
       <c r="K154" s="11"/>
@@ -2772,7 +2831,7 @@
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
       <c r="G155" s="11"/>
-      <c r="H155" s="16"/>
+      <c r="H155" s="13"/>
       <c r="I155" s="11"/>
       <c r="J155" s="11"/>
       <c r="K155" s="11"/>
@@ -2785,7 +2844,7 @@
       <c r="E156" s="9"/>
       <c r="F156" s="9"/>
       <c r="G156" s="11"/>
-      <c r="H156" s="16"/>
+      <c r="H156" s="13"/>
       <c r="I156" s="11"/>
       <c r="J156" s="11"/>
       <c r="K156" s="11"/>
@@ -2798,7 +2857,7 @@
       <c r="E157" s="9"/>
       <c r="F157" s="9"/>
       <c r="G157" s="11"/>
-      <c r="H157" s="16"/>
+      <c r="H157" s="13"/>
       <c r="I157" s="11"/>
       <c r="J157" s="11"/>
       <c r="K157" s="11"/>
@@ -2811,7 +2870,7 @@
       <c r="E158" s="9"/>
       <c r="F158" s="9"/>
       <c r="G158" s="11"/>
-      <c r="H158" s="16"/>
+      <c r="H158" s="13"/>
       <c r="I158" s="11"/>
       <c r="J158" s="11"/>
       <c r="K158" s="11"/>
@@ -2824,7 +2883,7 @@
       <c r="E159" s="9"/>
       <c r="F159" s="9"/>
       <c r="G159" s="11"/>
-      <c r="H159" s="16"/>
+      <c r="H159" s="13"/>
       <c r="I159" s="11"/>
       <c r="J159" s="11"/>
       <c r="K159" s="11"/>
@@ -2837,7 +2896,7 @@
       <c r="E160" s="9"/>
       <c r="F160" s="9"/>
       <c r="G160" s="11"/>
-      <c r="H160" s="16"/>
+      <c r="H160" s="13"/>
       <c r="I160" s="11"/>
       <c r="J160" s="11"/>
       <c r="K160" s="11"/>
@@ -2850,7 +2909,7 @@
       <c r="E161" s="9"/>
       <c r="F161" s="9"/>
       <c r="G161" s="11"/>
-      <c r="H161" s="16"/>
+      <c r="H161" s="13"/>
       <c r="I161" s="11"/>
       <c r="J161" s="11"/>
       <c r="K161" s="11"/>
@@ -2863,7 +2922,7 @@
       <c r="E162" s="9"/>
       <c r="F162" s="9"/>
       <c r="G162" s="11"/>
-      <c r="H162" s="16"/>
+      <c r="H162" s="13"/>
       <c r="I162" s="11"/>
       <c r="J162" s="11"/>
       <c r="K162" s="11"/>
@@ -2876,7 +2935,7 @@
       <c r="E163" s="9"/>
       <c r="F163" s="9"/>
       <c r="G163" s="11"/>
-      <c r="H163" s="16"/>
+      <c r="H163" s="13"/>
       <c r="I163" s="11"/>
       <c r="J163" s="11"/>
       <c r="K163" s="11"/>
@@ -2889,7 +2948,7 @@
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
       <c r="G164" s="11"/>
-      <c r="H164" s="16"/>
+      <c r="H164" s="13"/>
       <c r="I164" s="11"/>
       <c r="J164" s="11"/>
       <c r="K164" s="11"/>
@@ -2902,7 +2961,7 @@
       <c r="E165" s="9"/>
       <c r="F165" s="9"/>
       <c r="G165" s="11"/>
-      <c r="H165" s="16"/>
+      <c r="H165" s="13"/>
       <c r="I165" s="11"/>
       <c r="J165" s="11"/>
       <c r="K165" s="11"/>
@@ -2915,7 +2974,7 @@
       <c r="E166" s="9"/>
       <c r="F166" s="9"/>
       <c r="G166" s="11"/>
-      <c r="H166" s="16"/>
+      <c r="H166" s="13"/>
       <c r="I166" s="11"/>
       <c r="J166" s="11"/>
       <c r="K166" s="11"/>
@@ -2928,7 +2987,7 @@
       <c r="E167" s="9"/>
       <c r="F167" s="9"/>
       <c r="G167" s="11"/>
-      <c r="H167" s="16"/>
+      <c r="H167" s="13"/>
       <c r="I167" s="11"/>
       <c r="J167" s="11"/>
       <c r="K167" s="11"/>
@@ -2941,7 +3000,7 @@
       <c r="E168" s="9"/>
       <c r="F168" s="9"/>
       <c r="G168" s="11"/>
-      <c r="H168" s="16"/>
+      <c r="H168" s="13"/>
       <c r="I168" s="11"/>
       <c r="J168" s="11"/>
       <c r="K168" s="11"/>
@@ -2954,7 +3013,7 @@
       <c r="E169" s="9"/>
       <c r="F169" s="9"/>
       <c r="G169" s="11"/>
-      <c r="H169" s="16"/>
+      <c r="H169" s="13"/>
       <c r="I169" s="11"/>
       <c r="J169" s="11"/>
       <c r="K169" s="11"/>
@@ -2967,7 +3026,7 @@
       <c r="E170" s="9"/>
       <c r="F170" s="9"/>
       <c r="G170" s="11"/>
-      <c r="H170" s="16"/>
+      <c r="H170" s="13"/>
       <c r="I170" s="11"/>
       <c r="J170" s="11"/>
       <c r="K170" s="11"/>
@@ -2980,7 +3039,7 @@
       <c r="E171" s="9"/>
       <c r="F171" s="9"/>
       <c r="G171" s="11"/>
-      <c r="H171" s="16"/>
+      <c r="H171" s="13"/>
       <c r="I171" s="11"/>
       <c r="J171" s="11"/>
       <c r="K171" s="11"/>
@@ -2993,7 +3052,7 @@
       <c r="E172" s="9"/>
       <c r="F172" s="9"/>
       <c r="G172" s="11"/>
-      <c r="H172" s="16"/>
+      <c r="H172" s="13"/>
       <c r="I172" s="11"/>
       <c r="J172" s="11"/>
       <c r="K172" s="11"/>
@@ -3006,7 +3065,7 @@
       <c r="E173" s="9"/>
       <c r="F173" s="9"/>
       <c r="G173" s="11"/>
-      <c r="H173" s="16"/>
+      <c r="H173" s="13"/>
       <c r="I173" s="11"/>
       <c r="J173" s="11"/>
       <c r="K173" s="11"/>
@@ -3019,7 +3078,7 @@
       <c r="E174" s="9"/>
       <c r="F174" s="9"/>
       <c r="G174" s="11"/>
-      <c r="H174" s="16"/>
+      <c r="H174" s="13"/>
       <c r="I174" s="11"/>
       <c r="J174" s="11"/>
       <c r="K174" s="11"/>
@@ -3032,7 +3091,7 @@
       <c r="E175" s="9"/>
       <c r="F175" s="9"/>
       <c r="G175" s="11"/>
-      <c r="H175" s="16"/>
+      <c r="H175" s="13"/>
       <c r="I175" s="11"/>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
@@ -3045,7 +3104,7 @@
       <c r="E176" s="9"/>
       <c r="F176" s="9"/>
       <c r="G176" s="11"/>
-      <c r="H176" s="16"/>
+      <c r="H176" s="13"/>
       <c r="I176" s="11"/>
       <c r="J176" s="11"/>
       <c r="K176" s="11"/>
@@ -3058,7 +3117,7 @@
       <c r="E177" s="9"/>
       <c r="F177" s="9"/>
       <c r="G177" s="11"/>
-      <c r="H177" s="16"/>
+      <c r="H177" s="13"/>
       <c r="I177" s="11"/>
       <c r="J177" s="11"/>
       <c r="K177" s="11"/>
@@ -3071,7 +3130,7 @@
       <c r="E178" s="9"/>
       <c r="F178" s="9"/>
       <c r="G178" s="11"/>
-      <c r="H178" s="16"/>
+      <c r="H178" s="13"/>
       <c r="I178" s="11"/>
       <c r="J178" s="11"/>
       <c r="K178" s="11"/>
@@ -3084,7 +3143,7 @@
       <c r="E179" s="9"/>
       <c r="F179" s="9"/>
       <c r="G179" s="11"/>
-      <c r="H179" s="16"/>
+      <c r="H179" s="13"/>
       <c r="I179" s="11"/>
       <c r="J179" s="11"/>
       <c r="K179" s="11"/>
@@ -3097,7 +3156,7 @@
       <c r="E180" s="9"/>
       <c r="F180" s="9"/>
       <c r="G180" s="11"/>
-      <c r="H180" s="16"/>
+      <c r="H180" s="13"/>
       <c r="I180" s="11"/>
       <c r="J180" s="11"/>
       <c r="K180" s="11"/>
@@ -3110,7 +3169,7 @@
       <c r="E181" s="9"/>
       <c r="F181" s="9"/>
       <c r="G181" s="11"/>
-      <c r="H181" s="16"/>
+      <c r="H181" s="13"/>
       <c r="I181" s="11"/>
       <c r="J181" s="11"/>
       <c r="K181" s="11"/>
@@ -3123,7 +3182,7 @@
       <c r="E182" s="9"/>
       <c r="F182" s="9"/>
       <c r="G182" s="11"/>
-      <c r="H182" s="16"/>
+      <c r="H182" s="13"/>
       <c r="I182" s="11"/>
       <c r="J182" s="11"/>
       <c r="K182" s="11"/>
@@ -3136,7 +3195,7 @@
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
       <c r="G183" s="11"/>
-      <c r="H183" s="16"/>
+      <c r="H183" s="13"/>
       <c r="I183" s="11"/>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
@@ -3149,7 +3208,7 @@
       <c r="E184" s="9"/>
       <c r="F184" s="9"/>
       <c r="G184" s="11"/>
-      <c r="H184" s="16"/>
+      <c r="H184" s="13"/>
       <c r="I184" s="11"/>
       <c r="J184" s="11"/>
       <c r="K184" s="11"/>
@@ -3162,7 +3221,7 @@
       <c r="E185" s="9"/>
       <c r="F185" s="9"/>
       <c r="G185" s="11"/>
-      <c r="H185" s="16"/>
+      <c r="H185" s="13"/>
       <c r="I185" s="11"/>
       <c r="J185" s="11"/>
       <c r="K185" s="11"/>
@@ -3175,7 +3234,7 @@
       <c r="E186" s="9"/>
       <c r="F186" s="9"/>
       <c r="G186" s="11"/>
-      <c r="H186" s="16"/>
+      <c r="H186" s="13"/>
       <c r="I186" s="11"/>
       <c r="J186" s="11"/>
       <c r="K186" s="11"/>
@@ -3188,7 +3247,7 @@
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
       <c r="G187" s="11"/>
-      <c r="H187" s="16"/>
+      <c r="H187" s="13"/>
       <c r="I187" s="11"/>
       <c r="J187" s="11"/>
       <c r="K187" s="11"/>
@@ -3201,7 +3260,7 @@
       <c r="E188" s="9"/>
       <c r="F188" s="9"/>
       <c r="G188" s="11"/>
-      <c r="H188" s="16"/>
+      <c r="H188" s="13"/>
       <c r="I188" s="11"/>
       <c r="J188" s="11"/>
       <c r="K188" s="11"/>
@@ -3214,7 +3273,7 @@
       <c r="E189" s="9"/>
       <c r="F189" s="9"/>
       <c r="G189" s="11"/>
-      <c r="H189" s="16"/>
+      <c r="H189" s="13"/>
       <c r="I189" s="11"/>
       <c r="J189" s="11"/>
       <c r="K189" s="11"/>
@@ -3227,7 +3286,7 @@
       <c r="E190" s="9"/>
       <c r="F190" s="9"/>
       <c r="G190" s="11"/>
-      <c r="H190" s="16"/>
+      <c r="H190" s="13"/>
       <c r="I190" s="11"/>
       <c r="J190" s="11"/>
       <c r="K190" s="11"/>
@@ -3240,7 +3299,7 @@
       <c r="E191" s="9"/>
       <c r="F191" s="9"/>
       <c r="G191" s="11"/>
-      <c r="H191" s="16"/>
+      <c r="H191" s="13"/>
       <c r="I191" s="11"/>
       <c r="J191" s="11"/>
       <c r="K191" s="11"/>
@@ -3253,7 +3312,7 @@
       <c r="E192" s="9"/>
       <c r="F192" s="9"/>
       <c r="G192" s="11"/>
-      <c r="H192" s="16"/>
+      <c r="H192" s="13"/>
       <c r="I192" s="11"/>
       <c r="J192" s="11"/>
       <c r="K192" s="11"/>
@@ -3266,7 +3325,7 @@
       <c r="E193" s="9"/>
       <c r="F193" s="9"/>
       <c r="G193" s="11"/>
-      <c r="H193" s="16"/>
+      <c r="H193" s="13"/>
       <c r="I193" s="11"/>
       <c r="J193" s="11"/>
       <c r="K193" s="11"/>
@@ -3279,7 +3338,7 @@
       <c r="E194" s="9"/>
       <c r="F194" s="9"/>
       <c r="G194" s="11"/>
-      <c r="H194" s="16"/>
+      <c r="H194" s="13"/>
       <c r="I194" s="11"/>
       <c r="J194" s="11"/>
       <c r="K194" s="11"/>
@@ -3292,7 +3351,7 @@
       <c r="E195" s="9"/>
       <c r="F195" s="9"/>
       <c r="G195" s="11"/>
-      <c r="H195" s="16"/>
+      <c r="H195" s="13"/>
       <c r="I195" s="11"/>
       <c r="J195" s="11"/>
       <c r="K195" s="11"/>
@@ -3305,7 +3364,7 @@
       <c r="E196" s="9"/>
       <c r="F196" s="9"/>
       <c r="G196" s="11"/>
-      <c r="H196" s="16"/>
+      <c r="H196" s="13"/>
       <c r="I196" s="11"/>
       <c r="J196" s="11"/>
       <c r="K196" s="11"/>
@@ -3318,7 +3377,7 @@
       <c r="E197" s="9"/>
       <c r="F197" s="9"/>
       <c r="G197" s="11"/>
-      <c r="H197" s="16"/>
+      <c r="H197" s="13"/>
       <c r="I197" s="11"/>
       <c r="J197" s="11"/>
       <c r="K197" s="11"/>
@@ -3331,7 +3390,7 @@
       <c r="E198" s="9"/>
       <c r="F198" s="9"/>
       <c r="G198" s="11"/>
-      <c r="H198" s="16"/>
+      <c r="H198" s="13"/>
       <c r="I198" s="11"/>
       <c r="J198" s="11"/>
       <c r="K198" s="11"/>
@@ -3344,7 +3403,7 @@
       <c r="E199" s="9"/>
       <c r="F199" s="9"/>
       <c r="G199" s="11"/>
-      <c r="H199" s="16"/>
+      <c r="H199" s="13"/>
       <c r="I199" s="11"/>
       <c r="J199" s="11"/>
       <c r="K199" s="11"/>
@@ -3357,7 +3416,7 @@
       <c r="E200" s="9"/>
       <c r="F200" s="9"/>
       <c r="G200" s="11"/>
-      <c r="H200" s="16"/>
+      <c r="H200" s="13"/>
       <c r="I200" s="11"/>
       <c r="J200" s="11"/>
       <c r="K200" s="11"/>
@@ -3370,7 +3429,7 @@
       <c r="E201" s="9"/>
       <c r="F201" s="9"/>
       <c r="G201" s="11"/>
-      <c r="H201" s="16"/>
+      <c r="H201" s="13"/>
       <c r="I201" s="11"/>
       <c r="J201" s="11"/>
       <c r="K201" s="11"/>
@@ -3383,7 +3442,7 @@
       <c r="E202" s="9"/>
       <c r="F202" s="9"/>
       <c r="G202" s="11"/>
-      <c r="H202" s="16"/>
+      <c r="H202" s="13"/>
       <c r="I202" s="11"/>
       <c r="J202" s="11"/>
       <c r="K202" s="11"/>
@@ -3396,7 +3455,7 @@
       <c r="E203" s="9"/>
       <c r="F203" s="9"/>
       <c r="G203" s="11"/>
-      <c r="H203" s="16"/>
+      <c r="H203" s="13"/>
       <c r="I203" s="11"/>
       <c r="J203" s="11"/>
       <c r="K203" s="11"/>
@@ -3409,7 +3468,7 @@
       <c r="E204" s="9"/>
       <c r="F204" s="9"/>
       <c r="G204" s="11"/>
-      <c r="H204" s="16"/>
+      <c r="H204" s="13"/>
       <c r="I204" s="11"/>
       <c r="J204" s="11"/>
       <c r="K204" s="11"/>
@@ -3422,7 +3481,7 @@
       <c r="E205" s="9"/>
       <c r="F205" s="9"/>
       <c r="G205" s="11"/>
-      <c r="H205" s="16"/>
+      <c r="H205" s="13"/>
       <c r="I205" s="11"/>
       <c r="J205" s="11"/>
       <c r="K205" s="11"/>
@@ -3435,7 +3494,7 @@
       <c r="E206" s="9"/>
       <c r="F206" s="9"/>
       <c r="G206" s="11"/>
-      <c r="H206" s="16"/>
+      <c r="H206" s="13"/>
       <c r="I206" s="11"/>
       <c r="J206" s="11"/>
       <c r="K206" s="11"/>
@@ -3448,7 +3507,7 @@
       <c r="E207" s="9"/>
       <c r="F207" s="9"/>
       <c r="G207" s="11"/>
-      <c r="H207" s="16"/>
+      <c r="H207" s="13"/>
       <c r="I207" s="11"/>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
@@ -3461,7 +3520,7 @@
       <c r="E208" s="9"/>
       <c r="F208" s="9"/>
       <c r="G208" s="11"/>
-      <c r="H208" s="16"/>
+      <c r="H208" s="13"/>
       <c r="I208" s="11"/>
       <c r="J208" s="11"/>
       <c r="K208" s="11"/>
@@ -3474,7 +3533,7 @@
       <c r="E209" s="9"/>
       <c r="F209" s="9"/>
       <c r="G209" s="11"/>
-      <c r="H209" s="16"/>
+      <c r="H209" s="13"/>
       <c r="I209" s="11"/>
       <c r="J209" s="11"/>
       <c r="K209" s="11"/>
@@ -3487,7 +3546,7 @@
       <c r="E210" s="9"/>
       <c r="F210" s="9"/>
       <c r="G210" s="11"/>
-      <c r="H210" s="16"/>
+      <c r="H210" s="13"/>
       <c r="I210" s="11"/>
       <c r="J210" s="11"/>
       <c r="K210" s="11"/>
@@ -3500,7 +3559,7 @@
       <c r="E211" s="9"/>
       <c r="F211" s="9"/>
       <c r="G211" s="11"/>
-      <c r="H211" s="16"/>
+      <c r="H211" s="13"/>
       <c r="I211" s="11"/>
       <c r="J211" s="11"/>
       <c r="K211" s="11"/>
@@ -3513,7 +3572,7 @@
       <c r="E212" s="9"/>
       <c r="F212" s="9"/>
       <c r="G212" s="11"/>
-      <c r="H212" s="16"/>
+      <c r="H212" s="13"/>
       <c r="I212" s="11"/>
       <c r="J212" s="11"/>
       <c r="K212" s="11"/>
@@ -3526,7 +3585,7 @@
       <c r="E213" s="9"/>
       <c r="F213" s="9"/>
       <c r="G213" s="11"/>
-      <c r="H213" s="16"/>
+      <c r="H213" s="13"/>
       <c r="I213" s="11"/>
       <c r="J213" s="11"/>
       <c r="K213" s="11"/>
@@ -3539,7 +3598,7 @@
       <c r="E214" s="9"/>
       <c r="F214" s="9"/>
       <c r="G214" s="11"/>
-      <c r="H214" s="16"/>
+      <c r="H214" s="13"/>
       <c r="I214" s="11"/>
       <c r="J214" s="11"/>
       <c r="K214" s="11"/>
@@ -3552,7 +3611,7 @@
       <c r="E215" s="9"/>
       <c r="F215" s="9"/>
       <c r="G215" s="11"/>
-      <c r="H215" s="16"/>
+      <c r="H215" s="13"/>
       <c r="I215" s="11"/>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
@@ -3565,7 +3624,7 @@
       <c r="E216" s="9"/>
       <c r="F216" s="9"/>
       <c r="G216" s="11"/>
-      <c r="H216" s="16"/>
+      <c r="H216" s="13"/>
       <c r="I216" s="11"/>
       <c r="J216" s="11"/>
       <c r="K216" s="11"/>
@@ -3578,7 +3637,7 @@
       <c r="E217" s="9"/>
       <c r="F217" s="9"/>
       <c r="G217" s="11"/>
-      <c r="H217" s="16"/>
+      <c r="H217" s="13"/>
       <c r="I217" s="11"/>
       <c r="J217" s="11"/>
       <c r="K217" s="11"/>
@@ -3591,7 +3650,7 @@
       <c r="E218" s="9"/>
       <c r="F218" s="9"/>
       <c r="G218" s="11"/>
-      <c r="H218" s="16"/>
+      <c r="H218" s="13"/>
       <c r="I218" s="11"/>
       <c r="J218" s="11"/>
       <c r="K218" s="11"/>
@@ -3604,7 +3663,7 @@
       <c r="E219" s="9"/>
       <c r="F219" s="9"/>
       <c r="G219" s="11"/>
-      <c r="H219" s="16"/>
+      <c r="H219" s="13"/>
       <c r="I219" s="11"/>
       <c r="J219" s="11"/>
       <c r="K219" s="11"/>
@@ -3617,7 +3676,7 @@
       <c r="E220" s="9"/>
       <c r="F220" s="9"/>
       <c r="G220" s="11"/>
-      <c r="H220" s="16"/>
+      <c r="H220" s="13"/>
       <c r="I220" s="11"/>
       <c r="J220" s="11"/>
       <c r="K220" s="11"/>
@@ -3630,7 +3689,7 @@
       <c r="E221" s="9"/>
       <c r="F221" s="9"/>
       <c r="G221" s="11"/>
-      <c r="H221" s="16"/>
+      <c r="H221" s="13"/>
       <c r="I221" s="11"/>
       <c r="J221" s="11"/>
       <c r="K221" s="11"/>
@@ -3643,7 +3702,7 @@
       <c r="E222" s="9"/>
       <c r="F222" s="9"/>
       <c r="G222" s="11"/>
-      <c r="H222" s="16"/>
+      <c r="H222" s="13"/>
       <c r="I222" s="11"/>
       <c r="J222" s="11"/>
       <c r="K222" s="11"/>
@@ -3656,7 +3715,7 @@
       <c r="E223" s="9"/>
       <c r="F223" s="9"/>
       <c r="G223" s="11"/>
-      <c r="H223" s="16"/>
+      <c r="H223" s="13"/>
       <c r="I223" s="11"/>
       <c r="J223" s="11"/>
       <c r="K223" s="11"/>
@@ -3669,7 +3728,7 @@
       <c r="E224" s="9"/>
       <c r="F224" s="9"/>
       <c r="G224" s="11"/>
-      <c r="H224" s="16"/>
+      <c r="H224" s="13"/>
       <c r="I224" s="11"/>
       <c r="J224" s="11"/>
       <c r="K224" s="11"/>
@@ -3682,7 +3741,7 @@
       <c r="E225" s="9"/>
       <c r="F225" s="9"/>
       <c r="G225" s="11"/>
-      <c r="H225" s="16"/>
+      <c r="H225" s="13"/>
       <c r="I225" s="11"/>
       <c r="J225" s="11"/>
       <c r="K225" s="11"/>
@@ -3695,7 +3754,7 @@
       <c r="E226" s="9"/>
       <c r="F226" s="9"/>
       <c r="G226" s="11"/>
-      <c r="H226" s="16"/>
+      <c r="H226" s="13"/>
       <c r="I226" s="11"/>
       <c r="J226" s="11"/>
       <c r="K226" s="11"/>
@@ -3708,7 +3767,7 @@
       <c r="E227" s="9"/>
       <c r="F227" s="9"/>
       <c r="G227" s="11"/>
-      <c r="H227" s="16"/>
+      <c r="H227" s="13"/>
       <c r="I227" s="11"/>
       <c r="J227" s="11"/>
       <c r="K227" s="11"/>
@@ -3721,7 +3780,7 @@
       <c r="E228" s="9"/>
       <c r="F228" s="9"/>
       <c r="G228" s="11"/>
-      <c r="H228" s="16"/>
+      <c r="H228" s="13"/>
       <c r="I228" s="11"/>
       <c r="J228" s="11"/>
       <c r="K228" s="11"/>
@@ -3734,7 +3793,7 @@
       <c r="E229" s="9"/>
       <c r="F229" s="9"/>
       <c r="G229" s="11"/>
-      <c r="H229" s="16"/>
+      <c r="H229" s="13"/>
       <c r="I229" s="11"/>
       <c r="J229" s="11"/>
       <c r="K229" s="11"/>
@@ -3747,7 +3806,7 @@
       <c r="E230" s="9"/>
       <c r="F230" s="9"/>
       <c r="G230" s="11"/>
-      <c r="H230" s="16"/>
+      <c r="H230" s="13"/>
       <c r="I230" s="11"/>
       <c r="J230" s="11"/>
       <c r="K230" s="11"/>
@@ -3760,7 +3819,7 @@
       <c r="E231" s="9"/>
       <c r="F231" s="9"/>
       <c r="G231" s="11"/>
-      <c r="H231" s="16"/>
+      <c r="H231" s="13"/>
       <c r="I231" s="11"/>
       <c r="J231" s="11"/>
       <c r="K231" s="11"/>
@@ -3773,7 +3832,7 @@
       <c r="E232" s="9"/>
       <c r="F232" s="9"/>
       <c r="G232" s="11"/>
-      <c r="H232" s="16"/>
+      <c r="H232" s="13"/>
       <c r="I232" s="11"/>
       <c r="J232" s="11"/>
       <c r="K232" s="11"/>
@@ -3786,7 +3845,7 @@
       <c r="E233" s="9"/>
       <c r="F233" s="9"/>
       <c r="G233" s="11"/>
-      <c r="H233" s="16"/>
+      <c r="H233" s="13"/>
       <c r="I233" s="11"/>
       <c r="J233" s="11"/>
       <c r="K233" s="11"/>
@@ -3799,7 +3858,7 @@
       <c r="E234" s="9"/>
       <c r="F234" s="9"/>
       <c r="G234" s="11"/>
-      <c r="H234" s="16"/>
+      <c r="H234" s="13"/>
       <c r="I234" s="11"/>
       <c r="J234" s="11"/>
       <c r="K234" s="11"/>
@@ -3812,7 +3871,7 @@
       <c r="E235" s="9"/>
       <c r="F235" s="9"/>
       <c r="G235" s="11"/>
-      <c r="H235" s="16"/>
+      <c r="H235" s="13"/>
       <c r="I235" s="11"/>
       <c r="J235" s="11"/>
       <c r="K235" s="11"/>
@@ -3825,7 +3884,7 @@
       <c r="E236" s="9"/>
       <c r="F236" s="9"/>
       <c r="G236" s="11"/>
-      <c r="H236" s="16"/>
+      <c r="H236" s="13"/>
       <c r="I236" s="11"/>
       <c r="J236" s="11"/>
       <c r="K236" s="11"/>
@@ -3838,7 +3897,7 @@
       <c r="E237" s="9"/>
       <c r="F237" s="9"/>
       <c r="G237" s="11"/>
-      <c r="H237" s="16"/>
+      <c r="H237" s="13"/>
       <c r="I237" s="11"/>
       <c r="J237" s="11"/>
       <c r="K237" s="11"/>
@@ -3851,7 +3910,7 @@
       <c r="E238" s="9"/>
       <c r="F238" s="9"/>
       <c r="G238" s="11"/>
-      <c r="H238" s="16"/>
+      <c r="H238" s="13"/>
       <c r="I238" s="11"/>
       <c r="J238" s="11"/>
       <c r="K238" s="11"/>
@@ -3864,7 +3923,7 @@
       <c r="E239" s="9"/>
       <c r="F239" s="9"/>
       <c r="G239" s="11"/>
-      <c r="H239" s="16"/>
+      <c r="H239" s="13"/>
       <c r="I239" s="11"/>
       <c r="J239" s="11"/>
       <c r="K239" s="11"/>
@@ -3877,7 +3936,7 @@
       <c r="E240" s="9"/>
       <c r="F240" s="9"/>
       <c r="G240" s="11"/>
-      <c r="H240" s="16"/>
+      <c r="H240" s="13"/>
       <c r="I240" s="11"/>
       <c r="J240" s="11"/>
       <c r="K240" s="11"/>
@@ -3890,7 +3949,7 @@
       <c r="E241" s="9"/>
       <c r="F241" s="9"/>
       <c r="G241" s="11"/>
-      <c r="H241" s="16"/>
+      <c r="H241" s="13"/>
       <c r="I241" s="11"/>
       <c r="J241" s="11"/>
       <c r="K241" s="11"/>
@@ -3903,7 +3962,7 @@
       <c r="E242" s="9"/>
       <c r="F242" s="9"/>
       <c r="G242" s="11"/>
-      <c r="H242" s="16"/>
+      <c r="H242" s="13"/>
       <c r="I242" s="11"/>
       <c r="J242" s="11"/>
       <c r="K242" s="11"/>
@@ -3916,7 +3975,7 @@
       <c r="E243" s="9"/>
       <c r="F243" s="9"/>
       <c r="G243" s="11"/>
-      <c r="H243" s="16"/>
+      <c r="H243" s="13"/>
       <c r="I243" s="11"/>
       <c r="J243" s="11"/>
       <c r="K243" s="11"/>
@@ -3929,7 +3988,7 @@
       <c r="E244" s="9"/>
       <c r="F244" s="9"/>
       <c r="G244" s="11"/>
-      <c r="H244" s="16"/>
+      <c r="H244" s="13"/>
       <c r="I244" s="11"/>
       <c r="J244" s="11"/>
       <c r="K244" s="11"/>
@@ -3942,7 +4001,7 @@
       <c r="E245" s="9"/>
       <c r="F245" s="9"/>
       <c r="G245" s="11"/>
-      <c r="H245" s="16"/>
+      <c r="H245" s="13"/>
       <c r="I245" s="11"/>
       <c r="J245" s="11"/>
       <c r="K245" s="11"/>
@@ -3955,7 +4014,7 @@
       <c r="E246" s="9"/>
       <c r="F246" s="9"/>
       <c r="G246" s="11"/>
-      <c r="H246" s="16"/>
+      <c r="H246" s="13"/>
       <c r="I246" s="11"/>
       <c r="J246" s="11"/>
       <c r="K246" s="11"/>
@@ -3968,7 +4027,7 @@
       <c r="E247" s="9"/>
       <c r="F247" s="9"/>
       <c r="G247" s="11"/>
-      <c r="H247" s="16"/>
+      <c r="H247" s="13"/>
       <c r="I247" s="11"/>
       <c r="J247" s="11"/>
       <c r="K247" s="11"/>
@@ -3981,7 +4040,7 @@
       <c r="E248" s="9"/>
       <c r="F248" s="9"/>
       <c r="G248" s="11"/>
-      <c r="H248" s="16"/>
+      <c r="H248" s="13"/>
       <c r="I248" s="11"/>
       <c r="J248" s="11"/>
       <c r="K248" s="11"/>
@@ -3994,7 +4053,7 @@
       <c r="E249" s="9"/>
       <c r="F249" s="9"/>
       <c r="G249" s="11"/>
-      <c r="H249" s="16"/>
+      <c r="H249" s="13"/>
       <c r="I249" s="11"/>
       <c r="J249" s="11"/>
       <c r="K249" s="11"/>
@@ -4007,7 +4066,7 @@
       <c r="E250" s="9"/>
       <c r="F250" s="9"/>
       <c r="G250" s="11"/>
-      <c r="H250" s="16"/>
+      <c r="H250" s="13"/>
       <c r="I250" s="11"/>
       <c r="J250" s="11"/>
       <c r="K250" s="11"/>
@@ -4020,7 +4079,7 @@
       <c r="E251" s="9"/>
       <c r="F251" s="9"/>
       <c r="G251" s="11"/>
-      <c r="H251" s="16"/>
+      <c r="H251" s="13"/>
       <c r="I251" s="11"/>
       <c r="J251" s="11"/>
       <c r="K251" s="11"/>
@@ -4033,7 +4092,7 @@
       <c r="E252" s="9"/>
       <c r="F252" s="9"/>
       <c r="G252" s="11"/>
-      <c r="H252" s="16"/>
+      <c r="H252" s="13"/>
       <c r="I252" s="11"/>
       <c r="J252" s="11"/>
       <c r="K252" s="11"/>
@@ -4046,7 +4105,7 @@
       <c r="E253" s="9"/>
       <c r="F253" s="9"/>
       <c r="G253" s="11"/>
-      <c r="H253" s="16"/>
+      <c r="H253" s="13"/>
       <c r="I253" s="11"/>
       <c r="J253" s="11"/>
       <c r="K253" s="11"/>
@@ -4059,7 +4118,7 @@
       <c r="E254" s="9"/>
       <c r="F254" s="9"/>
       <c r="G254" s="11"/>
-      <c r="H254" s="16"/>
+      <c r="H254" s="13"/>
       <c r="I254" s="11"/>
       <c r="J254" s="11"/>
       <c r="K254" s="11"/>
@@ -4072,7 +4131,7 @@
       <c r="E255" s="9"/>
       <c r="F255" s="9"/>
       <c r="G255" s="11"/>
-      <c r="H255" s="16"/>
+      <c r="H255" s="13"/>
       <c r="I255" s="11"/>
       <c r="J255" s="11"/>
       <c r="K255" s="11"/>
@@ -4085,7 +4144,7 @@
       <c r="E256" s="9"/>
       <c r="F256" s="9"/>
       <c r="G256" s="11"/>
-      <c r="H256" s="16"/>
+      <c r="H256" s="13"/>
       <c r="I256" s="11"/>
       <c r="J256" s="11"/>
       <c r="K256" s="11"/>
@@ -4098,7 +4157,7 @@
       <c r="E257" s="9"/>
       <c r="F257" s="9"/>
       <c r="G257" s="11"/>
-      <c r="H257" s="16"/>
+      <c r="H257" s="13"/>
       <c r="I257" s="11"/>
       <c r="J257" s="11"/>
       <c r="K257" s="11"/>
@@ -4111,7 +4170,7 @@
       <c r="E258" s="9"/>
       <c r="F258" s="9"/>
       <c r="G258" s="11"/>
-      <c r="H258" s="16"/>
+      <c r="H258" s="13"/>
       <c r="I258" s="11"/>
       <c r="J258" s="11"/>
       <c r="K258" s="11"/>
@@ -4124,7 +4183,7 @@
       <c r="E259" s="9"/>
       <c r="F259" s="9"/>
       <c r="G259" s="11"/>
-      <c r="H259" s="16"/>
+      <c r="H259" s="13"/>
       <c r="I259" s="11"/>
       <c r="J259" s="11"/>
       <c r="K259" s="11"/>
@@ -4137,7 +4196,7 @@
       <c r="E260" s="9"/>
       <c r="F260" s="9"/>
       <c r="G260" s="11"/>
-      <c r="H260" s="16"/>
+      <c r="H260" s="13"/>
       <c r="I260" s="11"/>
       <c r="J260" s="11"/>
       <c r="K260" s="11"/>
@@ -4150,7 +4209,7 @@
       <c r="E261" s="9"/>
       <c r="F261" s="9"/>
       <c r="G261" s="11"/>
-      <c r="H261" s="16"/>
+      <c r="H261" s="13"/>
       <c r="I261" s="11"/>
       <c r="J261" s="11"/>
       <c r="K261" s="11"/>
@@ -4163,7 +4222,7 @@
       <c r="E262" s="9"/>
       <c r="F262" s="9"/>
       <c r="G262" s="11"/>
-      <c r="H262" s="16"/>
+      <c r="H262" s="13"/>
       <c r="I262" s="11"/>
       <c r="J262" s="11"/>
       <c r="K262" s="11"/>
@@ -4176,7 +4235,7 @@
       <c r="E263" s="9"/>
       <c r="F263" s="9"/>
       <c r="G263" s="11"/>
-      <c r="H263" s="16"/>
+      <c r="H263" s="13"/>
       <c r="I263" s="11"/>
       <c r="J263" s="11"/>
       <c r="K263" s="11"/>
@@ -4189,7 +4248,7 @@
       <c r="E264" s="9"/>
       <c r="F264" s="9"/>
       <c r="G264" s="11"/>
-      <c r="H264" s="16"/>
+      <c r="H264" s="13"/>
       <c r="I264" s="11"/>
       <c r="J264" s="11"/>
       <c r="K264" s="11"/>
@@ -4202,7 +4261,7 @@
       <c r="E265" s="9"/>
       <c r="F265" s="9"/>
       <c r="G265" s="11"/>
-      <c r="H265" s="16"/>
+      <c r="H265" s="13"/>
       <c r="I265" s="11"/>
       <c r="J265" s="11"/>
       <c r="K265" s="11"/>
@@ -4215,7 +4274,7 @@
       <c r="E266" s="9"/>
       <c r="F266" s="9"/>
       <c r="G266" s="11"/>
-      <c r="H266" s="16"/>
+      <c r="H266" s="13"/>
       <c r="I266" s="11"/>
       <c r="J266" s="11"/>
       <c r="K266" s="11"/>
@@ -4228,7 +4287,7 @@
       <c r="E267" s="9"/>
       <c r="F267" s="9"/>
       <c r="G267" s="11"/>
-      <c r="H267" s="16"/>
+      <c r="H267" s="13"/>
       <c r="I267" s="11"/>
       <c r="J267" s="11"/>
       <c r="K267" s="11"/>
@@ -4241,7 +4300,7 @@
       <c r="E268" s="9"/>
       <c r="F268" s="9"/>
       <c r="G268" s="11"/>
-      <c r="H268" s="16"/>
+      <c r="H268" s="13"/>
       <c r="I268" s="11"/>
       <c r="J268" s="11"/>
       <c r="K268" s="11"/>
@@ -4254,7 +4313,7 @@
       <c r="E269" s="9"/>
       <c r="F269" s="9"/>
       <c r="G269" s="11"/>
-      <c r="H269" s="16"/>
+      <c r="H269" s="13"/>
       <c r="I269" s="11"/>
       <c r="J269" s="11"/>
       <c r="K269" s="11"/>
@@ -4267,7 +4326,7 @@
       <c r="E270" s="9"/>
       <c r="F270" s="9"/>
       <c r="G270" s="11"/>
-      <c r="H270" s="16"/>
+      <c r="H270" s="13"/>
       <c r="I270" s="11"/>
       <c r="J270" s="11"/>
       <c r="K270" s="11"/>
@@ -4280,7 +4339,7 @@
       <c r="E271" s="9"/>
       <c r="F271" s="9"/>
       <c r="G271" s="11"/>
-      <c r="H271" s="16"/>
+      <c r="H271" s="13"/>
       <c r="I271" s="11"/>
       <c r="J271" s="11"/>
       <c r="K271" s="11"/>
@@ -4293,7 +4352,7 @@
       <c r="E272" s="9"/>
       <c r="F272" s="9"/>
       <c r="G272" s="11"/>
-      <c r="H272" s="16"/>
+      <c r="H272" s="13"/>
       <c r="I272" s="11"/>
       <c r="J272" s="11"/>
       <c r="K272" s="11"/>
@@ -4306,7 +4365,7 @@
       <c r="E273" s="9"/>
       <c r="F273" s="9"/>
       <c r="G273" s="11"/>
-      <c r="H273" s="16"/>
+      <c r="H273" s="13"/>
       <c r="I273" s="11"/>
       <c r="J273" s="11"/>
       <c r="K273" s="11"/>
@@ -4319,7 +4378,7 @@
       <c r="E274" s="9"/>
       <c r="F274" s="9"/>
       <c r="G274" s="11"/>
-      <c r="H274" s="16"/>
+      <c r="H274" s="13"/>
       <c r="I274" s="11"/>
       <c r="J274" s="11"/>
       <c r="K274" s="11"/>
@@ -4332,7 +4391,7 @@
       <c r="E275" s="9"/>
       <c r="F275" s="9"/>
       <c r="G275" s="11"/>
-      <c r="H275" s="16"/>
+      <c r="H275" s="13"/>
       <c r="I275" s="11"/>
       <c r="J275" s="11"/>
       <c r="K275" s="11"/>
@@ -4345,7 +4404,7 @@
       <c r="E276" s="9"/>
       <c r="F276" s="9"/>
       <c r="G276" s="11"/>
-      <c r="H276" s="16"/>
+      <c r="H276" s="13"/>
       <c r="I276" s="11"/>
       <c r="J276" s="11"/>
       <c r="K276" s="11"/>
@@ -4358,7 +4417,7 @@
       <c r="E277" s="9"/>
       <c r="F277" s="9"/>
       <c r="G277" s="11"/>
-      <c r="H277" s="16"/>
+      <c r="H277" s="13"/>
       <c r="I277" s="11"/>
       <c r="J277" s="11"/>
       <c r="K277" s="11"/>
@@ -4371,7 +4430,7 @@
       <c r="E278" s="9"/>
       <c r="F278" s="9"/>
       <c r="G278" s="11"/>
-      <c r="H278" s="16"/>
+      <c r="H278" s="13"/>
       <c r="I278" s="11"/>
       <c r="J278" s="11"/>
       <c r="K278" s="11"/>
@@ -4384,7 +4443,7 @@
       <c r="E279" s="9"/>
       <c r="F279" s="9"/>
       <c r="G279" s="11"/>
-      <c r="H279" s="16"/>
+      <c r="H279" s="13"/>
       <c r="I279" s="11"/>
       <c r="J279" s="11"/>
       <c r="K279" s="11"/>
@@ -4397,7 +4456,7 @@
       <c r="E280" s="9"/>
       <c r="F280" s="9"/>
       <c r="G280" s="11"/>
-      <c r="H280" s="16"/>
+      <c r="H280" s="13"/>
       <c r="I280" s="11"/>
       <c r="J280" s="11"/>
       <c r="K280" s="11"/>
@@ -4410,7 +4469,7 @@
       <c r="E281" s="9"/>
       <c r="F281" s="9"/>
       <c r="G281" s="11"/>
-      <c r="H281" s="16"/>
+      <c r="H281" s="13"/>
       <c r="I281" s="11"/>
       <c r="J281" s="11"/>
       <c r="K281" s="11"/>
@@ -4423,7 +4482,7 @@
       <c r="E282" s="9"/>
       <c r="F282" s="9"/>
       <c r="G282" s="11"/>
-      <c r="H282" s="16"/>
+      <c r="H282" s="13"/>
       <c r="I282" s="11"/>
       <c r="J282" s="11"/>
       <c r="K282" s="11"/>
@@ -4436,7 +4495,7 @@
       <c r="E283" s="9"/>
       <c r="F283" s="9"/>
       <c r="G283" s="11"/>
-      <c r="H283" s="16"/>
+      <c r="H283" s="13"/>
       <c r="I283" s="11"/>
       <c r="J283" s="11"/>
       <c r="K283" s="11"/>
@@ -4449,7 +4508,7 @@
       <c r="E284" s="9"/>
       <c r="F284" s="9"/>
       <c r="G284" s="11"/>
-      <c r="H284" s="16"/>
+      <c r="H284" s="13"/>
       <c r="I284" s="11"/>
       <c r="J284" s="11"/>
       <c r="K284" s="11"/>
@@ -4462,7 +4521,7 @@
       <c r="E285" s="9"/>
       <c r="F285" s="9"/>
       <c r="G285" s="11"/>
-      <c r="H285" s="16"/>
+      <c r="H285" s="13"/>
       <c r="I285" s="11"/>
       <c r="J285" s="11"/>
       <c r="K285" s="11"/>
@@ -4475,7 +4534,7 @@
       <c r="E286" s="9"/>
       <c r="F286" s="9"/>
       <c r="G286" s="11"/>
-      <c r="H286" s="16"/>
+      <c r="H286" s="13"/>
       <c r="I286" s="11"/>
       <c r="J286" s="11"/>
       <c r="K286" s="11"/>
@@ -4488,7 +4547,7 @@
       <c r="E287" s="9"/>
       <c r="F287" s="9"/>
       <c r="G287" s="11"/>
-      <c r="H287" s="16"/>
+      <c r="H287" s="13"/>
       <c r="I287" s="11"/>
       <c r="J287" s="11"/>
       <c r="K287" s="11"/>
@@ -4501,7 +4560,7 @@
       <c r="E288" s="9"/>
       <c r="F288" s="9"/>
       <c r="G288" s="11"/>
-      <c r="H288" s="16"/>
+      <c r="H288" s="13"/>
       <c r="I288" s="11"/>
       <c r="J288" s="11"/>
       <c r="K288" s="11"/>
@@ -4514,7 +4573,7 @@
       <c r="E289" s="9"/>
       <c r="F289" s="9"/>
       <c r="G289" s="11"/>
-      <c r="H289" s="16"/>
+      <c r="H289" s="13"/>
       <c r="I289" s="11"/>
       <c r="J289" s="11"/>
       <c r="K289" s="11"/>
@@ -4527,7 +4586,7 @@
       <c r="E290" s="9"/>
       <c r="F290" s="9"/>
       <c r="G290" s="11"/>
-      <c r="H290" s="16"/>
+      <c r="H290" s="13"/>
       <c r="I290" s="11"/>
       <c r="J290" s="11"/>
       <c r="K290" s="11"/>
@@ -4540,7 +4599,7 @@
       <c r="E291" s="9"/>
       <c r="F291" s="9"/>
       <c r="G291" s="11"/>
-      <c r="H291" s="16"/>
+      <c r="H291" s="13"/>
       <c r="I291" s="11"/>
       <c r="J291" s="11"/>
       <c r="K291" s="11"/>
@@ -4553,7 +4612,7 @@
       <c r="E292" s="9"/>
       <c r="F292" s="9"/>
       <c r="G292" s="11"/>
-      <c r="H292" s="16"/>
+      <c r="H292" s="13"/>
       <c r="I292" s="11"/>
       <c r="J292" s="11"/>
       <c r="K292" s="11"/>
@@ -4566,7 +4625,7 @@
       <c r="E293" s="9"/>
       <c r="F293" s="9"/>
       <c r="G293" s="11"/>
-      <c r="H293" s="16"/>
+      <c r="H293" s="13"/>
       <c r="I293" s="11"/>
       <c r="J293" s="11"/>
       <c r="K293" s="11"/>
@@ -4579,7 +4638,7 @@
       <c r="E294" s="9"/>
       <c r="F294" s="9"/>
       <c r="G294" s="11"/>
-      <c r="H294" s="16"/>
+      <c r="H294" s="13"/>
       <c r="I294" s="11"/>
       <c r="J294" s="11"/>
       <c r="K294" s="11"/>
@@ -4592,7 +4651,7 @@
       <c r="E295" s="9"/>
       <c r="F295" s="9"/>
       <c r="G295" s="11"/>
-      <c r="H295" s="16"/>
+      <c r="H295" s="13"/>
       <c r="I295" s="11"/>
       <c r="J295" s="11"/>
       <c r="K295" s="11"/>
@@ -4605,7 +4664,7 @@
       <c r="E296" s="9"/>
       <c r="F296" s="9"/>
       <c r="G296" s="11"/>
-      <c r="H296" s="16"/>
+      <c r="H296" s="13"/>
       <c r="I296" s="11"/>
       <c r="J296" s="11"/>
       <c r="K296" s="11"/>
@@ -4618,7 +4677,7 @@
       <c r="E297" s="9"/>
       <c r="F297" s="9"/>
       <c r="G297" s="11"/>
-      <c r="H297" s="16"/>
+      <c r="H297" s="13"/>
       <c r="I297" s="11"/>
       <c r="J297" s="11"/>
       <c r="K297" s="11"/>
@@ -4631,7 +4690,7 @@
       <c r="E298" s="9"/>
       <c r="F298" s="9"/>
       <c r="G298" s="11"/>
-      <c r="H298" s="16"/>
+      <c r="H298" s="13"/>
       <c r="I298" s="11"/>
       <c r="J298" s="11"/>
       <c r="K298" s="11"/>
@@ -4644,7 +4703,7 @@
       <c r="E299" s="9"/>
       <c r="F299" s="9"/>
       <c r="G299" s="11"/>
-      <c r="H299" s="16"/>
+      <c r="H299" s="13"/>
       <c r="I299" s="11"/>
       <c r="J299" s="11"/>
       <c r="K299" s="11"/>
@@ -4657,7 +4716,7 @@
       <c r="E300" s="9"/>
       <c r="F300" s="9"/>
       <c r="G300" s="11"/>
-      <c r="H300" s="16"/>
+      <c r="H300" s="13"/>
       <c r="I300" s="11"/>
       <c r="J300" s="11"/>
       <c r="K300" s="11"/>
@@ -4670,7 +4729,7 @@
       <c r="E301" s="9"/>
       <c r="F301" s="9"/>
       <c r="G301" s="11"/>
-      <c r="H301" s="16"/>
+      <c r="H301" s="13"/>
       <c r="I301" s="11"/>
       <c r="J301" s="11"/>
       <c r="K301" s="11"/>
@@ -4683,7 +4742,7 @@
       <c r="E302" s="9"/>
       <c r="F302" s="9"/>
       <c r="G302" s="11"/>
-      <c r="H302" s="16"/>
+      <c r="H302" s="13"/>
       <c r="I302" s="11"/>
       <c r="J302" s="11"/>
       <c r="K302" s="11"/>
@@ -4696,7 +4755,7 @@
       <c r="E303" s="9"/>
       <c r="F303" s="9"/>
       <c r="G303" s="11"/>
-      <c r="H303" s="16"/>
+      <c r="H303" s="13"/>
       <c r="I303" s="11"/>
       <c r="J303" s="11"/>
       <c r="K303" s="11"/>
@@ -4709,7 +4768,7 @@
       <c r="E304" s="9"/>
       <c r="F304" s="9"/>
       <c r="G304" s="11"/>
-      <c r="H304" s="16"/>
+      <c r="H304" s="13"/>
       <c r="I304" s="11"/>
       <c r="J304" s="11"/>
       <c r="K304" s="11"/>
@@ -4722,7 +4781,7 @@
       <c r="E305" s="9"/>
       <c r="F305" s="9"/>
       <c r="G305" s="11"/>
-      <c r="H305" s="16"/>
+      <c r="H305" s="13"/>
       <c r="I305" s="11"/>
       <c r="J305" s="11"/>
       <c r="K305" s="11"/>
@@ -4735,7 +4794,7 @@
       <c r="E306" s="9"/>
       <c r="F306" s="9"/>
       <c r="G306" s="11"/>
-      <c r="H306" s="16"/>
+      <c r="H306" s="13"/>
       <c r="I306" s="11"/>
       <c r="J306" s="11"/>
       <c r="K306" s="11"/>
@@ -4748,7 +4807,7 @@
       <c r="E307" s="9"/>
       <c r="F307" s="9"/>
       <c r="G307" s="11"/>
-      <c r="H307" s="16"/>
+      <c r="H307" s="13"/>
       <c r="I307" s="11"/>
       <c r="J307" s="11"/>
       <c r="K307" s="11"/>
@@ -4761,7 +4820,7 @@
       <c r="E308" s="9"/>
       <c r="F308" s="9"/>
       <c r="G308" s="11"/>
-      <c r="H308" s="16"/>
+      <c r="H308" s="13"/>
       <c r="I308" s="11"/>
       <c r="J308" s="11"/>
       <c r="K308" s="11"/>
@@ -4774,7 +4833,7 @@
       <c r="E309" s="9"/>
       <c r="F309" s="9"/>
       <c r="G309" s="11"/>
-      <c r="H309" s="16"/>
+      <c r="H309" s="13"/>
       <c r="I309" s="11"/>
       <c r="J309" s="11"/>
       <c r="K309" s="11"/>
@@ -4787,7 +4846,7 @@
       <c r="E310" s="9"/>
       <c r="F310" s="9"/>
       <c r="G310" s="11"/>
-      <c r="H310" s="16"/>
+      <c r="H310" s="13"/>
       <c r="I310" s="11"/>
       <c r="J310" s="11"/>
       <c r="K310" s="11"/>
@@ -4800,7 +4859,7 @@
       <c r="E311" s="9"/>
       <c r="F311" s="9"/>
       <c r="G311" s="11"/>
-      <c r="H311" s="16"/>
+      <c r="H311" s="13"/>
       <c r="I311" s="11"/>
       <c r="J311" s="11"/>
       <c r="K311" s="11"/>
@@ -4813,7 +4872,7 @@
       <c r="E312" s="9"/>
       <c r="F312" s="9"/>
       <c r="G312" s="11"/>
-      <c r="H312" s="16"/>
+      <c r="H312" s="13"/>
       <c r="I312" s="11"/>
       <c r="J312" s="11"/>
       <c r="K312" s="11"/>
@@ -4826,7 +4885,7 @@
       <c r="E313" s="9"/>
       <c r="F313" s="9"/>
       <c r="G313" s="11"/>
-      <c r="H313" s="16"/>
+      <c r="H313" s="13"/>
       <c r="I313" s="11"/>
       <c r="J313" s="11"/>
       <c r="K313" s="11"/>
@@ -4839,7 +4898,7 @@
       <c r="E314" s="9"/>
       <c r="F314" s="9"/>
       <c r="G314" s="11"/>
-      <c r="H314" s="16"/>
+      <c r="H314" s="13"/>
       <c r="I314" s="11"/>
       <c r="J314" s="11"/>
       <c r="K314" s="11"/>
@@ -4852,7 +4911,7 @@
       <c r="E315" s="9"/>
       <c r="F315" s="9"/>
       <c r="G315" s="11"/>
-      <c r="H315" s="16"/>
+      <c r="H315" s="13"/>
       <c r="I315" s="11"/>
       <c r="J315" s="11"/>
       <c r="K315" s="11"/>
@@ -4865,7 +4924,7 @@
       <c r="E316" s="9"/>
       <c r="F316" s="9"/>
       <c r="G316" s="11"/>
-      <c r="H316" s="16"/>
+      <c r="H316" s="13"/>
       <c r="I316" s="11"/>
       <c r="J316" s="11"/>
       <c r="K316" s="11"/>
@@ -4878,7 +4937,7 @@
       <c r="E317" s="9"/>
       <c r="F317" s="9"/>
       <c r="G317" s="11"/>
-      <c r="H317" s="16"/>
+      <c r="H317" s="13"/>
       <c r="I317" s="11"/>
       <c r="J317" s="11"/>
       <c r="K317" s="11"/>
@@ -4891,7 +4950,7 @@
       <c r="E318" s="9"/>
       <c r="F318" s="9"/>
       <c r="G318" s="11"/>
-      <c r="H318" s="16"/>
+      <c r="H318" s="13"/>
       <c r="I318" s="11"/>
       <c r="J318" s="11"/>
       <c r="K318" s="11"/>
@@ -4904,7 +4963,7 @@
       <c r="E319" s="9"/>
       <c r="F319" s="9"/>
       <c r="G319" s="11"/>
-      <c r="H319" s="16"/>
+      <c r="H319" s="13"/>
       <c r="I319" s="11"/>
       <c r="J319" s="11"/>
       <c r="K319" s="11"/>
@@ -4917,7 +4976,7 @@
       <c r="E320" s="9"/>
       <c r="F320" s="9"/>
       <c r="G320" s="11"/>
-      <c r="H320" s="16"/>
+      <c r="H320" s="13"/>
       <c r="I320" s="11"/>
       <c r="J320" s="11"/>
       <c r="K320" s="11"/>
@@ -4930,7 +4989,7 @@
       <c r="E321" s="9"/>
       <c r="F321" s="9"/>
       <c r="G321" s="11"/>
-      <c r="H321" s="16"/>
+      <c r="H321" s="13"/>
       <c r="I321" s="11"/>
       <c r="J321" s="11"/>
       <c r="K321" s="11"/>
@@ -4943,7 +5002,7 @@
       <c r="E322" s="9"/>
       <c r="F322" s="9"/>
       <c r="G322" s="11"/>
-      <c r="H322" s="16"/>
+      <c r="H322" s="13"/>
       <c r="I322" s="11"/>
       <c r="J322" s="11"/>
       <c r="K322" s="11"/>
@@ -4956,7 +5015,7 @@
       <c r="E323" s="9"/>
       <c r="F323" s="9"/>
       <c r="G323" s="11"/>
-      <c r="H323" s="16"/>
+      <c r="H323" s="13"/>
       <c r="I323" s="11"/>
       <c r="J323" s="11"/>
       <c r="K323" s="11"/>
@@ -4969,7 +5028,7 @@
       <c r="E324" s="9"/>
       <c r="F324" s="9"/>
       <c r="G324" s="11"/>
-      <c r="H324" s="16"/>
+      <c r="H324" s="13"/>
       <c r="I324" s="11"/>
       <c r="J324" s="11"/>
       <c r="K324" s="11"/>
@@ -4982,7 +5041,7 @@
       <c r="E325" s="9"/>
       <c r="F325" s="9"/>
       <c r="G325" s="11"/>
-      <c r="H325" s="16"/>
+      <c r="H325" s="13"/>
       <c r="I325" s="11"/>
       <c r="J325" s="11"/>
       <c r="K325" s="11"/>
@@ -4995,7 +5054,7 @@
       <c r="E326" s="9"/>
       <c r="F326" s="9"/>
       <c r="G326" s="11"/>
-      <c r="H326" s="16"/>
+      <c r="H326" s="13"/>
       <c r="I326" s="11"/>
       <c r="J326" s="11"/>
       <c r="K326" s="11"/>
@@ -5008,7 +5067,7 @@
       <c r="E327" s="9"/>
       <c r="F327" s="9"/>
       <c r="G327" s="11"/>
-      <c r="H327" s="16"/>
+      <c r="H327" s="13"/>
       <c r="I327" s="11"/>
       <c r="J327" s="11"/>
       <c r="K327" s="11"/>
@@ -5021,7 +5080,7 @@
       <c r="E328" s="9"/>
       <c r="F328" s="9"/>
       <c r="G328" s="11"/>
-      <c r="H328" s="16"/>
+      <c r="H328" s="13"/>
       <c r="I328" s="11"/>
       <c r="J328" s="11"/>
       <c r="K328" s="11"/>
@@ -5034,7 +5093,7 @@
       <c r="E329" s="9"/>
       <c r="F329" s="9"/>
       <c r="G329" s="11"/>
-      <c r="H329" s="16"/>
+      <c r="H329" s="13"/>
       <c r="I329" s="11"/>
       <c r="J329" s="11"/>
       <c r="K329" s="11"/>
@@ -5047,7 +5106,7 @@
       <c r="E330" s="9"/>
       <c r="F330" s="9"/>
       <c r="G330" s="11"/>
-      <c r="H330" s="16"/>
+      <c r="H330" s="13"/>
       <c r="I330" s="11"/>
       <c r="J330" s="11"/>
       <c r="K330" s="11"/>
@@ -5060,7 +5119,7 @@
       <c r="E331" s="9"/>
       <c r="F331" s="9"/>
       <c r="G331" s="11"/>
-      <c r="H331" s="16"/>
+      <c r="H331" s="13"/>
       <c r="I331" s="11"/>
       <c r="J331" s="11"/>
       <c r="K331" s="11"/>
@@ -5073,7 +5132,7 @@
       <c r="E332" s="9"/>
       <c r="F332" s="9"/>
       <c r="G332" s="11"/>
-      <c r="H332" s="16"/>
+      <c r="H332" s="13"/>
       <c r="I332" s="11"/>
       <c r="J332" s="11"/>
       <c r="K332" s="11"/>
@@ -5086,7 +5145,7 @@
       <c r="E333" s="9"/>
       <c r="F333" s="9"/>
       <c r="G333" s="11"/>
-      <c r="H333" s="16"/>
+      <c r="H333" s="13"/>
       <c r="I333" s="11"/>
       <c r="J333" s="11"/>
       <c r="K333" s="11"/>
@@ -5099,7 +5158,7 @@
       <c r="E334" s="9"/>
       <c r="F334" s="9"/>
       <c r="G334" s="11"/>
-      <c r="H334" s="16"/>
+      <c r="H334" s="13"/>
       <c r="I334" s="11"/>
       <c r="J334" s="11"/>
       <c r="K334" s="11"/>
@@ -5112,7 +5171,7 @@
       <c r="E335" s="9"/>
       <c r="F335" s="9"/>
       <c r="G335" s="11"/>
-      <c r="H335" s="16"/>
+      <c r="H335" s="13"/>
       <c r="I335" s="11"/>
       <c r="J335" s="11"/>
       <c r="K335" s="11"/>
@@ -5125,7 +5184,7 @@
       <c r="E336" s="9"/>
       <c r="F336" s="9"/>
       <c r="G336" s="11"/>
-      <c r="H336" s="16"/>
+      <c r="H336" s="13"/>
       <c r="I336" s="11"/>
       <c r="J336" s="11"/>
       <c r="K336" s="11"/>
@@ -5138,7 +5197,7 @@
       <c r="E337" s="9"/>
       <c r="F337" s="9"/>
       <c r="G337" s="11"/>
-      <c r="H337" s="16"/>
+      <c r="H337" s="13"/>
       <c r="I337" s="11"/>
       <c r="J337" s="11"/>
       <c r="K337" s="11"/>
@@ -5151,7 +5210,7 @@
       <c r="E338" s="9"/>
       <c r="F338" s="9"/>
       <c r="G338" s="11"/>
-      <c r="H338" s="16"/>
+      <c r="H338" s="13"/>
       <c r="I338" s="11"/>
       <c r="J338" s="11"/>
       <c r="K338" s="11"/>
@@ -5164,7 +5223,7 @@
       <c r="E339" s="9"/>
       <c r="F339" s="9"/>
       <c r="G339" s="11"/>
-      <c r="H339" s="16"/>
+      <c r="H339" s="13"/>
       <c r="I339" s="11"/>
       <c r="J339" s="11"/>
       <c r="K339" s="11"/>
@@ -5177,7 +5236,7 @@
       <c r="E340" s="9"/>
       <c r="F340" s="9"/>
       <c r="G340" s="11"/>
-      <c r="H340" s="16"/>
+      <c r="H340" s="13"/>
       <c r="I340" s="11"/>
       <c r="J340" s="11"/>
       <c r="K340" s="11"/>
@@ -5190,7 +5249,7 @@
       <c r="E341" s="9"/>
       <c r="F341" s="9"/>
       <c r="G341" s="11"/>
-      <c r="H341" s="16"/>
+      <c r="H341" s="13"/>
       <c r="I341" s="11"/>
       <c r="J341" s="11"/>
       <c r="K341" s="11"/>
@@ -5203,7 +5262,7 @@
       <c r="E342" s="9"/>
       <c r="F342" s="9"/>
       <c r="G342" s="11"/>
-      <c r="H342" s="16"/>
+      <c r="H342" s="13"/>
       <c r="I342" s="11"/>
       <c r="J342" s="11"/>
       <c r="K342" s="11"/>
@@ -5216,7 +5275,7 @@
       <c r="E343" s="9"/>
       <c r="F343" s="9"/>
       <c r="G343" s="11"/>
-      <c r="H343" s="16"/>
+      <c r="H343" s="13"/>
       <c r="I343" s="11"/>
       <c r="J343" s="11"/>
       <c r="K343" s="11"/>
@@ -5229,7 +5288,7 @@
       <c r="E344" s="9"/>
       <c r="F344" s="9"/>
       <c r="G344" s="11"/>
-      <c r="H344" s="16"/>
+      <c r="H344" s="13"/>
       <c r="I344" s="11"/>
       <c r="J344" s="11"/>
       <c r="K344" s="11"/>
@@ -5242,7 +5301,7 @@
       <c r="E345" s="9"/>
       <c r="F345" s="9"/>
       <c r="G345" s="11"/>
-      <c r="H345" s="16"/>
+      <c r="H345" s="13"/>
       <c r="I345" s="11"/>
       <c r="J345" s="11"/>
       <c r="K345" s="11"/>
@@ -5255,7 +5314,7 @@
       <c r="E346" s="9"/>
       <c r="F346" s="9"/>
       <c r="G346" s="11"/>
-      <c r="H346" s="16"/>
+      <c r="H346" s="13"/>
       <c r="I346" s="11"/>
       <c r="J346" s="11"/>
       <c r="K346" s="11"/>
@@ -5268,7 +5327,7 @@
       <c r="E347" s="9"/>
       <c r="F347" s="9"/>
       <c r="G347" s="11"/>
-      <c r="H347" s="16"/>
+      <c r="H347" s="13"/>
       <c r="I347" s="11"/>
       <c r="J347" s="11"/>
       <c r="K347" s="11"/>
@@ -5281,7 +5340,7 @@
       <c r="E348" s="9"/>
       <c r="F348" s="9"/>
       <c r="G348" s="11"/>
-      <c r="H348" s="16"/>
+      <c r="H348" s="13"/>
       <c r="I348" s="11"/>
       <c r="J348" s="11"/>
       <c r="K348" s="11"/>
@@ -5294,7 +5353,7 @@
       <c r="E349" s="9"/>
       <c r="F349" s="9"/>
       <c r="G349" s="11"/>
-      <c r="H349" s="16"/>
+      <c r="H349" s="13"/>
       <c r="I349" s="11"/>
       <c r="J349" s="11"/>
       <c r="K349" s="11"/>
@@ -5307,7 +5366,7 @@
       <c r="E350" s="9"/>
       <c r="F350" s="9"/>
       <c r="G350" s="11"/>
-      <c r="H350" s="16"/>
+      <c r="H350" s="13"/>
       <c r="I350" s="11"/>
       <c r="J350" s="11"/>
       <c r="K350" s="11"/>
@@ -5320,7 +5379,7 @@
       <c r="E351" s="9"/>
       <c r="F351" s="9"/>
       <c r="G351" s="11"/>
-      <c r="H351" s="16"/>
+      <c r="H351" s="13"/>
       <c r="I351" s="11"/>
       <c r="J351" s="11"/>
       <c r="K351" s="11"/>
@@ -5333,7 +5392,7 @@
       <c r="E352" s="9"/>
       <c r="F352" s="9"/>
       <c r="G352" s="11"/>
-      <c r="H352" s="16"/>
+      <c r="H352" s="13"/>
       <c r="I352" s="11"/>
       <c r="J352" s="11"/>
       <c r="K352" s="11"/>
@@ -5346,7 +5405,7 @@
       <c r="E353" s="9"/>
       <c r="F353" s="9"/>
       <c r="G353" s="11"/>
-      <c r="H353" s="16"/>
+      <c r="H353" s="13"/>
       <c r="I353" s="11"/>
       <c r="J353" s="11"/>
       <c r="K353" s="11"/>
@@ -5359,7 +5418,7 @@
       <c r="E354" s="9"/>
       <c r="F354" s="9"/>
       <c r="G354" s="11"/>
-      <c r="H354" s="16"/>
+      <c r="H354" s="13"/>
       <c r="I354" s="11"/>
       <c r="J354" s="11"/>
       <c r="K354" s="11"/>
@@ -5372,7 +5431,7 @@
       <c r="E355" s="9"/>
       <c r="F355" s="9"/>
       <c r="G355" s="11"/>
-      <c r="H355" s="16"/>
+      <c r="H355" s="13"/>
       <c r="I355" s="11"/>
       <c r="J355" s="11"/>
       <c r="K355" s="11"/>
@@ -5385,7 +5444,7 @@
       <c r="E356" s="9"/>
       <c r="F356" s="9"/>
       <c r="G356" s="11"/>
-      <c r="H356" s="16"/>
+      <c r="H356" s="13"/>
       <c r="I356" s="11"/>
       <c r="J356" s="11"/>
       <c r="K356" s="11"/>
@@ -5398,7 +5457,7 @@
       <c r="E357" s="9"/>
       <c r="F357" s="9"/>
       <c r="G357" s="11"/>
-      <c r="H357" s="16"/>
+      <c r="H357" s="13"/>
       <c r="I357" s="11"/>
       <c r="J357" s="11"/>
       <c r="K357" s="11"/>
@@ -5411,7 +5470,7 @@
       <c r="E358" s="9"/>
       <c r="F358" s="9"/>
       <c r="G358" s="11"/>
-      <c r="H358" s="16"/>
+      <c r="H358" s="13"/>
       <c r="I358" s="11"/>
       <c r="J358" s="11"/>
       <c r="K358" s="11"/>
@@ -5424,7 +5483,7 @@
       <c r="E359" s="9"/>
       <c r="F359" s="9"/>
       <c r="G359" s="11"/>
-      <c r="H359" s="16"/>
+      <c r="H359" s="13"/>
       <c r="I359" s="11"/>
       <c r="J359" s="11"/>
       <c r="K359" s="11"/>
@@ -5437,7 +5496,7 @@
       <c r="E360" s="9"/>
       <c r="F360" s="9"/>
       <c r="G360" s="11"/>
-      <c r="H360" s="16"/>
+      <c r="H360" s="13"/>
       <c r="I360" s="11"/>
       <c r="J360" s="11"/>
       <c r="K360" s="11"/>
@@ -5450,7 +5509,7 @@
       <c r="E361" s="9"/>
       <c r="F361" s="9"/>
       <c r="G361" s="11"/>
-      <c r="H361" s="16"/>
+      <c r="H361" s="13"/>
       <c r="I361" s="11"/>
       <c r="J361" s="11"/>
       <c r="K361" s="11"/>
@@ -5463,7 +5522,7 @@
       <c r="E362" s="9"/>
       <c r="F362" s="9"/>
       <c r="G362" s="11"/>
-      <c r="H362" s="16"/>
+      <c r="H362" s="13"/>
       <c r="I362" s="11"/>
       <c r="J362" s="11"/>
       <c r="K362" s="11"/>
@@ -5476,7 +5535,7 @@
       <c r="E363" s="9"/>
       <c r="F363" s="9"/>
       <c r="G363" s="11"/>
-      <c r="H363" s="16"/>
+      <c r="H363" s="13"/>
       <c r="I363" s="11"/>
       <c r="J363" s="11"/>
       <c r="K363" s="11"/>
@@ -5489,7 +5548,7 @@
       <c r="E364" s="9"/>
       <c r="F364" s="9"/>
       <c r="G364" s="11"/>
-      <c r="H364" s="16"/>
+      <c r="H364" s="13"/>
       <c r="I364" s="11"/>
       <c r="J364" s="11"/>
       <c r="K364" s="11"/>
@@ -5502,7 +5561,7 @@
       <c r="E365" s="9"/>
       <c r="F365" s="9"/>
       <c r="G365" s="11"/>
-      <c r="H365" s="16"/>
+      <c r="H365" s="13"/>
       <c r="I365" s="11"/>
       <c r="J365" s="11"/>
       <c r="K365" s="11"/>
@@ -5515,7 +5574,7 @@
       <c r="E366" s="9"/>
       <c r="F366" s="9"/>
       <c r="G366" s="11"/>
-      <c r="H366" s="16"/>
+      <c r="H366" s="13"/>
       <c r="I366" s="11"/>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
@@ -5528,7 +5587,7 @@
       <c r="E367" s="9"/>
       <c r="F367" s="9"/>
       <c r="G367" s="11"/>
-      <c r="H367" s="16"/>
+      <c r="H367" s="13"/>
       <c r="I367" s="11"/>
       <c r="J367" s="11"/>
       <c r="K367" s="11"/>
@@ -5541,7 +5600,7 @@
       <c r="E368" s="9"/>
       <c r="F368" s="9"/>
       <c r="G368" s="11"/>
-      <c r="H368" s="16"/>
+      <c r="H368" s="13"/>
       <c r="I368" s="11"/>
       <c r="J368" s="11"/>
       <c r="K368" s="11"/>
@@ -5554,7 +5613,7 @@
       <c r="E369" s="9"/>
       <c r="F369" s="9"/>
       <c r="G369" s="11"/>
-      <c r="H369" s="16"/>
+      <c r="H369" s="13"/>
       <c r="I369" s="11"/>
       <c r="J369" s="11"/>
       <c r="K369" s="11"/>
@@ -5567,7 +5626,7 @@
       <c r="E370" s="9"/>
       <c r="F370" s="9"/>
       <c r="G370" s="11"/>
-      <c r="H370" s="16"/>
+      <c r="H370" s="13"/>
       <c r="I370" s="11"/>
       <c r="J370" s="11"/>
       <c r="K370" s="11"/>
@@ -5580,7 +5639,7 @@
       <c r="E371" s="9"/>
       <c r="F371" s="9"/>
       <c r="G371" s="11"/>
-      <c r="H371" s="16"/>
+      <c r="H371" s="13"/>
       <c r="I371" s="11"/>
       <c r="J371" s="11"/>
       <c r="K371" s="11"/>
@@ -5593,7 +5652,7 @@
       <c r="E372" s="9"/>
       <c r="F372" s="9"/>
       <c r="G372" s="11"/>
-      <c r="H372" s="16"/>
+      <c r="H372" s="13"/>
       <c r="I372" s="11"/>
       <c r="J372" s="11"/>
       <c r="K372" s="11"/>
@@ -5606,7 +5665,7 @@
       <c r="E373" s="9"/>
       <c r="F373" s="9"/>
       <c r="G373" s="11"/>
-      <c r="H373" s="16"/>
+      <c r="H373" s="13"/>
       <c r="I373" s="11"/>
       <c r="J373" s="11"/>
       <c r="K373" s="11"/>
@@ -5619,7 +5678,7 @@
       <c r="E374" s="9"/>
       <c r="F374" s="9"/>
       <c r="G374" s="11"/>
-      <c r="H374" s="16"/>
+      <c r="H374" s="13"/>
       <c r="I374" s="11"/>
       <c r="J374" s="11"/>
       <c r="K374" s="11"/>
@@ -5632,7 +5691,7 @@
       <c r="E375" s="9"/>
       <c r="F375" s="9"/>
       <c r="G375" s="11"/>
-      <c r="H375" s="16"/>
+      <c r="H375" s="13"/>
       <c r="I375" s="11"/>
       <c r="J375" s="11"/>
       <c r="K375" s="11"/>
@@ -5645,7 +5704,7 @@
       <c r="E376" s="9"/>
       <c r="F376" s="9"/>
       <c r="G376" s="11"/>
-      <c r="H376" s="16"/>
+      <c r="H376" s="13"/>
       <c r="I376" s="11"/>
       <c r="J376" s="11"/>
       <c r="K376" s="11"/>
@@ -5658,7 +5717,7 @@
       <c r="E377" s="9"/>
       <c r="F377" s="9"/>
       <c r="G377" s="11"/>
-      <c r="H377" s="16"/>
+      <c r="H377" s="13"/>
       <c r="I377" s="11"/>
       <c r="J377" s="11"/>
       <c r="K377" s="11"/>
@@ -5671,7 +5730,7 @@
       <c r="E378" s="9"/>
       <c r="F378" s="9"/>
       <c r="G378" s="11"/>
-      <c r="H378" s="16"/>
+      <c r="H378" s="13"/>
       <c r="I378" s="11"/>
       <c r="J378" s="11"/>
       <c r="K378" s="11"/>
@@ -5684,7 +5743,7 @@
       <c r="E379" s="9"/>
       <c r="F379" s="9"/>
       <c r="G379" s="11"/>
-      <c r="H379" s="16"/>
+      <c r="H379" s="13"/>
       <c r="I379" s="11"/>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
@@ -5697,7 +5756,7 @@
       <c r="E380" s="9"/>
       <c r="F380" s="9"/>
       <c r="G380" s="11"/>
-      <c r="H380" s="16"/>
+      <c r="H380" s="13"/>
       <c r="I380" s="11"/>
       <c r="J380" s="11"/>
       <c r="K380" s="11"/>
@@ -5710,7 +5769,7 @@
       <c r="E381" s="9"/>
       <c r="F381" s="9"/>
       <c r="G381" s="11"/>
-      <c r="H381" s="16"/>
+      <c r="H381" s="13"/>
       <c r="I381" s="11"/>
       <c r="J381" s="11"/>
       <c r="K381" s="11"/>
@@ -5723,7 +5782,7 @@
       <c r="E382" s="9"/>
       <c r="F382" s="9"/>
       <c r="G382" s="11"/>
-      <c r="H382" s="16"/>
+      <c r="H382" s="13"/>
       <c r="I382" s="11"/>
       <c r="J382" s="11"/>
       <c r="K382" s="11"/>
@@ -5736,7 +5795,7 @@
       <c r="E383" s="9"/>
       <c r="F383" s="9"/>
       <c r="G383" s="11"/>
-      <c r="H383" s="16"/>
+      <c r="H383" s="13"/>
       <c r="I383" s="11"/>
       <c r="J383" s="11"/>
       <c r="K383" s="11"/>
@@ -5749,7 +5808,7 @@
       <c r="E384" s="9"/>
       <c r="F384" s="9"/>
       <c r="G384" s="11"/>
-      <c r="H384" s="16"/>
+      <c r="H384" s="13"/>
       <c r="I384" s="11"/>
       <c r="J384" s="11"/>
       <c r="K384" s="11"/>
@@ -5762,7 +5821,7 @@
       <c r="E385" s="9"/>
       <c r="F385" s="9"/>
       <c r="G385" s="11"/>
-      <c r="H385" s="16"/>
+      <c r="H385" s="13"/>
       <c r="I385" s="11"/>
       <c r="J385" s="11"/>
       <c r="K385" s="11"/>
@@ -5775,7 +5834,7 @@
       <c r="E386" s="9"/>
       <c r="F386" s="9"/>
       <c r="G386" s="11"/>
-      <c r="H386" s="16"/>
+      <c r="H386" s="13"/>
       <c r="I386" s="11"/>
       <c r="J386" s="11"/>
       <c r="K386" s="11"/>
@@ -5788,7 +5847,7 @@
       <c r="E387" s="9"/>
       <c r="F387" s="9"/>
       <c r="G387" s="11"/>
-      <c r="H387" s="16"/>
+      <c r="H387" s="13"/>
       <c r="I387" s="11"/>
       <c r="J387" s="11"/>
       <c r="K387" s="11"/>
@@ -5801,7 +5860,7 @@
       <c r="E388" s="9"/>
       <c r="F388" s="9"/>
       <c r="G388" s="11"/>
-      <c r="H388" s="16"/>
+      <c r="H388" s="13"/>
       <c r="I388" s="11"/>
       <c r="J388" s="11"/>
       <c r="K388" s="11"/>
@@ -5814,7 +5873,7 @@
       <c r="E389" s="9"/>
       <c r="F389" s="9"/>
       <c r="G389" s="11"/>
-      <c r="H389" s="16"/>
+      <c r="H389" s="13"/>
       <c r="I389" s="11"/>
       <c r="J389" s="11"/>
       <c r="K389" s="11"/>
@@ -5827,7 +5886,7 @@
       <c r="E390" s="9"/>
       <c r="F390" s="9"/>
       <c r="G390" s="11"/>
-      <c r="H390" s="16"/>
+      <c r="H390" s="13"/>
       <c r="I390" s="11"/>
       <c r="J390" s="11"/>
       <c r="K390" s="11"/>
@@ -5840,7 +5899,7 @@
       <c r="E391" s="9"/>
       <c r="F391" s="9"/>
       <c r="G391" s="11"/>
-      <c r="H391" s="16"/>
+      <c r="H391" s="13"/>
       <c r="I391" s="11"/>
       <c r="J391" s="11"/>
       <c r="K391" s="11"/>
@@ -5853,7 +5912,7 @@
       <c r="E392" s="9"/>
       <c r="F392" s="9"/>
       <c r="G392" s="11"/>
-      <c r="H392" s="16"/>
+      <c r="H392" s="13"/>
       <c r="I392" s="11"/>
       <c r="J392" s="11"/>
       <c r="K392" s="11"/>
@@ -5866,7 +5925,7 @@
       <c r="E393" s="9"/>
       <c r="F393" s="9"/>
       <c r="G393" s="11"/>
-      <c r="H393" s="16"/>
+      <c r="H393" s="13"/>
       <c r="I393" s="11"/>
       <c r="J393" s="11"/>
       <c r="K393" s="11"/>
@@ -5879,7 +5938,7 @@
       <c r="E394" s="9"/>
       <c r="F394" s="9"/>
       <c r="G394" s="11"/>
-      <c r="H394" s="16"/>
+      <c r="H394" s="13"/>
       <c r="I394" s="11"/>
       <c r="J394" s="11"/>
       <c r="K394" s="11"/>
@@ -5892,7 +5951,7 @@
       <c r="E395" s="9"/>
       <c r="F395" s="9"/>
       <c r="G395" s="11"/>
-      <c r="H395" s="16"/>
+      <c r="H395" s="13"/>
       <c r="I395" s="11"/>
       <c r="J395" s="11"/>
       <c r="K395" s="11"/>
@@ -5905,7 +5964,7 @@
       <c r="E396" s="9"/>
       <c r="F396" s="9"/>
       <c r="G396" s="11"/>
-      <c r="H396" s="16"/>
+      <c r="H396" s="13"/>
       <c r="I396" s="11"/>
       <c r="J396" s="11"/>
       <c r="K396" s="11"/>
@@ -5918,7 +5977,7 @@
       <c r="E397" s="9"/>
       <c r="F397" s="9"/>
       <c r="G397" s="11"/>
-      <c r="H397" s="16"/>
+      <c r="H397" s="13"/>
       <c r="I397" s="11"/>
       <c r="J397" s="11"/>
       <c r="K397" s="11"/>
@@ -5931,7 +5990,7 @@
       <c r="E398" s="9"/>
       <c r="F398" s="9"/>
       <c r="G398" s="11"/>
-      <c r="H398" s="16"/>
+      <c r="H398" s="13"/>
       <c r="I398" s="11"/>
       <c r="J398" s="11"/>
       <c r="K398" s="11"/>
@@ -5944,7 +6003,7 @@
       <c r="E399" s="9"/>
       <c r="F399" s="9"/>
       <c r="G399" s="11"/>
-      <c r="H399" s="16"/>
+      <c r="H399" s="13"/>
       <c r="I399" s="11"/>
       <c r="J399" s="11"/>
       <c r="K399" s="11"/>
@@ -5957,7 +6016,7 @@
       <c r="E400" s="9"/>
       <c r="F400" s="9"/>
       <c r="G400" s="11"/>
-      <c r="H400" s="16"/>
+      <c r="H400" s="13"/>
       <c r="I400" s="11"/>
       <c r="J400" s="11"/>
       <c r="K400" s="11"/>
@@ -5970,7 +6029,7 @@
       <c r="E401" s="9"/>
       <c r="F401" s="9"/>
       <c r="G401" s="11"/>
-      <c r="H401" s="16"/>
+      <c r="H401" s="13"/>
       <c r="I401" s="11"/>
       <c r="J401" s="11"/>
       <c r="K401" s="11"/>
@@ -5983,7 +6042,7 @@
       <c r="E402" s="9"/>
       <c r="F402" s="9"/>
       <c r="G402" s="11"/>
-      <c r="H402" s="16"/>
+      <c r="H402" s="13"/>
       <c r="I402" s="11"/>
       <c r="J402" s="11"/>
       <c r="K402" s="11"/>
@@ -5996,7 +6055,7 @@
       <c r="E403" s="9"/>
       <c r="F403" s="9"/>
       <c r="G403" s="11"/>
-      <c r="H403" s="16"/>
+      <c r="H403" s="13"/>
       <c r="I403" s="11"/>
       <c r="J403" s="11"/>
       <c r="K403" s="11"/>
@@ -6009,7 +6068,7 @@
       <c r="E404" s="9"/>
       <c r="F404" s="9"/>
       <c r="G404" s="11"/>
-      <c r="H404" s="16"/>
+      <c r="H404" s="13"/>
       <c r="I404" s="11"/>
       <c r="J404" s="11"/>
       <c r="K404" s="11"/>
@@ -6022,7 +6081,7 @@
       <c r="E405" s="9"/>
       <c r="F405" s="9"/>
       <c r="G405" s="11"/>
-      <c r="H405" s="16"/>
+      <c r="H405" s="13"/>
       <c r="I405" s="11"/>
       <c r="J405" s="11"/>
       <c r="K405" s="11"/>
@@ -6035,7 +6094,7 @@
       <c r="E406" s="9"/>
       <c r="F406" s="9"/>
       <c r="G406" s="11"/>
-      <c r="H406" s="16"/>
+      <c r="H406" s="13"/>
       <c r="I406" s="11"/>
       <c r="J406" s="11"/>
       <c r="K406" s="11"/>
@@ -6048,7 +6107,7 @@
       <c r="E407" s="9"/>
       <c r="F407" s="9"/>
       <c r="G407" s="11"/>
-      <c r="H407" s="16"/>
+      <c r="H407" s="13"/>
       <c r="I407" s="11"/>
       <c r="J407" s="11"/>
       <c r="K407" s="11"/>
@@ -6061,7 +6120,7 @@
       <c r="E408" s="9"/>
       <c r="F408" s="9"/>
       <c r="G408" s="11"/>
-      <c r="H408" s="16"/>
+      <c r="H408" s="13"/>
       <c r="I408" s="11"/>
       <c r="J408" s="11"/>
       <c r="K408" s="11"/>
@@ -6074,7 +6133,7 @@
       <c r="E409" s="9"/>
       <c r="F409" s="9"/>
       <c r="G409" s="11"/>
-      <c r="H409" s="16"/>
+      <c r="H409" s="13"/>
       <c r="I409" s="11"/>
       <c r="J409" s="11"/>
       <c r="K409" s="11"/>
@@ -6087,7 +6146,7 @@
       <c r="E410" s="9"/>
       <c r="F410" s="9"/>
       <c r="G410" s="11"/>
-      <c r="H410" s="16"/>
+      <c r="H410" s="13"/>
       <c r="I410" s="11"/>
       <c r="J410" s="11"/>
       <c r="K410" s="11"/>
@@ -6100,7 +6159,7 @@
       <c r="E411" s="9"/>
       <c r="F411" s="9"/>
       <c r="G411" s="11"/>
-      <c r="H411" s="16"/>
+      <c r="H411" s="13"/>
       <c r="I411" s="11"/>
       <c r="J411" s="11"/>
       <c r="K411" s="11"/>
@@ -6113,7 +6172,7 @@
       <c r="E412" s="9"/>
       <c r="F412" s="9"/>
       <c r="G412" s="11"/>
-      <c r="H412" s="16"/>
+      <c r="H412" s="13"/>
       <c r="I412" s="11"/>
       <c r="J412" s="11"/>
       <c r="K412" s="11"/>
@@ -6126,7 +6185,7 @@
       <c r="E413" s="9"/>
       <c r="F413" s="9"/>
       <c r="G413" s="11"/>
-      <c r="H413" s="16"/>
+      <c r="H413" s="13"/>
       <c r="I413" s="11"/>
       <c r="J413" s="11"/>
       <c r="K413" s="11"/>
@@ -6139,7 +6198,7 @@
       <c r="E414" s="9"/>
       <c r="F414" s="9"/>
       <c r="G414" s="11"/>
-      <c r="H414" s="16"/>
+      <c r="H414" s="13"/>
       <c r="I414" s="11"/>
       <c r="J414" s="11"/>
       <c r="K414" s="11"/>
@@ -6152,7 +6211,7 @@
       <c r="E415" s="9"/>
       <c r="F415" s="9"/>
       <c r="G415" s="11"/>
-      <c r="H415" s="16"/>
+      <c r="H415" s="13"/>
       <c r="I415" s="11"/>
       <c r="J415" s="11"/>
       <c r="K415" s="11"/>
@@ -6165,7 +6224,7 @@
       <c r="E416" s="9"/>
       <c r="F416" s="9"/>
       <c r="G416" s="11"/>
-      <c r="H416" s="16"/>
+      <c r="H416" s="13"/>
       <c r="I416" s="11"/>
       <c r="J416" s="11"/>
       <c r="K416" s="11"/>
@@ -6178,7 +6237,7 @@
       <c r="E417" s="9"/>
       <c r="F417" s="9"/>
       <c r="G417" s="11"/>
-      <c r="H417" s="16"/>
+      <c r="H417" s="13"/>
       <c r="I417" s="11"/>
       <c r="J417" s="11"/>
       <c r="K417" s="11"/>
@@ -6191,7 +6250,7 @@
       <c r="E418" s="9"/>
       <c r="F418" s="9"/>
       <c r="G418" s="11"/>
-      <c r="H418" s="16"/>
+      <c r="H418" s="13"/>
       <c r="I418" s="11"/>
       <c r="J418" s="11"/>
       <c r="K418" s="11"/>
@@ -6204,7 +6263,7 @@
       <c r="E419" s="9"/>
       <c r="F419" s="9"/>
       <c r="G419" s="11"/>
-      <c r="H419" s="16"/>
+      <c r="H419" s="13"/>
       <c r="I419" s="11"/>
       <c r="J419" s="11"/>
       <c r="K419" s="11"/>
@@ -6217,7 +6276,7 @@
       <c r="E420" s="9"/>
       <c r="F420" s="9"/>
       <c r="G420" s="11"/>
-      <c r="H420" s="16"/>
+      <c r="H420" s="13"/>
       <c r="I420" s="11"/>
       <c r="J420" s="11"/>
       <c r="K420" s="11"/>
@@ -6230,7 +6289,7 @@
       <c r="E421" s="9"/>
       <c r="F421" s="9"/>
       <c r="G421" s="11"/>
-      <c r="H421" s="16"/>
+      <c r="H421" s="13"/>
       <c r="I421" s="11"/>
       <c r="J421" s="11"/>
       <c r="K421" s="11"/>
@@ -6243,7 +6302,7 @@
       <c r="E422" s="9"/>
       <c r="F422" s="9"/>
       <c r="G422" s="11"/>
-      <c r="H422" s="16"/>
+      <c r="H422" s="13"/>
       <c r="I422" s="11"/>
       <c r="J422" s="11"/>
       <c r="K422" s="11"/>
@@ -6256,7 +6315,7 @@
       <c r="E423" s="9"/>
       <c r="F423" s="9"/>
       <c r="G423" s="11"/>
-      <c r="H423" s="16"/>
+      <c r="H423" s="13"/>
       <c r="I423" s="11"/>
       <c r="J423" s="11"/>
       <c r="K423" s="11"/>
@@ -6269,7 +6328,7 @@
       <c r="E424" s="9"/>
       <c r="F424" s="9"/>
       <c r="G424" s="11"/>
-      <c r="H424" s="16"/>
+      <c r="H424" s="13"/>
       <c r="I424" s="11"/>
       <c r="J424" s="11"/>
       <c r="K424" s="11"/>
@@ -6282,7 +6341,7 @@
       <c r="E425" s="9"/>
       <c r="F425" s="9"/>
       <c r="G425" s="11"/>
-      <c r="H425" s="16"/>
+      <c r="H425" s="13"/>
       <c r="I425" s="11"/>
       <c r="J425" s="11"/>
       <c r="K425" s="11"/>
@@ -6295,7 +6354,7 @@
       <c r="E426" s="9"/>
       <c r="F426" s="9"/>
       <c r="G426" s="11"/>
-      <c r="H426" s="16"/>
+      <c r="H426" s="13"/>
       <c r="I426" s="11"/>
       <c r="J426" s="11"/>
       <c r="K426" s="11"/>
@@ -6308,7 +6367,7 @@
       <c r="E427" s="9"/>
       <c r="F427" s="9"/>
       <c r="G427" s="11"/>
-      <c r="H427" s="16"/>
+      <c r="H427" s="13"/>
       <c r="I427" s="11"/>
       <c r="J427" s="11"/>
       <c r="K427" s="11"/>
@@ -6321,7 +6380,7 @@
       <c r="E428" s="9"/>
       <c r="F428" s="9"/>
       <c r="G428" s="11"/>
-      <c r="H428" s="16"/>
+      <c r="H428" s="13"/>
       <c r="I428" s="11"/>
       <c r="J428" s="11"/>
       <c r="K428" s="11"/>
@@ -6334,7 +6393,7 @@
       <c r="E429" s="9"/>
       <c r="F429" s="9"/>
       <c r="G429" s="11"/>
-      <c r="H429" s="16"/>
+      <c r="H429" s="13"/>
       <c r="I429" s="11"/>
       <c r="J429" s="11"/>
       <c r="K429" s="11"/>
@@ -6347,7 +6406,7 @@
       <c r="E430" s="9"/>
       <c r="F430" s="9"/>
       <c r="G430" s="11"/>
-      <c r="H430" s="16"/>
+      <c r="H430" s="13"/>
       <c r="I430" s="11"/>
       <c r="J430" s="11"/>
       <c r="K430" s="11"/>
@@ -6360,7 +6419,7 @@
       <c r="E431" s="9"/>
       <c r="F431" s="9"/>
       <c r="G431" s="11"/>
-      <c r="H431" s="16"/>
+      <c r="H431" s="13"/>
       <c r="I431" s="11"/>
       <c r="J431" s="11"/>
       <c r="K431" s="11"/>
@@ -6373,7 +6432,7 @@
       <c r="E432" s="9"/>
       <c r="F432" s="9"/>
       <c r="G432" s="11"/>
-      <c r="H432" s="16"/>
+      <c r="H432" s="13"/>
       <c r="I432" s="11"/>
       <c r="J432" s="11"/>
       <c r="K432" s="11"/>
@@ -6386,7 +6445,7 @@
       <c r="E433" s="9"/>
       <c r="F433" s="9"/>
       <c r="G433" s="11"/>
-      <c r="H433" s="16"/>
+      <c r="H433" s="13"/>
       <c r="I433" s="11"/>
       <c r="J433" s="11"/>
       <c r="K433" s="11"/>
@@ -6399,7 +6458,7 @@
       <c r="E434" s="9"/>
       <c r="F434" s="9"/>
       <c r="G434" s="11"/>
-      <c r="H434" s="16"/>
+      <c r="H434" s="13"/>
       <c r="I434" s="11"/>
       <c r="J434" s="11"/>
       <c r="K434" s="11"/>
@@ -6412,7 +6471,7 @@
       <c r="E435" s="9"/>
       <c r="F435" s="9"/>
       <c r="G435" s="11"/>
-      <c r="H435" s="16"/>
+      <c r="H435" s="13"/>
       <c r="I435" s="11"/>
       <c r="J435" s="11"/>
       <c r="K435" s="11"/>
@@ -6425,7 +6484,7 @@
       <c r="E436" s="9"/>
       <c r="F436" s="9"/>
       <c r="G436" s="11"/>
-      <c r="H436" s="16"/>
+      <c r="H436" s="13"/>
       <c r="I436" s="11"/>
       <c r="J436" s="11"/>
       <c r="K436" s="11"/>
@@ -6438,7 +6497,7 @@
       <c r="E437" s="9"/>
       <c r="F437" s="9"/>
       <c r="G437" s="11"/>
-      <c r="H437" s="16"/>
+      <c r="H437" s="13"/>
       <c r="I437" s="11"/>
       <c r="J437" s="11"/>
       <c r="K437" s="11"/>
@@ -6451,7 +6510,7 @@
       <c r="E438" s="9"/>
       <c r="F438" s="9"/>
       <c r="G438" s="11"/>
-      <c r="H438" s="16"/>
+      <c r="H438" s="13"/>
       <c r="I438" s="11"/>
       <c r="J438" s="11"/>
       <c r="K438" s="11"/>
@@ -6464,7 +6523,7 @@
       <c r="E439" s="9"/>
       <c r="F439" s="9"/>
       <c r="G439" s="11"/>
-      <c r="H439" s="16"/>
+      <c r="H439" s="13"/>
       <c r="I439" s="11"/>
       <c r="J439" s="11"/>
       <c r="K439" s="11"/>
@@ -6477,7 +6536,7 @@
       <c r="E440" s="9"/>
       <c r="F440" s="9"/>
       <c r="G440" s="11"/>
-      <c r="H440" s="16"/>
+      <c r="H440" s="13"/>
       <c r="I440" s="11"/>
       <c r="J440" s="11"/>
       <c r="K440" s="11"/>
@@ -6490,7 +6549,7 @@
       <c r="E441" s="9"/>
       <c r="F441" s="9"/>
       <c r="G441" s="11"/>
-      <c r="H441" s="16"/>
+      <c r="H441" s="13"/>
       <c r="I441" s="11"/>
       <c r="J441" s="11"/>
       <c r="K441" s="11"/>
@@ -6503,7 +6562,7 @@
       <c r="E442" s="9"/>
       <c r="F442" s="9"/>
       <c r="G442" s="11"/>
-      <c r="H442" s="16"/>
+      <c r="H442" s="13"/>
       <c r="I442" s="11"/>
       <c r="J442" s="11"/>
       <c r="K442" s="11"/>
@@ -6516,7 +6575,7 @@
       <c r="E443" s="9"/>
       <c r="F443" s="9"/>
       <c r="G443" s="11"/>
-      <c r="H443" s="16"/>
+      <c r="H443" s="13"/>
       <c r="I443" s="11"/>
       <c r="J443" s="11"/>
       <c r="K443" s="11"/>
@@ -6529,7 +6588,7 @@
       <c r="E444" s="9"/>
       <c r="F444" s="9"/>
       <c r="G444" s="11"/>
-      <c r="H444" s="16"/>
+      <c r="H444" s="13"/>
       <c r="I444" s="11"/>
       <c r="J444" s="11"/>
       <c r="K444" s="11"/>
@@ -6542,7 +6601,7 @@
       <c r="E445" s="9"/>
       <c r="F445" s="9"/>
       <c r="G445" s="11"/>
-      <c r="H445" s="16"/>
+      <c r="H445" s="13"/>
       <c r="I445" s="11"/>
       <c r="J445" s="11"/>
       <c r="K445" s="11"/>
@@ -6555,7 +6614,7 @@
       <c r="E446" s="9"/>
       <c r="F446" s="9"/>
       <c r="G446" s="11"/>
-      <c r="H446" s="16"/>
+      <c r="H446" s="13"/>
       <c r="I446" s="11"/>
       <c r="J446" s="11"/>
       <c r="K446" s="11"/>
@@ -6568,7 +6627,7 @@
       <c r="E447" s="9"/>
       <c r="F447" s="9"/>
       <c r="G447" s="11"/>
-      <c r="H447" s="16"/>
+      <c r="H447" s="13"/>
       <c r="I447" s="11"/>
       <c r="J447" s="11"/>
       <c r="K447" s="11"/>
@@ -6581,7 +6640,7 @@
       <c r="E448" s="9"/>
       <c r="F448" s="9"/>
       <c r="G448" s="11"/>
-      <c r="H448" s="16"/>
+      <c r="H448" s="13"/>
       <c r="I448" s="11"/>
       <c r="J448" s="11"/>
       <c r="K448" s="11"/>
@@ -6594,7 +6653,7 @@
       <c r="E449" s="9"/>
       <c r="F449" s="9"/>
       <c r="G449" s="11"/>
-      <c r="H449" s="16"/>
+      <c r="H449" s="13"/>
       <c r="I449" s="11"/>
       <c r="J449" s="11"/>
       <c r="K449" s="11"/>
@@ -6607,7 +6666,7 @@
       <c r="E450" s="9"/>
       <c r="F450" s="9"/>
       <c r="G450" s="11"/>
-      <c r="H450" s="16"/>
+      <c r="H450" s="13"/>
       <c r="I450" s="11"/>
       <c r="J450" s="11"/>
       <c r="K450" s="11"/>
@@ -6620,7 +6679,7 @@
       <c r="E451" s="9"/>
       <c r="F451" s="9"/>
       <c r="G451" s="11"/>
-      <c r="H451" s="16"/>
+      <c r="H451" s="13"/>
       <c r="I451" s="11"/>
       <c r="J451" s="11"/>
       <c r="K451" s="11"/>
@@ -6633,7 +6692,7 @@
       <c r="E452" s="9"/>
       <c r="F452" s="9"/>
       <c r="G452" s="11"/>
-      <c r="H452" s="16"/>
+      <c r="H452" s="13"/>
       <c r="I452" s="11"/>
       <c r="J452" s="11"/>
       <c r="K452" s="11"/>
@@ -6646,7 +6705,7 @@
       <c r="E453" s="9"/>
       <c r="F453" s="9"/>
       <c r="G453" s="11"/>
-      <c r="H453" s="16"/>
+      <c r="H453" s="13"/>
       <c r="I453" s="11"/>
       <c r="J453" s="11"/>
       <c r="K453" s="11"/>
@@ -6659,7 +6718,7 @@
       <c r="E454" s="9"/>
       <c r="F454" s="9"/>
       <c r="G454" s="11"/>
-      <c r="H454" s="16"/>
+      <c r="H454" s="13"/>
       <c r="I454" s="11"/>
       <c r="J454" s="11"/>
       <c r="K454" s="11"/>
@@ -6672,7 +6731,7 @@
       <c r="E455" s="9"/>
       <c r="F455" s="9"/>
       <c r="G455" s="11"/>
-      <c r="H455" s="16"/>
+      <c r="H455" s="13"/>
       <c r="I455" s="11"/>
       <c r="J455" s="11"/>
       <c r="K455" s="11"/>
@@ -6685,7 +6744,7 @@
       <c r="E456" s="9"/>
       <c r="F456" s="9"/>
       <c r="G456" s="11"/>
-      <c r="H456" s="16"/>
+      <c r="H456" s="13"/>
       <c r="I456" s="11"/>
       <c r="J456" s="11"/>
       <c r="K456" s="11"/>
@@ -6698,7 +6757,7 @@
       <c r="E457" s="9"/>
       <c r="F457" s="9"/>
       <c r="G457" s="11"/>
-      <c r="H457" s="16"/>
+      <c r="H457" s="13"/>
       <c r="I457" s="11"/>
       <c r="J457" s="11"/>
       <c r="K457" s="11"/>
@@ -6711,7 +6770,7 @@
       <c r="E458" s="9"/>
       <c r="F458" s="9"/>
       <c r="G458" s="11"/>
-      <c r="H458" s="16"/>
+      <c r="H458" s="13"/>
       <c r="I458" s="11"/>
       <c r="J458" s="11"/>
       <c r="K458" s="11"/>
@@ -6724,7 +6783,7 @@
       <c r="E459" s="9"/>
       <c r="F459" s="9"/>
       <c r="G459" s="11"/>
-      <c r="H459" s="16"/>
+      <c r="H459" s="13"/>
       <c r="I459" s="11"/>
       <c r="J459" s="11"/>
       <c r="K459" s="11"/>
@@ -6737,7 +6796,7 @@
       <c r="E460" s="9"/>
       <c r="F460" s="9"/>
       <c r="G460" s="11"/>
-      <c r="H460" s="16"/>
+      <c r="H460" s="13"/>
       <c r="I460" s="11"/>
       <c r="J460" s="11"/>
       <c r="K460" s="11"/>
@@ -6750,7 +6809,7 @@
       <c r="E461" s="9"/>
       <c r="F461" s="9"/>
       <c r="G461" s="11"/>
-      <c r="H461" s="16"/>
+      <c r="H461" s="13"/>
       <c r="I461" s="11"/>
       <c r="J461" s="11"/>
       <c r="K461" s="11"/>
@@ -6763,7 +6822,7 @@
       <c r="E462" s="9"/>
       <c r="F462" s="9"/>
       <c r="G462" s="11"/>
-      <c r="H462" s="16"/>
+      <c r="H462" s="13"/>
       <c r="I462" s="11"/>
       <c r="J462" s="11"/>
       <c r="K462" s="11"/>
@@ -6776,7 +6835,7 @@
       <c r="E463" s="9"/>
       <c r="F463" s="9"/>
       <c r="G463" s="11"/>
-      <c r="H463" s="16"/>
+      <c r="H463" s="13"/>
       <c r="I463" s="11"/>
       <c r="J463" s="11"/>
       <c r="K463" s="11"/>
@@ -6789,7 +6848,7 @@
       <c r="E464" s="9"/>
       <c r="F464" s="9"/>
       <c r="G464" s="11"/>
-      <c r="H464" s="16"/>
+      <c r="H464" s="13"/>
       <c r="I464" s="11"/>
       <c r="J464" s="11"/>
       <c r="K464" s="11"/>
@@ -6802,7 +6861,7 @@
       <c r="E465" s="9"/>
       <c r="F465" s="9"/>
       <c r="G465" s="11"/>
-      <c r="H465" s="16"/>
+      <c r="H465" s="13"/>
       <c r="I465" s="11"/>
       <c r="J465" s="11"/>
       <c r="K465" s="11"/>
@@ -6815,7 +6874,7 @@
       <c r="E466" s="9"/>
       <c r="F466" s="9"/>
       <c r="G466" s="11"/>
-      <c r="H466" s="16"/>
+      <c r="H466" s="13"/>
       <c r="I466" s="11"/>
       <c r="J466" s="11"/>
       <c r="K466" s="11"/>
@@ -6828,7 +6887,7 @@
       <c r="E467" s="9"/>
       <c r="F467" s="9"/>
       <c r="G467" s="11"/>
-      <c r="H467" s="16"/>
+      <c r="H467" s="13"/>
       <c r="I467" s="11"/>
       <c r="J467" s="11"/>
       <c r="K467" s="11"/>
@@ -6841,7 +6900,7 @@
       <c r="E468" s="9"/>
       <c r="F468" s="9"/>
       <c r="G468" s="11"/>
-      <c r="H468" s="16"/>
+      <c r="H468" s="13"/>
       <c r="I468" s="11"/>
       <c r="J468" s="11"/>
       <c r="K468" s="11"/>
@@ -6854,7 +6913,7 @@
       <c r="E469" s="9"/>
       <c r="F469" s="9"/>
       <c r="G469" s="11"/>
-      <c r="H469" s="16"/>
+      <c r="H469" s="13"/>
       <c r="I469" s="11"/>
       <c r="J469" s="11"/>
       <c r="K469" s="11"/>
@@ -6867,7 +6926,7 @@
       <c r="E470" s="9"/>
       <c r="F470" s="9"/>
       <c r="G470" s="11"/>
-      <c r="H470" s="16"/>
+      <c r="H470" s="13"/>
       <c r="I470" s="11"/>
       <c r="J470" s="11"/>
       <c r="K470" s="11"/>
@@ -6880,7 +6939,7 @@
       <c r="E471" s="9"/>
       <c r="F471" s="9"/>
       <c r="G471" s="11"/>
-      <c r="H471" s="16"/>
+      <c r="H471" s="13"/>
       <c r="I471" s="11"/>
       <c r="J471" s="11"/>
       <c r="K471" s="11"/>
@@ -6893,7 +6952,7 @@
       <c r="E472" s="9"/>
       <c r="F472" s="9"/>
       <c r="G472" s="11"/>
-      <c r="H472" s="16"/>
+      <c r="H472" s="13"/>
       <c r="I472" s="11"/>
       <c r="J472" s="11"/>
       <c r="K472" s="11"/>
@@ -6906,7 +6965,7 @@
       <c r="E473" s="9"/>
       <c r="F473" s="9"/>
       <c r="G473" s="11"/>
-      <c r="H473" s="16"/>
+      <c r="H473" s="13"/>
       <c r="I473" s="11"/>
       <c r="J473" s="11"/>
       <c r="K473" s="11"/>
@@ -6919,7 +6978,7 @@
       <c r="E474" s="9"/>
       <c r="F474" s="9"/>
       <c r="G474" s="11"/>
-      <c r="H474" s="16"/>
+      <c r="H474" s="13"/>
       <c r="I474" s="11"/>
       <c r="J474" s="11"/>
       <c r="K474" s="11"/>
@@ -6932,7 +6991,7 @@
       <c r="E475" s="9"/>
       <c r="F475" s="9"/>
       <c r="G475" s="11"/>
-      <c r="H475" s="16"/>
+      <c r="H475" s="13"/>
       <c r="I475" s="11"/>
       <c r="J475" s="11"/>
       <c r="K475" s="11"/>
@@ -6945,7 +7004,7 @@
       <c r="E476" s="9"/>
       <c r="F476" s="9"/>
       <c r="G476" s="11"/>
-      <c r="H476" s="16"/>
+      <c r="H476" s="13"/>
       <c r="I476" s="11"/>
       <c r="J476" s="11"/>
       <c r="K476" s="11"/>
@@ -6958,7 +7017,7 @@
       <c r="E477" s="9"/>
       <c r="F477" s="9"/>
       <c r="G477" s="11"/>
-      <c r="H477" s="16"/>
+      <c r="H477" s="13"/>
       <c r="I477" s="11"/>
       <c r="J477" s="11"/>
       <c r="K477" s="11"/>
@@ -6971,7 +7030,7 @@
       <c r="E478" s="9"/>
       <c r="F478" s="9"/>
       <c r="G478" s="11"/>
-      <c r="H478" s="16"/>
+      <c r="H478" s="13"/>
       <c r="I478" s="11"/>
       <c r="J478" s="11"/>
       <c r="K478" s="11"/>
@@ -6984,7 +7043,7 @@
       <c r="E479" s="9"/>
       <c r="F479" s="9"/>
       <c r="G479" s="11"/>
-      <c r="H479" s="16"/>
+      <c r="H479" s="13"/>
       <c r="I479" s="11"/>
       <c r="J479" s="11"/>
       <c r="K479" s="11"/>
@@ -6997,7 +7056,7 @@
       <c r="E480" s="9"/>
       <c r="F480" s="9"/>
       <c r="G480" s="11"/>
-      <c r="H480" s="16"/>
+      <c r="H480" s="13"/>
       <c r="I480" s="11"/>
       <c r="J480" s="11"/>
       <c r="K480" s="11"/>
@@ -7010,7 +7069,7 @@
       <c r="E481" s="9"/>
       <c r="F481" s="9"/>
       <c r="G481" s="11"/>
-      <c r="H481" s="16"/>
+      <c r="H481" s="13"/>
       <c r="I481" s="11"/>
       <c r="J481" s="11"/>
       <c r="K481" s="11"/>
@@ -7023,7 +7082,7 @@
       <c r="E482" s="9"/>
       <c r="F482" s="9"/>
       <c r="G482" s="11"/>
-      <c r="H482" s="16"/>
+      <c r="H482" s="13"/>
       <c r="I482" s="11"/>
       <c r="J482" s="11"/>
       <c r="K482" s="11"/>
@@ -7036,7 +7095,7 @@
       <c r="E483" s="9"/>
       <c r="F483" s="9"/>
       <c r="G483" s="11"/>
-      <c r="H483" s="16"/>
+      <c r="H483" s="13"/>
       <c r="I483" s="11"/>
       <c r="J483" s="11"/>
       <c r="K483" s="11"/>
@@ -7049,7 +7108,7 @@
       <c r="E484" s="9"/>
       <c r="F484" s="9"/>
       <c r="G484" s="11"/>
-      <c r="H484" s="16"/>
+      <c r="H484" s="13"/>
       <c r="I484" s="11"/>
       <c r="J484" s="11"/>
       <c r="K484" s="11"/>
@@ -7062,7 +7121,7 @@
       <c r="E485" s="9"/>
       <c r="F485" s="9"/>
       <c r="G485" s="11"/>
-      <c r="H485" s="16"/>
+      <c r="H485" s="13"/>
       <c r="I485" s="11"/>
       <c r="J485" s="11"/>
       <c r="K485" s="11"/>
@@ -7075,7 +7134,7 @@
       <c r="E486" s="9"/>
       <c r="F486" s="9"/>
       <c r="G486" s="11"/>
-      <c r="H486" s="16"/>
+      <c r="H486" s="13"/>
       <c r="I486" s="11"/>
       <c r="J486" s="11"/>
       <c r="K486" s="11"/>
@@ -7088,7 +7147,7 @@
       <c r="E487" s="9"/>
       <c r="F487" s="9"/>
       <c r="G487" s="11"/>
-      <c r="H487" s="16"/>
+      <c r="H487" s="13"/>
       <c r="I487" s="11"/>
       <c r="J487" s="11"/>
       <c r="K487" s="11"/>
@@ -7101,7 +7160,7 @@
       <c r="E488" s="9"/>
       <c r="F488" s="9"/>
       <c r="G488" s="11"/>
-      <c r="H488" s="16"/>
+      <c r="H488" s="13"/>
       <c r="I488" s="11"/>
       <c r="J488" s="11"/>
       <c r="K488" s="11"/>
@@ -7114,7 +7173,7 @@
       <c r="E489" s="9"/>
       <c r="F489" s="9"/>
       <c r="G489" s="11"/>
-      <c r="H489" s="16"/>
+      <c r="H489" s="13"/>
       <c r="I489" s="11"/>
       <c r="J489" s="11"/>
       <c r="K489" s="11"/>
@@ -7127,7 +7186,7 @@
       <c r="E490" s="9"/>
       <c r="F490" s="9"/>
       <c r="G490" s="11"/>
-      <c r="H490" s="16"/>
+      <c r="H490" s="13"/>
       <c r="I490" s="11"/>
       <c r="J490" s="11"/>
       <c r="K490" s="11"/>
@@ -7140,7 +7199,7 @@
       <c r="E491" s="9"/>
       <c r="F491" s="9"/>
       <c r="G491" s="11"/>
-      <c r="H491" s="16"/>
+      <c r="H491" s="13"/>
       <c r="I491" s="11"/>
       <c r="J491" s="11"/>
       <c r="K491" s="11"/>
@@ -7153,7 +7212,7 @@
       <c r="E492" s="9"/>
       <c r="F492" s="9"/>
       <c r="G492" s="11"/>
-      <c r="H492" s="16"/>
+      <c r="H492" s="13"/>
       <c r="I492" s="11"/>
       <c r="J492" s="11"/>
       <c r="K492" s="11"/>
@@ -7166,7 +7225,7 @@
       <c r="E493" s="9"/>
       <c r="F493" s="9"/>
       <c r="G493" s="11"/>
-      <c r="H493" s="16"/>
+      <c r="H493" s="13"/>
       <c r="I493" s="11"/>
       <c r="J493" s="11"/>
       <c r="K493" s="11"/>
@@ -7179,7 +7238,7 @@
       <c r="E494" s="9"/>
       <c r="F494" s="9"/>
       <c r="G494" s="11"/>
-      <c r="H494" s="16"/>
+      <c r="H494" s="13"/>
       <c r="I494" s="11"/>
       <c r="J494" s="11"/>
       <c r="K494" s="11"/>
@@ -7192,7 +7251,7 @@
       <c r="E495" s="9"/>
       <c r="F495" s="9"/>
       <c r="G495" s="11"/>
-      <c r="H495" s="16"/>
+      <c r="H495" s="13"/>
       <c r="I495" s="11"/>
       <c r="J495" s="11"/>
       <c r="K495" s="11"/>
@@ -7205,7 +7264,7 @@
       <c r="E496" s="9"/>
       <c r="F496" s="9"/>
       <c r="G496" s="11"/>
-      <c r="H496" s="16"/>
+      <c r="H496" s="13"/>
       <c r="I496" s="11"/>
       <c r="J496" s="11"/>
       <c r="K496" s="11"/>
@@ -7218,7 +7277,7 @@
       <c r="E497" s="9"/>
       <c r="F497" s="9"/>
       <c r="G497" s="11"/>
-      <c r="H497" s="16"/>
+      <c r="H497" s="13"/>
       <c r="I497" s="11"/>
       <c r="J497" s="11"/>
       <c r="K497" s="11"/>
@@ -7231,7 +7290,7 @@
       <c r="E498" s="9"/>
       <c r="F498" s="9"/>
       <c r="G498" s="11"/>
-      <c r="H498" s="16"/>
+      <c r="H498" s="13"/>
       <c r="I498" s="11"/>
       <c r="J498" s="11"/>
       <c r="K498" s="11"/>
@@ -7244,7 +7303,7 @@
       <c r="E499" s="9"/>
       <c r="F499" s="9"/>
       <c r="G499" s="11"/>
-      <c r="H499" s="16"/>
+      <c r="H499" s="13"/>
       <c r="I499" s="11"/>
       <c r="J499" s="11"/>
       <c r="K499" s="11"/>
@@ -7257,7 +7316,7 @@
       <c r="E500" s="9"/>
       <c r="F500" s="9"/>
       <c r="G500" s="11"/>
-      <c r="H500" s="16"/>
+      <c r="H500" s="13"/>
       <c r="I500" s="11"/>
       <c r="J500" s="11"/>
       <c r="K500" s="11"/>
@@ -7270,7 +7329,7 @@
       <c r="E501" s="9"/>
       <c r="F501" s="9"/>
       <c r="G501" s="11"/>
-      <c r="H501" s="16"/>
+      <c r="H501" s="13"/>
       <c r="I501" s="11"/>
       <c r="J501" s="11"/>
       <c r="K501" s="11"/>
@@ -7283,7 +7342,7 @@
       <c r="E502" s="9"/>
       <c r="F502" s="9"/>
       <c r="G502" s="11"/>
-      <c r="H502" s="16"/>
+      <c r="H502" s="13"/>
       <c r="I502" s="11"/>
       <c r="J502" s="11"/>
       <c r="K502" s="11"/>
@@ -7296,7 +7355,7 @@
       <c r="E503" s="9"/>
       <c r="F503" s="9"/>
       <c r="G503" s="11"/>
-      <c r="H503" s="16"/>
+      <c r="H503" s="13"/>
       <c r="I503" s="11"/>
       <c r="J503" s="11"/>
       <c r="K503" s="11"/>
@@ -7309,7 +7368,7 @@
       <c r="E504" s="9"/>
       <c r="F504" s="9"/>
       <c r="G504" s="11"/>
-      <c r="H504" s="16"/>
+      <c r="H504" s="13"/>
       <c r="I504" s="11"/>
       <c r="J504" s="11"/>
       <c r="K504" s="11"/>
@@ -7322,7 +7381,7 @@
       <c r="E505" s="9"/>
       <c r="F505" s="9"/>
       <c r="G505" s="11"/>
-      <c r="H505" s="16"/>
+      <c r="H505" s="13"/>
       <c r="I505" s="11"/>
       <c r="J505" s="11"/>
       <c r="K505" s="11"/>
@@ -7335,7 +7394,7 @@
       <c r="E506" s="9"/>
       <c r="F506" s="9"/>
       <c r="G506" s="11"/>
-      <c r="H506" s="16"/>
+      <c r="H506" s="13"/>
       <c r="I506" s="11"/>
       <c r="J506" s="11"/>
       <c r="K506" s="11"/>
@@ -7348,7 +7407,7 @@
       <c r="E507" s="9"/>
       <c r="F507" s="9"/>
       <c r="G507" s="11"/>
-      <c r="H507" s="16"/>
+      <c r="H507" s="13"/>
       <c r="I507" s="11"/>
       <c r="J507" s="11"/>
       <c r="K507" s="11"/>
@@ -7361,7 +7420,7 @@
       <c r="E508" s="9"/>
       <c r="F508" s="9"/>
       <c r="G508" s="11"/>
-      <c r="H508" s="16"/>
+      <c r="H508" s="13"/>
       <c r="I508" s="11"/>
       <c r="J508" s="11"/>
       <c r="K508" s="11"/>
@@ -7374,7 +7433,7 @@
       <c r="E509" s="9"/>
       <c r="F509" s="9"/>
       <c r="G509" s="11"/>
-      <c r="H509" s="16"/>
+      <c r="H509" s="13"/>
       <c r="I509" s="11"/>
       <c r="J509" s="11"/>
       <c r="K509" s="11"/>
@@ -7387,7 +7446,7 @@
       <c r="E510" s="9"/>
       <c r="F510" s="9"/>
       <c r="G510" s="11"/>
-      <c r="H510" s="16"/>
+      <c r="H510" s="13"/>
       <c r="I510" s="11"/>
       <c r="J510" s="11"/>
       <c r="K510" s="11"/>
@@ -7400,7 +7459,7 @@
       <c r="E511" s="9"/>
       <c r="F511" s="9"/>
       <c r="G511" s="11"/>
-      <c r="H511" s="16"/>
+      <c r="H511" s="13"/>
       <c r="I511" s="11"/>
       <c r="J511" s="11"/>
       <c r="K511" s="11"/>
@@ -7413,7 +7472,7 @@
       <c r="E512" s="9"/>
       <c r="F512" s="9"/>
       <c r="G512" s="11"/>
-      <c r="H512" s="16"/>
+      <c r="H512" s="13"/>
       <c r="I512" s="11"/>
       <c r="J512" s="11"/>
       <c r="K512" s="11"/>
@@ -7426,7 +7485,7 @@
       <c r="E513" s="9"/>
       <c r="F513" s="9"/>
       <c r="G513" s="11"/>
-      <c r="H513" s="16"/>
+      <c r="H513" s="13"/>
       <c r="I513" s="11"/>
       <c r="J513" s="11"/>
       <c r="K513" s="11"/>
@@ -7439,7 +7498,7 @@
       <c r="E514" s="9"/>
       <c r="F514" s="9"/>
       <c r="G514" s="11"/>
-      <c r="H514" s="16"/>
+      <c r="H514" s="13"/>
       <c r="I514" s="11"/>
       <c r="J514" s="11"/>
       <c r="K514" s="11"/>
@@ -7452,7 +7511,7 @@
       <c r="E515" s="9"/>
       <c r="F515" s="9"/>
       <c r="G515" s="11"/>
-      <c r="H515" s="16"/>
+      <c r="H515" s="13"/>
       <c r="I515" s="11"/>
       <c r="J515" s="11"/>
       <c r="K515" s="11"/>
@@ -7465,7 +7524,7 @@
       <c r="E516" s="9"/>
       <c r="F516" s="9"/>
       <c r="G516" s="11"/>
-      <c r="H516" s="16"/>
+      <c r="H516" s="13"/>
       <c r="I516" s="11"/>
       <c r="J516" s="11"/>
       <c r="K516" s="11"/>
@@ -7478,7 +7537,7 @@
       <c r="E517" s="9"/>
       <c r="F517" s="9"/>
       <c r="G517" s="11"/>
-      <c r="H517" s="16"/>
+      <c r="H517" s="13"/>
       <c r="I517" s="11"/>
       <c r="J517" s="11"/>
       <c r="K517" s="11"/>
@@ -7491,7 +7550,7 @@
       <c r="E518" s="9"/>
       <c r="F518" s="9"/>
       <c r="G518" s="11"/>
-      <c r="H518" s="16"/>
+      <c r="H518" s="13"/>
       <c r="I518" s="11"/>
       <c r="J518" s="11"/>
       <c r="K518" s="11"/>
@@ -7504,7 +7563,7 @@
       <c r="E519" s="9"/>
       <c r="F519" s="9"/>
       <c r="G519" s="11"/>
-      <c r="H519" s="16"/>
+      <c r="H519" s="13"/>
       <c r="I519" s="11"/>
       <c r="J519" s="11"/>
       <c r="K519" s="11"/>
@@ -7517,7 +7576,7 @@
       <c r="E520" s="9"/>
       <c r="F520" s="9"/>
       <c r="G520" s="11"/>
-      <c r="H520" s="16"/>
+      <c r="H520" s="13"/>
       <c r="I520" s="11"/>
       <c r="J520" s="11"/>
       <c r="K520" s="11"/>
@@ -7530,7 +7589,7 @@
       <c r="E521" s="9"/>
       <c r="F521" s="9"/>
       <c r="G521" s="11"/>
-      <c r="H521" s="16"/>
+      <c r="H521" s="13"/>
       <c r="I521" s="11"/>
       <c r="J521" s="11"/>
       <c r="K521" s="11"/>
@@ -7543,7 +7602,7 @@
       <c r="E522" s="9"/>
       <c r="F522" s="9"/>
       <c r="G522" s="11"/>
-      <c r="H522" s="16"/>
+      <c r="H522" s="13"/>
       <c r="I522" s="11"/>
       <c r="J522" s="11"/>
       <c r="K522" s="11"/>
@@ -7556,7 +7615,7 @@
       <c r="E523" s="9"/>
       <c r="F523" s="9"/>
       <c r="G523" s="11"/>
-      <c r="H523" s="16"/>
+      <c r="H523" s="13"/>
       <c r="I523" s="11"/>
       <c r="J523" s="11"/>
       <c r="K523" s="11"/>
@@ -7569,7 +7628,7 @@
       <c r="E524" s="9"/>
       <c r="F524" s="9"/>
       <c r="G524" s="11"/>
-      <c r="H524" s="16"/>
+      <c r="H524" s="13"/>
       <c r="I524" s="11"/>
       <c r="J524" s="11"/>
       <c r="K524" s="11"/>
@@ -7582,7 +7641,7 @@
       <c r="E525" s="9"/>
       <c r="F525" s="9"/>
       <c r="G525" s="11"/>
-      <c r="H525" s="16"/>
+      <c r="H525" s="13"/>
       <c r="I525" s="11"/>
       <c r="J525" s="11"/>
       <c r="K525" s="11"/>
@@ -7595,7 +7654,7 @@
       <c r="E526" s="9"/>
       <c r="F526" s="9"/>
       <c r="G526" s="11"/>
-      <c r="H526" s="16"/>
+      <c r="H526" s="13"/>
       <c r="I526" s="11"/>
       <c r="J526" s="11"/>
       <c r="K526" s="11"/>
@@ -7608,7 +7667,7 @@
       <c r="E527" s="9"/>
       <c r="F527" s="9"/>
       <c r="G527" s="11"/>
-      <c r="H527" s="16"/>
+      <c r="H527" s="13"/>
       <c r="I527" s="11"/>
       <c r="J527" s="11"/>
       <c r="K527" s="11"/>
@@ -7621,7 +7680,7 @@
       <c r="E528" s="9"/>
       <c r="F528" s="9"/>
       <c r="G528" s="11"/>
-      <c r="H528" s="16"/>
+      <c r="H528" s="13"/>
       <c r="I528" s="11"/>
       <c r="J528" s="11"/>
       <c r="K528" s="11"/>
@@ -7634,7 +7693,7 @@
       <c r="E529" s="9"/>
       <c r="F529" s="9"/>
       <c r="G529" s="11"/>
-      <c r="H529" s="16"/>
+      <c r="H529" s="13"/>
       <c r="I529" s="11"/>
       <c r="J529" s="11"/>
       <c r="K529" s="11"/>
@@ -7647,7 +7706,7 @@
       <c r="E530" s="9"/>
       <c r="F530" s="9"/>
       <c r="G530" s="11"/>
-      <c r="H530" s="16"/>
+      <c r="H530" s="13"/>
       <c r="I530" s="11"/>
       <c r="J530" s="11"/>
       <c r="K530" s="11"/>
@@ -7660,7 +7719,7 @@
       <c r="E531" s="9"/>
       <c r="F531" s="9"/>
       <c r="G531" s="11"/>
-      <c r="H531" s="16"/>
+      <c r="H531" s="13"/>
       <c r="I531" s="11"/>
       <c r="J531" s="11"/>
       <c r="K531" s="11"/>
@@ -7673,7 +7732,7 @@
       <c r="E532" s="9"/>
       <c r="F532" s="9"/>
       <c r="G532" s="11"/>
-      <c r="H532" s="16"/>
+      <c r="H532" s="13"/>
       <c r="I532" s="11"/>
       <c r="J532" s="11"/>
       <c r="K532" s="11"/>
@@ -7686,7 +7745,7 @@
       <c r="E533" s="9"/>
       <c r="F533" s="9"/>
       <c r="G533" s="11"/>
-      <c r="H533" s="16"/>
+      <c r="H533" s="13"/>
       <c r="I533" s="11"/>
       <c r="J533" s="11"/>
       <c r="K533" s="11"/>
@@ -7699,7 +7758,7 @@
       <c r="E534" s="9"/>
       <c r="F534" s="9"/>
       <c r="G534" s="11"/>
-      <c r="H534" s="16"/>
+      <c r="H534" s="13"/>
       <c r="I534" s="11"/>
       <c r="J534" s="11"/>
       <c r="K534" s="11"/>
@@ -7712,7 +7771,7 @@
       <c r="E535" s="9"/>
       <c r="F535" s="9"/>
       <c r="G535" s="11"/>
-      <c r="H535" s="16"/>
+      <c r="H535" s="13"/>
       <c r="I535" s="11"/>
       <c r="J535" s="11"/>
       <c r="K535" s="11"/>
@@ -7725,7 +7784,7 @@
       <c r="E536" s="9"/>
       <c r="F536" s="9"/>
       <c r="G536" s="11"/>
-      <c r="H536" s="16"/>
+      <c r="H536" s="13"/>
       <c r="I536" s="11"/>
       <c r="J536" s="11"/>
       <c r="K536" s="11"/>
@@ -7738,7 +7797,7 @@
       <c r="E537" s="9"/>
       <c r="F537" s="9"/>
       <c r="G537" s="11"/>
-      <c r="H537" s="16"/>
+      <c r="H537" s="13"/>
       <c r="I537" s="11"/>
       <c r="J537" s="11"/>
       <c r="K537" s="11"/>
@@ -7751,7 +7810,7 @@
       <c r="E538" s="9"/>
       <c r="F538" s="9"/>
       <c r="G538" s="11"/>
-      <c r="H538" s="16"/>
+      <c r="H538" s="13"/>
       <c r="I538" s="11"/>
       <c r="J538" s="11"/>
       <c r="K538" s="11"/>
@@ -7764,7 +7823,7 @@
       <c r="E539" s="9"/>
       <c r="F539" s="9"/>
       <c r="G539" s="11"/>
-      <c r="H539" s="16"/>
+      <c r="H539" s="13"/>
       <c r="I539" s="11"/>
       <c r="J539" s="11"/>
       <c r="K539" s="11"/>
@@ -7777,7 +7836,7 @@
       <c r="E540" s="9"/>
       <c r="F540" s="9"/>
       <c r="G540" s="11"/>
-      <c r="H540" s="16"/>
+      <c r="H540" s="13"/>
       <c r="I540" s="11"/>
       <c r="J540" s="11"/>
       <c r="K540" s="11"/>
@@ -7790,7 +7849,7 @@
       <c r="E541" s="9"/>
       <c r="F541" s="9"/>
       <c r="G541" s="11"/>
-      <c r="H541" s="16"/>
+      <c r="H541" s="13"/>
       <c r="I541" s="11"/>
       <c r="J541" s="11"/>
       <c r="K541" s="11"/>
@@ -7803,7 +7862,7 @@
       <c r="E542" s="9"/>
       <c r="F542" s="9"/>
       <c r="G542" s="11"/>
-      <c r="H542" s="16"/>
+      <c r="H542" s="13"/>
       <c r="I542" s="11"/>
       <c r="J542" s="11"/>
       <c r="K542" s="11"/>
@@ -7816,7 +7875,7 @@
       <c r="E543" s="9"/>
       <c r="F543" s="9"/>
       <c r="G543" s="11"/>
-      <c r="H543" s="16"/>
+      <c r="H543" s="13"/>
       <c r="I543" s="11"/>
       <c r="J543" s="11"/>
       <c r="K543" s="11"/>
@@ -7829,7 +7888,7 @@
       <c r="E544" s="9"/>
       <c r="F544" s="9"/>
       <c r="G544" s="11"/>
-      <c r="H544" s="16"/>
+      <c r="H544" s="13"/>
       <c r="I544" s="11"/>
       <c r="J544" s="11"/>
       <c r="K544" s="11"/>
@@ -7842,7 +7901,7 @@
       <c r="E545" s="9"/>
       <c r="F545" s="9"/>
       <c r="G545" s="11"/>
-      <c r="H545" s="16"/>
+      <c r="H545" s="13"/>
       <c r="I545" s="11"/>
       <c r="J545" s="11"/>
       <c r="K545" s="11"/>
@@ -7855,7 +7914,7 @@
       <c r="E546" s="9"/>
       <c r="F546" s="9"/>
       <c r="G546" s="11"/>
-      <c r="H546" s="16"/>
+      <c r="H546" s="13"/>
       <c r="I546" s="11"/>
       <c r="J546" s="11"/>
       <c r="K546" s="11"/>
@@ -7868,7 +7927,7 @@
       <c r="E547" s="9"/>
       <c r="F547" s="9"/>
       <c r="G547" s="11"/>
-      <c r="H547" s="16"/>
+      <c r="H547" s="13"/>
       <c r="I547" s="11"/>
       <c r="J547" s="11"/>
       <c r="K547" s="11"/>
@@ -7881,7 +7940,7 @@
       <c r="E548" s="9"/>
       <c r="F548" s="9"/>
       <c r="G548" s="11"/>
-      <c r="H548" s="16"/>
+      <c r="H548" s="13"/>
       <c r="I548" s="11"/>
       <c r="J548" s="11"/>
       <c r="K548" s="11"/>
@@ -7894,7 +7953,7 @@
       <c r="E549" s="9"/>
       <c r="F549" s="9"/>
       <c r="G549" s="11"/>
-      <c r="H549" s="16"/>
+      <c r="H549" s="13"/>
       <c r="I549" s="11"/>
       <c r="J549" s="11"/>
       <c r="K549" s="11"/>
@@ -7907,7 +7966,7 @@
       <c r="E550" s="9"/>
       <c r="F550" s="9"/>
       <c r="G550" s="11"/>
-      <c r="H550" s="16"/>
+      <c r="H550" s="13"/>
       <c r="I550" s="11"/>
       <c r="J550" s="11"/>
       <c r="K550" s="11"/>
@@ -7920,7 +7979,7 @@
       <c r="E551" s="9"/>
       <c r="F551" s="9"/>
       <c r="G551" s="11"/>
-      <c r="H551" s="16"/>
+      <c r="H551" s="13"/>
       <c r="I551" s="11"/>
       <c r="J551" s="11"/>
       <c r="K551" s="11"/>
@@ -7933,7 +7992,7 @@
       <c r="E552" s="9"/>
       <c r="F552" s="9"/>
       <c r="G552" s="11"/>
-      <c r="H552" s="16"/>
+      <c r="H552" s="13"/>
       <c r="I552" s="11"/>
       <c r="J552" s="11"/>
       <c r="K552" s="11"/>
@@ -7946,7 +8005,7 @@
       <c r="E553" s="9"/>
       <c r="F553" s="9"/>
       <c r="G553" s="11"/>
-      <c r="H553" s="16"/>
+      <c r="H553" s="13"/>
       <c r="I553" s="11"/>
       <c r="J553" s="11"/>
       <c r="K553" s="11"/>
@@ -7959,7 +8018,7 @@
       <c r="E554" s="9"/>
       <c r="F554" s="9"/>
       <c r="G554" s="11"/>
-      <c r="H554" s="16"/>
+      <c r="H554" s="13"/>
       <c r="I554" s="11"/>
       <c r="J554" s="11"/>
       <c r="K554" s="11"/>
@@ -7972,7 +8031,7 @@
       <c r="E555" s="9"/>
       <c r="F555" s="9"/>
       <c r="G555" s="11"/>
-      <c r="H555" s="16"/>
+      <c r="H555" s="13"/>
       <c r="I555" s="11"/>
       <c r="J555" s="11"/>
       <c r="K555" s="11"/>
@@ -7985,7 +8044,7 @@
       <c r="E556" s="9"/>
       <c r="F556" s="9"/>
       <c r="G556" s="11"/>
-      <c r="H556" s="16"/>
+      <c r="H556" s="13"/>
       <c r="I556" s="11"/>
       <c r="J556" s="11"/>
       <c r="K556" s="11"/>
@@ -7998,7 +8057,7 @@
       <c r="E557" s="9"/>
       <c r="F557" s="9"/>
       <c r="G557" s="11"/>
-      <c r="H557" s="16"/>
+      <c r="H557" s="13"/>
       <c r="I557" s="11"/>
       <c r="J557" s="11"/>
       <c r="K557" s="11"/>
@@ -8011,7 +8070,7 @@
       <c r="E558" s="9"/>
       <c r="F558" s="9"/>
       <c r="G558" s="11"/>
-      <c r="H558" s="16"/>
+      <c r="H558" s="13"/>
       <c r="I558" s="11"/>
       <c r="J558" s="11"/>
       <c r="K558" s="11"/>
@@ -8024,7 +8083,7 @@
       <c r="E559" s="9"/>
       <c r="F559" s="9"/>
       <c r="G559" s="11"/>
-      <c r="H559" s="16"/>
+      <c r="H559" s="13"/>
       <c r="I559" s="11"/>
       <c r="J559" s="11"/>
       <c r="K559" s="11"/>
@@ -8037,7 +8096,7 @@
       <c r="E560" s="9"/>
       <c r="F560" s="9"/>
       <c r="G560" s="11"/>
-      <c r="H560" s="16"/>
+      <c r="H560" s="13"/>
       <c r="I560" s="11"/>
       <c r="J560" s="11"/>
       <c r="K560" s="11"/>
@@ -8050,7 +8109,7 @@
       <c r="E561" s="9"/>
       <c r="F561" s="9"/>
       <c r="G561" s="11"/>
-      <c r="H561" s="16"/>
+      <c r="H561" s="13"/>
       <c r="I561" s="11"/>
       <c r="J561" s="11"/>
       <c r="K561" s="11"/>
@@ -8063,7 +8122,7 @@
       <c r="E562" s="9"/>
       <c r="F562" s="9"/>
       <c r="G562" s="11"/>
-      <c r="H562" s="16"/>
+      <c r="H562" s="13"/>
       <c r="I562" s="11"/>
       <c r="J562" s="11"/>
       <c r="K562" s="11"/>
@@ -8076,7 +8135,7 @@
       <c r="E563" s="9"/>
       <c r="F563" s="9"/>
       <c r="G563" s="11"/>
-      <c r="H563" s="16"/>
+      <c r="H563" s="13"/>
       <c r="I563" s="11"/>
       <c r="J563" s="11"/>
       <c r="K563" s="11"/>
@@ -8089,7 +8148,7 @@
       <c r="E564" s="9"/>
       <c r="F564" s="9"/>
       <c r="G564" s="11"/>
-      <c r="H564" s="16"/>
+      <c r="H564" s="13"/>
       <c r="I564" s="11"/>
       <c r="J564" s="11"/>
       <c r="K564" s="11"/>
@@ -8102,7 +8161,7 @@
       <c r="E565" s="9"/>
       <c r="F565" s="9"/>
       <c r="G565" s="11"/>
-      <c r="H565" s="16"/>
+      <c r="H565" s="13"/>
       <c r="I565" s="11"/>
       <c r="J565" s="11"/>
       <c r="K565" s="11"/>
@@ -8115,7 +8174,7 @@
       <c r="E566" s="9"/>
       <c r="F566" s="9"/>
       <c r="G566" s="11"/>
-      <c r="H566" s="16"/>
+      <c r="H566" s="13"/>
       <c r="I566" s="11"/>
       <c r="J566" s="11"/>
       <c r="K566" s="11"/>
@@ -8128,7 +8187,7 @@
       <c r="E567" s="9"/>
       <c r="F567" s="9"/>
       <c r="G567" s="11"/>
-      <c r="H567" s="16"/>
+      <c r="H567" s="13"/>
       <c r="I567" s="11"/>
       <c r="J567" s="11"/>
       <c r="K567" s="11"/>
@@ -8141,7 +8200,7 @@
       <c r="E568" s="9"/>
       <c r="F568" s="9"/>
       <c r="G568" s="11"/>
-      <c r="H568" s="16"/>
+      <c r="H568" s="13"/>
       <c r="I568" s="11"/>
       <c r="J568" s="11"/>
       <c r="K568" s="11"/>
@@ -8154,7 +8213,7 @@
       <c r="E569" s="9"/>
       <c r="F569" s="9"/>
       <c r="G569" s="11"/>
-      <c r="H569" s="16"/>
+      <c r="H569" s="13"/>
       <c r="I569" s="11"/>
       <c r="J569" s="11"/>
       <c r="K569" s="11"/>
@@ -8167,7 +8226,7 @@
       <c r="E570" s="9"/>
       <c r="F570" s="9"/>
       <c r="G570" s="11"/>
-      <c r="H570" s="16"/>
+      <c r="H570" s="13"/>
       <c r="I570" s="11"/>
       <c r="J570" s="11"/>
       <c r="K570" s="11"/>
@@ -8180,7 +8239,7 @@
       <c r="E571" s="9"/>
       <c r="F571" s="9"/>
       <c r="G571" s="11"/>
-      <c r="H571" s="16"/>
+      <c r="H571" s="13"/>
       <c r="I571" s="11"/>
       <c r="J571" s="11"/>
       <c r="K571" s="11"/>
@@ -8193,7 +8252,7 @@
       <c r="E572" s="9"/>
       <c r="F572" s="9"/>
       <c r="G572" s="11"/>
-      <c r="H572" s="16"/>
+      <c r="H572" s="13"/>
       <c r="I572" s="11"/>
       <c r="J572" s="11"/>
       <c r="K572" s="11"/>
@@ -8206,7 +8265,7 @@
       <c r="E573" s="9"/>
       <c r="F573" s="9"/>
       <c r="G573" s="11"/>
-      <c r="H573" s="16"/>
+      <c r="H573" s="13"/>
       <c r="I573" s="11"/>
       <c r="J573" s="11"/>
       <c r="K573" s="11"/>
@@ -8219,7 +8278,7 @@
       <c r="E574" s="9"/>
       <c r="F574" s="9"/>
       <c r="G574" s="11"/>
-      <c r="H574" s="16"/>
+      <c r="H574" s="13"/>
       <c r="I574" s="11"/>
       <c r="J574" s="11"/>
       <c r="K574" s="11"/>
@@ -8232,7 +8291,7 @@
       <c r="E575" s="9"/>
       <c r="F575" s="9"/>
       <c r="G575" s="11"/>
-      <c r="H575" s="16"/>
+      <c r="H575" s="13"/>
       <c r="I575" s="11"/>
       <c r="J575" s="11"/>
       <c r="K575" s="11"/>
@@ -8245,7 +8304,7 @@
       <c r="E576" s="9"/>
       <c r="F576" s="9"/>
       <c r="G576" s="11"/>
-      <c r="H576" s="16"/>
+      <c r="H576" s="13"/>
       <c r="I576" s="11"/>
       <c r="J576" s="11"/>
       <c r="K576" s="11"/>
@@ -8258,7 +8317,7 @@
       <c r="E577" s="9"/>
       <c r="F577" s="9"/>
       <c r="G577" s="11"/>
-      <c r="H577" s="16"/>
+      <c r="H577" s="13"/>
       <c r="I577" s="11"/>
       <c r="J577" s="11"/>
       <c r="K577" s="11"/>
@@ -8271,7 +8330,7 @@
       <c r="E578" s="9"/>
       <c r="F578" s="9"/>
       <c r="G578" s="11"/>
-      <c r="H578" s="16"/>
+      <c r="H578" s="13"/>
       <c r="I578" s="11"/>
       <c r="J578" s="11"/>
       <c r="K578" s="11"/>
@@ -8284,7 +8343,7 @@
       <c r="E579" s="9"/>
       <c r="F579" s="9"/>
       <c r="G579" s="11"/>
-      <c r="H579" s="16"/>
+      <c r="H579" s="13"/>
       <c r="I579" s="11"/>
       <c r="J579" s="11"/>
       <c r="K579" s="11"/>
@@ -8297,7 +8356,7 @@
       <c r="E580" s="9"/>
       <c r="F580" s="9"/>
       <c r="G580" s="11"/>
-      <c r="H580" s="16"/>
+      <c r="H580" s="13"/>
       <c r="I580" s="11"/>
       <c r="J580" s="11"/>
       <c r="K580" s="11"/>
@@ -8310,7 +8369,7 @@
       <c r="E581" s="9"/>
       <c r="F581" s="9"/>
       <c r="G581" s="11"/>
-      <c r="H581" s="16"/>
+      <c r="H581" s="13"/>
       <c r="I581" s="11"/>
       <c r="J581" s="11"/>
       <c r="K581" s="11"/>
@@ -8323,7 +8382,7 @@
       <c r="E582" s="9"/>
       <c r="F582" s="9"/>
       <c r="G582" s="11"/>
-      <c r="H582" s="16"/>
+      <c r="H582" s="13"/>
       <c r="I582" s="11"/>
       <c r="J582" s="11"/>
       <c r="K582" s="11"/>
@@ -8336,7 +8395,7 @@
       <c r="E583" s="9"/>
       <c r="F583" s="9"/>
       <c r="G583" s="11"/>
-      <c r="H583" s="16"/>
+      <c r="H583" s="13"/>
       <c r="I583" s="11"/>
       <c r="J583" s="11"/>
       <c r="K583" s="11"/>
@@ -8349,7 +8408,7 @@
       <c r="E584" s="9"/>
       <c r="F584" s="9"/>
       <c r="G584" s="11"/>
-      <c r="H584" s="16"/>
+      <c r="H584" s="13"/>
       <c r="I584" s="11"/>
       <c r="J584" s="11"/>
       <c r="K584" s="11"/>
@@ -8362,7 +8421,7 @@
       <c r="E585" s="9"/>
       <c r="F585" s="9"/>
       <c r="G585" s="11"/>
-      <c r="H585" s="16"/>
+      <c r="H585" s="13"/>
       <c r="I585" s="11"/>
       <c r="J585" s="11"/>
       <c r="K585" s="11"/>
@@ -8375,7 +8434,7 @@
       <c r="E586" s="9"/>
       <c r="F586" s="9"/>
       <c r="G586" s="11"/>
-      <c r="H586" s="16"/>
+      <c r="H586" s="13"/>
       <c r="I586" s="11"/>
       <c r="J586" s="11"/>
       <c r="K586" s="11"/>
@@ -8388,7 +8447,7 @@
       <c r="E587" s="9"/>
       <c r="F587" s="9"/>
       <c r="G587" s="11"/>
-      <c r="H587" s="16"/>
+      <c r="H587" s="13"/>
       <c r="I587" s="11"/>
       <c r="J587" s="11"/>
       <c r="K587" s="11"/>
@@ -8401,7 +8460,7 @@
       <c r="E588" s="9"/>
       <c r="F588" s="9"/>
       <c r="G588" s="11"/>
-      <c r="H588" s="16"/>
+      <c r="H588" s="13"/>
       <c r="I588" s="11"/>
       <c r="J588" s="11"/>
       <c r="K588" s="11"/>
@@ -8414,7 +8473,7 @@
       <c r="E589" s="9"/>
       <c r="F589" s="9"/>
       <c r="G589" s="11"/>
-      <c r="H589" s="16"/>
+      <c r="H589" s="13"/>
       <c r="I589" s="11"/>
       <c r="J589" s="11"/>
       <c r="K589" s="11"/>
@@ -8427,7 +8486,7 @@
       <c r="E590" s="9"/>
       <c r="F590" s="9"/>
       <c r="G590" s="11"/>
-      <c r="H590" s="16"/>
+      <c r="H590" s="13"/>
       <c r="I590" s="11"/>
       <c r="J590" s="11"/>
       <c r="K590" s="11"/>
@@ -8440,7 +8499,7 @@
       <c r="E591" s="9"/>
       <c r="F591" s="9"/>
       <c r="G591" s="11"/>
-      <c r="H591" s="16"/>
+      <c r="H591" s="13"/>
       <c r="I591" s="11"/>
       <c r="J591" s="11"/>
       <c r="K591" s="11"/>
@@ -8453,7 +8512,7 @@
       <c r="E592" s="9"/>
       <c r="F592" s="9"/>
       <c r="G592" s="11"/>
-      <c r="H592" s="16"/>
+      <c r="H592" s="13"/>
       <c r="I592" s="11"/>
       <c r="J592" s="11"/>
       <c r="K592" s="11"/>
@@ -8466,7 +8525,7 @@
       <c r="E593" s="9"/>
       <c r="F593" s="9"/>
       <c r="G593" s="11"/>
-      <c r="H593" s="16"/>
+      <c r="H593" s="13"/>
       <c r="I593" s="11"/>
       <c r="J593" s="11"/>
       <c r="K593" s="11"/>
@@ -8479,7 +8538,7 @@
       <c r="E594" s="9"/>
       <c r="F594" s="9"/>
       <c r="G594" s="11"/>
-      <c r="H594" s="16"/>
+      <c r="H594" s="13"/>
       <c r="I594" s="11"/>
       <c r="J594" s="11"/>
       <c r="K594" s="11"/>
@@ -8492,7 +8551,7 @@
       <c r="E595" s="9"/>
       <c r="F595" s="9"/>
       <c r="G595" s="11"/>
-      <c r="H595" s="16"/>
+      <c r="H595" s="13"/>
       <c r="I595" s="11"/>
       <c r="J595" s="11"/>
       <c r="K595" s="11"/>
@@ -8505,7 +8564,7 @@
       <c r="E596" s="9"/>
       <c r="F596" s="9"/>
       <c r="G596" s="11"/>
-      <c r="H596" s="16"/>
+      <c r="H596" s="13"/>
       <c r="I596" s="11"/>
       <c r="J596" s="11"/>
       <c r="K596" s="11"/>
@@ -8518,7 +8577,7 @@
       <c r="E597" s="9"/>
       <c r="F597" s="9"/>
       <c r="G597" s="11"/>
-      <c r="H597" s="16"/>
+      <c r="H597" s="13"/>
       <c r="I597" s="11"/>
       <c r="J597" s="11"/>
       <c r="K597" s="11"/>
@@ -8531,7 +8590,7 @@
       <c r="E598" s="9"/>
       <c r="F598" s="9"/>
       <c r="G598" s="11"/>
-      <c r="H598" s="16"/>
+      <c r="H598" s="13"/>
       <c r="I598" s="11"/>
       <c r="J598" s="11"/>
       <c r="K598" s="11"/>
@@ -8544,7 +8603,7 @@
       <c r="E599" s="9"/>
       <c r="F599" s="9"/>
       <c r="G599" s="11"/>
-      <c r="H599" s="16"/>
+      <c r="H599" s="13"/>
       <c r="I599" s="11"/>
       <c r="J599" s="11"/>
       <c r="K599" s="11"/>
@@ -8557,7 +8616,7 @@
       <c r="E600" s="9"/>
       <c r="F600" s="9"/>
       <c r="G600" s="11"/>
-      <c r="H600" s="16"/>
+      <c r="H600" s="13"/>
       <c r="I600" s="11"/>
       <c r="J600" s="11"/>
       <c r="K600" s="11"/>
@@ -8570,7 +8629,7 @@
       <c r="E601" s="9"/>
       <c r="F601" s="9"/>
       <c r="G601" s="11"/>
-      <c r="H601" s="16"/>
+      <c r="H601" s="13"/>
       <c r="I601" s="11"/>
       <c r="J601" s="11"/>
       <c r="K601" s="11"/>
@@ -8583,7 +8642,7 @@
       <c r="E602" s="9"/>
       <c r="F602" s="9"/>
       <c r="G602" s="11"/>
-      <c r="H602" s="16"/>
+      <c r="H602" s="13"/>
       <c r="I602" s="11"/>
       <c r="J602" s="11"/>
       <c r="K602" s="11"/>
@@ -8596,7 +8655,7 @@
       <c r="E603" s="9"/>
       <c r="F603" s="9"/>
       <c r="G603" s="11"/>
-      <c r="H603" s="16"/>
+      <c r="H603" s="13"/>
       <c r="I603" s="11"/>
       <c r="J603" s="11"/>
       <c r="K603" s="11"/>
@@ -8609,7 +8668,7 @@
       <c r="E604" s="9"/>
       <c r="F604" s="9"/>
       <c r="G604" s="11"/>
-      <c r="H604" s="16"/>
+      <c r="H604" s="13"/>
       <c r="I604" s="11"/>
       <c r="J604" s="11"/>
       <c r="K604" s="11"/>
@@ -8622,7 +8681,7 @@
       <c r="E605" s="9"/>
       <c r="F605" s="9"/>
       <c r="G605" s="11"/>
-      <c r="H605" s="16"/>
+      <c r="H605" s="13"/>
       <c r="I605" s="11"/>
       <c r="J605" s="11"/>
       <c r="K605" s="11"/>
@@ -8635,7 +8694,7 @@
       <c r="E606" s="9"/>
       <c r="F606" s="9"/>
       <c r="G606" s="11"/>
-      <c r="H606" s="16"/>
+      <c r="H606" s="13"/>
       <c r="I606" s="11"/>
       <c r="J606" s="11"/>
       <c r="K606" s="11"/>
@@ -8648,7 +8707,7 @@
       <c r="E607" s="9"/>
       <c r="F607" s="9"/>
       <c r="G607" s="11"/>
-      <c r="H607" s="16"/>
+      <c r="H607" s="13"/>
       <c r="I607" s="11"/>
       <c r="J607" s="11"/>
       <c r="K607" s="11"/>
@@ -8661,7 +8720,7 @@
       <c r="E608" s="9"/>
       <c r="F608" s="9"/>
       <c r="G608" s="11"/>
-      <c r="H608" s="16"/>
+      <c r="H608" s="13"/>
       <c r="I608" s="11"/>
       <c r="J608" s="11"/>
       <c r="K608" s="11"/>
@@ -8674,7 +8733,7 @@
       <c r="E609" s="9"/>
       <c r="F609" s="9"/>
       <c r="G609" s="11"/>
-      <c r="H609" s="16"/>
+      <c r="H609" s="13"/>
       <c r="I609" s="11"/>
       <c r="J609" s="11"/>
       <c r="K609" s="11"/>
@@ -8687,7 +8746,7 @@
       <c r="E610" s="9"/>
       <c r="F610" s="9"/>
       <c r="G610" s="11"/>
-      <c r="H610" s="16"/>
+      <c r="H610" s="13"/>
       <c r="I610" s="11"/>
       <c r="J610" s="11"/>
       <c r="K610" s="11"/>
@@ -8700,7 +8759,7 @@
       <c r="E611" s="9"/>
       <c r="F611" s="9"/>
       <c r="G611" s="11"/>
-      <c r="H611" s="16"/>
+      <c r="H611" s="13"/>
       <c r="I611" s="11"/>
       <c r="J611" s="11"/>
       <c r="K611" s="11"/>
@@ -8713,7 +8772,7 @@
       <c r="E612" s="9"/>
       <c r="F612" s="9"/>
       <c r="G612" s="11"/>
-      <c r="H612" s="16"/>
+      <c r="H612" s="13"/>
       <c r="I612" s="11"/>
       <c r="J612" s="11"/>
       <c r="K612" s="11"/>
@@ -8726,7 +8785,7 @@
       <c r="E613" s="9"/>
       <c r="F613" s="9"/>
       <c r="G613" s="11"/>
-      <c r="H613" s="16"/>
+      <c r="H613" s="13"/>
       <c r="I613" s="11"/>
       <c r="J613" s="11"/>
       <c r="K613" s="11"/>
@@ -8739,7 +8798,7 @@
       <c r="E614" s="9"/>
       <c r="F614" s="9"/>
       <c r="G614" s="11"/>
-      <c r="H614" s="16"/>
+      <c r="H614" s="13"/>
       <c r="I614" s="11"/>
       <c r="J614" s="11"/>
       <c r="K614" s="11"/>
@@ -8752,7 +8811,7 @@
       <c r="E615" s="9"/>
       <c r="F615" s="9"/>
       <c r="G615" s="11"/>
-      <c r="H615" s="16"/>
+      <c r="H615" s="13"/>
       <c r="I615" s="11"/>
       <c r="J615" s="11"/>
       <c r="K615" s="11"/>
@@ -8765,7 +8824,7 @@
       <c r="E616" s="9"/>
       <c r="F616" s="9"/>
       <c r="G616" s="11"/>
-      <c r="H616" s="16"/>
+      <c r="H616" s="13"/>
       <c r="I616" s="11"/>
       <c r="J616" s="11"/>
       <c r="K616" s="11"/>
@@ -8778,7 +8837,7 @@
       <c r="E617" s="9"/>
       <c r="F617" s="9"/>
       <c r="G617" s="11"/>
-      <c r="H617" s="16"/>
+      <c r="H617" s="13"/>
       <c r="I617" s="11"/>
       <c r="J617" s="11"/>
       <c r="K617" s="11"/>
@@ -8791,7 +8850,7 @@
       <c r="E618" s="9"/>
       <c r="F618" s="9"/>
       <c r="G618" s="11"/>
-      <c r="H618" s="16"/>
+      <c r="H618" s="13"/>
       <c r="I618" s="11"/>
       <c r="J618" s="11"/>
       <c r="K618" s="11"/>
@@ -8804,7 +8863,7 @@
       <c r="E619" s="9"/>
       <c r="F619" s="9"/>
       <c r="G619" s="11"/>
-      <c r="H619" s="16"/>
+      <c r="H619" s="13"/>
       <c r="I619" s="11"/>
       <c r="J619" s="11"/>
       <c r="K619" s="11"/>
@@ -8817,7 +8876,7 @@
       <c r="E620" s="9"/>
       <c r="F620" s="9"/>
       <c r="G620" s="11"/>
-      <c r="H620" s="16"/>
+      <c r="H620" s="13"/>
       <c r="I620" s="11"/>
       <c r="J620" s="11"/>
       <c r="K620" s="11"/>
@@ -8830,7 +8889,7 @@
       <c r="E621" s="9"/>
       <c r="F621" s="9"/>
       <c r="G621" s="11"/>
-      <c r="H621" s="16"/>
+      <c r="H621" s="13"/>
       <c r="I621" s="11"/>
       <c r="J621" s="11"/>
       <c r="K621" s="11"/>
@@ -8843,7 +8902,7 @@
       <c r="E622" s="9"/>
       <c r="F622" s="9"/>
       <c r="G622" s="11"/>
-      <c r="H622" s="16"/>
+      <c r="H622" s="13"/>
       <c r="I622" s="11"/>
       <c r="J622" s="11"/>
       <c r="K622" s="11"/>
@@ -8856,7 +8915,7 @@
       <c r="E623" s="9"/>
       <c r="F623" s="9"/>
       <c r="G623" s="11"/>
-      <c r="H623" s="16"/>
+      <c r="H623" s="13"/>
       <c r="I623" s="11"/>
       <c r="J623" s="11"/>
       <c r="K623" s="11"/>
@@ -8869,7 +8928,7 @@
       <c r="E624" s="9"/>
       <c r="F624" s="9"/>
       <c r="G624" s="11"/>
-      <c r="H624" s="16"/>
+      <c r="H624" s="13"/>
       <c r="I624" s="11"/>
       <c r="J624" s="11"/>
       <c r="K624" s="11"/>
@@ -8882,7 +8941,7 @@
       <c r="E625" s="9"/>
       <c r="F625" s="9"/>
       <c r="G625" s="11"/>
-      <c r="H625" s="16"/>
+      <c r="H625" s="13"/>
       <c r="I625" s="11"/>
       <c r="J625" s="11"/>
       <c r="K625" s="11"/>
@@ -8895,7 +8954,7 @@
       <c r="E626" s="9"/>
       <c r="F626" s="9"/>
       <c r="G626" s="11"/>
-      <c r="H626" s="16"/>
+      <c r="H626" s="13"/>
       <c r="I626" s="11"/>
       <c r="J626" s="11"/>
       <c r="K626" s="11"/>
@@ -8908,7 +8967,7 @@
       <c r="E627" s="9"/>
       <c r="F627" s="9"/>
       <c r="G627" s="11"/>
-      <c r="H627" s="16"/>
+      <c r="H627" s="13"/>
       <c r="I627" s="11"/>
       <c r="J627" s="11"/>
       <c r="K627" s="11"/>
@@ -8921,7 +8980,7 @@
       <c r="E628" s="9"/>
       <c r="F628" s="9"/>
       <c r="G628" s="11"/>
-      <c r="H628" s="16"/>
+      <c r="H628" s="13"/>
       <c r="I628" s="11"/>
       <c r="J628" s="11"/>
       <c r="K628" s="11"/>
@@ -8934,7 +8993,7 @@
       <c r="E629" s="9"/>
       <c r="F629" s="9"/>
       <c r="G629" s="11"/>
-      <c r="H629" s="16"/>
+      <c r="H629" s="13"/>
       <c r="I629" s="11"/>
       <c r="J629" s="11"/>
       <c r="K629" s="11"/>
@@ -8947,7 +9006,7 @@
       <c r="E630" s="9"/>
       <c r="F630" s="9"/>
       <c r="G630" s="11"/>
-      <c r="H630" s="16"/>
+      <c r="H630" s="13"/>
       <c r="I630" s="11"/>
       <c r="J630" s="11"/>
       <c r="K630" s="11"/>
@@ -8960,7 +9019,7 @@
       <c r="E631" s="9"/>
       <c r="F631" s="9"/>
       <c r="G631" s="11"/>
-      <c r="H631" s="16"/>
+      <c r="H631" s="13"/>
       <c r="I631" s="11"/>
       <c r="J631" s="11"/>
       <c r="K631" s="11"/>
@@ -8973,7 +9032,7 @@
       <c r="E632" s="9"/>
       <c r="F632" s="9"/>
       <c r="G632" s="11"/>
-      <c r="H632" s="16"/>
+      <c r="H632" s="13"/>
       <c r="I632" s="11"/>
       <c r="J632" s="11"/>
       <c r="K632" s="11"/>
@@ -8986,7 +9045,7 @@
       <c r="E633" s="9"/>
       <c r="F633" s="9"/>
       <c r="G633" s="11"/>
-      <c r="H633" s="16"/>
+      <c r="H633" s="13"/>
       <c r="I633" s="11"/>
       <c r="J633" s="11"/>
       <c r="K633" s="11"/>
@@ -8999,7 +9058,7 @@
       <c r="E634" s="9"/>
       <c r="F634" s="9"/>
       <c r="G634" s="11"/>
-      <c r="H634" s="16"/>
+      <c r="H634" s="13"/>
       <c r="I634" s="11"/>
       <c r="J634" s="11"/>
       <c r="K634" s="11"/>
@@ -9012,7 +9071,7 @@
       <c r="E635" s="9"/>
       <c r="F635" s="9"/>
       <c r="G635" s="11"/>
-      <c r="H635" s="16"/>
+      <c r="H635" s="13"/>
       <c r="I635" s="11"/>
       <c r="J635" s="11"/>
       <c r="K635" s="11"/>
@@ -9025,7 +9084,7 @@
       <c r="E636" s="9"/>
       <c r="F636" s="9"/>
       <c r="G636" s="11"/>
-      <c r="H636" s="16"/>
+      <c r="H636" s="13"/>
       <c r="I636" s="11"/>
       <c r="J636" s="11"/>
       <c r="K636" s="11"/>
@@ -9038,7 +9097,7 @@
       <c r="E637" s="9"/>
       <c r="F637" s="9"/>
       <c r="G637" s="11"/>
-      <c r="H637" s="16"/>
+      <c r="H637" s="13"/>
       <c r="I637" s="11"/>
       <c r="J637" s="11"/>
       <c r="K637" s="11"/>
@@ -9051,7 +9110,7 @@
       <c r="E638" s="9"/>
       <c r="F638" s="9"/>
       <c r="G638" s="11"/>
-      <c r="H638" s="16"/>
+      <c r="H638" s="13"/>
       <c r="I638" s="11"/>
       <c r="J638" s="11"/>
       <c r="K638" s="11"/>
@@ -9064,7 +9123,7 @@
       <c r="E639" s="9"/>
       <c r="F639" s="9"/>
       <c r="G639" s="11"/>
-      <c r="H639" s="16"/>
+      <c r="H639" s="13"/>
       <c r="I639" s="11"/>
       <c r="J639" s="11"/>
       <c r="K639" s="11"/>
@@ -9077,7 +9136,7 @@
       <c r="E640" s="9"/>
       <c r="F640" s="9"/>
       <c r="G640" s="11"/>
-      <c r="H640" s="16"/>
+      <c r="H640" s="13"/>
       <c r="I640" s="11"/>
       <c r="J640" s="11"/>
       <c r="K640" s="11"/>
@@ -9090,7 +9149,7 @@
       <c r="E641" s="9"/>
       <c r="F641" s="9"/>
       <c r="G641" s="11"/>
-      <c r="H641" s="16"/>
+      <c r="H641" s="13"/>
       <c r="I641" s="11"/>
       <c r="J641" s="11"/>
       <c r="K641" s="11"/>
@@ -9103,7 +9162,7 @@
       <c r="E642" s="9"/>
       <c r="F642" s="9"/>
       <c r="G642" s="11"/>
-      <c r="H642" s="16"/>
+      <c r="H642" s="13"/>
       <c r="I642" s="11"/>
       <c r="J642" s="11"/>
       <c r="K642" s="11"/>
@@ -9116,7 +9175,7 @@
       <c r="E643" s="9"/>
       <c r="F643" s="9"/>
       <c r="G643" s="11"/>
-      <c r="H643" s="16"/>
+      <c r="H643" s="13"/>
       <c r="I643" s="11"/>
       <c r="J643" s="11"/>
       <c r="K643" s="11"/>
@@ -9129,7 +9188,7 @@
       <c r="E644" s="9"/>
       <c r="F644" s="9"/>
       <c r="G644" s="11"/>
-      <c r="H644" s="16"/>
+      <c r="H644" s="13"/>
       <c r="I644" s="11"/>
       <c r="J644" s="11"/>
       <c r="K644" s="11"/>
@@ -9142,7 +9201,7 @@
       <c r="E645" s="9"/>
       <c r="F645" s="9"/>
       <c r="G645" s="11"/>
-      <c r="H645" s="16"/>
+      <c r="H645" s="13"/>
       <c r="I645" s="11"/>
       <c r="J645" s="11"/>
       <c r="K645" s="11"/>
@@ -9155,7 +9214,7 @@
       <c r="E646" s="9"/>
       <c r="F646" s="9"/>
       <c r="G646" s="11"/>
-      <c r="H646" s="16"/>
+      <c r="H646" s="13"/>
       <c r="I646" s="11"/>
       <c r="J646" s="11"/>
       <c r="K646" s="11"/>
@@ -9168,7 +9227,7 @@
       <c r="E647" s="9"/>
       <c r="F647" s="9"/>
       <c r="G647" s="11"/>
-      <c r="H647" s="16"/>
+      <c r="H647" s="13"/>
       <c r="I647" s="11"/>
       <c r="J647" s="11"/>
       <c r="K647" s="11"/>
@@ -9181,7 +9240,7 @@
       <c r="E648" s="9"/>
       <c r="F648" s="9"/>
       <c r="G648" s="11"/>
-      <c r="H648" s="16"/>
+      <c r="H648" s="13"/>
       <c r="I648" s="11"/>
       <c r="J648" s="11"/>
       <c r="K648" s="11"/>
@@ -9194,7 +9253,7 @@
       <c r="E649" s="9"/>
       <c r="F649" s="9"/>
       <c r="G649" s="11"/>
-      <c r="H649" s="16"/>
+      <c r="H649" s="13"/>
       <c r="I649" s="11"/>
       <c r="J649" s="11"/>
       <c r="K649" s="11"/>
@@ -9207,7 +9266,7 @@
       <c r="E650" s="9"/>
       <c r="F650" s="9"/>
       <c r="G650" s="11"/>
-      <c r="H650" s="16"/>
+      <c r="H650" s="13"/>
       <c r="I650" s="11"/>
       <c r="J650" s="11"/>
       <c r="K650" s="11"/>
@@ -9220,7 +9279,7 @@
       <c r="E651" s="9"/>
       <c r="F651" s="9"/>
       <c r="G651" s="11"/>
-      <c r="H651" s="16"/>
+      <c r="H651" s="13"/>
       <c r="I651" s="11"/>
       <c r="J651" s="11"/>
       <c r="K651" s="11"/>
@@ -9233,7 +9292,7 @@
       <c r="E652" s="9"/>
       <c r="F652" s="9"/>
       <c r="G652" s="11"/>
-      <c r="H652" s="16"/>
+      <c r="H652" s="13"/>
       <c r="I652" s="11"/>
       <c r="J652" s="11"/>
       <c r="K652" s="11"/>
@@ -9246,7 +9305,7 @@
       <c r="E653" s="9"/>
       <c r="F653" s="9"/>
       <c r="G653" s="11"/>
-      <c r="H653" s="16"/>
+      <c r="H653" s="13"/>
       <c r="I653" s="11"/>
       <c r="J653" s="11"/>
       <c r="K653" s="11"/>
@@ -9259,7 +9318,7 @@
       <c r="E654" s="9"/>
       <c r="F654" s="9"/>
       <c r="G654" s="11"/>
-      <c r="H654" s="16"/>
+      <c r="H654" s="13"/>
       <c r="I654" s="11"/>
       <c r="J654" s="11"/>
       <c r="K654" s="11"/>
@@ -9272,7 +9331,7 @@
       <c r="E655" s="9"/>
       <c r="F655" s="9"/>
       <c r="G655" s="11"/>
-      <c r="H655" s="16"/>
+      <c r="H655" s="13"/>
       <c r="I655" s="11"/>
       <c r="J655" s="11"/>
       <c r="K655" s="11"/>
@@ -9285,7 +9344,7 @@
       <c r="E656" s="9"/>
       <c r="F656" s="9"/>
       <c r="G656" s="11"/>
-      <c r="H656" s="16"/>
+      <c r="H656" s="13"/>
       <c r="I656" s="11"/>
       <c r="J656" s="11"/>
       <c r="K656" s="11"/>
@@ -9298,7 +9357,7 @@
       <c r="E657" s="9"/>
       <c r="F657" s="9"/>
       <c r="G657" s="11"/>
-      <c r="H657" s="16"/>
+      <c r="H657" s="13"/>
       <c r="I657" s="11"/>
       <c r="J657" s="11"/>
       <c r="K657" s="11"/>
@@ -9311,7 +9370,7 @@
       <c r="E658" s="9"/>
       <c r="F658" s="9"/>
       <c r="G658" s="11"/>
-      <c r="H658" s="16"/>
+      <c r="H658" s="13"/>
       <c r="I658" s="11"/>
       <c r="J658" s="11"/>
       <c r="K658" s="11"/>
@@ -9324,7 +9383,7 @@
       <c r="E659" s="9"/>
       <c r="F659" s="9"/>
       <c r="G659" s="11"/>
-      <c r="H659" s="16"/>
+      <c r="H659" s="13"/>
       <c r="I659" s="11"/>
       <c r="J659" s="11"/>
       <c r="K659" s="11"/>
@@ -9337,7 +9396,7 @@
       <c r="E660" s="9"/>
       <c r="F660" s="9"/>
       <c r="G660" s="11"/>
-      <c r="H660" s="16"/>
+      <c r="H660" s="13"/>
       <c r="I660" s="11"/>
       <c r="J660" s="11"/>
       <c r="K660" s="11"/>
@@ -9350,7 +9409,7 @@
       <c r="E661" s="9"/>
       <c r="F661" s="9"/>
       <c r="G661" s="11"/>
-      <c r="H661" s="16"/>
+      <c r="H661" s="13"/>
       <c r="I661" s="11"/>
       <c r="J661" s="11"/>
       <c r="K661" s="11"/>
@@ -9363,7 +9422,7 @@
       <c r="E662" s="9"/>
       <c r="F662" s="9"/>
       <c r="G662" s="11"/>
-      <c r="H662" s="16"/>
+      <c r="H662" s="13"/>
       <c r="I662" s="11"/>
       <c r="J662" s="11"/>
       <c r="K662" s="11"/>
@@ -9376,7 +9435,7 @@
       <c r="E663" s="9"/>
       <c r="F663" s="9"/>
       <c r="G663" s="11"/>
-      <c r="H663" s="16"/>
+      <c r="H663" s="13"/>
       <c r="I663" s="11"/>
       <c r="J663" s="11"/>
       <c r="K663" s="11"/>
@@ -9389,7 +9448,7 @@
       <c r="E664" s="9"/>
       <c r="F664" s="9"/>
       <c r="G664" s="11"/>
-      <c r="H664" s="16"/>
+      <c r="H664" s="13"/>
       <c r="I664" s="11"/>
       <c r="J664" s="11"/>
       <c r="K664" s="11"/>
@@ -9402,7 +9461,7 @@
       <c r="E665" s="9"/>
       <c r="F665" s="9"/>
       <c r="G665" s="11"/>
-      <c r="H665" s="16"/>
+      <c r="H665" s="13"/>
       <c r="I665" s="11"/>
       <c r="J665" s="11"/>
       <c r="K665" s="11"/>
@@ -9415,7 +9474,7 @@
       <c r="E666" s="9"/>
       <c r="F666" s="9"/>
       <c r="G666" s="11"/>
-      <c r="H666" s="16"/>
+      <c r="H666" s="13"/>
       <c r="I666" s="11"/>
       <c r="J666" s="11"/>
       <c r="K666" s="11"/>
@@ -9428,7 +9487,7 @@
       <c r="E667" s="9"/>
       <c r="F667" s="9"/>
       <c r="G667" s="11"/>
-      <c r="H667" s="16"/>
+      <c r="H667" s="13"/>
       <c r="I667" s="11"/>
       <c r="J667" s="11"/>
       <c r="K667" s="11"/>
@@ -9441,7 +9500,7 @@
       <c r="E668" s="9"/>
       <c r="F668" s="9"/>
       <c r="G668" s="11"/>
-      <c r="H668" s="16"/>
+      <c r="H668" s="13"/>
       <c r="I668" s="11"/>
       <c r="J668" s="11"/>
       <c r="K668" s="11"/>
@@ -9454,7 +9513,7 @@
       <c r="E669" s="9"/>
       <c r="F669" s="9"/>
       <c r="G669" s="11"/>
-      <c r="H669" s="16"/>
+      <c r="H669" s="13"/>
       <c r="I669" s="11"/>
       <c r="J669" s="11"/>
       <c r="K669" s="11"/>
@@ -9467,7 +9526,7 @@
       <c r="E670" s="9"/>
       <c r="F670" s="9"/>
       <c r="G670" s="11"/>
-      <c r="H670" s="16"/>
+      <c r="H670" s="13"/>
       <c r="I670" s="11"/>
       <c r="J670" s="11"/>
       <c r="K670" s="11"/>
@@ -9480,7 +9539,7 @@
       <c r="E671" s="9"/>
       <c r="F671" s="9"/>
       <c r="G671" s="11"/>
-      <c r="H671" s="16"/>
+      <c r="H671" s="13"/>
       <c r="I671" s="11"/>
       <c r="J671" s="11"/>
       <c r="K671" s="11"/>
@@ -9493,7 +9552,7 @@
       <c r="E672" s="9"/>
       <c r="F672" s="9"/>
       <c r="G672" s="11"/>
-      <c r="H672" s="16"/>
+      <c r="H672" s="13"/>
       <c r="I672" s="11"/>
       <c r="J672" s="11"/>
       <c r="K672" s="11"/>
@@ -9506,7 +9565,7 @@
       <c r="E673" s="9"/>
       <c r="F673" s="9"/>
       <c r="G673" s="11"/>
-      <c r="H673" s="16"/>
+      <c r="H673" s="13"/>
       <c r="I673" s="11"/>
       <c r="J673" s="11"/>
       <c r="K673" s="11"/>
@@ -9519,7 +9578,7 @@
       <c r="E674" s="9"/>
       <c r="F674" s="9"/>
       <c r="G674" s="11"/>
-      <c r="H674" s="16"/>
+      <c r="H674" s="13"/>
       <c r="I674" s="11"/>
       <c r="J674" s="11"/>
       <c r="K674" s="11"/>
@@ -9532,7 +9591,7 @@
       <c r="E675" s="9"/>
       <c r="F675" s="9"/>
       <c r="G675" s="11"/>
-      <c r="H675" s="16"/>
+      <c r="H675" s="13"/>
       <c r="I675" s="11"/>
       <c r="J675" s="11"/>
       <c r="K675" s="11"/>
@@ -9545,7 +9604,7 @@
       <c r="E676" s="9"/>
       <c r="F676" s="9"/>
       <c r="G676" s="11"/>
-      <c r="H676" s="16"/>
+      <c r="H676" s="13"/>
       <c r="I676" s="11"/>
       <c r="J676" s="11"/>
       <c r="K676" s="11"/>
@@ -9558,7 +9617,7 @@
       <c r="E677" s="9"/>
       <c r="F677" s="9"/>
       <c r="G677" s="11"/>
-      <c r="H677" s="16"/>
+      <c r="H677" s="13"/>
       <c r="I677" s="11"/>
       <c r="J677" s="11"/>
       <c r="K677" s="11"/>
@@ -9571,7 +9630,7 @@
       <c r="E678" s="9"/>
       <c r="F678" s="9"/>
       <c r="G678" s="11"/>
-      <c r="H678" s="16"/>
+      <c r="H678" s="13"/>
       <c r="I678" s="11"/>
       <c r="J678" s="11"/>
       <c r="K678" s="11"/>
@@ -9584,7 +9643,7 @@
       <c r="E679" s="9"/>
       <c r="F679" s="9"/>
       <c r="G679" s="11"/>
-      <c r="H679" s="16"/>
+      <c r="H679" s="13"/>
       <c r="I679" s="11"/>
       <c r="J679" s="11"/>
       <c r="K679" s="11"/>
@@ -9597,7 +9656,7 @@
       <c r="E680" s="9"/>
       <c r="F680" s="9"/>
       <c r="G680" s="11"/>
-      <c r="H680" s="16"/>
+      <c r="H680" s="13"/>
       <c r="I680" s="11"/>
       <c r="J680" s="11"/>
       <c r="K680" s="11"/>
@@ -9610,7 +9669,7 @@
       <c r="E681" s="9"/>
       <c r="F681" s="9"/>
       <c r="G681" s="11"/>
-      <c r="H681" s="16"/>
+      <c r="H681" s="13"/>
       <c r="I681" s="11"/>
       <c r="J681" s="11"/>
       <c r="K681" s="11"/>
@@ -9623,7 +9682,7 @@
       <c r="E682" s="9"/>
       <c r="F682" s="9"/>
       <c r="G682" s="11"/>
-      <c r="H682" s="16"/>
+      <c r="H682" s="13"/>
       <c r="I682" s="11"/>
       <c r="J682" s="11"/>
       <c r="K682" s="11"/>
@@ -9636,7 +9695,7 @@
       <c r="E683" s="9"/>
       <c r="F683" s="9"/>
       <c r="G683" s="11"/>
-      <c r="H683" s="16"/>
+      <c r="H683" s="13"/>
       <c r="I683" s="11"/>
       <c r="J683" s="11"/>
       <c r="K683" s="11"/>
@@ -9649,7 +9708,7 @@
       <c r="E684" s="9"/>
       <c r="F684" s="9"/>
       <c r="G684" s="11"/>
-      <c r="H684" s="16"/>
+      <c r="H684" s="13"/>
       <c r="I684" s="11"/>
       <c r="J684" s="11"/>
       <c r="K684" s="11"/>
@@ -9662,7 +9721,7 @@
       <c r="E685" s="9"/>
       <c r="F685" s="9"/>
       <c r="G685" s="11"/>
-      <c r="H685" s="16"/>
+      <c r="H685" s="13"/>
       <c r="I685" s="11"/>
       <c r="J685" s="11"/>
       <c r="K685" s="11"/>
@@ -9675,7 +9734,7 @@
       <c r="E686" s="9"/>
       <c r="F686" s="9"/>
       <c r="G686" s="11"/>
-      <c r="H686" s="16"/>
+      <c r="H686" s="13"/>
       <c r="I686" s="11"/>
       <c r="J686" s="11"/>
       <c r="K686" s="11"/>
@@ -9688,7 +9747,7 @@
       <c r="E687" s="9"/>
       <c r="F687" s="9"/>
       <c r="G687" s="11"/>
-      <c r="H687" s="16"/>
+      <c r="H687" s="13"/>
       <c r="I687" s="11"/>
       <c r="J687" s="11"/>
       <c r="K687" s="11"/>
@@ -9701,7 +9760,7 @@
       <c r="E688" s="9"/>
       <c r="F688" s="9"/>
       <c r="G688" s="11"/>
-      <c r="H688" s="16"/>
+      <c r="H688" s="13"/>
       <c r="I688" s="11"/>
       <c r="J688" s="11"/>
       <c r="K688" s="11"/>
@@ -9714,7 +9773,7 @@
       <c r="E689" s="9"/>
       <c r="F689" s="9"/>
       <c r="G689" s="11"/>
-      <c r="H689" s="16"/>
+      <c r="H689" s="13"/>
       <c r="I689" s="11"/>
       <c r="J689" s="11"/>
       <c r="K689" s="11"/>
@@ -9727,7 +9786,7 @@
       <c r="E690" s="9"/>
       <c r="F690" s="9"/>
       <c r="G690" s="11"/>
-      <c r="H690" s="16"/>
+      <c r="H690" s="13"/>
       <c r="I690" s="11"/>
       <c r="J690" s="11"/>
       <c r="K690" s="11"/>
@@ -9740,7 +9799,7 @@
       <c r="E691" s="9"/>
       <c r="F691" s="9"/>
       <c r="G691" s="11"/>
-      <c r="H691" s="16"/>
+      <c r="H691" s="13"/>
       <c r="I691" s="11"/>
       <c r="J691" s="11"/>
       <c r="K691" s="11"/>
@@ -9753,7 +9812,7 @@
       <c r="E692" s="9"/>
       <c r="F692" s="9"/>
       <c r="G692" s="11"/>
-      <c r="H692" s="16"/>
+      <c r="H692" s="13"/>
       <c r="I692" s="11"/>
       <c r="J692" s="11"/>
       <c r="K692" s="11"/>
@@ -9766,7 +9825,7 @@
       <c r="E693" s="9"/>
       <c r="F693" s="9"/>
       <c r="G693" s="11"/>
-      <c r="H693" s="16"/>
+      <c r="H693" s="13"/>
       <c r="I693" s="11"/>
       <c r="J693" s="11"/>
       <c r="K693" s="11"/>
@@ -9779,7 +9838,7 @@
       <c r="E694" s="9"/>
       <c r="F694" s="9"/>
       <c r="G694" s="11"/>
-      <c r="H694" s="16"/>
+      <c r="H694" s="13"/>
       <c r="I694" s="11"/>
       <c r="J694" s="11"/>
       <c r="K694" s="11"/>
@@ -9792,7 +9851,7 @@
       <c r="E695" s="9"/>
       <c r="F695" s="9"/>
       <c r="G695" s="11"/>
-      <c r="H695" s="16"/>
+      <c r="H695" s="13"/>
       <c r="I695" s="11"/>
       <c r="J695" s="11"/>
       <c r="K695" s="11"/>
@@ -9805,7 +9864,7 @@
       <c r="E696" s="9"/>
       <c r="F696" s="9"/>
       <c r="G696" s="11"/>
-      <c r="H696" s="16"/>
+      <c r="H696" s="13"/>
       <c r="I696" s="11"/>
       <c r="J696" s="11"/>
       <c r="K696" s="11"/>
@@ -9818,7 +9877,7 @@
       <c r="E697" s="9"/>
       <c r="F697" s="9"/>
       <c r="G697" s="11"/>
-      <c r="H697" s="16"/>
+      <c r="H697" s="13"/>
       <c r="I697" s="11"/>
       <c r="J697" s="11"/>
       <c r="K697" s="11"/>
@@ -9831,7 +9890,7 @@
       <c r="E698" s="9"/>
       <c r="F698" s="9"/>
       <c r="G698" s="11"/>
-      <c r="H698" s="16"/>
+      <c r="H698" s="13"/>
       <c r="I698" s="11"/>
       <c r="J698" s="11"/>
       <c r="K698" s="11"/>
@@ -9844,7 +9903,7 @@
       <c r="E699" s="9"/>
       <c r="F699" s="9"/>
       <c r="G699" s="11"/>
-      <c r="H699" s="16"/>
+      <c r="H699" s="13"/>
       <c r="I699" s="11"/>
       <c r="J699" s="11"/>
       <c r="K699" s="11"/>
@@ -9857,7 +9916,7 @@
       <c r="E700" s="9"/>
       <c r="F700" s="9"/>
       <c r="G700" s="11"/>
-      <c r="H700" s="16"/>
+      <c r="H700" s="13"/>
       <c r="I700" s="11"/>
       <c r="J700" s="11"/>
       <c r="K700" s="11"/>
@@ -9870,7 +9929,7 @@
       <c r="E701" s="9"/>
       <c r="F701" s="9"/>
       <c r="G701" s="11"/>
-      <c r="H701" s="16"/>
+      <c r="H701" s="13"/>
       <c r="I701" s="11"/>
       <c r="J701" s="11"/>
       <c r="K701" s="11"/>
@@ -9883,7 +9942,7 @@
       <c r="E702" s="9"/>
       <c r="F702" s="9"/>
       <c r="G702" s="11"/>
-      <c r="H702" s="16"/>
+      <c r="H702" s="13"/>
       <c r="I702" s="11"/>
       <c r="J702" s="11"/>
       <c r="K702" s="11"/>
@@ -9896,7 +9955,7 @@
       <c r="E703" s="9"/>
       <c r="F703" s="9"/>
       <c r="G703" s="11"/>
-      <c r="H703" s="16"/>
+      <c r="H703" s="13"/>
       <c r="I703" s="11"/>
       <c r="J703" s="11"/>
       <c r="K703" s="11"/>
@@ -9909,7 +9968,7 @@
       <c r="E704" s="9"/>
       <c r="F704" s="9"/>
       <c r="G704" s="11"/>
-      <c r="H704" s="16"/>
+      <c r="H704" s="13"/>
       <c r="I704" s="11"/>
       <c r="J704" s="11"/>
       <c r="K704" s="11"/>
@@ -9922,7 +9981,7 @@
       <c r="E705" s="9"/>
       <c r="F705" s="9"/>
       <c r="G705" s="11"/>
-      <c r="H705" s="16"/>
+      <c r="H705" s="13"/>
       <c r="I705" s="11"/>
       <c r="J705" s="11"/>
       <c r="K705" s="11"/>
@@ -9935,7 +9994,7 @@
       <c r="E706" s="9"/>
       <c r="F706" s="9"/>
       <c r="G706" s="11"/>
-      <c r="H706" s="16"/>
+      <c r="H706" s="13"/>
       <c r="I706" s="11"/>
       <c r="J706" s="11"/>
       <c r="K706" s="11"/>
@@ -9948,7 +10007,7 @@
       <c r="E707" s="9"/>
       <c r="F707" s="9"/>
       <c r="G707" s="11"/>
-      <c r="H707" s="16"/>
+      <c r="H707" s="13"/>
       <c r="I707" s="11"/>
       <c r="J707" s="11"/>
       <c r="K707" s="11"/>
@@ -9961,7 +10020,7 @@
       <c r="E708" s="9"/>
       <c r="F708" s="9"/>
       <c r="G708" s="11"/>
-      <c r="H708" s="16"/>
+      <c r="H708" s="13"/>
       <c r="I708" s="11"/>
       <c r="J708" s="11"/>
       <c r="K708" s="11"/>
@@ -9974,7 +10033,7 @@
       <c r="E709" s="9"/>
       <c r="F709" s="9"/>
       <c r="G709" s="11"/>
-      <c r="H709" s="16"/>
+      <c r="H709" s="13"/>
       <c r="I709" s="11"/>
       <c r="J709" s="11"/>
       <c r="K709" s="11"/>
@@ -9987,7 +10046,7 @@
       <c r="E710" s="9"/>
       <c r="F710" s="9"/>
       <c r="G710" s="11"/>
-      <c r="H710" s="16"/>
+      <c r="H710" s="13"/>
       <c r="I710" s="11"/>
       <c r="J710" s="11"/>
       <c r="K710" s="11"/>
@@ -10000,7 +10059,7 @@
       <c r="E711" s="9"/>
       <c r="F711" s="9"/>
       <c r="G711" s="11"/>
-      <c r="H711" s="16"/>
+      <c r="H711" s="13"/>
       <c r="I711" s="11"/>
       <c r="J711" s="11"/>
       <c r="K711" s="11"/>
@@ -10013,7 +10072,7 @@
       <c r="E712" s="9"/>
       <c r="F712" s="9"/>
       <c r="G712" s="11"/>
-      <c r="H712" s="16"/>
+      <c r="H712" s="13"/>
       <c r="I712" s="11"/>
       <c r="J712" s="11"/>
       <c r="K712" s="11"/>
@@ -10026,7 +10085,7 @@
       <c r="E713" s="9"/>
       <c r="F713" s="9"/>
       <c r="G713" s="11"/>
-      <c r="H713" s="16"/>
+      <c r="H713" s="13"/>
       <c r="I713" s="11"/>
       <c r="J713" s="11"/>
       <c r="K713" s="11"/>
@@ -10039,7 +10098,7 @@
       <c r="E714" s="9"/>
       <c r="F714" s="9"/>
       <c r="G714" s="11"/>
-      <c r="H714" s="16"/>
+      <c r="H714" s="13"/>
       <c r="I714" s="11"/>
       <c r="J714" s="11"/>
       <c r="K714" s="11"/>
@@ -10052,7 +10111,7 @@
       <c r="E715" s="9"/>
       <c r="F715" s="9"/>
       <c r="G715" s="11"/>
-      <c r="H715" s="16"/>
+      <c r="H715" s="13"/>
       <c r="I715" s="11"/>
       <c r="J715" s="11"/>
       <c r="K715" s="11"/>
@@ -10065,7 +10124,7 @@
       <c r="E716" s="9"/>
       <c r="F716" s="9"/>
       <c r="G716" s="11"/>
-      <c r="H716" s="16"/>
+      <c r="H716" s="13"/>
       <c r="I716" s="11"/>
       <c r="J716" s="11"/>
       <c r="K716" s="11"/>
@@ -10078,7 +10137,7 @@
       <c r="E717" s="9"/>
       <c r="F717" s="9"/>
       <c r="G717" s="11"/>
-      <c r="H717" s="16"/>
+      <c r="H717" s="13"/>
       <c r="I717" s="11"/>
       <c r="J717" s="11"/>
       <c r="K717" s="11"/>
@@ -10091,7 +10150,7 @@
       <c r="E718" s="9"/>
       <c r="F718" s="9"/>
       <c r="G718" s="11"/>
-      <c r="H718" s="16"/>
+      <c r="H718" s="13"/>
       <c r="I718" s="11"/>
       <c r="J718" s="11"/>
       <c r="K718" s="11"/>
@@ -10104,7 +10163,7 @@
       <c r="E719" s="9"/>
       <c r="F719" s="9"/>
       <c r="G719" s="11"/>
-      <c r="H719" s="16"/>
+      <c r="H719" s="13"/>
       <c r="I719" s="11"/>
       <c r="J719" s="11"/>
       <c r="K719" s="11"/>
@@ -10117,7 +10176,7 @@
       <c r="E720" s="9"/>
       <c r="F720" s="9"/>
       <c r="G720" s="11"/>
-      <c r="H720" s="16"/>
+      <c r="H720" s="13"/>
       <c r="I720" s="11"/>
       <c r="J720" s="11"/>
       <c r="K720" s="11"/>
@@ -10130,7 +10189,7 @@
       <c r="E721" s="9"/>
       <c r="F721" s="9"/>
       <c r="G721" s="11"/>
-      <c r="H721" s="16"/>
+      <c r="H721" s="13"/>
       <c r="I721" s="11"/>
       <c r="J721" s="11"/>
       <c r="K721" s="11"/>
@@ -10143,7 +10202,7 @@
       <c r="E722" s="9"/>
       <c r="F722" s="9"/>
       <c r="G722" s="11"/>
-      <c r="H722" s="16"/>
+      <c r="H722" s="13"/>
       <c r="I722" s="11"/>
       <c r="J722" s="11"/>
       <c r="K722" s="11"/>
@@ -10156,7 +10215,7 @@
       <c r="E723" s="9"/>
       <c r="F723" s="9"/>
       <c r="G723" s="11"/>
-      <c r="H723" s="16"/>
+      <c r="H723" s="13"/>
       <c r="I723" s="11"/>
       <c r="J723" s="11"/>
       <c r="K723" s="11"/>
@@ -10169,7 +10228,7 @@
       <c r="E724" s="9"/>
       <c r="F724" s="9"/>
       <c r="G724" s="11"/>
-      <c r="H724" s="16"/>
+      <c r="H724" s="13"/>
       <c r="I724" s="11"/>
       <c r="J724" s="11"/>
       <c r="K724" s="11"/>
@@ -10182,7 +10241,7 @@
       <c r="E725" s="9"/>
       <c r="F725" s="9"/>
       <c r="G725" s="11"/>
-      <c r="H725" s="16"/>
+      <c r="H725" s="13"/>
       <c r="I725" s="11"/>
       <c r="J725" s="11"/>
       <c r="K725" s="11"/>
@@ -10195,7 +10254,7 @@
       <c r="E726" s="9"/>
       <c r="F726" s="9"/>
       <c r="G726" s="11"/>
-      <c r="H726" s="16"/>
+      <c r="H726" s="13"/>
       <c r="I726" s="11"/>
       <c r="J726" s="11"/>
       <c r="K726" s="11"/>
@@ -10208,7 +10267,7 @@
       <c r="E727" s="9"/>
       <c r="F727" s="9"/>
       <c r="G727" s="11"/>
-      <c r="H727" s="16"/>
+      <c r="H727" s="13"/>
       <c r="I727" s="11"/>
       <c r="J727" s="11"/>
       <c r="K727" s="11"/>
@@ -10221,7 +10280,7 @@
       <c r="E728" s="9"/>
       <c r="F728" s="9"/>
       <c r="G728" s="11"/>
-      <c r="H728" s="16"/>
+      <c r="H728" s="13"/>
       <c r="I728" s="11"/>
       <c r="J728" s="11"/>
       <c r="K728" s="11"/>
@@ -10234,7 +10293,7 @@
       <c r="E729" s="9"/>
       <c r="F729" s="9"/>
       <c r="G729" s="11"/>
-      <c r="H729" s="16"/>
+      <c r="H729" s="13"/>
       <c r="I729" s="11"/>
       <c r="J729" s="11"/>
       <c r="K729" s="11"/>
@@ -10247,7 +10306,7 @@
       <c r="E730" s="9"/>
       <c r="F730" s="9"/>
       <c r="G730" s="11"/>
-      <c r="H730" s="16"/>
+      <c r="H730" s="13"/>
       <c r="I730" s="11"/>
       <c r="J730" s="11"/>
       <c r="K730" s="11"/>
@@ -10260,7 +10319,7 @@
       <c r="E731" s="9"/>
       <c r="F731" s="9"/>
       <c r="G731" s="11"/>
-      <c r="H731" s="16"/>
+      <c r="H731" s="13"/>
       <c r="I731" s="11"/>
       <c r="J731" s="11"/>
       <c r="K731" s="11"/>
@@ -10273,7 +10332,7 @@
       <c r="E732" s="9"/>
       <c r="F732" s="9"/>
       <c r="G732" s="11"/>
-      <c r="H732" s="16"/>
+      <c r="H732" s="13"/>
       <c r="I732" s="11"/>
       <c r="J732" s="11"/>
       <c r="K732" s="11"/>
@@ -10286,7 +10345,7 @@
       <c r="E733" s="9"/>
       <c r="F733" s="9"/>
       <c r="G733" s="11"/>
-      <c r="H733" s="16"/>
+      <c r="H733" s="13"/>
       <c r="I733" s="11"/>
       <c r="J733" s="11"/>
       <c r="K733" s="11"/>
@@ -10299,7 +10358,7 @@
       <c r="E734" s="9"/>
       <c r="F734" s="9"/>
       <c r="G734" s="11"/>
-      <c r="H734" s="16"/>
+      <c r="H734" s="13"/>
       <c r="I734" s="11"/>
       <c r="J734" s="11"/>
       <c r="K734" s="11"/>
@@ -10312,7 +10371,7 @@
       <c r="E735" s="9"/>
       <c r="F735" s="9"/>
       <c r="G735" s="11"/>
-      <c r="H735" s="16"/>
+      <c r="H735" s="13"/>
       <c r="I735" s="11"/>
       <c r="J735" s="11"/>
       <c r="K735" s="11"/>
@@ -10325,7 +10384,7 @@
       <c r="E736" s="9"/>
       <c r="F736" s="9"/>
       <c r="G736" s="11"/>
-      <c r="H736" s="16"/>
+      <c r="H736" s="13"/>
       <c r="I736" s="11"/>
       <c r="J736" s="11"/>
       <c r="K736" s="11"/>
@@ -10338,7 +10397,7 @@
       <c r="E737" s="9"/>
       <c r="F737" s="9"/>
       <c r="G737" s="11"/>
-      <c r="H737" s="16"/>
+      <c r="H737" s="13"/>
       <c r="I737" s="11"/>
       <c r="J737" s="11"/>
       <c r="K737" s="11"/>
@@ -10351,7 +10410,7 @@
       <c r="E738" s="9"/>
       <c r="F738" s="9"/>
       <c r="G738" s="11"/>
-      <c r="H738" s="16"/>
+      <c r="H738" s="13"/>
       <c r="I738" s="11"/>
       <c r="J738" s="11"/>
       <c r="K738" s="11"/>
@@ -10364,7 +10423,7 @@
       <c r="E739" s="9"/>
       <c r="F739" s="9"/>
       <c r="G739" s="11"/>
-      <c r="H739" s="16"/>
+      <c r="H739" s="13"/>
       <c r="I739" s="11"/>
       <c r="J739" s="11"/>
       <c r="K739" s="11"/>
@@ -10377,7 +10436,7 @@
       <c r="E740" s="9"/>
       <c r="F740" s="9"/>
       <c r="G740" s="11"/>
-      <c r="H740" s="16"/>
+      <c r="H740" s="13"/>
       <c r="I740" s="11"/>
       <c r="J740" s="11"/>
       <c r="K740" s="11"/>
@@ -10390,7 +10449,7 @@
       <c r="E741" s="9"/>
       <c r="F741" s="9"/>
       <c r="G741" s="11"/>
-      <c r="H741" s="16"/>
+      <c r="H741" s="13"/>
       <c r="I741" s="11"/>
       <c r="J741" s="11"/>
       <c r="K741" s="11"/>
@@ -10403,7 +10462,7 @@
       <c r="E742" s="9"/>
       <c r="F742" s="9"/>
       <c r="G742" s="11"/>
-      <c r="H742" s="16"/>
+      <c r="H742" s="13"/>
       <c r="I742" s="11"/>
       <c r="J742" s="11"/>
       <c r="K742" s="11"/>
@@ -10416,7 +10475,7 @@
       <c r="E743" s="9"/>
       <c r="F743" s="9"/>
       <c r="G743" s="11"/>
-      <c r="H743" s="16"/>
+      <c r="H743" s="13"/>
       <c r="I743" s="11"/>
       <c r="J743" s="11"/>
       <c r="K743" s="11"/>
@@ -10429,7 +10488,7 @@
       <c r="E744" s="9"/>
       <c r="F744" s="9"/>
       <c r="G744" s="11"/>
-      <c r="H744" s="16"/>
+      <c r="H744" s="13"/>
       <c r="I744" s="11"/>
       <c r="J744" s="11"/>
       <c r="K744" s="11"/>
@@ -10442,7 +10501,7 @@
       <c r="E745" s="9"/>
       <c r="F745" s="9"/>
       <c r="G745" s="11"/>
-      <c r="H745" s="16"/>
+      <c r="H745" s="13"/>
       <c r="I745" s="11"/>
       <c r="J745" s="11"/>
       <c r="K745" s="11"/>
@@ -10455,7 +10514,7 @@
       <c r="E746" s="9"/>
       <c r="F746" s="9"/>
       <c r="G746" s="11"/>
-      <c r="H746" s="16"/>
+      <c r="H746" s="13"/>
       <c r="I746" s="11"/>
       <c r="J746" s="11"/>
       <c r="K746" s="11"/>
@@ -10468,7 +10527,7 @@
       <c r="E747" s="9"/>
       <c r="F747" s="9"/>
       <c r="G747" s="11"/>
-      <c r="H747" s="16"/>
+      <c r="H747" s="13"/>
       <c r="I747" s="11"/>
       <c r="J747" s="11"/>
       <c r="K747" s="11"/>
@@ -10481,7 +10540,7 @@
       <c r="E748" s="9"/>
       <c r="F748" s="9"/>
       <c r="G748" s="11"/>
-      <c r="H748" s="16"/>
+      <c r="H748" s="13"/>
       <c r="I748" s="11"/>
       <c r="J748" s="11"/>
       <c r="K748" s="11"/>
@@ -10494,7 +10553,7 @@
       <c r="E749" s="9"/>
       <c r="F749" s="9"/>
       <c r="G749" s="11"/>
-      <c r="H749" s="16"/>
+      <c r="H749" s="13"/>
       <c r="I749" s="11"/>
       <c r="J749" s="11"/>
       <c r="K749" s="11"/>
@@ -10507,7 +10566,7 @@
       <c r="E750" s="9"/>
       <c r="F750" s="9"/>
       <c r="G750" s="11"/>
-      <c r="H750" s="16"/>
+      <c r="H750" s="13"/>
       <c r="I750" s="11"/>
       <c r="J750" s="11"/>
       <c r="K750" s="11"/>
@@ -10520,7 +10579,7 @@
       <c r="E751" s="9"/>
       <c r="F751" s="9"/>
       <c r="G751" s="11"/>
-      <c r="H751" s="16"/>
+      <c r="H751" s="13"/>
       <c r="I751" s="11"/>
       <c r="J751" s="11"/>
       <c r="K751" s="11"/>
@@ -10533,7 +10592,7 @@
       <c r="E752" s="9"/>
       <c r="F752" s="9"/>
       <c r="G752" s="11"/>
-      <c r="H752" s="16"/>
+      <c r="H752" s="13"/>
       <c r="I752" s="11"/>
       <c r="J752" s="11"/>
       <c r="K752" s="11"/>
@@ -10546,7 +10605,7 @@
       <c r="E753" s="9"/>
       <c r="F753" s="9"/>
       <c r="G753" s="11"/>
-      <c r="H753" s="16"/>
+      <c r="H753" s="13"/>
       <c r="I753" s="11"/>
       <c r="J753" s="11"/>
       <c r="K753" s="11"/>
@@ -10559,7 +10618,7 @@
       <c r="E754" s="9"/>
       <c r="F754" s="9"/>
       <c r="G754" s="11"/>
-      <c r="H754" s="16"/>
+      <c r="H754" s="13"/>
       <c r="I754" s="11"/>
       <c r="J754" s="11"/>
       <c r="K754" s="11"/>
@@ -10572,7 +10631,7 @@
       <c r="E755" s="9"/>
       <c r="F755" s="9"/>
       <c r="G755" s="11"/>
-      <c r="H755" s="16"/>
+      <c r="H755" s="13"/>
       <c r="I755" s="11"/>
       <c r="J755" s="11"/>
       <c r="K755" s="11"/>
@@ -10585,7 +10644,7 @@
       <c r="E756" s="9"/>
       <c r="F756" s="9"/>
       <c r="G756" s="11"/>
-      <c r="H756" s="16"/>
+      <c r="H756" s="13"/>
       <c r="I756" s="11"/>
       <c r="J756" s="11"/>
       <c r="K756" s="11"/>
@@ -10598,7 +10657,7 @@
       <c r="E757" s="9"/>
       <c r="F757" s="9"/>
       <c r="G757" s="11"/>
-      <c r="H757" s="16"/>
+      <c r="H757" s="13"/>
       <c r="I757" s="11"/>
       <c r="J757" s="11"/>
       <c r="K757" s="11"/>
@@ -10611,7 +10670,7 @@
       <c r="E758" s="9"/>
       <c r="F758" s="9"/>
       <c r="G758" s="11"/>
-      <c r="H758" s="16"/>
+      <c r="H758" s="13"/>
       <c r="I758" s="11"/>
       <c r="J758" s="11"/>
       <c r="K758" s="11"/>
@@ -10624,7 +10683,7 @@
       <c r="E759" s="9"/>
       <c r="F759" s="9"/>
       <c r="G759" s="11"/>
-      <c r="H759" s="16"/>
+      <c r="H759" s="13"/>
       <c r="I759" s="11"/>
       <c r="J759" s="11"/>
       <c r="K759" s="11"/>
@@ -10637,7 +10696,7 @@
       <c r="E760" s="9"/>
       <c r="F760" s="9"/>
       <c r="G760" s="11"/>
-      <c r="H760" s="16"/>
+      <c r="H760" s="13"/>
       <c r="I760" s="11"/>
       <c r="J760" s="11"/>
       <c r="K760" s="11"/>
@@ -10650,7 +10709,7 @@
       <c r="E761" s="9"/>
       <c r="F761" s="9"/>
       <c r="G761" s="11"/>
-      <c r="H761" s="16"/>
+      <c r="H761" s="13"/>
       <c r="I761" s="11"/>
       <c r="J761" s="11"/>
       <c r="K761" s="11"/>
@@ -10663,7 +10722,7 @@
       <c r="E762" s="9"/>
       <c r="F762" s="9"/>
       <c r="G762" s="11"/>
-      <c r="H762" s="16"/>
+      <c r="H762" s="13"/>
       <c r="I762" s="11"/>
       <c r="J762" s="11"/>
       <c r="K762" s="11"/>
@@ -10676,7 +10735,7 @@
       <c r="E763" s="9"/>
       <c r="F763" s="9"/>
       <c r="G763" s="11"/>
-      <c r="H763" s="16"/>
+      <c r="H763" s="13"/>
       <c r="I763" s="11"/>
       <c r="J763" s="11"/>
       <c r="K763" s="11"/>
@@ -10689,7 +10748,7 @@
       <c r="E764" s="9"/>
       <c r="F764" s="9"/>
       <c r="G764" s="11"/>
-      <c r="H764" s="16"/>
+      <c r="H764" s="13"/>
       <c r="I764" s="11"/>
       <c r="J764" s="11"/>
       <c r="K764" s="11"/>
@@ -10702,7 +10761,7 @@
       <c r="E765" s="9"/>
       <c r="F765" s="9"/>
       <c r="G765" s="11"/>
-      <c r="H765" s="16"/>
+      <c r="H765" s="13"/>
       <c r="I765" s="11"/>
       <c r="J765" s="11"/>
       <c r="K765" s="11"/>
@@ -10715,7 +10774,7 @@
       <c r="E766" s="9"/>
       <c r="F766" s="9"/>
       <c r="G766" s="11"/>
-      <c r="H766" s="16"/>
+      <c r="H766" s="13"/>
       <c r="I766" s="11"/>
       <c r="J766" s="11"/>
       <c r="K766" s="11"/>
@@ -10728,7 +10787,7 @@
       <c r="E767" s="9"/>
       <c r="F767" s="9"/>
       <c r="G767" s="11"/>
-      <c r="H767" s="16"/>
+      <c r="H767" s="13"/>
       <c r="I767" s="11"/>
       <c r="J767" s="11"/>
       <c r="K767" s="11"/>
@@ -10741,7 +10800,7 @@
       <c r="E768" s="9"/>
       <c r="F768" s="9"/>
       <c r="G768" s="11"/>
-      <c r="H768" s="16"/>
+      <c r="H768" s="13"/>
       <c r="I768" s="11"/>
       <c r="J768" s="11"/>
       <c r="K768" s="11"/>
@@ -10754,7 +10813,7 @@
       <c r="E769" s="9"/>
       <c r="F769" s="9"/>
       <c r="G769" s="11"/>
-      <c r="H769" s="16"/>
+      <c r="H769" s="13"/>
       <c r="I769" s="11"/>
       <c r="J769" s="11"/>
       <c r="K769" s="11"/>
@@ -10767,7 +10826,7 @@
       <c r="E770" s="9"/>
       <c r="F770" s="9"/>
       <c r="G770" s="11"/>
-      <c r="H770" s="16"/>
+      <c r="H770" s="13"/>
       <c r="I770" s="11"/>
       <c r="J770" s="11"/>
       <c r="K770" s="11"/>
@@ -10780,7 +10839,7 @@
       <c r="E771" s="9"/>
       <c r="F771" s="9"/>
       <c r="G771" s="11"/>
-      <c r="H771" s="16"/>
+      <c r="H771" s="13"/>
       <c r="I771" s="11"/>
       <c r="J771" s="11"/>
       <c r="K771" s="11"/>
@@ -10793,7 +10852,7 @@
       <c r="E772" s="9"/>
       <c r="F772" s="9"/>
       <c r="G772" s="11"/>
-      <c r="H772" s="16"/>
+      <c r="H772" s="13"/>
       <c r="I772" s="11"/>
       <c r="J772" s="11"/>
       <c r="K772" s="11"/>
@@ -10806,7 +10865,7 @@
       <c r="E773" s="9"/>
       <c r="F773" s="9"/>
       <c r="G773" s="11"/>
-      <c r="H773" s="16"/>
+      <c r="H773" s="13"/>
       <c r="I773" s="11"/>
       <c r="J773" s="11"/>
       <c r="K773" s="11"/>
@@ -10819,7 +10878,7 @@
       <c r="E774" s="9"/>
       <c r="F774" s="9"/>
       <c r="G774" s="11"/>
-      <c r="H774" s="16"/>
+      <c r="H774" s="13"/>
       <c r="I774" s="11"/>
       <c r="J774" s="11"/>
       <c r="K774" s="11"/>
@@ -10832,7 +10891,7 @@
       <c r="E775" s="9"/>
       <c r="F775" s="9"/>
       <c r="G775" s="11"/>
-      <c r="H775" s="16"/>
+      <c r="H775" s="13"/>
       <c r="I775" s="11"/>
       <c r="J775" s="11"/>
       <c r="K775" s="11"/>
@@ -10845,7 +10904,7 @@
       <c r="E776" s="9"/>
       <c r="F776" s="9"/>
       <c r="G776" s="11"/>
-      <c r="H776" s="16"/>
+      <c r="H776" s="13"/>
       <c r="I776" s="11"/>
       <c r="J776" s="11"/>
       <c r="K776" s="11"/>
@@ -10858,7 +10917,7 @@
       <c r="E777" s="9"/>
       <c r="F777" s="9"/>
       <c r="G777" s="11"/>
-      <c r="H777" s="16"/>
+      <c r="H777" s="13"/>
       <c r="I777" s="11"/>
       <c r="J777" s="11"/>
       <c r="K777" s="11"/>
@@ -10871,7 +10930,7 @@
       <c r="E778" s="9"/>
       <c r="F778" s="9"/>
       <c r="G778" s="11"/>
-      <c r="H778" s="16"/>
+      <c r="H778" s="13"/>
       <c r="I778" s="11"/>
       <c r="J778" s="11"/>
       <c r="K778" s="11"/>
@@ -10884,7 +10943,7 @@
       <c r="E779" s="9"/>
       <c r="F779" s="9"/>
       <c r="G779" s="11"/>
-      <c r="H779" s="16"/>
+      <c r="H779" s="13"/>
       <c r="I779" s="11"/>
       <c r="J779" s="11"/>
       <c r="K779" s="11"/>
@@ -10897,7 +10956,7 @@
       <c r="E780" s="9"/>
       <c r="F780" s="9"/>
       <c r="G780" s="11"/>
-      <c r="H780" s="16"/>
+      <c r="H780" s="13"/>
       <c r="I780" s="11"/>
       <c r="J780" s="11"/>
       <c r="K780" s="11"/>
@@ -10910,7 +10969,7 @@
       <c r="E781" s="9"/>
       <c r="F781" s="9"/>
       <c r="G781" s="11"/>
-      <c r="H781" s="16"/>
+      <c r="H781" s="13"/>
       <c r="I781" s="11"/>
       <c r="J781" s="11"/>
       <c r="K781" s="11"/>
@@ -10923,7 +10982,7 @@
       <c r="E782" s="9"/>
       <c r="F782" s="9"/>
       <c r="G782" s="11"/>
-      <c r="H782" s="16"/>
+      <c r="H782" s="13"/>
       <c r="I782" s="11"/>
       <c r="J782" s="11"/>
       <c r="K782" s="11"/>
@@ -10936,7 +10995,7 @@
       <c r="E783" s="9"/>
       <c r="F783" s="9"/>
       <c r="G783" s="11"/>
-      <c r="H783" s="16"/>
+      <c r="H783" s="13"/>
       <c r="I783" s="11"/>
       <c r="J783" s="11"/>
       <c r="K783" s="11"/>
@@ -10949,7 +11008,7 @@
       <c r="E784" s="9"/>
       <c r="F784" s="9"/>
       <c r="G784" s="11"/>
-      <c r="H784" s="16"/>
+      <c r="H784" s="13"/>
       <c r="I784" s="11"/>
       <c r="J784" s="11"/>
       <c r="K784" s="11"/>
@@ -10962,7 +11021,7 @@
       <c r="E785" s="9"/>
       <c r="F785" s="9"/>
       <c r="G785" s="11"/>
-      <c r="H785" s="16"/>
+      <c r="H785" s="13"/>
       <c r="I785" s="11"/>
       <c r="J785" s="11"/>
       <c r="K785" s="11"/>
@@ -10975,7 +11034,7 @@
       <c r="E786" s="9"/>
       <c r="F786" s="9"/>
       <c r="G786" s="11"/>
-      <c r="H786" s="16"/>
+      <c r="H786" s="13"/>
       <c r="I786" s="11"/>
       <c r="J786" s="11"/>
       <c r="K786" s="11"/>
@@ -10988,7 +11047,7 @@
       <c r="E787" s="9"/>
       <c r="F787" s="9"/>
       <c r="G787" s="11"/>
-      <c r="H787" s="16"/>
+      <c r="H787" s="13"/>
       <c r="I787" s="11"/>
       <c r="J787" s="11"/>
       <c r="K787" s="11"/>
@@ -11001,7 +11060,7 @@
       <c r="E788" s="9"/>
       <c r="F788" s="9"/>
       <c r="G788" s="11"/>
-      <c r="H788" s="16"/>
+      <c r="H788" s="13"/>
       <c r="I788" s="11"/>
       <c r="J788" s="11"/>
       <c r="K788" s="11"/>
@@ -11014,7 +11073,7 @@
       <c r="E789" s="9"/>
       <c r="F789" s="9"/>
       <c r="G789" s="11"/>
-      <c r="H789" s="16"/>
+      <c r="H789" s="13"/>
       <c r="I789" s="11"/>
       <c r="J789" s="11"/>
       <c r="K789" s="11"/>
@@ -11027,7 +11086,7 @@
       <c r="E790" s="9"/>
       <c r="F790" s="9"/>
       <c r="G790" s="11"/>
-      <c r="H790" s="16"/>
+      <c r="H790" s="13"/>
       <c r="I790" s="11"/>
       <c r="J790" s="11"/>
       <c r="K790" s="11"/>
@@ -11040,7 +11099,7 @@
       <c r="E791" s="9"/>
       <c r="F791" s="9"/>
       <c r="G791" s="11"/>
-      <c r="H791" s="16"/>
+      <c r="H791" s="13"/>
       <c r="I791" s="11"/>
       <c r="J791" s="11"/>
       <c r="K791" s="11"/>
@@ -11053,7 +11112,7 @@
       <c r="E792" s="9"/>
       <c r="F792" s="9"/>
       <c r="G792" s="11"/>
-      <c r="H792" s="16"/>
+      <c r="H792" s="13"/>
       <c r="I792" s="11"/>
       <c r="J792" s="11"/>
       <c r="K792" s="11"/>
@@ -11066,7 +11125,7 @@
       <c r="E793" s="9"/>
       <c r="F793" s="9"/>
       <c r="G793" s="11"/>
-      <c r="H793" s="16"/>
+      <c r="H793" s="13"/>
       <c r="I793" s="11"/>
       <c r="J793" s="11"/>
       <c r="K793" s="11"/>
@@ -11079,7 +11138,7 @@
       <c r="E794" s="9"/>
       <c r="F794" s="9"/>
       <c r="G794" s="11"/>
-      <c r="H794" s="16"/>
+      <c r="H794" s="13"/>
       <c r="I794" s="11"/>
       <c r="J794" s="11"/>
       <c r="K794" s="11"/>
@@ -11092,7 +11151,7 @@
       <c r="E795" s="9"/>
       <c r="F795" s="9"/>
       <c r="G795" s="11"/>
-      <c r="H795" s="16"/>
+      <c r="H795" s="13"/>
       <c r="I795" s="11"/>
       <c r="J795" s="11"/>
       <c r="K795" s="11"/>
@@ -11105,7 +11164,7 @@
       <c r="E796" s="9"/>
       <c r="F796" s="9"/>
       <c r="G796" s="11"/>
-      <c r="H796" s="16"/>
+      <c r="H796" s="13"/>
       <c r="I796" s="11"/>
       <c r="J796" s="11"/>
       <c r="K796" s="11"/>
@@ -11118,7 +11177,7 @@
       <c r="E797" s="9"/>
       <c r="F797" s="9"/>
       <c r="G797" s="11"/>
-      <c r="H797" s="16"/>
+      <c r="H797" s="13"/>
       <c r="I797" s="11"/>
       <c r="J797" s="11"/>
       <c r="K797" s="11"/>
@@ -11131,7 +11190,7 @@
       <c r="E798" s="9"/>
       <c r="F798" s="9"/>
       <c r="G798" s="11"/>
-      <c r="H798" s="16"/>
+      <c r="H798" s="13"/>
       <c r="I798" s="11"/>
       <c r="J798" s="11"/>
       <c r="K798" s="11"/>
@@ -11144,7 +11203,7 @@
       <c r="E799" s="9"/>
       <c r="F799" s="9"/>
       <c r="G799" s="11"/>
-      <c r="H799" s="16"/>
+      <c r="H799" s="13"/>
       <c r="I799" s="11"/>
       <c r="J799" s="11"/>
       <c r="K799" s="11"/>
@@ -11157,7 +11216,7 @@
       <c r="E800" s="9"/>
       <c r="F800" s="9"/>
       <c r="G800" s="11"/>
-      <c r="H800" s="16"/>
+      <c r="H800" s="13"/>
       <c r="I800" s="11"/>
       <c r="J800" s="11"/>
       <c r="K800" s="11"/>
@@ -11170,7 +11229,7 @@
       <c r="E801" s="9"/>
       <c r="F801" s="9"/>
       <c r="G801" s="11"/>
-      <c r="H801" s="16"/>
+      <c r="H801" s="13"/>
       <c r="I801" s="11"/>
       <c r="J801" s="11"/>
       <c r="K801" s="11"/>
@@ -11183,7 +11242,7 @@
       <c r="E802" s="9"/>
       <c r="F802" s="9"/>
       <c r="G802" s="11"/>
-      <c r="H802" s="16"/>
+      <c r="H802" s="13"/>
       <c r="I802" s="11"/>
       <c r="J802" s="11"/>
       <c r="K802" s="11"/>
@@ -11196,7 +11255,7 @@
       <c r="E803" s="9"/>
       <c r="F803" s="9"/>
       <c r="G803" s="11"/>
-      <c r="H803" s="16"/>
+      <c r="H803" s="13"/>
       <c r="I803" s="11"/>
       <c r="J803" s="11"/>
       <c r="K803" s="11"/>
@@ -11209,7 +11268,7 @@
       <c r="E804" s="9"/>
       <c r="F804" s="9"/>
       <c r="G804" s="11"/>
-      <c r="H804" s="16"/>
+      <c r="H804" s="13"/>
       <c r="I804" s="11"/>
       <c r="J804" s="11"/>
       <c r="K804" s="11"/>
@@ -11222,7 +11281,7 @@
       <c r="E805" s="9"/>
       <c r="F805" s="9"/>
       <c r="G805" s="11"/>
-      <c r="H805" s="16"/>
+      <c r="H805" s="13"/>
       <c r="I805" s="11"/>
       <c r="J805" s="11"/>
       <c r="K805" s="11"/>
@@ -11235,7 +11294,7 @@
       <c r="E806" s="9"/>
       <c r="F806" s="9"/>
       <c r="G806" s="11"/>
-      <c r="H806" s="16"/>
+      <c r="H806" s="13"/>
       <c r="I806" s="11"/>
       <c r="J806" s="11"/>
       <c r="K806" s="11"/>
@@ -11248,7 +11307,7 @@
       <c r="E807" s="9"/>
       <c r="F807" s="9"/>
       <c r="G807" s="11"/>
-      <c r="H807" s="16"/>
+      <c r="H807" s="13"/>
       <c r="I807" s="11"/>
       <c r="J807" s="11"/>
       <c r="K807" s="11"/>
@@ -11261,7 +11320,7 @@
       <c r="E808" s="9"/>
       <c r="F808" s="9"/>
       <c r="G808" s="11"/>
-      <c r="H808" s="16"/>
+      <c r="H808" s="13"/>
       <c r="I808" s="11"/>
       <c r="J808" s="11"/>
       <c r="K808" s="11"/>
@@ -11274,7 +11333,7 @@
       <c r="E809" s="9"/>
       <c r="F809" s="9"/>
       <c r="G809" s="11"/>
-      <c r="H809" s="16"/>
+      <c r="H809" s="13"/>
       <c r="I809" s="11"/>
       <c r="J809" s="11"/>
       <c r="K809" s="11"/>
@@ -11287,7 +11346,7 @@
       <c r="E810" s="9"/>
       <c r="F810" s="9"/>
       <c r="G810" s="11"/>
-      <c r="H810" s="16"/>
+      <c r="H810" s="13"/>
       <c r="I810" s="11"/>
       <c r="J810" s="11"/>
       <c r="K810" s="11"/>
@@ -11300,7 +11359,7 @@
       <c r="E811" s="9"/>
       <c r="F811" s="9"/>
       <c r="G811" s="11"/>
-      <c r="H811" s="16"/>
+      <c r="H811" s="13"/>
       <c r="I811" s="11"/>
       <c r="J811" s="11"/>
       <c r="K811" s="11"/>
@@ -11313,7 +11372,7 @@
       <c r="E812" s="9"/>
       <c r="F812" s="9"/>
       <c r="G812" s="11"/>
-      <c r="H812" s="16"/>
+      <c r="H812" s="13"/>
       <c r="I812" s="11"/>
       <c r="J812" s="11"/>
       <c r="K812" s="11"/>
@@ -11326,7 +11385,7 @@
       <c r="E813" s="9"/>
       <c r="F813" s="9"/>
       <c r="G813" s="11"/>
-      <c r="H813" s="16"/>
+      <c r="H813" s="13"/>
       <c r="I813" s="11"/>
       <c r="J813" s="11"/>
       <c r="K813" s="11"/>
@@ -11339,7 +11398,7 @@
       <c r="E814" s="9"/>
       <c r="F814" s="9"/>
       <c r="G814" s="11"/>
-      <c r="H814" s="16"/>
+      <c r="H814" s="13"/>
       <c r="I814" s="11"/>
       <c r="J814" s="11"/>
       <c r="K814" s="11"/>
@@ -11352,7 +11411,7 @@
       <c r="E815" s="9"/>
       <c r="F815" s="9"/>
       <c r="G815" s="11"/>
-      <c r="H815" s="16"/>
+      <c r="H815" s="13"/>
       <c r="I815" s="11"/>
       <c r="J815" s="11"/>
       <c r="K815" s="11"/>
@@ -11365,7 +11424,7 @@
       <c r="E816" s="9"/>
       <c r="F816" s="9"/>
       <c r="G816" s="11"/>
-      <c r="H816" s="16"/>
+      <c r="H816" s="13"/>
       <c r="I816" s="11"/>
       <c r="J816" s="11"/>
       <c r="K816" s="11"/>
@@ -11378,7 +11437,7 @@
       <c r="E817" s="9"/>
       <c r="F817" s="9"/>
       <c r="G817" s="11"/>
-      <c r="H817" s="16"/>
+      <c r="H817" s="13"/>
       <c r="I817" s="11"/>
       <c r="J817" s="11"/>
       <c r="K817" s="11"/>
@@ -11391,7 +11450,7 @@
       <c r="E818" s="9"/>
       <c r="F818" s="9"/>
       <c r="G818" s="11"/>
-      <c r="H818" s="16"/>
+      <c r="H818" s="13"/>
       <c r="I818" s="11"/>
       <c r="J818" s="11"/>
       <c r="K818" s="11"/>
@@ -11404,7 +11463,7 @@
       <c r="E819" s="9"/>
       <c r="F819" s="9"/>
       <c r="G819" s="11"/>
-      <c r="H819" s="16"/>
+      <c r="H819" s="13"/>
       <c r="I819" s="11"/>
       <c r="J819" s="11"/>
       <c r="K819" s="11"/>
@@ -11417,7 +11476,7 @@
       <c r="E820" s="9"/>
       <c r="F820" s="9"/>
       <c r="G820" s="11"/>
-      <c r="H820" s="16"/>
+      <c r="H820" s="13"/>
       <c r="I820" s="11"/>
       <c r="J820" s="11"/>
       <c r="K820" s="11"/>
@@ -11430,7 +11489,7 @@
       <c r="E821" s="9"/>
       <c r="F821" s="9"/>
       <c r="G821" s="11"/>
-      <c r="H821" s="16"/>
+      <c r="H821" s="13"/>
       <c r="I821" s="11"/>
       <c r="J821" s="11"/>
       <c r="K821" s="11"/>
@@ -11443,7 +11502,7 @@
       <c r="E822" s="9"/>
       <c r="F822" s="9"/>
       <c r="G822" s="11"/>
-      <c r="H822" s="16"/>
+      <c r="H822" s="13"/>
       <c r="I822" s="11"/>
       <c r="J822" s="11"/>
       <c r="K822" s="11"/>
@@ -11456,7 +11515,7 @@
       <c r="E823" s="9"/>
       <c r="F823" s="9"/>
       <c r="G823" s="11"/>
-      <c r="H823" s="16"/>
+      <c r="H823" s="13"/>
       <c r="I823" s="11"/>
       <c r="J823" s="11"/>
       <c r="K823" s="11"/>
@@ -11469,7 +11528,7 @@
       <c r="E824" s="9"/>
       <c r="F824" s="9"/>
       <c r="G824" s="11"/>
-      <c r="H824" s="16"/>
+      <c r="H824" s="13"/>
       <c r="I824" s="11"/>
       <c r="J824" s="11"/>
       <c r="K824" s="11"/>
@@ -11482,7 +11541,7 @@
       <c r="E825" s="9"/>
       <c r="F825" s="9"/>
       <c r="G825" s="11"/>
-      <c r="H825" s="16"/>
+      <c r="H825" s="13"/>
       <c r="I825" s="11"/>
       <c r="J825" s="11"/>
       <c r="K825" s="11"/>
@@ -11495,7 +11554,7 @@
       <c r="E826" s="9"/>
       <c r="F826" s="9"/>
       <c r="G826" s="11"/>
-      <c r="H826" s="16"/>
+      <c r="H826" s="13"/>
       <c r="I826" s="11"/>
       <c r="J826" s="11"/>
       <c r="K826" s="11"/>
@@ -11508,7 +11567,7 @@
       <c r="E827" s="9"/>
       <c r="F827" s="9"/>
       <c r="G827" s="11"/>
-      <c r="H827" s="16"/>
+      <c r="H827" s="13"/>
       <c r="I827" s="11"/>
       <c r="J827" s="11"/>
       <c r="K827" s="11"/>
@@ -11521,7 +11580,7 @@
       <c r="E828" s="9"/>
       <c r="F828" s="9"/>
       <c r="G828" s="11"/>
-      <c r="H828" s="16"/>
+      <c r="H828" s="13"/>
       <c r="I828" s="11"/>
       <c r="J828" s="11"/>
       <c r="K828" s="11"/>
@@ -11534,7 +11593,7 @@
       <c r="E829" s="9"/>
       <c r="F829" s="9"/>
       <c r="G829" s="11"/>
-      <c r="H829" s="16"/>
+      <c r="H829" s="13"/>
       <c r="I829" s="11"/>
       <c r="J829" s="11"/>
       <c r="K829" s="11"/>
@@ -11547,7 +11606,7 @@
       <c r="E830" s="9"/>
       <c r="F830" s="9"/>
       <c r="G830" s="11"/>
-      <c r="H830" s="16"/>
+      <c r="H830" s="13"/>
       <c r="I830" s="11"/>
       <c r="J830" s="11"/>
       <c r="K830" s="11"/>
@@ -11560,7 +11619,7 @@
       <c r="E831" s="9"/>
       <c r="F831" s="9"/>
       <c r="G831" s="11"/>
-      <c r="H831" s="16"/>
+      <c r="H831" s="13"/>
       <c r="I831" s="11"/>
       <c r="J831" s="11"/>
       <c r="K831" s="11"/>
@@ -11573,7 +11632,7 @@
       <c r="E832" s="9"/>
       <c r="F832" s="9"/>
       <c r="G832" s="11"/>
-      <c r="H832" s="16"/>
+      <c r="H832" s="13"/>
       <c r="I832" s="11"/>
       <c r="J832" s="11"/>
       <c r="K832" s="11"/>
@@ -11586,7 +11645,7 @@
       <c r="E833" s="9"/>
       <c r="F833" s="9"/>
       <c r="G833" s="11"/>
-      <c r="H833" s="16"/>
+      <c r="H833" s="13"/>
       <c r="I833" s="11"/>
       <c r="J833" s="11"/>
       <c r="K833" s="11"/>
@@ -11599,7 +11658,7 @@
       <c r="E834" s="9"/>
       <c r="F834" s="9"/>
       <c r="G834" s="11"/>
-      <c r="H834" s="16"/>
+      <c r="H834" s="13"/>
       <c r="I834" s="11"/>
       <c r="J834" s="11"/>
       <c r="K834" s="11"/>
@@ -11612,7 +11671,7 @@
       <c r="E835" s="9"/>
       <c r="F835" s="9"/>
       <c r="G835" s="11"/>
-      <c r="H835" s="16"/>
+      <c r="H835" s="13"/>
       <c r="I835" s="11"/>
       <c r="J835" s="11"/>
       <c r="K835" s="11"/>
@@ -11625,7 +11684,7 @@
       <c r="E836" s="9"/>
       <c r="F836" s="9"/>
       <c r="G836" s="11"/>
-      <c r="H836" s="16"/>
+      <c r="H836" s="13"/>
       <c r="I836" s="11"/>
       <c r="J836" s="11"/>
       <c r="K836" s="11"/>
@@ -11638,7 +11697,7 @@
       <c r="E837" s="9"/>
       <c r="F837" s="9"/>
       <c r="G837" s="11"/>
-      <c r="H837" s="16"/>
+      <c r="H837" s="13"/>
       <c r="I837" s="11"/>
       <c r="J837" s="11"/>
       <c r="K837" s="11"/>
@@ -11651,7 +11710,7 @@
       <c r="E838" s="9"/>
       <c r="F838" s="9"/>
       <c r="G838" s="11"/>
-      <c r="H838" s="16"/>
+      <c r="H838" s="13"/>
       <c r="I838" s="11"/>
       <c r="J838" s="11"/>
       <c r="K838" s="11"/>
@@ -11664,7 +11723,7 @@
       <c r="E839" s="9"/>
       <c r="F839" s="9"/>
       <c r="G839" s="11"/>
-      <c r="H839" s="16"/>
+      <c r="H839" s="13"/>
       <c r="I839" s="11"/>
       <c r="J839" s="11"/>
       <c r="K839" s="11"/>
@@ -11677,7 +11736,7 @@
       <c r="E840" s="9"/>
       <c r="F840" s="9"/>
       <c r="G840" s="11"/>
-      <c r="H840" s="16"/>
+      <c r="H840" s="13"/>
       <c r="I840" s="11"/>
       <c r="J840" s="11"/>
       <c r="K840" s="11"/>
@@ -11690,7 +11749,7 @@
       <c r="E841" s="9"/>
       <c r="F841" s="9"/>
       <c r="G841" s="11"/>
-      <c r="H841" s="16"/>
+      <c r="H841" s="13"/>
       <c r="I841" s="11"/>
       <c r="J841" s="11"/>
       <c r="K841" s="11"/>
@@ -11703,7 +11762,7 @@
       <c r="E842" s="9"/>
       <c r="F842" s="9"/>
       <c r="G842" s="11"/>
-      <c r="H842" s="16"/>
+      <c r="H842" s="13"/>
       <c r="I842" s="11"/>
       <c r="J842" s="11"/>
       <c r="K842" s="11"/>
@@ -11716,7 +11775,7 @@
       <c r="E843" s="9"/>
       <c r="F843" s="9"/>
       <c r="G843" s="11"/>
-      <c r="H843" s="16"/>
+      <c r="H843" s="13"/>
       <c r="I843" s="11"/>
       <c r="J843" s="11"/>
       <c r="K843" s="11"/>
@@ -11729,7 +11788,7 @@
       <c r="E844" s="9"/>
       <c r="F844" s="9"/>
       <c r="G844" s="11"/>
-      <c r="H844" s="16"/>
+      <c r="H844" s="13"/>
       <c r="I844" s="11"/>
       <c r="J844" s="11"/>
       <c r="K844" s="11"/>
@@ -11742,7 +11801,7 @@
       <c r="E845" s="9"/>
       <c r="F845" s="9"/>
       <c r="G845" s="11"/>
-      <c r="H845" s="16"/>
+      <c r="H845" s="13"/>
       <c r="I845" s="11"/>
       <c r="J845" s="11"/>
       <c r="K845" s="11"/>
@@ -11755,7 +11814,7 @@
       <c r="E846" s="9"/>
       <c r="F846" s="9"/>
       <c r="G846" s="11"/>
-      <c r="H846" s="16"/>
+      <c r="H846" s="13"/>
       <c r="I846" s="11"/>
       <c r="J846" s="11"/>
       <c r="K846" s="11"/>
@@ -11768,7 +11827,7 @@
       <c r="E847" s="9"/>
       <c r="F847" s="9"/>
       <c r="G847" s="11"/>
-      <c r="H847" s="16"/>
+      <c r="H847" s="13"/>
       <c r="I847" s="11"/>
       <c r="J847" s="11"/>
       <c r="K847" s="11"/>
@@ -11781,7 +11840,7 @@
       <c r="E848" s="9"/>
       <c r="F848" s="9"/>
       <c r="G848" s="11"/>
-      <c r="H848" s="16"/>
+      <c r="H848" s="13"/>
       <c r="I848" s="11"/>
       <c r="J848" s="11"/>
       <c r="K848" s="11"/>
@@ -11794,7 +11853,7 @@
       <c r="E849" s="9"/>
       <c r="F849" s="9"/>
       <c r="G849" s="11"/>
-      <c r="H849" s="16"/>
+      <c r="H849" s="13"/>
       <c r="I849" s="11"/>
       <c r="J849" s="11"/>
       <c r="K849" s="11"/>
@@ -11807,7 +11866,7 @@
       <c r="E850" s="9"/>
       <c r="F850" s="9"/>
       <c r="G850" s="11"/>
-      <c r="H850" s="16"/>
+      <c r="H850" s="13"/>
       <c r="I850" s="11"/>
       <c r="J850" s="11"/>
       <c r="K850" s="11"/>
@@ -11820,7 +11879,7 @@
       <c r="E851" s="9"/>
       <c r="F851" s="9"/>
       <c r="G851" s="11"/>
-      <c r="H851" s="16"/>
+      <c r="H851" s="13"/>
       <c r="I851" s="11"/>
       <c r="J851" s="11"/>
       <c r="K851" s="11"/>
@@ -11833,7 +11892,7 @@
       <c r="E852" s="9"/>
       <c r="F852" s="9"/>
       <c r="G852" s="11"/>
-      <c r="H852" s="16"/>
+      <c r="H852" s="13"/>
       <c r="I852" s="11"/>
       <c r="J852" s="11"/>
       <c r="K852" s="11"/>
@@ -11846,7 +11905,7 @@
       <c r="E853" s="9"/>
       <c r="F853" s="9"/>
       <c r="G853" s="11"/>
-      <c r="H853" s="16"/>
+      <c r="H853" s="13"/>
       <c r="I853" s="11"/>
       <c r="J853" s="11"/>
       <c r="K853" s="11"/>
@@ -11859,7 +11918,7 @@
       <c r="E854" s="9"/>
       <c r="F854" s="9"/>
       <c r="G854" s="11"/>
-      <c r="H854" s="16"/>
+      <c r="H854" s="13"/>
       <c r="I854" s="11"/>
       <c r="J854" s="11"/>
       <c r="K854" s="11"/>
@@ -11872,7 +11931,7 @@
       <c r="E855" s="9"/>
       <c r="F855" s="9"/>
       <c r="G855" s="11"/>
-      <c r="H855" s="16"/>
+      <c r="H855" s="13"/>
       <c r="I855" s="11"/>
       <c r="J855" s="11"/>
       <c r="K855" s="11"/>
@@ -11885,7 +11944,7 @@
       <c r="E856" s="9"/>
       <c r="F856" s="9"/>
       <c r="G856" s="11"/>
-      <c r="H856" s="16"/>
+      <c r="H856" s="13"/>
       <c r="I856" s="11"/>
       <c r="J856" s="11"/>
       <c r="K856" s="11"/>
@@ -11898,7 +11957,7 @@
       <c r="E857" s="9"/>
       <c r="F857" s="9"/>
       <c r="G857" s="11"/>
-      <c r="H857" s="16"/>
+      <c r="H857" s="13"/>
       <c r="I857" s="11"/>
       <c r="J857" s="11"/>
       <c r="K857" s="11"/>
@@ -11911,7 +11970,7 @@
       <c r="E858" s="9"/>
       <c r="F858" s="9"/>
       <c r="G858" s="11"/>
-      <c r="H858" s="16"/>
+      <c r="H858" s="13"/>
       <c r="I858" s="11"/>
       <c r="J858" s="11"/>
       <c r="K858" s="11"/>
@@ -11924,7 +11983,7 @@
       <c r="E859" s="9"/>
       <c r="F859" s="9"/>
       <c r="G859" s="11"/>
-      <c r="H859" s="16"/>
+      <c r="H859" s="13"/>
       <c r="I859" s="11"/>
       <c r="J859" s="11"/>
       <c r="K859" s="11"/>
@@ -11937,7 +11996,7 @@
       <c r="E860" s="9"/>
       <c r="F860" s="9"/>
       <c r="G860" s="11"/>
-      <c r="H860" s="16"/>
+      <c r="H860" s="13"/>
       <c r="I860" s="11"/>
       <c r="J860" s="11"/>
       <c r="K860" s="11"/>
@@ -11950,7 +12009,7 @@
       <c r="E861" s="9"/>
       <c r="F861" s="9"/>
       <c r="G861" s="11"/>
-      <c r="H861" s="16"/>
+      <c r="H861" s="13"/>
       <c r="I861" s="11"/>
       <c r="J861" s="11"/>
       <c r="K861" s="11"/>
@@ -11963,7 +12022,7 @@
       <c r="E862" s="9"/>
       <c r="F862" s="9"/>
       <c r="G862" s="11"/>
-      <c r="H862" s="16"/>
+      <c r="H862" s="13"/>
       <c r="I862" s="11"/>
       <c r="J862" s="11"/>
       <c r="K862" s="11"/>
@@ -11976,7 +12035,7 @@
       <c r="E863" s="9"/>
       <c r="F863" s="9"/>
       <c r="G863" s="11"/>
-      <c r="H863" s="16"/>
+      <c r="H863" s="13"/>
       <c r="I863" s="11"/>
       <c r="J863" s="11"/>
       <c r="K863" s="11"/>
@@ -11989,7 +12048,7 @@
       <c r="E864" s="9"/>
       <c r="F864" s="9"/>
       <c r="G864" s="11"/>
-      <c r="H864" s="16"/>
+      <c r="H864" s="13"/>
       <c r="I864" s="11"/>
       <c r="J864" s="11"/>
       <c r="K864" s="11"/>
@@ -12002,7 +12061,7 @@
       <c r="E865" s="9"/>
       <c r="F865" s="9"/>
       <c r="G865" s="11"/>
-      <c r="H865" s="16"/>
+      <c r="H865" s="13"/>
       <c r="I865" s="11"/>
       <c r="J865" s="11"/>
       <c r="K865" s="11"/>
@@ -12015,7 +12074,7 @@
       <c r="E866" s="9"/>
       <c r="F866" s="9"/>
       <c r="G866" s="11"/>
-      <c r="H866" s="16"/>
+      <c r="H866" s="13"/>
       <c r="I866" s="11"/>
       <c r="J866" s="11"/>
       <c r="K866" s="11"/>
@@ -12028,7 +12087,7 @@
       <c r="E867" s="9"/>
       <c r="F867" s="9"/>
       <c r="G867" s="11"/>
-      <c r="H867" s="16"/>
+      <c r="H867" s="13"/>
       <c r="I867" s="11"/>
       <c r="J867" s="11"/>
       <c r="K867" s="11"/>
@@ -12041,7 +12100,7 @@
       <c r="E868" s="9"/>
       <c r="F868" s="9"/>
       <c r="G868" s="11"/>
-      <c r="H868" s="16"/>
+      <c r="H868" s="13"/>
       <c r="I868" s="11"/>
       <c r="J868" s="11"/>
       <c r="K868" s="11"/>
@@ -12054,7 +12113,7 @@
       <c r="E869" s="9"/>
       <c r="F869" s="9"/>
       <c r="G869" s="11"/>
-      <c r="H869" s="16"/>
+      <c r="H869" s="13"/>
       <c r="I869" s="11"/>
       <c r="J869" s="11"/>
       <c r="K869" s="11"/>
@@ -12067,7 +12126,7 @@
       <c r="E870" s="9"/>
       <c r="F870" s="9"/>
       <c r="G870" s="11"/>
-      <c r="H870" s="16"/>
+      <c r="H870" s="13"/>
       <c r="I870" s="11"/>
       <c r="J870" s="11"/>
       <c r="K870" s="11"/>
@@ -12080,7 +12139,7 @@
       <c r="E871" s="9"/>
       <c r="F871" s="9"/>
       <c r="G871" s="11"/>
-      <c r="H871" s="16"/>
+      <c r="H871" s="13"/>
       <c r="I871" s="11"/>
       <c r="J871" s="11"/>
       <c r="K871" s="11"/>
@@ -12093,7 +12152,7 @@
       <c r="E872" s="9"/>
       <c r="F872" s="9"/>
       <c r="G872" s="11"/>
-      <c r="H872" s="16"/>
+      <c r="H872" s="13"/>
       <c r="I872" s="11"/>
       <c r="J872" s="11"/>
       <c r="K872" s="11"/>
@@ -12106,7 +12165,7 @@
       <c r="E873" s="9"/>
       <c r="F873" s="9"/>
       <c r="G873" s="11"/>
-      <c r="H873" s="16"/>
+      <c r="H873" s="13"/>
       <c r="I873" s="11"/>
       <c r="J873" s="11"/>
       <c r="K873" s="11"/>
@@ -12119,7 +12178,7 @@
       <c r="E874" s="9"/>
       <c r="F874" s="9"/>
       <c r="G874" s="11"/>
-      <c r="H874" s="16"/>
+      <c r="H874" s="13"/>
       <c r="I874" s="11"/>
       <c r="J874" s="11"/>
       <c r="K874" s="11"/>
@@ -12132,7 +12191,7 @@
       <c r="E875" s="9"/>
       <c r="F875" s="9"/>
       <c r="G875" s="11"/>
-      <c r="H875" s="16"/>
+      <c r="H875" s="13"/>
       <c r="I875" s="11"/>
       <c r="J875" s="11"/>
       <c r="K875" s="11"/>
@@ -12145,7 +12204,7 @@
       <c r="E876" s="9"/>
       <c r="F876" s="9"/>
       <c r="G876" s="11"/>
-      <c r="H876" s="16"/>
+      <c r="H876" s="13"/>
       <c r="I876" s="11"/>
       <c r="J876" s="11"/>
       <c r="K876" s="11"/>
@@ -12158,7 +12217,7 @@
       <c r="E877" s="9"/>
       <c r="F877" s="9"/>
       <c r="G877" s="11"/>
-      <c r="H877" s="16"/>
+      <c r="H877" s="13"/>
       <c r="I877" s="11"/>
       <c r="J877" s="11"/>
       <c r="K877" s="11"/>
@@ -12171,7 +12230,7 @@
       <c r="E878" s="9"/>
       <c r="F878" s="9"/>
       <c r="G878" s="11"/>
-      <c r="H878" s="16"/>
+      <c r="H878" s="13"/>
       <c r="I878" s="11"/>
       <c r="J878" s="11"/>
       <c r="K878" s="11"/>
@@ -12184,7 +12243,7 @@
       <c r="E879" s="9"/>
       <c r="F879" s="9"/>
       <c r="G879" s="11"/>
-      <c r="H879" s="16"/>
+      <c r="H879" s="13"/>
       <c r="I879" s="11"/>
       <c r="J879" s="11"/>
       <c r="K879" s="11"/>
@@ -12197,7 +12256,7 @@
       <c r="E880" s="9"/>
       <c r="F880" s="9"/>
       <c r="G880" s="11"/>
-      <c r="H880" s="16"/>
+      <c r="H880" s="13"/>
       <c r="I880" s="11"/>
       <c r="J880" s="11"/>
       <c r="K880" s="11"/>
@@ -12210,7 +12269,7 @@
       <c r="E881" s="9"/>
       <c r="F881" s="9"/>
       <c r="G881" s="11"/>
-      <c r="H881" s="16"/>
+      <c r="H881" s="13"/>
       <c r="I881" s="11"/>
       <c r="J881" s="11"/>
       <c r="K881" s="11"/>
@@ -12223,7 +12282,7 @@
       <c r="E882" s="9"/>
       <c r="F882" s="9"/>
       <c r="G882" s="11"/>
-      <c r="H882" s="16"/>
+      <c r="H882" s="13"/>
       <c r="I882" s="11"/>
       <c r="J882" s="11"/>
       <c r="K882" s="11"/>
@@ -12236,7 +12295,7 @@
       <c r="E883" s="9"/>
       <c r="F883" s="9"/>
       <c r="G883" s="11"/>
-      <c r="H883" s="16"/>
+      <c r="H883" s="13"/>
       <c r="I883" s="11"/>
       <c r="J883" s="11"/>
       <c r="K883" s="11"/>
@@ -12249,7 +12308,7 @@
       <c r="E884" s="9"/>
       <c r="F884" s="9"/>
       <c r="G884" s="11"/>
-      <c r="H884" s="16"/>
+      <c r="H884" s="13"/>
       <c r="I884" s="11"/>
       <c r="J884" s="11"/>
       <c r="K884" s="11"/>
@@ -12262,7 +12321,7 @@
       <c r="E885" s="9"/>
       <c r="F885" s="9"/>
       <c r="G885" s="11"/>
-      <c r="H885" s="16"/>
+      <c r="H885" s="13"/>
       <c r="I885" s="11"/>
       <c r="J885" s="11"/>
       <c r="K885" s="11"/>
@@ -12275,7 +12334,7 @@
       <c r="E886" s="9"/>
       <c r="F886" s="9"/>
       <c r="G886" s="11"/>
-      <c r="H886" s="16"/>
+      <c r="H886" s="13"/>
       <c r="I886" s="11"/>
       <c r="J886" s="11"/>
       <c r="K886" s="11"/>
@@ -12288,7 +12347,7 @@
       <c r="E887" s="9"/>
       <c r="F887" s="9"/>
       <c r="G887" s="11"/>
-      <c r="H887" s="16"/>
+      <c r="H887" s="13"/>
       <c r="I887" s="11"/>
       <c r="J887" s="11"/>
       <c r="K887" s="11"/>
@@ -12301,7 +12360,7 @@
       <c r="E888" s="9"/>
       <c r="F888" s="9"/>
       <c r="G888" s="11"/>
-      <c r="H888" s="16"/>
+      <c r="H888" s="13"/>
       <c r="I888" s="11"/>
       <c r="J888" s="11"/>
       <c r="K888" s="11"/>
@@ -12314,7 +12373,7 @@
       <c r="E889" s="9"/>
       <c r="F889" s="9"/>
       <c r="G889" s="11"/>
-      <c r="H889" s="16"/>
+      <c r="H889" s="13"/>
       <c r="I889" s="11"/>
       <c r="J889" s="11"/>
       <c r="K889" s="11"/>
@@ -12327,7 +12386,7 @@
       <c r="E890" s="9"/>
       <c r="F890" s="9"/>
       <c r="G890" s="11"/>
-      <c r="H890" s="16"/>
+      <c r="H890" s="13"/>
       <c r="I890" s="11"/>
       <c r="J890" s="11"/>
       <c r="K890" s="11"/>
@@ -12340,7 +12399,7 @@
       <c r="E891" s="9"/>
       <c r="F891" s="9"/>
       <c r="G891" s="11"/>
-      <c r="H891" s="16"/>
+      <c r="H891" s="13"/>
       <c r="I891" s="11"/>
       <c r="J891" s="11"/>
       <c r="K891" s="11"/>
@@ -12353,7 +12412,7 @@
       <c r="E892" s="9"/>
       <c r="F892" s="9"/>
       <c r="G892" s="11"/>
-      <c r="H892" s="16"/>
+      <c r="H892" s="13"/>
       <c r="I892" s="11"/>
       <c r="J892" s="11"/>
       <c r="K892" s="11"/>
@@ -12366,7 +12425,7 @@
       <c r="E893" s="9"/>
       <c r="F893" s="9"/>
       <c r="G893" s="11"/>
-      <c r="H893" s="16"/>
+      <c r="H893" s="13"/>
       <c r="I893" s="11"/>
       <c r="J893" s="11"/>
       <c r="K893" s="11"/>
@@ -12379,7 +12438,7 @@
       <c r="E894" s="9"/>
       <c r="F894" s="9"/>
       <c r="G894" s="11"/>
-      <c r="H894" s="16"/>
+      <c r="H894" s="13"/>
       <c r="I894" s="11"/>
       <c r="J894" s="11"/>
       <c r="K894" s="11"/>
@@ -12392,7 +12451,7 @@
       <c r="E895" s="9"/>
       <c r="F895" s="9"/>
       <c r="G895" s="11"/>
-      <c r="H895" s="16"/>
+      <c r="H895" s="13"/>
       <c r="I895" s="11"/>
       <c r="J895" s="11"/>
       <c r="K895" s="11"/>
@@ -12405,7 +12464,7 @@
       <c r="E896" s="9"/>
       <c r="F896" s="9"/>
       <c r="G896" s="11"/>
-      <c r="H896" s="16"/>
+      <c r="H896" s="13"/>
       <c r="I896" s="11"/>
       <c r="J896" s="11"/>
       <c r="K896" s="11"/>
@@ -12418,7 +12477,7 @@
       <c r="E897" s="9"/>
       <c r="F897" s="9"/>
       <c r="G897" s="11"/>
-      <c r="H897" s="16"/>
+      <c r="H897" s="13"/>
       <c r="I897" s="11"/>
       <c r="J897" s="11"/>
       <c r="K897" s="11"/>
@@ -12431,7 +12490,7 @@
       <c r="E898" s="9"/>
       <c r="F898" s="9"/>
       <c r="G898" s="11"/>
-      <c r="H898" s="16"/>
+      <c r="H898" s="13"/>
       <c r="I898" s="11"/>
       <c r="J898" s="11"/>
       <c r="K898" s="11"/>
@@ -12444,7 +12503,7 @@
       <c r="E899" s="9"/>
       <c r="F899" s="9"/>
       <c r="G899" s="11"/>
-      <c r="H899" s="16"/>
+      <c r="H899" s="13"/>
       <c r="I899" s="11"/>
       <c r="J899" s="11"/>
       <c r="K899" s="11"/>
@@ -12457,7 +12516,7 @@
       <c r="E900" s="9"/>
       <c r="F900" s="9"/>
       <c r="G900" s="11"/>
-      <c r="H900" s="16"/>
+      <c r="H900" s="13"/>
       <c r="I900" s="11"/>
       <c r="J900" s="11"/>
       <c r="K900" s="11"/>
@@ -12470,7 +12529,7 @@
       <c r="E901" s="9"/>
       <c r="F901" s="9"/>
       <c r="G901" s="11"/>
-      <c r="H901" s="16"/>
+      <c r="H901" s="13"/>
       <c r="I901" s="11"/>
       <c r="J901" s="11"/>
       <c r="K901" s="11"/>
@@ -12483,7 +12542,7 @@
       <c r="E902" s="9"/>
       <c r="F902" s="9"/>
       <c r="G902" s="11"/>
-      <c r="H902" s="16"/>
+      <c r="H902" s="13"/>
       <c r="I902" s="11"/>
       <c r="J902" s="11"/>
       <c r="K902" s="11"/>
@@ -12496,7 +12555,7 @@
       <c r="E903" s="9"/>
       <c r="F903" s="9"/>
       <c r="G903" s="11"/>
-      <c r="H903" s="16"/>
+      <c r="H903" s="13"/>
       <c r="I903" s="11"/>
       <c r="J903" s="11"/>
       <c r="K903" s="11"/>
@@ -12509,7 +12568,7 @@
       <c r="E904" s="9"/>
       <c r="F904" s="9"/>
       <c r="G904" s="11"/>
-      <c r="H904" s="16"/>
+      <c r="H904" s="13"/>
       <c r="I904" s="11"/>
       <c r="J904" s="11"/>
       <c r="K904" s="11"/>
@@ -12522,7 +12581,7 @@
       <c r="E905" s="9"/>
       <c r="F905" s="9"/>
       <c r="G905" s="11"/>
-      <c r="H905" s="16"/>
+      <c r="H905" s="13"/>
       <c r="I905" s="11"/>
       <c r="J905" s="11"/>
       <c r="K905" s="11"/>
@@ -12535,7 +12594,7 @@
       <c r="E906" s="9"/>
       <c r="F906" s="9"/>
       <c r="G906" s="11"/>
-      <c r="H906" s="16"/>
+      <c r="H906" s="13"/>
       <c r="I906" s="11"/>
       <c r="J906" s="11"/>
       <c r="K906" s="11"/>
@@ -12548,7 +12607,7 @@
       <c r="E907" s="9"/>
       <c r="F907" s="9"/>
       <c r="G907" s="11"/>
-      <c r="H907" s="16"/>
+      <c r="H907" s="13"/>
       <c r="I907" s="11"/>
       <c r="J907" s="11"/>
       <c r="K907" s="11"/>
@@ -12561,7 +12620,7 @@
       <c r="E908" s="9"/>
       <c r="F908" s="9"/>
       <c r="G908" s="11"/>
-      <c r="H908" s="16"/>
+      <c r="H908" s="13"/>
       <c r="I908" s="11"/>
       <c r="J908" s="11"/>
       <c r="K908" s="11"/>
@@ -12574,7 +12633,7 @@
       <c r="E909" s="9"/>
       <c r="F909" s="9"/>
       <c r="G909" s="11"/>
-      <c r="H909" s="16"/>
+      <c r="H909" s="13"/>
       <c r="I909" s="11"/>
       <c r="J909" s="11"/>
       <c r="K909" s="11"/>
@@ -12587,7 +12646,7 @@
       <c r="E910" s="9"/>
       <c r="F910" s="9"/>
       <c r="G910" s="11"/>
-      <c r="H910" s="16"/>
+      <c r="H910" s="13"/>
       <c r="I910" s="11"/>
       <c r="J910" s="11"/>
       <c r="K910" s="11"/>
@@ -12600,7 +12659,7 @@
       <c r="E911" s="9"/>
       <c r="F911" s="9"/>
       <c r="G911" s="11"/>
-      <c r="H911" s="16"/>
+      <c r="H911" s="13"/>
       <c r="I911" s="11"/>
       <c r="J911" s="11"/>
       <c r="K911" s="11"/>
@@ -12613,7 +12672,7 @@
       <c r="E912" s="9"/>
       <c r="F912" s="9"/>
       <c r="G912" s="11"/>
-      <c r="H912" s="16"/>
+      <c r="H912" s="13"/>
       <c r="I912" s="11"/>
       <c r="J912" s="11"/>
       <c r="K912" s="11"/>
@@ -12626,7 +12685,7 @@
       <c r="E913" s="9"/>
       <c r="F913" s="9"/>
       <c r="G913" s="11"/>
-      <c r="H913" s="16"/>
+      <c r="H913" s="13"/>
       <c r="I913" s="11"/>
       <c r="J913" s="11"/>
       <c r="K913" s="11"/>
@@ -12639,7 +12698,7 @@
       <c r="E914" s="9"/>
       <c r="F914" s="9"/>
       <c r="G914" s="11"/>
-      <c r="H914" s="16"/>
+      <c r="H914" s="13"/>
       <c r="I914" s="11"/>
       <c r="J914" s="11"/>
       <c r="K914" s="11"/>
@@ -12652,7 +12711,7 @@
       <c r="E915" s="9"/>
       <c r="F915" s="9"/>
       <c r="G915" s="11"/>
-      <c r="H915" s="16"/>
+      <c r="H915" s="13"/>
       <c r="I915" s="11"/>
       <c r="J915" s="11"/>
       <c r="K915" s="11"/>
@@ -12665,7 +12724,7 @@
       <c r="E916" s="9"/>
       <c r="F916" s="9"/>
       <c r="G916" s="11"/>
-      <c r="H916" s="16"/>
+      <c r="H916" s="13"/>
       <c r="I916" s="11"/>
       <c r="J916" s="11"/>
       <c r="K916" s="11"/>
@@ -12678,7 +12737,7 @@
       <c r="E917" s="9"/>
       <c r="F917" s="9"/>
       <c r="G917" s="11"/>
-      <c r="H917" s="16"/>
+      <c r="H917" s="13"/>
       <c r="I917" s="11"/>
       <c r="J917" s="11"/>
       <c r="K917" s="11"/>
@@ -12691,7 +12750,7 @@
       <c r="E918" s="9"/>
       <c r="F918" s="9"/>
       <c r="G918" s="11"/>
-      <c r="H918" s="16"/>
+      <c r="H918" s="13"/>
       <c r="I918" s="11"/>
       <c r="J918" s="11"/>
       <c r="K918" s="11"/>
@@ -12704,7 +12763,7 @@
       <c r="E919" s="9"/>
       <c r="F919" s="9"/>
       <c r="G919" s="11"/>
-      <c r="H919" s="16"/>
+      <c r="H919" s="13"/>
       <c r="I919" s="11"/>
       <c r="J919" s="11"/>
       <c r="K919" s="11"/>
@@ -12717,7 +12776,7 @@
       <c r="E920" s="9"/>
       <c r="F920" s="9"/>
       <c r="G920" s="11"/>
-      <c r="H920" s="16"/>
+      <c r="H920" s="13"/>
       <c r="I920" s="11"/>
       <c r="J920" s="11"/>
       <c r="K920" s="11"/>
@@ -12730,7 +12789,7 @@
       <c r="E921" s="9"/>
       <c r="F921" s="9"/>
       <c r="G921" s="11"/>
-      <c r="H921" s="16"/>
+      <c r="H921" s="13"/>
       <c r="I921" s="11"/>
       <c r="J921" s="11"/>
       <c r="K921" s="11"/>
@@ -12743,7 +12802,7 @@
       <c r="E922" s="9"/>
       <c r="F922" s="9"/>
       <c r="G922" s="11"/>
-      <c r="H922" s="16"/>
+      <c r="H922" s="13"/>
       <c r="I922" s="11"/>
       <c r="J922" s="11"/>
       <c r="K922" s="11"/>
@@ -12756,7 +12815,7 @@
       <c r="E923" s="9"/>
       <c r="F923" s="9"/>
       <c r="G923" s="11"/>
-      <c r="H923" s="16"/>
+      <c r="H923" s="13"/>
       <c r="I923" s="11"/>
       <c r="J923" s="11"/>
       <c r="K923" s="11"/>
@@ -12769,7 +12828,7 @@
       <c r="E924" s="9"/>
       <c r="F924" s="9"/>
       <c r="G924" s="11"/>
-      <c r="H924" s="16"/>
+      <c r="H924" s="13"/>
       <c r="I924" s="11"/>
       <c r="J924" s="11"/>
       <c r="K924" s="11"/>
@@ -12782,7 +12841,7 @@
       <c r="E925" s="9"/>
       <c r="F925" s="9"/>
       <c r="G925" s="11"/>
-      <c r="H925" s="16"/>
+      <c r="H925" s="13"/>
       <c r="I925" s="11"/>
       <c r="J925" s="11"/>
       <c r="K925" s="11"/>
@@ -12795,7 +12854,7 @@
       <c r="E926" s="9"/>
       <c r="F926" s="9"/>
       <c r="G926" s="11"/>
-      <c r="H926" s="16"/>
+      <c r="H926" s="13"/>
       <c r="I926" s="11"/>
       <c r="J926" s="11"/>
       <c r="K926" s="11"/>
@@ -12808,7 +12867,7 @@
       <c r="E927" s="9"/>
       <c r="F927" s="9"/>
       <c r="G927" s="11"/>
-      <c r="H927" s="16"/>
+      <c r="H927" s="13"/>
       <c r="I927" s="11"/>
       <c r="J927" s="11"/>
       <c r="K927" s="11"/>
@@ -12821,7 +12880,7 @@
       <c r="E928" s="9"/>
       <c r="F928" s="9"/>
       <c r="G928" s="11"/>
-      <c r="H928" s="16"/>
+      <c r="H928" s="13"/>
       <c r="I928" s="11"/>
       <c r="J928" s="11"/>
       <c r="K928" s="11"/>
@@ -12834,7 +12893,7 @@
       <c r="E929" s="9"/>
       <c r="F929" s="9"/>
       <c r="G929" s="11"/>
-      <c r="H929" s="16"/>
+      <c r="H929" s="13"/>
       <c r="I929" s="11"/>
       <c r="J929" s="11"/>
       <c r="K929" s="11"/>
@@ -12847,7 +12906,7 @@
       <c r="E930" s="9"/>
       <c r="F930" s="9"/>
       <c r="G930" s="11"/>
-      <c r="H930" s="16"/>
+      <c r="H930" s="13"/>
       <c r="I930" s="11"/>
       <c r="J930" s="11"/>
       <c r="K930" s="11"/>
@@ -12860,7 +12919,7 @@
       <c r="E931" s="9"/>
       <c r="F931" s="9"/>
       <c r="G931" s="11"/>
-      <c r="H931" s="16"/>
+      <c r="H931" s="13"/>
       <c r="I931" s="11"/>
       <c r="J931" s="11"/>
       <c r="K931" s="11"/>
@@ -12873,7 +12932,7 @@
       <c r="E932" s="9"/>
       <c r="F932" s="9"/>
       <c r="G932" s="11"/>
-      <c r="H932" s="16"/>
+      <c r="H932" s="13"/>
       <c r="I932" s="11"/>
       <c r="J932" s="11"/>
       <c r="K932" s="11"/>
@@ -12886,7 +12945,7 @@
       <c r="E933" s="9"/>
       <c r="F933" s="9"/>
       <c r="G933" s="11"/>
-      <c r="H933" s="16"/>
+      <c r="H933" s="13"/>
       <c r="I933" s="11"/>
       <c r="J933" s="11"/>
       <c r="K933" s="11"/>
@@ -12899,7 +12958,7 @@
       <c r="E934" s="9"/>
       <c r="F934" s="9"/>
       <c r="G934" s="11"/>
-      <c r="H934" s="16"/>
+      <c r="H934" s="13"/>
       <c r="I934" s="11"/>
       <c r="J934" s="11"/>
       <c r="K934" s="11"/>
@@ -12912,7 +12971,7 @@
       <c r="E935" s="9"/>
       <c r="F935" s="9"/>
       <c r="G935" s="11"/>
-      <c r="H935" s="16"/>
+      <c r="H935" s="13"/>
       <c r="I935" s="11"/>
       <c r="J935" s="11"/>
       <c r="K935" s="11"/>
@@ -12925,7 +12984,7 @@
       <c r="E936" s="9"/>
       <c r="F936" s="9"/>
       <c r="G936" s="11"/>
-      <c r="H936" s="16"/>
+      <c r="H936" s="13"/>
       <c r="I936" s="11"/>
       <c r="J936" s="11"/>
       <c r="K936" s="11"/>
@@ -12938,7 +12997,7 @@
       <c r="E937" s="9"/>
       <c r="F937" s="9"/>
       <c r="G937" s="11"/>
-      <c r="H937" s="16"/>
+      <c r="H937" s="13"/>
       <c r="I937" s="11"/>
       <c r="J937" s="11"/>
       <c r="K937" s="11"/>
@@ -12951,7 +13010,7 @@
       <c r="E938" s="9"/>
       <c r="F938" s="9"/>
       <c r="G938" s="11"/>
-      <c r="H938" s="16"/>
+      <c r="H938" s="13"/>
       <c r="I938" s="11"/>
       <c r="J938" s="11"/>
       <c r="K938" s="11"/>
@@ -12964,7 +13023,7 @@
       <c r="E939" s="9"/>
       <c r="F939" s="9"/>
       <c r="G939" s="11"/>
-      <c r="H939" s="16"/>
+      <c r="H939" s="13"/>
       <c r="I939" s="11"/>
       <c r="J939" s="11"/>
       <c r="K939" s="11"/>
@@ -12977,7 +13036,7 @@
       <c r="E940" s="9"/>
       <c r="F940" s="9"/>
       <c r="G940" s="11"/>
-      <c r="H940" s="16"/>
+      <c r="H940" s="13"/>
       <c r="I940" s="11"/>
       <c r="J940" s="11"/>
       <c r="K940" s="11"/>
@@ -12990,7 +13049,7 @@
       <c r="E941" s="9"/>
       <c r="F941" s="9"/>
       <c r="G941" s="11"/>
-      <c r="H941" s="16"/>
+      <c r="H941" s="13"/>
       <c r="I941" s="11"/>
       <c r="J941" s="11"/>
       <c r="K941" s="11"/>
@@ -13003,7 +13062,7 @@
       <c r="E942" s="9"/>
       <c r="F942" s="9"/>
       <c r="G942" s="11"/>
-      <c r="H942" s="16"/>
+      <c r="H942" s="13"/>
       <c r="I942" s="11"/>
       <c r="J942" s="11"/>
       <c r="K942" s="11"/>
@@ -13016,7 +13075,7 @@
       <c r="E943" s="9"/>
       <c r="F943" s="9"/>
       <c r="G943" s="11"/>
-      <c r="H943" s="16"/>
+      <c r="H943" s="13"/>
       <c r="I943" s="11"/>
       <c r="J943" s="11"/>
       <c r="K943" s="11"/>
@@ -13029,7 +13088,7 @@
       <c r="E944" s="9"/>
       <c r="F944" s="9"/>
       <c r="G944" s="11"/>
-      <c r="H944" s="16"/>
+      <c r="H944" s="13"/>
       <c r="I944" s="11"/>
       <c r="J944" s="11"/>
       <c r="K944" s="11"/>
@@ -13042,7 +13101,7 @@
       <c r="E945" s="9"/>
       <c r="F945" s="9"/>
       <c r="G945" s="11"/>
-      <c r="H945" s="16"/>
+      <c r="H945" s="13"/>
       <c r="I945" s="11"/>
       <c r="J945" s="11"/>
       <c r="K945" s="11"/>
@@ -13055,7 +13114,7 @@
       <c r="E946" s="9"/>
       <c r="F946" s="9"/>
       <c r="G946" s="11"/>
-      <c r="H946" s="16"/>
+      <c r="H946" s="13"/>
       <c r="I946" s="11"/>
       <c r="J946" s="11"/>
       <c r="K946" s="11"/>
@@ -13068,7 +13127,7 @@
       <c r="E947" s="9"/>
       <c r="F947" s="9"/>
       <c r="G947" s="11"/>
-      <c r="H947" s="16"/>
+      <c r="H947" s="13"/>
       <c r="I947" s="11"/>
       <c r="J947" s="11"/>
       <c r="K947" s="11"/>
@@ -13081,7 +13140,7 @@
       <c r="E948" s="9"/>
       <c r="F948" s="9"/>
       <c r="G948" s="11"/>
-      <c r="H948" s="16"/>
+      <c r="H948" s="13"/>
       <c r="I948" s="11"/>
       <c r="J948" s="11"/>
       <c r="K948" s="11"/>
@@ -13094,7 +13153,7 @@
       <c r="E949" s="9"/>
       <c r="F949" s="9"/>
       <c r="G949" s="11"/>
-      <c r="H949" s="16"/>
+      <c r="H949" s="13"/>
       <c r="I949" s="11"/>
       <c r="J949" s="11"/>
       <c r="K949" s="11"/>
@@ -13107,7 +13166,7 @@
       <c r="E950" s="9"/>
       <c r="F950" s="9"/>
       <c r="G950" s="11"/>
-      <c r="H950" s="16"/>
+      <c r="H950" s="13"/>
       <c r="I950" s="11"/>
       <c r="J950" s="11"/>
       <c r="K950" s="11"/>
@@ -13120,7 +13179,7 @@
       <c r="E951" s="9"/>
       <c r="F951" s="9"/>
       <c r="G951" s="11"/>
-      <c r="H951" s="16"/>
+      <c r="H951" s="13"/>
       <c r="I951" s="11"/>
       <c r="J951" s="11"/>
       <c r="K951" s="11"/>
@@ -13133,7 +13192,7 @@
       <c r="E952" s="9"/>
       <c r="F952" s="9"/>
       <c r="G952" s="11"/>
-      <c r="H952" s="16"/>
+      <c r="H952" s="13"/>
       <c r="I952" s="11"/>
       <c r="J952" s="11"/>
       <c r="K952" s="11"/>
@@ -13146,7 +13205,7 @@
       <c r="E953" s="9"/>
       <c r="F953" s="9"/>
       <c r="G953" s="11"/>
-      <c r="H953" s="16"/>
+      <c r="H953" s="13"/>
       <c r="I953" s="11"/>
       <c r="J953" s="11"/>
       <c r="K953" s="11"/>
@@ -13159,7 +13218,7 @@
       <c r="E954" s="9"/>
       <c r="F954" s="9"/>
       <c r="G954" s="11"/>
-      <c r="H954" s="16"/>
+      <c r="H954" s="13"/>
       <c r="I954" s="11"/>
       <c r="J954" s="11"/>
       <c r="K954" s="11"/>
@@ -13172,7 +13231,7 @@
       <c r="E955" s="9"/>
       <c r="F955" s="9"/>
       <c r="G955" s="11"/>
-      <c r="H955" s="16"/>
+      <c r="H955" s="13"/>
       <c r="I955" s="11"/>
       <c r="J955" s="11"/>
       <c r="K955" s="11"/>
@@ -13185,7 +13244,7 @@
       <c r="E956" s="9"/>
       <c r="F956" s="9"/>
       <c r="G956" s="11"/>
-      <c r="H956" s="16"/>
+      <c r="H956" s="13"/>
       <c r="I956" s="11"/>
       <c r="J956" s="11"/>
       <c r="K956" s="11"/>
@@ -13198,7 +13257,7 @@
       <c r="E957" s="9"/>
       <c r="F957" s="9"/>
       <c r="G957" s="11"/>
-      <c r="H957" s="16"/>
+      <c r="H957" s="13"/>
       <c r="I957" s="11"/>
       <c r="J957" s="11"/>
       <c r="K957" s="11"/>
@@ -13211,7 +13270,7 @@
       <c r="E958" s="9"/>
       <c r="F958" s="9"/>
       <c r="G958" s="11"/>
-      <c r="H958" s="16"/>
+      <c r="H958" s="13"/>
       <c r="I958" s="11"/>
       <c r="J958" s="11"/>
       <c r="K958" s="11"/>
@@ -13224,7 +13283,7 @@
       <c r="E959" s="9"/>
       <c r="F959" s="9"/>
       <c r="G959" s="11"/>
-      <c r="H959" s="16"/>
+      <c r="H959" s="13"/>
       <c r="I959" s="11"/>
       <c r="J959" s="11"/>
       <c r="K959" s="11"/>
@@ -13237,7 +13296,7 @@
       <c r="E960" s="9"/>
       <c r="F960" s="9"/>
       <c r="G960" s="11"/>
-      <c r="H960" s="16"/>
+      <c r="H960" s="13"/>
       <c r="I960" s="11"/>
       <c r="J960" s="11"/>
       <c r="K960" s="11"/>
@@ -13250,7 +13309,7 @@
       <c r="E961" s="9"/>
       <c r="F961" s="9"/>
       <c r="G961" s="11"/>
-      <c r="H961" s="16"/>
+      <c r="H961" s="13"/>
       <c r="I961" s="11"/>
       <c r="J961" s="11"/>
       <c r="K961" s="11"/>
@@ -13263,7 +13322,7 @@
       <c r="E962" s="9"/>
       <c r="F962" s="9"/>
       <c r="G962" s="11"/>
-      <c r="H962" s="16"/>
+      <c r="H962" s="13"/>
       <c r="I962" s="11"/>
       <c r="J962" s="11"/>
       <c r="K962" s="11"/>
@@ -13276,7 +13335,7 @@
       <c r="E963" s="9"/>
       <c r="F963" s="9"/>
       <c r="G963" s="11"/>
-      <c r="H963" s="16"/>
+      <c r="H963" s="13"/>
       <c r="I963" s="11"/>
       <c r="J963" s="11"/>
       <c r="K963" s="11"/>
@@ -13289,7 +13348,7 @@
       <c r="E964" s="9"/>
       <c r="F964" s="9"/>
       <c r="G964" s="11"/>
-      <c r="H964" s="16"/>
+      <c r="H964" s="13"/>
       <c r="I964" s="11"/>
       <c r="J964" s="11"/>
       <c r="K964" s="11"/>
@@ -13302,7 +13361,7 @@
       <c r="E965" s="9"/>
       <c r="F965" s="9"/>
       <c r="G965" s="11"/>
-      <c r="H965" s="16"/>
+      <c r="H965" s="13"/>
       <c r="I965" s="11"/>
       <c r="J965" s="11"/>
       <c r="K965" s="11"/>
@@ -13315,7 +13374,7 @@
       <c r="E966" s="9"/>
       <c r="F966" s="9"/>
       <c r="G966" s="11"/>
-      <c r="H966" s="16"/>
+      <c r="H966" s="13"/>
       <c r="I966" s="11"/>
       <c r="J966" s="11"/>
       <c r="K966" s="11"/>
@@ -13328,7 +13387,7 @@
       <c r="E967" s="9"/>
       <c r="F967" s="9"/>
       <c r="G967" s="11"/>
-      <c r="H967" s="16"/>
+      <c r="H967" s="13"/>
       <c r="I967" s="11"/>
       <c r="J967" s="11"/>
       <c r="K967" s="11"/>
@@ -13341,7 +13400,7 @@
       <c r="E968" s="9"/>
       <c r="F968" s="9"/>
       <c r="G968" s="11"/>
-      <c r="H968" s="16"/>
+      <c r="H968" s="13"/>
       <c r="I968" s="11"/>
       <c r="J968" s="11"/>
       <c r="K968" s="11"/>
@@ -13354,7 +13413,7 @@
       <c r="E969" s="9"/>
       <c r="F969" s="9"/>
       <c r="G969" s="11"/>
-      <c r="H969" s="16"/>
+      <c r="H969" s="13"/>
       <c r="I969" s="11"/>
       <c r="J969" s="11"/>
       <c r="K969" s="11"/>
@@ -13367,7 +13426,7 @@
       <c r="E970" s="9"/>
       <c r="F970" s="9"/>
       <c r="G970" s="11"/>
-      <c r="H970" s="16"/>
+      <c r="H970" s="13"/>
       <c r="I970" s="11"/>
       <c r="J970" s="11"/>
       <c r="K970" s="11"/>
@@ -13380,7 +13439,7 @@
       <c r="E971" s="9"/>
       <c r="F971" s="9"/>
       <c r="G971" s="11"/>
-      <c r="H971" s="16"/>
+      <c r="H971" s="13"/>
       <c r="I971" s="11"/>
       <c r="J971" s="11"/>
       <c r="K971" s="11"/>
@@ -13393,7 +13452,7 @@
       <c r="E972" s="9"/>
       <c r="F972" s="9"/>
       <c r="G972" s="11"/>
-      <c r="H972" s="16"/>
+      <c r="H972" s="13"/>
       <c r="I972" s="11"/>
       <c r="J972" s="11"/>
       <c r="K972" s="11"/>
@@ -13406,7 +13465,7 @@
       <c r="E973" s="9"/>
       <c r="F973" s="9"/>
       <c r="G973" s="11"/>
-      <c r="H973" s="16"/>
+      <c r="H973" s="13"/>
       <c r="I973" s="11"/>
       <c r="J973" s="11"/>
       <c r="K973" s="11"/>
@@ -13419,7 +13478,7 @@
       <c r="E974" s="9"/>
       <c r="F974" s="9"/>
       <c r="G974" s="11"/>
-      <c r="H974" s="16"/>
+      <c r="H974" s="13"/>
       <c r="I974" s="11"/>
       <c r="J974" s="11"/>
       <c r="K974" s="11"/>
@@ -13432,7 +13491,7 @@
       <c r="E975" s="9"/>
       <c r="F975" s="9"/>
       <c r="G975" s="11"/>
-      <c r="H975" s="16"/>
+      <c r="H975" s="13"/>
       <c r="I975" s="11"/>
       <c r="J975" s="11"/>
       <c r="K975" s="11"/>
@@ -13445,7 +13504,7 @@
       <c r="E976" s="9"/>
       <c r="F976" s="9"/>
       <c r="G976" s="11"/>
-      <c r="H976" s="16"/>
+      <c r="H976" s="13"/>
       <c r="I976" s="11"/>
       <c r="J976" s="11"/>
       <c r="K976" s="11"/>
@@ -13458,7 +13517,7 @@
       <c r="E977" s="9"/>
       <c r="F977" s="9"/>
       <c r="G977" s="11"/>
-      <c r="H977" s="16"/>
+      <c r="H977" s="13"/>
       <c r="I977" s="11"/>
       <c r="J977" s="11"/>
       <c r="K977" s="11"/>
@@ -13471,7 +13530,7 @@
       <c r="E978" s="9"/>
       <c r="F978" s="9"/>
       <c r="G978" s="11"/>
-      <c r="H978" s="16"/>
+      <c r="H978" s="13"/>
       <c r="I978" s="11"/>
       <c r="J978" s="11"/>
       <c r="K978" s="11"/>
@@ -13484,7 +13543,7 @@
       <c r="E979" s="9"/>
       <c r="F979" s="9"/>
       <c r="G979" s="11"/>
-      <c r="H979" s="16"/>
+      <c r="H979" s="13"/>
       <c r="I979" s="11"/>
       <c r="J979" s="11"/>
       <c r="K979" s="11"/>
@@ -13497,7 +13556,7 @@
       <c r="E980" s="9"/>
       <c r="F980" s="9"/>
       <c r="G980" s="11"/>
-      <c r="H980" s="16"/>
+      <c r="H980" s="13"/>
       <c r="I980" s="11"/>
       <c r="J980" s="11"/>
       <c r="K980" s="11"/>
@@ -13510,7 +13569,7 @@
       <c r="E981" s="9"/>
       <c r="F981" s="9"/>
       <c r="G981" s="11"/>
-      <c r="H981" s="16"/>
+      <c r="H981" s="13"/>
       <c r="I981" s="11"/>
       <c r="J981" s="11"/>
       <c r="K981" s="11"/>
@@ -13523,7 +13582,7 @@
       <c r="E982" s="9"/>
       <c r="F982" s="9"/>
       <c r="G982" s="11"/>
-      <c r="H982" s="16"/>
+      <c r="H982" s="13"/>
       <c r="I982" s="11"/>
       <c r="J982" s="11"/>
       <c r="K982" s="11"/>
@@ -13536,7 +13595,7 @@
       <c r="E983" s="9"/>
       <c r="F983" s="9"/>
       <c r="G983" s="11"/>
-      <c r="H983" s="16"/>
+      <c r="H983" s="13"/>
       <c r="I983" s="11"/>
       <c r="J983" s="11"/>
       <c r="K983" s="11"/>
@@ -13549,7 +13608,7 @@
       <c r="E984" s="9"/>
       <c r="F984" s="9"/>
       <c r="G984" s="11"/>
-      <c r="H984" s="16"/>
+      <c r="H984" s="13"/>
       <c r="I984" s="11"/>
       <c r="J984" s="11"/>
       <c r="K984" s="11"/>
@@ -13562,7 +13621,7 @@
       <c r="E985" s="9"/>
       <c r="F985" s="9"/>
       <c r="G985" s="11"/>
-      <c r="H985" s="16"/>
+      <c r="H985" s="13"/>
       <c r="I985" s="11"/>
       <c r="J985" s="11"/>
       <c r="K985" s="11"/>
@@ -13575,7 +13634,7 @@
       <c r="E986" s="9"/>
       <c r="F986" s="9"/>
       <c r="G986" s="11"/>
-      <c r="H986" s="16"/>
+      <c r="H986" s="13"/>
       <c r="I986" s="11"/>
       <c r="J986" s="11"/>
       <c r="K986" s="11"/>
@@ -13588,7 +13647,7 @@
       <c r="E987" s="9"/>
       <c r="F987" s="9"/>
       <c r="G987" s="11"/>
-      <c r="H987" s="16"/>
+      <c r="H987" s="13"/>
       <c r="I987" s="11"/>
       <c r="J987" s="11"/>
       <c r="K987" s="11"/>
@@ -13601,7 +13660,7 @@
       <c r="E988" s="9"/>
       <c r="F988" s="9"/>
       <c r="G988" s="11"/>
-      <c r="H988" s="16"/>
+      <c r="H988" s="13"/>
       <c r="I988" s="11"/>
       <c r="J988" s="11"/>
       <c r="K988" s="11"/>
@@ -13614,7 +13673,7 @@
       <c r="E989" s="9"/>
       <c r="F989" s="9"/>
       <c r="G989" s="11"/>
-      <c r="H989" s="16"/>
+      <c r="H989" s="13"/>
       <c r="I989" s="11"/>
       <c r="J989" s="11"/>
       <c r="K989" s="11"/>
@@ -13627,7 +13686,7 @@
       <c r="E990" s="9"/>
       <c r="F990" s="9"/>
       <c r="G990" s="11"/>
-      <c r="H990" s="16"/>
+      <c r="H990" s="13"/>
       <c r="I990" s="11"/>
       <c r="J990" s="11"/>
       <c r="K990" s="11"/>
@@ -13640,7 +13699,7 @@
       <c r="E991" s="9"/>
       <c r="F991" s="9"/>
       <c r="G991" s="11"/>
-      <c r="H991" s="16"/>
+      <c r="H991" s="13"/>
       <c r="I991" s="11"/>
       <c r="J991" s="11"/>
       <c r="K991" s="11"/>
@@ -13653,7 +13712,7 @@
       <c r="E992" s="9"/>
       <c r="F992" s="9"/>
       <c r="G992" s="11"/>
-      <c r="H992" s="16"/>
+      <c r="H992" s="13"/>
       <c r="I992" s="11"/>
       <c r="J992" s="11"/>
       <c r="K992" s="11"/>
@@ -13666,7 +13725,7 @@
       <c r="E993" s="9"/>
       <c r="F993" s="9"/>
       <c r="G993" s="11"/>
-      <c r="H993" s="16"/>
+      <c r="H993" s="13"/>
       <c r="I993" s="11"/>
       <c r="J993" s="11"/>
       <c r="K993" s="11"/>
@@ -13679,7 +13738,7 @@
       <c r="E994" s="9"/>
       <c r="F994" s="9"/>
       <c r="G994" s="11"/>
-      <c r="H994" s="16"/>
+      <c r="H994" s="13"/>
       <c r="I994" s="11"/>
       <c r="J994" s="11"/>
       <c r="K994" s="11"/>
@@ -13692,7 +13751,7 @@
       <c r="E995" s="9"/>
       <c r="F995" s="9"/>
       <c r="G995" s="11"/>
-      <c r="H995" s="16"/>
+      <c r="H995" s="13"/>
       <c r="I995" s="11"/>
       <c r="J995" s="11"/>
       <c r="K995" s="11"/>
@@ -13705,7 +13764,7 @@
       <c r="E996" s="9"/>
       <c r="F996" s="9"/>
       <c r="G996" s="11"/>
-      <c r="H996" s="16"/>
+      <c r="H996" s="13"/>
       <c r="I996" s="11"/>
       <c r="J996" s="11"/>
       <c r="K996" s="11"/>
@@ -13718,7 +13777,7 @@
       <c r="E997" s="9"/>
       <c r="F997" s="9"/>
       <c r="G997" s="11"/>
-      <c r="H997" s="16"/>
+      <c r="H997" s="13"/>
       <c r="I997" s="11"/>
       <c r="J997" s="11"/>
       <c r="K997" s="11"/>
@@ -13731,7 +13790,7 @@
       <c r="E998" s="9"/>
       <c r="F998" s="9"/>
       <c r="G998" s="11"/>
-      <c r="H998" s="16"/>
+      <c r="H998" s="13"/>
       <c r="I998" s="11"/>
       <c r="J998" s="11"/>
       <c r="K998" s="11"/>
@@ -13744,7 +13803,7 @@
       <c r="E999" s="9"/>
       <c r="F999" s="9"/>
       <c r="G999" s="11"/>
-      <c r="H999" s="16"/>
+      <c r="H999" s="13"/>
       <c r="I999" s="11"/>
       <c r="J999" s="11"/>
       <c r="K999" s="11"/>
@@ -13757,16 +13816,17 @@
       <c r="E1000" s="9"/>
       <c r="F1000" s="9"/>
       <c r="G1000" s="11"/>
-      <c r="H1000" s="16"/>
+      <c r="H1000" s="13"/>
       <c r="I1000" s="11"/>
       <c r="J1000" s="11"/>
       <c r="K1000" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/BACKEND/EjemplosExcels/file-AF.xlsx
+++ b/BACKEND/EjemplosExcels/file-AF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVE-System\BACKEND\EjemplosExcels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\SVS-System\BACKEND\EjemplosExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAD23E2-3633-4462-B1CF-6DAC58F6E851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE425A1-A60D-4F95-95FA-40A13263A53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>Apellido y nombre</t>
   </si>
@@ -177,15 +177,12 @@
   <si>
     <t>1ro</t>
   </si>
-  <si>
-    <t>DNI - 94177248</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,18 +205,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -241,7 +226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -279,24 +264,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -332,29 +304,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +380,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:K8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:K7">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Apellido y nombre"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Documento"/>
@@ -895,35 +854,17 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="17">
-        <v>2023</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
@@ -933,7 +874,7 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="13"/>
+      <c r="H9" s="16"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
@@ -946,7 +887,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="11"/>
-      <c r="H10" s="13"/>
+      <c r="H10" s="16"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -959,7 +900,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="11"/>
-      <c r="H11" s="13"/>
+      <c r="H11" s="16"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -972,20 +913,20 @@
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="11"/>
-      <c r="H12" s="13"/>
+      <c r="H12" s="16"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
-      <c r="B13" s="21"/>
+      <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="13"/>
+      <c r="H13" s="16"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
@@ -998,7 +939,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="11"/>
-      <c r="H14" s="13"/>
+      <c r="H14" s="16"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -1011,7 +952,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="11"/>
-      <c r="H15" s="13"/>
+      <c r="H15" s="16"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -1024,7 +965,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="13"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
@@ -1037,7 +978,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="13"/>
+      <c r="H17" s="16"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -1050,7 +991,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="13"/>
+      <c r="H18" s="16"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -1063,7 +1004,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="13"/>
+      <c r="H19" s="16"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
@@ -1076,7 +1017,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="11"/>
-      <c r="H20" s="13"/>
+      <c r="H20" s="16"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -1089,7 +1030,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="13"/>
+      <c r="H21" s="16"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
@@ -1102,7 +1043,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="11"/>
-      <c r="H22" s="13"/>
+      <c r="H22" s="16"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -1115,7 +1056,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="11"/>
-      <c r="H23" s="13"/>
+      <c r="H23" s="16"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -1128,7 +1069,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="11"/>
-      <c r="H24" s="13"/>
+      <c r="H24" s="16"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -1141,7 +1082,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="11"/>
-      <c r="H25" s="13"/>
+      <c r="H25" s="16"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -1154,7 +1095,7 @@
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="11"/>
-      <c r="H26" s="13"/>
+      <c r="H26" s="16"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -1167,7 +1108,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="11"/>
-      <c r="H27" s="13"/>
+      <c r="H27" s="16"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -1180,7 +1121,7 @@
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="11"/>
-      <c r="H28" s="13"/>
+      <c r="H28" s="16"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -1193,7 +1134,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="11"/>
-      <c r="H29" s="13"/>
+      <c r="H29" s="16"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
@@ -1206,7 +1147,7 @@
       <c r="E30" s="9"/>
       <c r="F30" s="9"/>
       <c r="G30" s="11"/>
-      <c r="H30" s="13"/>
+      <c r="H30" s="16"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -1219,7 +1160,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="11"/>
-      <c r="H31" s="13"/>
+      <c r="H31" s="16"/>
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
@@ -1232,7 +1173,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
       <c r="G32" s="11"/>
-      <c r="H32" s="13"/>
+      <c r="H32" s="16"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -1245,7 +1186,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="11"/>
-      <c r="H33" s="13"/>
+      <c r="H33" s="16"/>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
@@ -1258,7 +1199,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
       <c r="G34" s="11"/>
-      <c r="H34" s="13"/>
+      <c r="H34" s="16"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -1271,7 +1212,7 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
       <c r="G35" s="11"/>
-      <c r="H35" s="13"/>
+      <c r="H35" s="16"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -1284,7 +1225,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
       <c r="G36" s="11"/>
-      <c r="H36" s="13"/>
+      <c r="H36" s="16"/>
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -1297,7 +1238,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
       <c r="G37" s="11"/>
-      <c r="H37" s="13"/>
+      <c r="H37" s="16"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
@@ -1310,7 +1251,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
       <c r="G38" s="11"/>
-      <c r="H38" s="13"/>
+      <c r="H38" s="16"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -1323,7 +1264,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
       <c r="G39" s="11"/>
-      <c r="H39" s="13"/>
+      <c r="H39" s="16"/>
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
@@ -1336,7 +1277,7 @@
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
       <c r="G40" s="11"/>
-      <c r="H40" s="13"/>
+      <c r="H40" s="16"/>
       <c r="I40" s="11"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -1349,7 +1290,7 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
       <c r="G41" s="11"/>
-      <c r="H41" s="13"/>
+      <c r="H41" s="16"/>
       <c r="I41" s="11"/>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
@@ -1362,7 +1303,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
       <c r="G42" s="11"/>
-      <c r="H42" s="13"/>
+      <c r="H42" s="16"/>
       <c r="I42" s="11"/>
       <c r="J42" s="11"/>
       <c r="K42" s="11"/>
@@ -1375,7 +1316,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" s="11"/>
-      <c r="H43" s="13"/>
+      <c r="H43" s="16"/>
       <c r="I43" s="11"/>
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
@@ -1388,7 +1329,7 @@
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" s="11"/>
-      <c r="H44" s="13"/>
+      <c r="H44" s="16"/>
       <c r="I44" s="11"/>
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
@@ -1401,7 +1342,7 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" s="11"/>
-      <c r="H45" s="13"/>
+      <c r="H45" s="16"/>
       <c r="I45" s="11"/>
       <c r="J45" s="11"/>
       <c r="K45" s="11"/>
@@ -1414,7 +1355,7 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" s="11"/>
-      <c r="H46" s="13"/>
+      <c r="H46" s="16"/>
       <c r="I46" s="11"/>
       <c r="J46" s="11"/>
       <c r="K46" s="11"/>
@@ -1427,7 +1368,7 @@
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" s="11"/>
-      <c r="H47" s="13"/>
+      <c r="H47" s="16"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
@@ -1440,7 +1381,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" s="11"/>
-      <c r="H48" s="13"/>
+      <c r="H48" s="16"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
       <c r="K48" s="11"/>
@@ -1453,7 +1394,7 @@
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
       <c r="G49" s="11"/>
-      <c r="H49" s="13"/>
+      <c r="H49" s="16"/>
       <c r="I49" s="11"/>
       <c r="J49" s="11"/>
       <c r="K49" s="11"/>
@@ -1466,7 +1407,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
       <c r="G50" s="11"/>
-      <c r="H50" s="13"/>
+      <c r="H50" s="16"/>
       <c r="I50" s="11"/>
       <c r="J50" s="11"/>
       <c r="K50" s="11"/>
@@ -1479,7 +1420,7 @@
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
       <c r="G51" s="11"/>
-      <c r="H51" s="13"/>
+      <c r="H51" s="16"/>
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
       <c r="K51" s="11"/>
@@ -1492,7 +1433,7 @@
       <c r="E52" s="9"/>
       <c r="F52" s="9"/>
       <c r="G52" s="11"/>
-      <c r="H52" s="13"/>
+      <c r="H52" s="16"/>
       <c r="I52" s="11"/>
       <c r="J52" s="11"/>
       <c r="K52" s="11"/>
@@ -1505,7 +1446,7 @@
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
       <c r="G53" s="11"/>
-      <c r="H53" s="13"/>
+      <c r="H53" s="16"/>
       <c r="I53" s="11"/>
       <c r="J53" s="11"/>
       <c r="K53" s="11"/>
@@ -1518,7 +1459,7 @@
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
       <c r="G54" s="11"/>
-      <c r="H54" s="13"/>
+      <c r="H54" s="16"/>
       <c r="I54" s="11"/>
       <c r="J54" s="11"/>
       <c r="K54" s="11"/>
@@ -1531,7 +1472,7 @@
       <c r="E55" s="9"/>
       <c r="F55" s="9"/>
       <c r="G55" s="11"/>
-      <c r="H55" s="13"/>
+      <c r="H55" s="16"/>
       <c r="I55" s="11"/>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
@@ -1544,7 +1485,7 @@
       <c r="E56" s="9"/>
       <c r="F56" s="9"/>
       <c r="G56" s="11"/>
-      <c r="H56" s="13"/>
+      <c r="H56" s="16"/>
       <c r="I56" s="11"/>
       <c r="J56" s="11"/>
       <c r="K56" s="11"/>
@@ -1557,7 +1498,7 @@
       <c r="E57" s="9"/>
       <c r="F57" s="9"/>
       <c r="G57" s="11"/>
-      <c r="H57" s="13"/>
+      <c r="H57" s="16"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
@@ -1570,7 +1511,7 @@
       <c r="E58" s="9"/>
       <c r="F58" s="9"/>
       <c r="G58" s="11"/>
-      <c r="H58" s="13"/>
+      <c r="H58" s="16"/>
       <c r="I58" s="11"/>
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
@@ -1583,7 +1524,7 @@
       <c r="E59" s="9"/>
       <c r="F59" s="9"/>
       <c r="G59" s="11"/>
-      <c r="H59" s="13"/>
+      <c r="H59" s="16"/>
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
@@ -1596,7 +1537,7 @@
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="11"/>
-      <c r="H60" s="13"/>
+      <c r="H60" s="16"/>
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
@@ -1609,7 +1550,7 @@
       <c r="E61" s="9"/>
       <c r="F61" s="9"/>
       <c r="G61" s="11"/>
-      <c r="H61" s="13"/>
+      <c r="H61" s="16"/>
       <c r="I61" s="11"/>
       <c r="J61" s="11"/>
       <c r="K61" s="11"/>
@@ -1622,7 +1563,7 @@
       <c r="E62" s="9"/>
       <c r="F62" s="9"/>
       <c r="G62" s="11"/>
-      <c r="H62" s="13"/>
+      <c r="H62" s="16"/>
       <c r="I62" s="11"/>
       <c r="J62" s="11"/>
       <c r="K62" s="11"/>
@@ -1635,7 +1576,7 @@
       <c r="E63" s="9"/>
       <c r="F63" s="9"/>
       <c r="G63" s="11"/>
-      <c r="H63" s="13"/>
+      <c r="H63" s="16"/>
       <c r="I63" s="11"/>
       <c r="J63" s="11"/>
       <c r="K63" s="11"/>
@@ -1648,7 +1589,7 @@
       <c r="E64" s="9"/>
       <c r="F64" s="9"/>
       <c r="G64" s="11"/>
-      <c r="H64" s="13"/>
+      <c r="H64" s="16"/>
       <c r="I64" s="11"/>
       <c r="J64" s="11"/>
       <c r="K64" s="11"/>
@@ -1661,7 +1602,7 @@
       <c r="E65" s="9"/>
       <c r="F65" s="9"/>
       <c r="G65" s="11"/>
-      <c r="H65" s="13"/>
+      <c r="H65" s="16"/>
       <c r="I65" s="11"/>
       <c r="J65" s="11"/>
       <c r="K65" s="11"/>
@@ -1674,7 +1615,7 @@
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
       <c r="G66" s="11"/>
-      <c r="H66" s="13"/>
+      <c r="H66" s="16"/>
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
       <c r="K66" s="11"/>
@@ -1687,7 +1628,7 @@
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
       <c r="G67" s="11"/>
-      <c r="H67" s="13"/>
+      <c r="H67" s="16"/>
       <c r="I67" s="11"/>
       <c r="J67" s="11"/>
       <c r="K67" s="11"/>
@@ -1700,7 +1641,7 @@
       <c r="E68" s="9"/>
       <c r="F68" s="9"/>
       <c r="G68" s="11"/>
-      <c r="H68" s="13"/>
+      <c r="H68" s="16"/>
       <c r="I68" s="11"/>
       <c r="J68" s="11"/>
       <c r="K68" s="11"/>
@@ -1713,7 +1654,7 @@
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
       <c r="G69" s="11"/>
-      <c r="H69" s="13"/>
+      <c r="H69" s="16"/>
       <c r="I69" s="11"/>
       <c r="J69" s="11"/>
       <c r="K69" s="11"/>
@@ -1726,7 +1667,7 @@
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
       <c r="G70" s="11"/>
-      <c r="H70" s="13"/>
+      <c r="H70" s="16"/>
       <c r="I70" s="11"/>
       <c r="J70" s="11"/>
       <c r="K70" s="11"/>
@@ -1739,7 +1680,7 @@
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
       <c r="G71" s="11"/>
-      <c r="H71" s="13"/>
+      <c r="H71" s="16"/>
       <c r="I71" s="11"/>
       <c r="J71" s="11"/>
       <c r="K71" s="11"/>
@@ -1752,7 +1693,7 @@
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
       <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
+      <c r="H72" s="16"/>
       <c r="I72" s="11"/>
       <c r="J72" s="11"/>
       <c r="K72" s="11"/>
@@ -1765,7 +1706,7 @@
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
       <c r="G73" s="11"/>
-      <c r="H73" s="13"/>
+      <c r="H73" s="16"/>
       <c r="I73" s="11"/>
       <c r="J73" s="11"/>
       <c r="K73" s="11"/>
@@ -1778,7 +1719,7 @@
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
       <c r="G74" s="11"/>
-      <c r="H74" s="13"/>
+      <c r="H74" s="16"/>
       <c r="I74" s="11"/>
       <c r="J74" s="11"/>
       <c r="K74" s="11"/>
@@ -1791,7 +1732,7 @@
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
       <c r="G75" s="11"/>
-      <c r="H75" s="13"/>
+      <c r="H75" s="16"/>
       <c r="I75" s="11"/>
       <c r="J75" s="11"/>
       <c r="K75" s="11"/>
@@ -1804,7 +1745,7 @@
       <c r="E76" s="9"/>
       <c r="F76" s="9"/>
       <c r="G76" s="11"/>
-      <c r="H76" s="13"/>
+      <c r="H76" s="16"/>
       <c r="I76" s="11"/>
       <c r="J76" s="11"/>
       <c r="K76" s="11"/>
@@ -1817,7 +1758,7 @@
       <c r="E77" s="9"/>
       <c r="F77" s="9"/>
       <c r="G77" s="11"/>
-      <c r="H77" s="13"/>
+      <c r="H77" s="16"/>
       <c r="I77" s="11"/>
       <c r="J77" s="11"/>
       <c r="K77" s="11"/>
@@ -1830,7 +1771,7 @@
       <c r="E78" s="9"/>
       <c r="F78" s="9"/>
       <c r="G78" s="11"/>
-      <c r="H78" s="13"/>
+      <c r="H78" s="16"/>
       <c r="I78" s="11"/>
       <c r="J78" s="11"/>
       <c r="K78" s="11"/>
@@ -1843,7 +1784,7 @@
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
       <c r="G79" s="11"/>
-      <c r="H79" s="13"/>
+      <c r="H79" s="16"/>
       <c r="I79" s="11"/>
       <c r="J79" s="11"/>
       <c r="K79" s="11"/>
@@ -1856,7 +1797,7 @@
       <c r="E80" s="9"/>
       <c r="F80" s="9"/>
       <c r="G80" s="11"/>
-      <c r="H80" s="13"/>
+      <c r="H80" s="16"/>
       <c r="I80" s="11"/>
       <c r="J80" s="11"/>
       <c r="K80" s="11"/>
@@ -1869,7 +1810,7 @@
       <c r="E81" s="9"/>
       <c r="F81" s="9"/>
       <c r="G81" s="11"/>
-      <c r="H81" s="13"/>
+      <c r="H81" s="16"/>
       <c r="I81" s="11"/>
       <c r="J81" s="11"/>
       <c r="K81" s="11"/>
@@ -1882,7 +1823,7 @@
       <c r="E82" s="9"/>
       <c r="F82" s="9"/>
       <c r="G82" s="11"/>
-      <c r="H82" s="13"/>
+      <c r="H82" s="16"/>
       <c r="I82" s="11"/>
       <c r="J82" s="11"/>
       <c r="K82" s="11"/>
@@ -1895,7 +1836,7 @@
       <c r="E83" s="9"/>
       <c r="F83" s="9"/>
       <c r="G83" s="11"/>
-      <c r="H83" s="13"/>
+      <c r="H83" s="16"/>
       <c r="I83" s="11"/>
       <c r="J83" s="11"/>
       <c r="K83" s="11"/>
@@ -1908,7 +1849,7 @@
       <c r="E84" s="9"/>
       <c r="F84" s="9"/>
       <c r="G84" s="11"/>
-      <c r="H84" s="13"/>
+      <c r="H84" s="16"/>
       <c r="I84" s="11"/>
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
@@ -1921,7 +1862,7 @@
       <c r="E85" s="9"/>
       <c r="F85" s="9"/>
       <c r="G85" s="11"/>
-      <c r="H85" s="13"/>
+      <c r="H85" s="16"/>
       <c r="I85" s="11"/>
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
@@ -1934,7 +1875,7 @@
       <c r="E86" s="9"/>
       <c r="F86" s="9"/>
       <c r="G86" s="11"/>
-      <c r="H86" s="13"/>
+      <c r="H86" s="16"/>
       <c r="I86" s="11"/>
       <c r="J86" s="11"/>
       <c r="K86" s="11"/>
@@ -1947,7 +1888,7 @@
       <c r="E87" s="9"/>
       <c r="F87" s="9"/>
       <c r="G87" s="11"/>
-      <c r="H87" s="13"/>
+      <c r="H87" s="16"/>
       <c r="I87" s="11"/>
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
@@ -1960,7 +1901,7 @@
       <c r="E88" s="9"/>
       <c r="F88" s="9"/>
       <c r="G88" s="11"/>
-      <c r="H88" s="13"/>
+      <c r="H88" s="16"/>
       <c r="I88" s="11"/>
       <c r="J88" s="11"/>
       <c r="K88" s="11"/>
@@ -1973,7 +1914,7 @@
       <c r="E89" s="9"/>
       <c r="F89" s="9"/>
       <c r="G89" s="11"/>
-      <c r="H89" s="13"/>
+      <c r="H89" s="16"/>
       <c r="I89" s="11"/>
       <c r="J89" s="11"/>
       <c r="K89" s="11"/>
@@ -1986,7 +1927,7 @@
       <c r="E90" s="9"/>
       <c r="F90" s="9"/>
       <c r="G90" s="11"/>
-      <c r="H90" s="13"/>
+      <c r="H90" s="16"/>
       <c r="I90" s="11"/>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
@@ -1999,7 +1940,7 @@
       <c r="E91" s="9"/>
       <c r="F91" s="9"/>
       <c r="G91" s="11"/>
-      <c r="H91" s="13"/>
+      <c r="H91" s="16"/>
       <c r="I91" s="11"/>
       <c r="J91" s="11"/>
       <c r="K91" s="11"/>
@@ -2012,7 +1953,7 @@
       <c r="E92" s="9"/>
       <c r="F92" s="9"/>
       <c r="G92" s="11"/>
-      <c r="H92" s="13"/>
+      <c r="H92" s="16"/>
       <c r="I92" s="11"/>
       <c r="J92" s="11"/>
       <c r="K92" s="11"/>
@@ -2025,7 +1966,7 @@
       <c r="E93" s="9"/>
       <c r="F93" s="9"/>
       <c r="G93" s="11"/>
-      <c r="H93" s="13"/>
+      <c r="H93" s="16"/>
       <c r="I93" s="11"/>
       <c r="J93" s="11"/>
       <c r="K93" s="11"/>
@@ -2038,7 +1979,7 @@
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
       <c r="G94" s="11"/>
-      <c r="H94" s="13"/>
+      <c r="H94" s="16"/>
       <c r="I94" s="11"/>
       <c r="J94" s="11"/>
       <c r="K94" s="11"/>
@@ -2051,7 +1992,7 @@
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
       <c r="G95" s="11"/>
-      <c r="H95" s="13"/>
+      <c r="H95" s="16"/>
       <c r="I95" s="11"/>
       <c r="J95" s="11"/>
       <c r="K95" s="11"/>
@@ -2064,7 +2005,7 @@
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
       <c r="G96" s="11"/>
-      <c r="H96" s="13"/>
+      <c r="H96" s="16"/>
       <c r="I96" s="11"/>
       <c r="J96" s="11"/>
       <c r="K96" s="11"/>
@@ -2077,7 +2018,7 @@
       <c r="E97" s="9"/>
       <c r="F97" s="9"/>
       <c r="G97" s="11"/>
-      <c r="H97" s="13"/>
+      <c r="H97" s="16"/>
       <c r="I97" s="11"/>
       <c r="J97" s="11"/>
       <c r="K97" s="11"/>
@@ -2090,7 +2031,7 @@
       <c r="E98" s="9"/>
       <c r="F98" s="9"/>
       <c r="G98" s="11"/>
-      <c r="H98" s="13"/>
+      <c r="H98" s="16"/>
       <c r="I98" s="11"/>
       <c r="J98" s="11"/>
       <c r="K98" s="11"/>
@@ -2103,7 +2044,7 @@
       <c r="E99" s="9"/>
       <c r="F99" s="9"/>
       <c r="G99" s="11"/>
-      <c r="H99" s="13"/>
+      <c r="H99" s="16"/>
       <c r="I99" s="11"/>
       <c r="J99" s="11"/>
       <c r="K99" s="11"/>
@@ -2116,7 +2057,7 @@
       <c r="E100" s="9"/>
       <c r="F100" s="9"/>
       <c r="G100" s="11"/>
-      <c r="H100" s="13"/>
+      <c r="H100" s="16"/>
       <c r="I100" s="11"/>
       <c r="J100" s="11"/>
       <c r="K100" s="11"/>
@@ -2129,7 +2070,7 @@
       <c r="E101" s="9"/>
       <c r="F101" s="9"/>
       <c r="G101" s="11"/>
-      <c r="H101" s="13"/>
+      <c r="H101" s="16"/>
       <c r="I101" s="11"/>
       <c r="J101" s="11"/>
       <c r="K101" s="11"/>
@@ -2142,7 +2083,7 @@
       <c r="E102" s="9"/>
       <c r="F102" s="9"/>
       <c r="G102" s="11"/>
-      <c r="H102" s="13"/>
+      <c r="H102" s="16"/>
       <c r="I102" s="11"/>
       <c r="J102" s="11"/>
       <c r="K102" s="11"/>
@@ -2155,7 +2096,7 @@
       <c r="E103" s="9"/>
       <c r="F103" s="9"/>
       <c r="G103" s="11"/>
-      <c r="H103" s="13"/>
+      <c r="H103" s="16"/>
       <c r="I103" s="11"/>
       <c r="J103" s="11"/>
       <c r="K103" s="11"/>
@@ -2168,7 +2109,7 @@
       <c r="E104" s="9"/>
       <c r="F104" s="9"/>
       <c r="G104" s="11"/>
-      <c r="H104" s="13"/>
+      <c r="H104" s="16"/>
       <c r="I104" s="11"/>
       <c r="J104" s="11"/>
       <c r="K104" s="11"/>
@@ -2181,7 +2122,7 @@
       <c r="E105" s="9"/>
       <c r="F105" s="9"/>
       <c r="G105" s="11"/>
-      <c r="H105" s="13"/>
+      <c r="H105" s="16"/>
       <c r="I105" s="11"/>
       <c r="J105" s="11"/>
       <c r="K105" s="11"/>
@@ -2194,7 +2135,7 @@
       <c r="E106" s="9"/>
       <c r="F106" s="9"/>
       <c r="G106" s="11"/>
-      <c r="H106" s="13"/>
+      <c r="H106" s="16"/>
       <c r="I106" s="11"/>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
@@ -2207,7 +2148,7 @@
       <c r="E107" s="9"/>
       <c r="F107" s="9"/>
       <c r="G107" s="11"/>
-      <c r="H107" s="13"/>
+      <c r="H107" s="16"/>
       <c r="I107" s="11"/>
       <c r="J107" s="11"/>
       <c r="K107" s="11"/>
@@ -2220,7 +2161,7 @@
       <c r="E108" s="9"/>
       <c r="F108" s="9"/>
       <c r="G108" s="11"/>
-      <c r="H108" s="13"/>
+      <c r="H108" s="16"/>
       <c r="I108" s="11"/>
       <c r="J108" s="11"/>
       <c r="K108" s="11"/>
@@ -2233,7 +2174,7 @@
       <c r="E109" s="9"/>
       <c r="F109" s="9"/>
       <c r="G109" s="11"/>
-      <c r="H109" s="13"/>
+      <c r="H109" s="16"/>
       <c r="I109" s="11"/>
       <c r="J109" s="11"/>
       <c r="K109" s="11"/>
@@ -2246,7 +2187,7 @@
       <c r="E110" s="9"/>
       <c r="F110" s="9"/>
       <c r="G110" s="11"/>
-      <c r="H110" s="13"/>
+      <c r="H110" s="16"/>
       <c r="I110" s="11"/>
       <c r="J110" s="11"/>
       <c r="K110" s="11"/>
@@ -2259,7 +2200,7 @@
       <c r="E111" s="9"/>
       <c r="F111" s="9"/>
       <c r="G111" s="11"/>
-      <c r="H111" s="13"/>
+      <c r="H111" s="16"/>
       <c r="I111" s="11"/>
       <c r="J111" s="11"/>
       <c r="K111" s="11"/>
@@ -2272,7 +2213,7 @@
       <c r="E112" s="9"/>
       <c r="F112" s="9"/>
       <c r="G112" s="11"/>
-      <c r="H112" s="13"/>
+      <c r="H112" s="16"/>
       <c r="I112" s="11"/>
       <c r="J112" s="11"/>
       <c r="K112" s="11"/>
@@ -2285,7 +2226,7 @@
       <c r="E113" s="9"/>
       <c r="F113" s="9"/>
       <c r="G113" s="11"/>
-      <c r="H113" s="13"/>
+      <c r="H113" s="16"/>
       <c r="I113" s="11"/>
       <c r="J113" s="11"/>
       <c r="K113" s="11"/>
@@ -2298,7 +2239,7 @@
       <c r="E114" s="9"/>
       <c r="F114" s="9"/>
       <c r="G114" s="11"/>
-      <c r="H114" s="13"/>
+      <c r="H114" s="16"/>
       <c r="I114" s="11"/>
       <c r="J114" s="11"/>
       <c r="K114" s="11"/>
@@ -2311,7 +2252,7 @@
       <c r="E115" s="9"/>
       <c r="F115" s="9"/>
       <c r="G115" s="11"/>
-      <c r="H115" s="13"/>
+      <c r="H115" s="16"/>
       <c r="I115" s="11"/>
       <c r="J115" s="11"/>
       <c r="K115" s="11"/>
@@ -2324,7 +2265,7 @@
       <c r="E116" s="9"/>
       <c r="F116" s="9"/>
       <c r="G116" s="11"/>
-      <c r="H116" s="13"/>
+      <c r="H116" s="16"/>
       <c r="I116" s="11"/>
       <c r="J116" s="11"/>
       <c r="K116" s="11"/>
@@ -2337,7 +2278,7 @@
       <c r="E117" s="9"/>
       <c r="F117" s="9"/>
       <c r="G117" s="11"/>
-      <c r="H117" s="13"/>
+      <c r="H117" s="16"/>
       <c r="I117" s="11"/>
       <c r="J117" s="11"/>
       <c r="K117" s="11"/>
@@ -2350,7 +2291,7 @@
       <c r="E118" s="9"/>
       <c r="F118" s="9"/>
       <c r="G118" s="11"/>
-      <c r="H118" s="13"/>
+      <c r="H118" s="16"/>
       <c r="I118" s="11"/>
       <c r="J118" s="11"/>
       <c r="K118" s="11"/>
@@ -2363,7 +2304,7 @@
       <c r="E119" s="9"/>
       <c r="F119" s="9"/>
       <c r="G119" s="11"/>
-      <c r="H119" s="13"/>
+      <c r="H119" s="16"/>
       <c r="I119" s="11"/>
       <c r="J119" s="11"/>
       <c r="K119" s="11"/>
@@ -2376,7 +2317,7 @@
       <c r="E120" s="9"/>
       <c r="F120" s="9"/>
       <c r="G120" s="11"/>
-      <c r="H120" s="13"/>
+      <c r="H120" s="16"/>
       <c r="I120" s="11"/>
       <c r="J120" s="11"/>
       <c r="K120" s="11"/>
@@ -2389,7 +2330,7 @@
       <c r="E121" s="9"/>
       <c r="F121" s="9"/>
       <c r="G121" s="11"/>
-      <c r="H121" s="13"/>
+      <c r="H121" s="16"/>
       <c r="I121" s="11"/>
       <c r="J121" s="11"/>
       <c r="K121" s="11"/>
@@ -2402,7 +2343,7 @@
       <c r="E122" s="9"/>
       <c r="F122" s="9"/>
       <c r="G122" s="11"/>
-      <c r="H122" s="13"/>
+      <c r="H122" s="16"/>
       <c r="I122" s="11"/>
       <c r="J122" s="11"/>
       <c r="K122" s="11"/>
@@ -2415,7 +2356,7 @@
       <c r="E123" s="9"/>
       <c r="F123" s="9"/>
       <c r="G123" s="11"/>
-      <c r="H123" s="13"/>
+      <c r="H123" s="16"/>
       <c r="I123" s="11"/>
       <c r="J123" s="11"/>
       <c r="K123" s="11"/>
@@ -2428,7 +2369,7 @@
       <c r="E124" s="9"/>
       <c r="F124" s="9"/>
       <c r="G124" s="11"/>
-      <c r="H124" s="13"/>
+      <c r="H124" s="16"/>
       <c r="I124" s="11"/>
       <c r="J124" s="11"/>
       <c r="K124" s="11"/>
@@ -2441,7 +2382,7 @@
       <c r="E125" s="9"/>
       <c r="F125" s="9"/>
       <c r="G125" s="11"/>
-      <c r="H125" s="13"/>
+      <c r="H125" s="16"/>
       <c r="I125" s="11"/>
       <c r="J125" s="11"/>
       <c r="K125" s="11"/>
@@ -2454,7 +2395,7 @@
       <c r="E126" s="9"/>
       <c r="F126" s="9"/>
       <c r="G126" s="11"/>
-      <c r="H126" s="13"/>
+      <c r="H126" s="16"/>
       <c r="I126" s="11"/>
       <c r="J126" s="11"/>
       <c r="K126" s="11"/>
@@ -2467,7 +2408,7 @@
       <c r="E127" s="9"/>
       <c r="F127" s="9"/>
       <c r="G127" s="11"/>
-      <c r="H127" s="13"/>
+      <c r="H127" s="16"/>
       <c r="I127" s="11"/>
       <c r="J127" s="11"/>
       <c r="K127" s="11"/>
@@ -2480,7 +2421,7 @@
       <c r="E128" s="9"/>
       <c r="F128" s="9"/>
       <c r="G128" s="11"/>
-      <c r="H128" s="13"/>
+      <c r="H128" s="16"/>
       <c r="I128" s="11"/>
       <c r="J128" s="11"/>
       <c r="K128" s="11"/>
@@ -2493,7 +2434,7 @@
       <c r="E129" s="9"/>
       <c r="F129" s="9"/>
       <c r="G129" s="11"/>
-      <c r="H129" s="13"/>
+      <c r="H129" s="16"/>
       <c r="I129" s="11"/>
       <c r="J129" s="11"/>
       <c r="K129" s="11"/>
@@ -2506,7 +2447,7 @@
       <c r="E130" s="9"/>
       <c r="F130" s="9"/>
       <c r="G130" s="11"/>
-      <c r="H130" s="13"/>
+      <c r="H130" s="16"/>
       <c r="I130" s="11"/>
       <c r="J130" s="11"/>
       <c r="K130" s="11"/>
@@ -2519,7 +2460,7 @@
       <c r="E131" s="9"/>
       <c r="F131" s="9"/>
       <c r="G131" s="11"/>
-      <c r="H131" s="13"/>
+      <c r="H131" s="16"/>
       <c r="I131" s="11"/>
       <c r="J131" s="11"/>
       <c r="K131" s="11"/>
@@ -2532,7 +2473,7 @@
       <c r="E132" s="9"/>
       <c r="F132" s="9"/>
       <c r="G132" s="11"/>
-      <c r="H132" s="13"/>
+      <c r="H132" s="16"/>
       <c r="I132" s="11"/>
       <c r="J132" s="11"/>
       <c r="K132" s="11"/>
@@ -2545,7 +2486,7 @@
       <c r="E133" s="9"/>
       <c r="F133" s="9"/>
       <c r="G133" s="11"/>
-      <c r="H133" s="13"/>
+      <c r="H133" s="16"/>
       <c r="I133" s="11"/>
       <c r="J133" s="11"/>
       <c r="K133" s="11"/>
@@ -2558,7 +2499,7 @@
       <c r="E134" s="9"/>
       <c r="F134" s="9"/>
       <c r="G134" s="11"/>
-      <c r="H134" s="13"/>
+      <c r="H134" s="16"/>
       <c r="I134" s="11"/>
       <c r="J134" s="11"/>
       <c r="K134" s="11"/>
@@ -2571,7 +2512,7 @@
       <c r="E135" s="9"/>
       <c r="F135" s="9"/>
       <c r="G135" s="11"/>
-      <c r="H135" s="13"/>
+      <c r="H135" s="16"/>
       <c r="I135" s="11"/>
       <c r="J135" s="11"/>
       <c r="K135" s="11"/>
@@ -2584,7 +2525,7 @@
       <c r="E136" s="9"/>
       <c r="F136" s="9"/>
       <c r="G136" s="11"/>
-      <c r="H136" s="13"/>
+      <c r="H136" s="16"/>
       <c r="I136" s="11"/>
       <c r="J136" s="11"/>
       <c r="K136" s="11"/>
@@ -2597,7 +2538,7 @@
       <c r="E137" s="9"/>
       <c r="F137" s="9"/>
       <c r="G137" s="11"/>
-      <c r="H137" s="13"/>
+      <c r="H137" s="16"/>
       <c r="I137" s="11"/>
       <c r="J137" s="11"/>
       <c r="K137" s="11"/>
@@ -2610,7 +2551,7 @@
       <c r="E138" s="9"/>
       <c r="F138" s="9"/>
       <c r="G138" s="11"/>
-      <c r="H138" s="13"/>
+      <c r="H138" s="16"/>
       <c r="I138" s="11"/>
       <c r="J138" s="11"/>
       <c r="K138" s="11"/>
@@ -2623,7 +2564,7 @@
       <c r="E139" s="9"/>
       <c r="F139" s="9"/>
       <c r="G139" s="11"/>
-      <c r="H139" s="13"/>
+      <c r="H139" s="16"/>
       <c r="I139" s="11"/>
       <c r="J139" s="11"/>
       <c r="K139" s="11"/>
@@ -2636,7 +2577,7 @@
       <c r="E140" s="9"/>
       <c r="F140" s="9"/>
       <c r="G140" s="11"/>
-      <c r="H140" s="13"/>
+      <c r="H140" s="16"/>
       <c r="I140" s="11"/>
       <c r="J140" s="11"/>
       <c r="K140" s="11"/>
@@ -2649,7 +2590,7 @@
       <c r="E141" s="9"/>
       <c r="F141" s="9"/>
       <c r="G141" s="11"/>
-      <c r="H141" s="13"/>
+      <c r="H141" s="16"/>
       <c r="I141" s="11"/>
       <c r="J141" s="11"/>
       <c r="K141" s="11"/>
@@ -2662,7 +2603,7 @@
       <c r="E142" s="9"/>
       <c r="F142" s="9"/>
       <c r="G142" s="11"/>
-      <c r="H142" s="13"/>
+      <c r="H142" s="16"/>
       <c r="I142" s="11"/>
       <c r="J142" s="11"/>
       <c r="K142" s="11"/>
@@ -2675,7 +2616,7 @@
       <c r="E143" s="9"/>
       <c r="F143" s="9"/>
       <c r="G143" s="11"/>
-      <c r="H143" s="13"/>
+      <c r="H143" s="16"/>
       <c r="I143" s="11"/>
       <c r="J143" s="11"/>
       <c r="K143" s="11"/>
@@ -2688,7 +2629,7 @@
       <c r="E144" s="9"/>
       <c r="F144" s="9"/>
       <c r="G144" s="11"/>
-      <c r="H144" s="13"/>
+      <c r="H144" s="16"/>
       <c r="I144" s="11"/>
       <c r="J144" s="11"/>
       <c r="K144" s="11"/>
@@ -2701,7 +2642,7 @@
       <c r="E145" s="9"/>
       <c r="F145" s="9"/>
       <c r="G145" s="11"/>
-      <c r="H145" s="13"/>
+      <c r="H145" s="16"/>
       <c r="I145" s="11"/>
       <c r="J145" s="11"/>
       <c r="K145" s="11"/>
@@ -2714,7 +2655,7 @@
       <c r="E146" s="9"/>
       <c r="F146" s="9"/>
       <c r="G146" s="11"/>
-      <c r="H146" s="13"/>
+      <c r="H146" s="16"/>
       <c r="I146" s="11"/>
       <c r="J146" s="11"/>
       <c r="K146" s="11"/>
@@ -2727,7 +2668,7 @@
       <c r="E147" s="9"/>
       <c r="F147" s="9"/>
       <c r="G147" s="11"/>
-      <c r="H147" s="13"/>
+      <c r="H147" s="16"/>
       <c r="I147" s="11"/>
       <c r="J147" s="11"/>
       <c r="K147" s="11"/>
@@ -2740,7 +2681,7 @@
       <c r="E148" s="9"/>
       <c r="F148" s="9"/>
       <c r="G148" s="11"/>
-      <c r="H148" s="13"/>
+      <c r="H148" s="16"/>
       <c r="I148" s="11"/>
       <c r="J148" s="11"/>
       <c r="K148" s="11"/>
@@ -2753,7 +2694,7 @@
       <c r="E149" s="9"/>
       <c r="F149" s="9"/>
       <c r="G149" s="11"/>
-      <c r="H149" s="13"/>
+      <c r="H149" s="16"/>
       <c r="I149" s="11"/>
       <c r="J149" s="11"/>
       <c r="K149" s="11"/>
@@ -2766,7 +2707,7 @@
       <c r="E150" s="9"/>
       <c r="F150" s="9"/>
       <c r="G150" s="11"/>
-      <c r="H150" s="13"/>
+      <c r="H150" s="16"/>
       <c r="I150" s="11"/>
       <c r="J150" s="11"/>
       <c r="K150" s="11"/>
@@ -2779,7 +2720,7 @@
       <c r="E151" s="9"/>
       <c r="F151" s="9"/>
       <c r="G151" s="11"/>
-      <c r="H151" s="13"/>
+      <c r="H151" s="16"/>
       <c r="I151" s="11"/>
       <c r="J151" s="11"/>
       <c r="K151" s="11"/>
@@ -2792,7 +2733,7 @@
       <c r="E152" s="9"/>
       <c r="F152" s="9"/>
       <c r="G152" s="11"/>
-      <c r="H152" s="13"/>
+      <c r="H152" s="16"/>
       <c r="I152" s="11"/>
       <c r="J152" s="11"/>
       <c r="K152" s="11"/>
@@ -2805,7 +2746,7 @@
       <c r="E153" s="9"/>
       <c r="F153" s="9"/>
       <c r="G153" s="11"/>
-      <c r="H153" s="13"/>
+      <c r="H153" s="16"/>
       <c r="I153" s="11"/>
       <c r="J153" s="11"/>
       <c r="K153" s="11"/>
@@ -2818,7 +2759,7 @@
       <c r="E154" s="9"/>
       <c r="F154" s="9"/>
       <c r="G154" s="11"/>
-      <c r="H154" s="13"/>
+      <c r="H154" s="16"/>
       <c r="I154" s="11"/>
       <c r="J154" s="11"/>
       <c r="K154" s="11"/>
@@ -2831,7 +2772,7 @@
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
       <c r="G155" s="11"/>
-      <c r="H155" s="13"/>
+      <c r="H155" s="16"/>
       <c r="I155" s="11"/>
       <c r="J155" s="11"/>
       <c r="K155" s="11"/>
@@ -2844,7 +2785,7 @@
       <c r="E156" s="9"/>
       <c r="F156" s="9"/>
       <c r="G156" s="11"/>
-      <c r="H156" s="13"/>
+      <c r="H156" s="16"/>
       <c r="I156" s="11"/>
       <c r="J156" s="11"/>
       <c r="K156" s="11"/>
@@ -2857,7 +2798,7 @@
       <c r="E157" s="9"/>
       <c r="F157" s="9"/>
       <c r="G157" s="11"/>
-      <c r="H157" s="13"/>
+      <c r="H157" s="16"/>
       <c r="I157" s="11"/>
       <c r="J157" s="11"/>
       <c r="K157" s="11"/>
@@ -2870,7 +2811,7 @@
       <c r="E158" s="9"/>
       <c r="F158" s="9"/>
       <c r="G158" s="11"/>
-      <c r="H158" s="13"/>
+      <c r="H158" s="16"/>
       <c r="I158" s="11"/>
       <c r="J158" s="11"/>
       <c r="K158" s="11"/>
@@ -2883,7 +2824,7 @@
       <c r="E159" s="9"/>
       <c r="F159" s="9"/>
       <c r="G159" s="11"/>
-      <c r="H159" s="13"/>
+      <c r="H159" s="16"/>
       <c r="I159" s="11"/>
       <c r="J159" s="11"/>
       <c r="K159" s="11"/>
@@ -2896,7 +2837,7 @@
       <c r="E160" s="9"/>
       <c r="F160" s="9"/>
       <c r="G160" s="11"/>
-      <c r="H160" s="13"/>
+      <c r="H160" s="16"/>
       <c r="I160" s="11"/>
       <c r="J160" s="11"/>
       <c r="K160" s="11"/>
@@ -2909,7 +2850,7 @@
       <c r="E161" s="9"/>
       <c r="F161" s="9"/>
       <c r="G161" s="11"/>
-      <c r="H161" s="13"/>
+      <c r="H161" s="16"/>
       <c r="I161" s="11"/>
       <c r="J161" s="11"/>
       <c r="K161" s="11"/>
@@ -2922,7 +2863,7 @@
       <c r="E162" s="9"/>
       <c r="F162" s="9"/>
       <c r="G162" s="11"/>
-      <c r="H162" s="13"/>
+      <c r="H162" s="16"/>
       <c r="I162" s="11"/>
       <c r="J162" s="11"/>
       <c r="K162" s="11"/>
@@ -2935,7 +2876,7 @@
       <c r="E163" s="9"/>
       <c r="F163" s="9"/>
       <c r="G163" s="11"/>
-      <c r="H163" s="13"/>
+      <c r="H163" s="16"/>
       <c r="I163" s="11"/>
       <c r="J163" s="11"/>
       <c r="K163" s="11"/>
@@ -2948,7 +2889,7 @@
       <c r="E164" s="9"/>
       <c r="F164" s="9"/>
       <c r="G164" s="11"/>
-      <c r="H164" s="13"/>
+      <c r="H164" s="16"/>
       <c r="I164" s="11"/>
       <c r="J164" s="11"/>
       <c r="K164" s="11"/>
@@ -2961,7 +2902,7 @@
       <c r="E165" s="9"/>
       <c r="F165" s="9"/>
       <c r="G165" s="11"/>
-      <c r="H165" s="13"/>
+      <c r="H165" s="16"/>
       <c r="I165" s="11"/>
       <c r="J165" s="11"/>
       <c r="K165" s="11"/>
@@ -2974,7 +2915,7 @@
       <c r="E166" s="9"/>
       <c r="F166" s="9"/>
       <c r="G166" s="11"/>
-      <c r="H166" s="13"/>
+      <c r="H166" s="16"/>
       <c r="I166" s="11"/>
       <c r="J166" s="11"/>
       <c r="K166" s="11"/>
@@ -2987,7 +2928,7 @@
       <c r="E167" s="9"/>
       <c r="F167" s="9"/>
       <c r="G167" s="11"/>
-      <c r="H167" s="13"/>
+      <c r="H167" s="16"/>
       <c r="I167" s="11"/>
       <c r="J167" s="11"/>
       <c r="K167" s="11"/>
@@ -3000,7 +2941,7 @@
       <c r="E168" s="9"/>
       <c r="F168" s="9"/>
       <c r="G168" s="11"/>
-      <c r="H168" s="13"/>
+      <c r="H168" s="16"/>
       <c r="I168" s="11"/>
       <c r="J168" s="11"/>
       <c r="K168" s="11"/>
@@ -3013,7 +2954,7 @@
       <c r="E169" s="9"/>
       <c r="F169" s="9"/>
       <c r="G169" s="11"/>
-      <c r="H169" s="13"/>
+      <c r="H169" s="16"/>
       <c r="I169" s="11"/>
       <c r="J169" s="11"/>
       <c r="K169" s="11"/>
@@ -3026,7 +2967,7 @@
       <c r="E170" s="9"/>
       <c r="F170" s="9"/>
       <c r="G170" s="11"/>
-      <c r="H170" s="13"/>
+      <c r="H170" s="16"/>
       <c r="I170" s="11"/>
       <c r="J170" s="11"/>
       <c r="K170" s="11"/>
@@ -3039,7 +2980,7 @@
       <c r="E171" s="9"/>
       <c r="F171" s="9"/>
       <c r="G171" s="11"/>
-      <c r="H171" s="13"/>
+      <c r="H171" s="16"/>
       <c r="I171" s="11"/>
       <c r="J171" s="11"/>
       <c r="K171" s="11"/>
@@ -3052,7 +2993,7 @@
       <c r="E172" s="9"/>
       <c r="F172" s="9"/>
       <c r="G172" s="11"/>
-      <c r="H172" s="13"/>
+      <c r="H172" s="16"/>
       <c r="I172" s="11"/>
       <c r="J172" s="11"/>
       <c r="K172" s="11"/>
@@ -3065,7 +3006,7 @@
       <c r="E173" s="9"/>
       <c r="F173" s="9"/>
       <c r="G173" s="11"/>
-      <c r="H173" s="13"/>
+      <c r="H173" s="16"/>
       <c r="I173" s="11"/>
       <c r="J173" s="11"/>
       <c r="K173" s="11"/>
@@ -3078,7 +3019,7 @@
       <c r="E174" s="9"/>
       <c r="F174" s="9"/>
       <c r="G174" s="11"/>
-      <c r="H174" s="13"/>
+      <c r="H174" s="16"/>
       <c r="I174" s="11"/>
       <c r="J174" s="11"/>
       <c r="K174" s="11"/>
@@ -3091,7 +3032,7 @@
       <c r="E175" s="9"/>
       <c r="F175" s="9"/>
       <c r="G175" s="11"/>
-      <c r="H175" s="13"/>
+      <c r="H175" s="16"/>
       <c r="I175" s="11"/>
       <c r="J175" s="11"/>
       <c r="K175" s="11"/>
@@ -3104,7 +3045,7 @@
       <c r="E176" s="9"/>
       <c r="F176" s="9"/>
       <c r="G176" s="11"/>
-      <c r="H176" s="13"/>
+      <c r="H176" s="16"/>
       <c r="I176" s="11"/>
       <c r="J176" s="11"/>
       <c r="K176" s="11"/>
@@ -3117,7 +3058,7 @@
       <c r="E177" s="9"/>
       <c r="F177" s="9"/>
       <c r="G177" s="11"/>
-      <c r="H177" s="13"/>
+      <c r="H177" s="16"/>
       <c r="I177" s="11"/>
       <c r="J177" s="11"/>
       <c r="K177" s="11"/>
@@ -3130,7 +3071,7 @@
       <c r="E178" s="9"/>
       <c r="F178" s="9"/>
       <c r="G178" s="11"/>
-      <c r="H178" s="13"/>
+      <c r="H178" s="16"/>
       <c r="I178" s="11"/>
       <c r="J178" s="11"/>
       <c r="K178" s="11"/>
@@ -3143,7 +3084,7 @@
       <c r="E179" s="9"/>
       <c r="F179" s="9"/>
       <c r="G179" s="11"/>
-      <c r="H179" s="13"/>
+      <c r="H179" s="16"/>
       <c r="I179" s="11"/>
       <c r="J179" s="11"/>
       <c r="K179" s="11"/>
@@ -3156,7 +3097,7 @@
       <c r="E180" s="9"/>
       <c r="F180" s="9"/>
       <c r="G180" s="11"/>
-      <c r="H180" s="13"/>
+      <c r="H180" s="16"/>
       <c r="I180" s="11"/>
       <c r="J180" s="11"/>
       <c r="K180" s="11"/>
@@ -3169,7 +3110,7 @@
       <c r="E181" s="9"/>
       <c r="F181" s="9"/>
       <c r="G181" s="11"/>
-      <c r="H181" s="13"/>
+      <c r="H181" s="16"/>
       <c r="I181" s="11"/>
       <c r="J181" s="11"/>
       <c r="K181" s="11"/>
@@ -3182,7 +3123,7 @@
       <c r="E182" s="9"/>
       <c r="F182" s="9"/>
       <c r="G182" s="11"/>
-      <c r="H182" s="13"/>
+      <c r="H182" s="16"/>
       <c r="I182" s="11"/>
       <c r="J182" s="11"/>
       <c r="K182" s="11"/>
@@ -3195,7 +3136,7 @@
       <c r="E183" s="9"/>
       <c r="F183" s="9"/>
       <c r="G183" s="11"/>
-      <c r="H183" s="13"/>
+      <c r="H183" s="16"/>
       <c r="I183" s="11"/>
       <c r="J183" s="11"/>
       <c r="K183" s="11"/>
@@ -3208,7 +3149,7 @@
       <c r="E184" s="9"/>
       <c r="F184" s="9"/>
       <c r="G184" s="11"/>
-      <c r="H184" s="13"/>
+      <c r="H184" s="16"/>
       <c r="I184" s="11"/>
       <c r="J184" s="11"/>
       <c r="K184" s="11"/>
@@ -3221,7 +3162,7 @@
       <c r="E185" s="9"/>
       <c r="F185" s="9"/>
       <c r="G185" s="11"/>
-      <c r="H185" s="13"/>
+      <c r="H185" s="16"/>
       <c r="I185" s="11"/>
       <c r="J185" s="11"/>
       <c r="K185" s="11"/>
@@ -3234,7 +3175,7 @@
       <c r="E186" s="9"/>
       <c r="F186" s="9"/>
       <c r="G186" s="11"/>
-      <c r="H186" s="13"/>
+      <c r="H186" s="16"/>
       <c r="I186" s="11"/>
       <c r="J186" s="11"/>
       <c r="K186" s="11"/>
@@ -3247,7 +3188,7 @@
       <c r="E187" s="9"/>
       <c r="F187" s="9"/>
       <c r="G187" s="11"/>
-      <c r="H187" s="13"/>
+      <c r="H187" s="16"/>
       <c r="I187" s="11"/>
       <c r="J187" s="11"/>
       <c r="K187" s="11"/>
@@ -3260,7 +3201,7 @@
       <c r="E188" s="9"/>
       <c r="F188" s="9"/>
       <c r="G188" s="11"/>
-      <c r="H188" s="13"/>
+      <c r="H188" s="16"/>
       <c r="I188" s="11"/>
       <c r="J188" s="11"/>
       <c r="K188" s="11"/>
@@ -3273,7 +3214,7 @@
       <c r="E189" s="9"/>
       <c r="F189" s="9"/>
       <c r="G189" s="11"/>
-      <c r="H189" s="13"/>
+      <c r="H189" s="16"/>
       <c r="I189" s="11"/>
       <c r="J189" s="11"/>
       <c r="K189" s="11"/>
@@ -3286,7 +3227,7 @@
       <c r="E190" s="9"/>
       <c r="F190" s="9"/>
       <c r="G190" s="11"/>
-      <c r="H190" s="13"/>
+      <c r="H190" s="16"/>
       <c r="I190" s="11"/>
       <c r="J190" s="11"/>
       <c r="K190" s="11"/>
@@ -3299,7 +3240,7 @@
       <c r="E191" s="9"/>
       <c r="F191" s="9"/>
       <c r="G191" s="11"/>
-      <c r="H191" s="13"/>
+      <c r="H191" s="16"/>
       <c r="I191" s="11"/>
       <c r="J191" s="11"/>
       <c r="K191" s="11"/>
@@ -3312,7 +3253,7 @@
       <c r="E192" s="9"/>
       <c r="F192" s="9"/>
       <c r="G192" s="11"/>
-      <c r="H192" s="13"/>
+      <c r="H192" s="16"/>
       <c r="I192" s="11"/>
       <c r="J192" s="11"/>
       <c r="K192" s="11"/>
@@ -3325,7 +3266,7 @@
       <c r="E193" s="9"/>
       <c r="F193" s="9"/>
       <c r="G193" s="11"/>
-      <c r="H193" s="13"/>
+      <c r="H193" s="16"/>
       <c r="I193" s="11"/>
       <c r="J193" s="11"/>
       <c r="K193" s="11"/>
@@ -3338,7 +3279,7 @@
       <c r="E194" s="9"/>
       <c r="F194" s="9"/>
       <c r="G194" s="11"/>
-      <c r="H194" s="13"/>
+      <c r="H194" s="16"/>
       <c r="I194" s="11"/>
       <c r="J194" s="11"/>
       <c r="K194" s="11"/>
@@ -3351,7 +3292,7 @@
       <c r="E195" s="9"/>
       <c r="F195" s="9"/>
       <c r="G195" s="11"/>
-      <c r="H195" s="13"/>
+      <c r="H195" s="16"/>
       <c r="I195" s="11"/>
       <c r="J195" s="11"/>
       <c r="K195" s="11"/>
@@ -3364,7 +3305,7 @@
       <c r="E196" s="9"/>
       <c r="F196" s="9"/>
       <c r="G196" s="11"/>
-      <c r="H196" s="13"/>
+      <c r="H196" s="16"/>
       <c r="I196" s="11"/>
       <c r="J196" s="11"/>
       <c r="K196" s="11"/>
@@ -3377,7 +3318,7 @@
       <c r="E197" s="9"/>
       <c r="F197" s="9"/>
       <c r="G197" s="11"/>
-      <c r="H197" s="13"/>
+      <c r="H197" s="16"/>
       <c r="I197" s="11"/>
       <c r="J197" s="11"/>
       <c r="K197" s="11"/>
@@ -3390,7 +3331,7 @@
       <c r="E198" s="9"/>
       <c r="F198" s="9"/>
       <c r="G198" s="11"/>
-      <c r="H198" s="13"/>
+      <c r="H198" s="16"/>
       <c r="I198" s="11"/>
       <c r="J198" s="11"/>
       <c r="K198" s="11"/>
@@ -3403,7 +3344,7 @@
       <c r="E199" s="9"/>
       <c r="F199" s="9"/>
       <c r="G199" s="11"/>
-      <c r="H199" s="13"/>
+      <c r="H199" s="16"/>
       <c r="I199" s="11"/>
       <c r="J199" s="11"/>
       <c r="K199" s="11"/>
@@ -3416,7 +3357,7 @@
       <c r="E200" s="9"/>
       <c r="F200" s="9"/>
       <c r="G200" s="11"/>
-      <c r="H200" s="13"/>
+      <c r="H200" s="16"/>
       <c r="I200" s="11"/>
       <c r="J200" s="11"/>
       <c r="K200" s="11"/>
@@ -3429,7 +3370,7 @@
       <c r="E201" s="9"/>
       <c r="F201" s="9"/>
       <c r="G201" s="11"/>
-      <c r="H201" s="13"/>
+      <c r="H201" s="16"/>
       <c r="I201" s="11"/>
       <c r="J201" s="11"/>
       <c r="K201" s="11"/>
@@ -3442,7 +3383,7 @@
       <c r="E202" s="9"/>
       <c r="F202" s="9"/>
       <c r="G202" s="11"/>
-      <c r="H202" s="13"/>
+      <c r="H202" s="16"/>
       <c r="I202" s="11"/>
       <c r="J202" s="11"/>
       <c r="K202" s="11"/>
@@ -3455,7 +3396,7 @@
       <c r="E203" s="9"/>
       <c r="F203" s="9"/>
       <c r="G203" s="11"/>
-      <c r="H203" s="13"/>
+      <c r="H203" s="16"/>
       <c r="I203" s="11"/>
       <c r="J203" s="11"/>
       <c r="K203" s="11"/>
@@ -3468,7 +3409,7 @@
       <c r="E204" s="9"/>
       <c r="F204" s="9"/>
       <c r="G204" s="11"/>
-      <c r="H204" s="13"/>
+      <c r="H204" s="16"/>
       <c r="I204" s="11"/>
       <c r="J204" s="11"/>
       <c r="K204" s="11"/>
@@ -3481,7 +3422,7 @@
       <c r="E205" s="9"/>
       <c r="F205" s="9"/>
       <c r="G205" s="11"/>
-      <c r="H205" s="13"/>
+      <c r="H205" s="16"/>
       <c r="I205" s="11"/>
       <c r="J205" s="11"/>
       <c r="K205" s="11"/>
@@ -3494,7 +3435,7 @@
       <c r="E206" s="9"/>
       <c r="F206" s="9"/>
       <c r="G206" s="11"/>
-      <c r="H206" s="13"/>
+      <c r="H206" s="16"/>
       <c r="I206" s="11"/>
       <c r="J206" s="11"/>
       <c r="K206" s="11"/>
@@ -3507,7 +3448,7 @@
       <c r="E207" s="9"/>
       <c r="F207" s="9"/>
       <c r="G207" s="11"/>
-      <c r="H207" s="13"/>
+      <c r="H207" s="16"/>
       <c r="I207" s="11"/>
       <c r="J207" s="11"/>
       <c r="K207" s="11"/>
@@ -3520,7 +3461,7 @@
       <c r="E208" s="9"/>
       <c r="F208" s="9"/>
       <c r="G208" s="11"/>
-      <c r="H208" s="13"/>
+      <c r="H208" s="16"/>
       <c r="I208" s="11"/>
       <c r="J208" s="11"/>
       <c r="K208" s="11"/>
@@ -3533,7 +3474,7 @@
       <c r="E209" s="9"/>
       <c r="F209" s="9"/>
       <c r="G209" s="11"/>
-      <c r="H209" s="13"/>
+      <c r="H209" s="16"/>
       <c r="I209" s="11"/>
       <c r="J209" s="11"/>
       <c r="K209" s="11"/>
@@ -3546,7 +3487,7 @@
       <c r="E210" s="9"/>
       <c r="F210" s="9"/>
       <c r="G210" s="11"/>
-      <c r="H210" s="13"/>
+      <c r="H210" s="16"/>
       <c r="I210" s="11"/>
       <c r="J210" s="11"/>
       <c r="K210" s="11"/>
@@ -3559,7 +3500,7 @@
       <c r="E211" s="9"/>
       <c r="F211" s="9"/>
       <c r="G211" s="11"/>
-      <c r="H211" s="13"/>
+      <c r="H211" s="16"/>
       <c r="I211" s="11"/>
       <c r="J211" s="11"/>
       <c r="K211" s="11"/>
@@ -3572,7 +3513,7 @@
       <c r="E212" s="9"/>
       <c r="F212" s="9"/>
       <c r="G212" s="11"/>
-      <c r="H212" s="13"/>
+      <c r="H212" s="16"/>
       <c r="I212" s="11"/>
       <c r="J212" s="11"/>
       <c r="K212" s="11"/>
@@ -3585,7 +3526,7 @@
       <c r="E213" s="9"/>
       <c r="F213" s="9"/>
       <c r="G213" s="11"/>
-      <c r="H213" s="13"/>
+      <c r="H213" s="16"/>
       <c r="I213" s="11"/>
       <c r="J213" s="11"/>
       <c r="K213" s="11"/>
@@ -3598,7 +3539,7 @@
       <c r="E214" s="9"/>
       <c r="F214" s="9"/>
       <c r="G214" s="11"/>
-      <c r="H214" s="13"/>
+      <c r="H214" s="16"/>
       <c r="I214" s="11"/>
       <c r="J214" s="11"/>
       <c r="K214" s="11"/>
@@ -3611,7 +3552,7 @@
       <c r="E215" s="9"/>
       <c r="F215" s="9"/>
       <c r="G215" s="11"/>
-      <c r="H215" s="13"/>
+      <c r="H215" s="16"/>
       <c r="I215" s="11"/>
       <c r="J215" s="11"/>
       <c r="K215" s="11"/>
@@ -3624,7 +3565,7 @@
       <c r="E216" s="9"/>
       <c r="F216" s="9"/>
       <c r="G216" s="11"/>
-      <c r="H216" s="13"/>
+      <c r="H216" s="16"/>
       <c r="I216" s="11"/>
       <c r="J216" s="11"/>
       <c r="K216" s="11"/>
@@ -3637,7 +3578,7 @@
       <c r="E217" s="9"/>
       <c r="F217" s="9"/>
       <c r="G217" s="11"/>
-      <c r="H217" s="13"/>
+      <c r="H217" s="16"/>
       <c r="I217" s="11"/>
       <c r="J217" s="11"/>
       <c r="K217" s="11"/>
@@ -3650,7 +3591,7 @@
       <c r="E218" s="9"/>
       <c r="F218" s="9"/>
       <c r="G218" s="11"/>
-      <c r="H218" s="13"/>
+      <c r="H218" s="16"/>
       <c r="I218" s="11"/>
       <c r="J218" s="11"/>
       <c r="K218" s="11"/>
@@ -3663,7 +3604,7 @@
       <c r="E219" s="9"/>
       <c r="F219" s="9"/>
       <c r="G219" s="11"/>
-      <c r="H219" s="13"/>
+      <c r="H219" s="16"/>
       <c r="I219" s="11"/>
       <c r="J219" s="11"/>
       <c r="K219" s="11"/>
@@ -3676,7 +3617,7 @@
       <c r="E220" s="9"/>
       <c r="F220" s="9"/>
       <c r="G220" s="11"/>
-      <c r="H220" s="13"/>
+      <c r="H220" s="16"/>
       <c r="I220" s="11"/>
       <c r="J220" s="11"/>
       <c r="K220" s="11"/>
@@ -3689,7 +3630,7 @@
       <c r="E221" s="9"/>
       <c r="F221" s="9"/>
       <c r="G221" s="11"/>
-      <c r="H221" s="13"/>
+      <c r="H221" s="16"/>
       <c r="I221" s="11"/>
       <c r="J221" s="11"/>
       <c r="K221" s="11"/>
@@ -3702,7 +3643,7 @@
       <c r="E222" s="9"/>
       <c r="F222" s="9"/>
       <c r="G222" s="11"/>
-      <c r="H222" s="13"/>
+      <c r="H222" s="16"/>
       <c r="I222" s="11"/>
       <c r="J222" s="11"/>
       <c r="K222" s="11"/>
@@ -3715,7 +3656,7 @@
       <c r="E223" s="9"/>
       <c r="F223" s="9"/>
       <c r="G223" s="11"/>
-      <c r="H223" s="13"/>
+      <c r="H223" s="16"/>
       <c r="I223" s="11"/>
       <c r="J223" s="11"/>
       <c r="K223" s="11"/>
@@ -3728,7 +3669,7 @@
       <c r="E224" s="9"/>
       <c r="F224" s="9"/>
       <c r="G224" s="11"/>
-      <c r="H224" s="13"/>
+      <c r="H224" s="16"/>
       <c r="I224" s="11"/>
       <c r="J224" s="11"/>
       <c r="K224" s="11"/>
@@ -3741,7 +3682,7 @@
       <c r="E225" s="9"/>
       <c r="F225" s="9"/>
       <c r="G225" s="11"/>
-      <c r="H225" s="13"/>
+      <c r="H225" s="16"/>
       <c r="I225" s="11"/>
       <c r="J225" s="11"/>
       <c r="K225" s="11"/>
@@ -3754,7 +3695,7 @@
       <c r="E226" s="9"/>
       <c r="F226" s="9"/>
       <c r="G226" s="11"/>
-      <c r="H226" s="13"/>
+      <c r="H226" s="16"/>
       <c r="I226" s="11"/>
       <c r="J226" s="11"/>
       <c r="K226" s="11"/>
@@ -3767,7 +3708,7 @@
       <c r="E227" s="9"/>
       <c r="F227" s="9"/>
       <c r="G227" s="11"/>
-      <c r="H227" s="13"/>
+      <c r="H227" s="16"/>
       <c r="I227" s="11"/>
       <c r="J227" s="11"/>
       <c r="K227" s="11"/>
@@ -3780,7 +3721,7 @@
       <c r="E228" s="9"/>
       <c r="F228" s="9"/>
       <c r="G228" s="11"/>
-      <c r="H228" s="13"/>
+      <c r="H228" s="16"/>
       <c r="I228" s="11"/>
       <c r="J228" s="11"/>
       <c r="K228" s="11"/>
@@ -3793,7 +3734,7 @@
       <c r="E229" s="9"/>
       <c r="F229" s="9"/>
       <c r="G229" s="11"/>
-      <c r="H229" s="13"/>
+      <c r="H229" s="16"/>
       <c r="I229" s="11"/>
       <c r="J229" s="11"/>
       <c r="K229" s="11"/>
@@ -3806,7 +3747,7 @@
       <c r="E230" s="9"/>
       <c r="F230" s="9"/>
       <c r="G230" s="11"/>
-      <c r="H230" s="13"/>
+      <c r="H230" s="16"/>
       <c r="I230" s="11"/>
       <c r="J230" s="11"/>
       <c r="K230" s="11"/>
@@ -3819,7 +3760,7 @@
       <c r="E231" s="9"/>
       <c r="F231" s="9"/>
       <c r="G231" s="11"/>
-      <c r="H231" s="13"/>
+      <c r="H231" s="16"/>
       <c r="I231" s="11"/>
       <c r="J231" s="11"/>
       <c r="K231" s="11"/>
@@ -3832,7 +3773,7 @@
       <c r="E232" s="9"/>
       <c r="F232" s="9"/>
       <c r="G232" s="11"/>
-      <c r="H232" s="13"/>
+      <c r="H232" s="16"/>
       <c r="I232" s="11"/>
       <c r="J232" s="11"/>
       <c r="K232" s="11"/>
@@ -3845,7 +3786,7 @@
       <c r="E233" s="9"/>
       <c r="F233" s="9"/>
       <c r="G233" s="11"/>
-      <c r="H233" s="13"/>
+      <c r="H233" s="16"/>
       <c r="I233" s="11"/>
       <c r="J233" s="11"/>
       <c r="K233" s="11"/>
@@ -3858,7 +3799,7 @@
       <c r="E234" s="9"/>
       <c r="F234" s="9"/>
       <c r="G234" s="11"/>
-      <c r="H234" s="13"/>
+      <c r="H234" s="16"/>
       <c r="I234" s="11"/>
       <c r="J234" s="11"/>
       <c r="K234" s="11"/>
@@ -3871,7 +3812,7 @@
       <c r="E235" s="9"/>
       <c r="F235" s="9"/>
       <c r="G235" s="11"/>
-      <c r="H235" s="13"/>
+      <c r="H235" s="16"/>
       <c r="I235" s="11"/>
       <c r="J235" s="11"/>
       <c r="K235" s="11"/>
@@ -3884,7 +3825,7 @@
       <c r="E236" s="9"/>
       <c r="F236" s="9"/>
       <c r="G236" s="11"/>
-      <c r="H236" s="13"/>
+      <c r="H236" s="16"/>
       <c r="I236" s="11"/>
       <c r="J236" s="11"/>
       <c r="K236" s="11"/>
@@ -3897,7 +3838,7 @@
       <c r="E237" s="9"/>
       <c r="F237" s="9"/>
       <c r="G237" s="11"/>
-      <c r="H237" s="13"/>
+      <c r="H237" s="16"/>
       <c r="I237" s="11"/>
       <c r="J237" s="11"/>
       <c r="K237" s="11"/>
@@ -3910,7 +3851,7 @@
       <c r="E238" s="9"/>
       <c r="F238" s="9"/>
       <c r="G238" s="11"/>
-      <c r="H238" s="13"/>
+      <c r="H238" s="16"/>
       <c r="I238" s="11"/>
       <c r="J238" s="11"/>
       <c r="K238" s="11"/>
@@ -3923,7 +3864,7 @@
       <c r="E239" s="9"/>
       <c r="F239" s="9"/>
       <c r="G239" s="11"/>
-      <c r="H239" s="13"/>
+      <c r="H239" s="16"/>
       <c r="I239" s="11"/>
       <c r="J239" s="11"/>
       <c r="K239" s="11"/>
@@ -3936,7 +3877,7 @@
       <c r="E240" s="9"/>
       <c r="F240" s="9"/>
       <c r="G240" s="11"/>
-      <c r="H240" s="13"/>
+      <c r="H240" s="16"/>
       <c r="I240" s="11"/>
       <c r="J240" s="11"/>
       <c r="K240" s="11"/>
@@ -3949,7 +3890,7 @@
       <c r="E241" s="9"/>
       <c r="F241" s="9"/>
       <c r="G241" s="11"/>
-      <c r="H241" s="13"/>
+      <c r="H241" s="16"/>
       <c r="I241" s="11"/>
       <c r="J241" s="11"/>
       <c r="K241" s="11"/>
@@ -3962,7 +3903,7 @@
       <c r="E242" s="9"/>
       <c r="F242" s="9"/>
       <c r="G242" s="11"/>
-      <c r="H242" s="13"/>
+      <c r="H242" s="16"/>
       <c r="I242" s="11"/>
       <c r="J242" s="11"/>
       <c r="K242" s="11"/>
@@ -3975,7 +3916,7 @@
       <c r="E243" s="9"/>
       <c r="F243" s="9"/>
       <c r="G243" s="11"/>
-      <c r="H243" s="13"/>
+      <c r="H243" s="16"/>
       <c r="I243" s="11"/>
       <c r="J243" s="11"/>
       <c r="K243" s="11"/>
@@ -3988,7 +3929,7 @@
       <c r="E244" s="9"/>
       <c r="F244" s="9"/>
       <c r="G244" s="11"/>
-      <c r="H244" s="13"/>
+      <c r="H244" s="16"/>
       <c r="I244" s="11"/>
       <c r="J244" s="11"/>
       <c r="K244" s="11"/>
@@ -4001,7 +3942,7 @@
       <c r="E245" s="9"/>
       <c r="F245" s="9"/>
       <c r="G245" s="11"/>
-      <c r="H245" s="13"/>
+      <c r="H245" s="16"/>
       <c r="I245" s="11"/>
       <c r="J245" s="11"/>
       <c r="K245" s="11"/>
@@ -4014,7 +3955,7 @@
       <c r="E246" s="9"/>
       <c r="F246" s="9"/>
       <c r="G246" s="11"/>
-      <c r="H246" s="13"/>
+      <c r="H246" s="16"/>
       <c r="I246" s="11"/>
       <c r="J246" s="11"/>
       <c r="K246" s="11"/>
@@ -4027,7 +3968,7 @@
       <c r="E247" s="9"/>
       <c r="F247" s="9"/>
       <c r="G247" s="11"/>
-      <c r="H247" s="13"/>
+      <c r="H247" s="16"/>
       <c r="I247" s="11"/>
       <c r="J247" s="11"/>
       <c r="K247" s="11"/>
@@ -4040,7 +3981,7 @@
       <c r="E248" s="9"/>
       <c r="F248" s="9"/>
       <c r="G248" s="11"/>
-      <c r="H248" s="13"/>
+      <c r="H248" s="16"/>
       <c r="I248" s="11"/>
       <c r="J248" s="11"/>
       <c r="K248" s="11"/>
@@ -4053,7 +3994,7 @@
       <c r="E249" s="9"/>
       <c r="F249" s="9"/>
       <c r="G249" s="11"/>
-      <c r="H249" s="13"/>
+      <c r="H249" s="16"/>
       <c r="I249" s="11"/>
       <c r="J249" s="11"/>
       <c r="K249" s="11"/>
@@ -4066,7 +4007,7 @@
       <c r="E250" s="9"/>
       <c r="F250" s="9"/>
       <c r="G250" s="11"/>
-      <c r="H250" s="13"/>
+      <c r="H250" s="16"/>
       <c r="I250" s="11"/>
       <c r="J250" s="11"/>
       <c r="K250" s="11"/>
@@ -4079,7 +4020,7 @@
       <c r="E251" s="9"/>
       <c r="F251" s="9"/>
       <c r="G251" s="11"/>
-      <c r="H251" s="13"/>
+      <c r="H251" s="16"/>
       <c r="I251" s="11"/>
       <c r="J251" s="11"/>
       <c r="K251" s="11"/>
@@ -4092,7 +4033,7 @@
       <c r="E252" s="9"/>
       <c r="F252" s="9"/>
       <c r="G252" s="11"/>
-      <c r="H252" s="13"/>
+      <c r="H252" s="16"/>
       <c r="I252" s="11"/>
       <c r="J252" s="11"/>
       <c r="K252" s="11"/>
@@ -4105,7 +4046,7 @@
       <c r="E253" s="9"/>
       <c r="F253" s="9"/>
       <c r="G253" s="11"/>
-      <c r="H253" s="13"/>
+      <c r="H253" s="16"/>
       <c r="I253" s="11"/>
       <c r="J253" s="11"/>
       <c r="K253" s="11"/>
@@ -4118,7 +4059,7 @@
       <c r="E254" s="9"/>
       <c r="F254" s="9"/>
       <c r="G254" s="11"/>
-      <c r="H254" s="13"/>
+      <c r="H254" s="16"/>
       <c r="I254" s="11"/>
       <c r="J254" s="11"/>
       <c r="K254" s="11"/>
@@ -4131,7 +4072,7 @@
       <c r="E255" s="9"/>
       <c r="F255" s="9"/>
       <c r="G255" s="11"/>
-      <c r="H255" s="13"/>
+      <c r="H255" s="16"/>
       <c r="I255" s="11"/>
       <c r="J255" s="11"/>
       <c r="K255" s="11"/>
@@ -4144,7 +4085,7 @@
       <c r="E256" s="9"/>
       <c r="F256" s="9"/>
       <c r="G256" s="11"/>
-      <c r="H256" s="13"/>
+      <c r="H256" s="16"/>
       <c r="I256" s="11"/>
       <c r="J256" s="11"/>
       <c r="K256" s="11"/>
@@ -4157,7 +4098,7 @@
       <c r="E257" s="9"/>
       <c r="F257" s="9"/>
       <c r="G257" s="11"/>
-      <c r="H257" s="13"/>
+      <c r="H257" s="16"/>
       <c r="I257" s="11"/>
       <c r="J257" s="11"/>
       <c r="K257" s="11"/>
@@ -4170,7 +4111,7 @@
       <c r="E258" s="9"/>
       <c r="F258" s="9"/>
       <c r="G258" s="11"/>
-      <c r="H258" s="13"/>
+      <c r="H258" s="16"/>
       <c r="I258" s="11"/>
       <c r="J258" s="11"/>
       <c r="K258" s="11"/>
@@ -4183,7 +4124,7 @@
       <c r="E259" s="9"/>
       <c r="F259" s="9"/>
       <c r="G259" s="11"/>
-      <c r="H259" s="13"/>
+      <c r="H259" s="16"/>
       <c r="I259" s="11"/>
       <c r="J259" s="11"/>
       <c r="K259" s="11"/>
@@ -4196,7 +4137,7 @@
       <c r="E260" s="9"/>
       <c r="F260" s="9"/>
       <c r="G260" s="11"/>
-      <c r="H260" s="13"/>
+      <c r="H260" s="16"/>
       <c r="I260" s="11"/>
       <c r="J260" s="11"/>
       <c r="K260" s="11"/>
@@ -4209,7 +4150,7 @@
       <c r="E261" s="9"/>
       <c r="F261" s="9"/>
       <c r="G261" s="11"/>
-      <c r="H261" s="13"/>
+      <c r="H261" s="16"/>
       <c r="I261" s="11"/>
       <c r="J261" s="11"/>
       <c r="K261" s="11"/>
@@ -4222,7 +4163,7 @@
       <c r="E262" s="9"/>
       <c r="F262" s="9"/>
       <c r="G262" s="11"/>
-      <c r="H262" s="13"/>
+      <c r="H262" s="16"/>
       <c r="I262" s="11"/>
       <c r="J262" s="11"/>
       <c r="K262" s="11"/>
@@ -4235,7 +4176,7 @@
       <c r="E263" s="9"/>
       <c r="F263" s="9"/>
       <c r="G263" s="11"/>
-      <c r="H263" s="13"/>
+      <c r="H263" s="16"/>
       <c r="I263" s="11"/>
       <c r="J263" s="11"/>
       <c r="K263" s="11"/>
@@ -4248,7 +4189,7 @@
       <c r="E264" s="9"/>
       <c r="F264" s="9"/>
       <c r="G264" s="11"/>
-      <c r="H264" s="13"/>
+      <c r="H264" s="16"/>
       <c r="I264" s="11"/>
       <c r="J264" s="11"/>
       <c r="K264" s="11"/>
@@ -4261,7 +4202,7 @@
       <c r="E265" s="9"/>
       <c r="F265" s="9"/>
       <c r="G265" s="11"/>
-      <c r="H265" s="13"/>
+      <c r="H265" s="16"/>
       <c r="I265" s="11"/>
       <c r="J265" s="11"/>
       <c r="K265" s="11"/>
@@ -4274,7 +4215,7 @@
       <c r="E266" s="9"/>
       <c r="F266" s="9"/>
       <c r="G266" s="11"/>
-      <c r="H266" s="13"/>
+      <c r="H266" s="16"/>
       <c r="I266" s="11"/>
       <c r="J266" s="11"/>
       <c r="K266" s="11"/>
@@ -4287,7 +4228,7 @@
       <c r="E267" s="9"/>
       <c r="F267" s="9"/>
       <c r="G267" s="11"/>
-      <c r="H267" s="13"/>
+      <c r="H267" s="16"/>
       <c r="I267" s="11"/>
       <c r="J267" s="11"/>
       <c r="K267" s="11"/>
@@ -4300,7 +4241,7 @@
       <c r="E268" s="9"/>
       <c r="F268" s="9"/>
       <c r="G268" s="11"/>
-      <c r="H268" s="13"/>
+      <c r="H268" s="16"/>
       <c r="I268" s="11"/>
       <c r="J268" s="11"/>
       <c r="K268" s="11"/>
@@ -4313,7 +4254,7 @@
       <c r="E269" s="9"/>
       <c r="F269" s="9"/>
       <c r="G269" s="11"/>
-      <c r="H269" s="13"/>
+      <c r="H269" s="16"/>
       <c r="I269" s="11"/>
       <c r="J269" s="11"/>
       <c r="K269" s="11"/>
@@ -4326,7 +4267,7 @@
       <c r="E270" s="9"/>
       <c r="F270" s="9"/>
       <c r="G270" s="11"/>
-      <c r="H270" s="13"/>
+      <c r="H270" s="16"/>
       <c r="I270" s="11"/>
       <c r="J270" s="11"/>
       <c r="K270" s="11"/>
@@ -4339,7 +4280,7 @@
       <c r="E271" s="9"/>
       <c r="F271" s="9"/>
       <c r="G271" s="11"/>
-      <c r="H271" s="13"/>
+      <c r="H271" s="16"/>
       <c r="I271" s="11"/>
       <c r="J271" s="11"/>
       <c r="K271" s="11"/>
@@ -4352,7 +4293,7 @@
       <c r="E272" s="9"/>
       <c r="F272" s="9"/>
       <c r="G272" s="11"/>
-      <c r="H272" s="13"/>
+      <c r="H272" s="16"/>
       <c r="I272" s="11"/>
       <c r="J272" s="11"/>
       <c r="K272" s="11"/>
@@ -4365,7 +4306,7 @@
       <c r="E273" s="9"/>
       <c r="F273" s="9"/>
       <c r="G273" s="11"/>
-      <c r="H273" s="13"/>
+      <c r="H273" s="16"/>
       <c r="I273" s="11"/>
       <c r="J273" s="11"/>
       <c r="K273" s="11"/>
@@ -4378,7 +4319,7 @@
       <c r="E274" s="9"/>
       <c r="F274" s="9"/>
       <c r="G274" s="11"/>
-      <c r="H274" s="13"/>
+      <c r="H274" s="16"/>
       <c r="I274" s="11"/>
       <c r="J274" s="11"/>
       <c r="K274" s="11"/>
@@ -4391,7 +4332,7 @@
       <c r="E275" s="9"/>
       <c r="F275" s="9"/>
       <c r="G275" s="11"/>
-      <c r="H275" s="13"/>
+      <c r="H275" s="16"/>
       <c r="I275" s="11"/>
       <c r="J275" s="11"/>
       <c r="K275" s="11"/>
@@ -4404,7 +4345,7 @@
       <c r="E276" s="9"/>
       <c r="F276" s="9"/>
       <c r="G276" s="11"/>
-      <c r="H276" s="13"/>
+      <c r="H276" s="16"/>
       <c r="I276" s="11"/>
       <c r="J276" s="11"/>
       <c r="K276" s="11"/>
@@ -4417,7 +4358,7 @@
       <c r="E277" s="9"/>
       <c r="F277" s="9"/>
       <c r="G277" s="11"/>
-      <c r="H277" s="13"/>
+      <c r="H277" s="16"/>
       <c r="I277" s="11"/>
       <c r="J277" s="11"/>
       <c r="K277" s="11"/>
@@ -4430,7 +4371,7 @@
       <c r="E278" s="9"/>
       <c r="F278" s="9"/>
       <c r="G278" s="11"/>
-      <c r="H278" s="13"/>
+      <c r="H278" s="16"/>
       <c r="I278" s="11"/>
       <c r="J278" s="11"/>
       <c r="K278" s="11"/>
@@ -4443,7 +4384,7 @@
       <c r="E279" s="9"/>
       <c r="F279" s="9"/>
       <c r="G279" s="11"/>
-      <c r="H279" s="13"/>
+      <c r="H279" s="16"/>
       <c r="I279" s="11"/>
       <c r="J279" s="11"/>
       <c r="K279" s="11"/>
@@ -4456,7 +4397,7 @@
       <c r="E280" s="9"/>
       <c r="F280" s="9"/>
       <c r="G280" s="11"/>
-      <c r="H280" s="13"/>
+      <c r="H280" s="16"/>
       <c r="I280" s="11"/>
       <c r="J280" s="11"/>
       <c r="K280" s="11"/>
@@ -4469,7 +4410,7 @@
       <c r="E281" s="9"/>
       <c r="F281" s="9"/>
       <c r="G281" s="11"/>
-      <c r="H281" s="13"/>
+      <c r="H281" s="16"/>
       <c r="I281" s="11"/>
       <c r="J281" s="11"/>
       <c r="K281" s="11"/>
@@ -4482,7 +4423,7 @@
       <c r="E282" s="9"/>
       <c r="F282" s="9"/>
       <c r="G282" s="11"/>
-      <c r="H282" s="13"/>
+      <c r="H282" s="16"/>
       <c r="I282" s="11"/>
       <c r="J282" s="11"/>
       <c r="K282" s="11"/>
@@ -4495,7 +4436,7 @@
       <c r="E283" s="9"/>
       <c r="F283" s="9"/>
       <c r="G283" s="11"/>
-      <c r="H283" s="13"/>
+      <c r="H283" s="16"/>
       <c r="I283" s="11"/>
       <c r="J283" s="11"/>
       <c r="K283" s="11"/>
@@ -4508,7 +4449,7 @@
       <c r="E284" s="9"/>
       <c r="F284" s="9"/>
       <c r="G284" s="11"/>
-      <c r="H284" s="13"/>
+      <c r="H284" s="16"/>
       <c r="I284" s="11"/>
       <c r="J284" s="11"/>
       <c r="K284" s="11"/>
@@ -4521,7 +4462,7 @@
       <c r="E285" s="9"/>
       <c r="F285" s="9"/>
       <c r="G285" s="11"/>
-      <c r="H285" s="13"/>
+      <c r="H285" s="16"/>
       <c r="I285" s="11"/>
       <c r="J285" s="11"/>
       <c r="K285" s="11"/>
@@ -4534,7 +4475,7 @@
       <c r="E286" s="9"/>
       <c r="F286" s="9"/>
       <c r="G286" s="11"/>
-      <c r="H286" s="13"/>
+      <c r="H286" s="16"/>
       <c r="I286" s="11"/>
       <c r="J286" s="11"/>
       <c r="K286" s="11"/>
@@ -4547,7 +4488,7 @@
       <c r="E287" s="9"/>
       <c r="F287" s="9"/>
       <c r="G287" s="11"/>
-      <c r="H287" s="13"/>
+      <c r="H287" s="16"/>
       <c r="I287" s="11"/>
       <c r="J287" s="11"/>
       <c r="K287" s="11"/>
@@ -4560,7 +4501,7 @@
       <c r="E288" s="9"/>
       <c r="F288" s="9"/>
       <c r="G288" s="11"/>
-      <c r="H288" s="13"/>
+      <c r="H288" s="16"/>
       <c r="I288" s="11"/>
       <c r="J288" s="11"/>
       <c r="K288" s="11"/>
@@ -4573,7 +4514,7 @@
       <c r="E289" s="9"/>
       <c r="F289" s="9"/>
       <c r="G289" s="11"/>
-      <c r="H289" s="13"/>
+      <c r="H289" s="16"/>
       <c r="I289" s="11"/>
       <c r="J289" s="11"/>
       <c r="K289" s="11"/>
@@ -4586,7 +4527,7 @@
       <c r="E290" s="9"/>
       <c r="F290" s="9"/>
       <c r="G290" s="11"/>
-      <c r="H290" s="13"/>
+      <c r="H290" s="16"/>
       <c r="I290" s="11"/>
       <c r="J290" s="11"/>
       <c r="K290" s="11"/>
@@ -4599,7 +4540,7 @@
       <c r="E291" s="9"/>
       <c r="F291" s="9"/>
       <c r="G291" s="11"/>
-      <c r="H291" s="13"/>
+      <c r="H291" s="16"/>
       <c r="I291" s="11"/>
       <c r="J291" s="11"/>
       <c r="K291" s="11"/>
@@ -4612,7 +4553,7 @@
       <c r="E292" s="9"/>
       <c r="F292" s="9"/>
       <c r="G292" s="11"/>
-      <c r="H292" s="13"/>
+      <c r="H292" s="16"/>
       <c r="I292" s="11"/>
       <c r="J292" s="11"/>
       <c r="K292" s="11"/>
@@ -4625,7 +4566,7 @@
       <c r="E293" s="9"/>
       <c r="F293" s="9"/>
       <c r="G293" s="11"/>
-      <c r="H293" s="13"/>
+      <c r="H293" s="16"/>
       <c r="I293" s="11"/>
       <c r="J293" s="11"/>
       <c r="K293" s="11"/>
@@ -4638,7 +4579,7 @@
       <c r="E294" s="9"/>
       <c r="F294" s="9"/>
       <c r="G294" s="11"/>
-      <c r="H294" s="13"/>
+      <c r="H294" s="16"/>
       <c r="I294" s="11"/>
       <c r="J294" s="11"/>
       <c r="K294" s="11"/>
@@ -4651,7 +4592,7 @@
       <c r="E295" s="9"/>
       <c r="F295" s="9"/>
       <c r="G295" s="11"/>
-      <c r="H295" s="13"/>
+      <c r="H295" s="16"/>
       <c r="I295" s="11"/>
       <c r="J295" s="11"/>
       <c r="K295" s="11"/>
@@ -4664,7 +4605,7 @@
       <c r="E296" s="9"/>
       <c r="F296" s="9"/>
       <c r="G296" s="11"/>
-      <c r="H296" s="13"/>
+      <c r="H296" s="16"/>
       <c r="I296" s="11"/>
       <c r="J296" s="11"/>
       <c r="K296" s="11"/>
@@ -4677,7 +4618,7 @@
       <c r="E297" s="9"/>
       <c r="F297" s="9"/>
       <c r="G297" s="11"/>
-      <c r="H297" s="13"/>
+      <c r="H297" s="16"/>
       <c r="I297" s="11"/>
       <c r="J297" s="11"/>
       <c r="K297" s="11"/>
@@ -4690,7 +4631,7 @@
       <c r="E298" s="9"/>
       <c r="F298" s="9"/>
       <c r="G298" s="11"/>
-      <c r="H298" s="13"/>
+      <c r="H298" s="16"/>
       <c r="I298" s="11"/>
       <c r="J298" s="11"/>
       <c r="K298" s="11"/>
@@ -4703,7 +4644,7 @@
       <c r="E299" s="9"/>
       <c r="F299" s="9"/>
       <c r="G299" s="11"/>
-      <c r="H299" s="13"/>
+      <c r="H299" s="16"/>
       <c r="I299" s="11"/>
       <c r="J299" s="11"/>
       <c r="K299" s="11"/>
@@ -4716,7 +4657,7 @@
       <c r="E300" s="9"/>
       <c r="F300" s="9"/>
       <c r="G300" s="11"/>
-      <c r="H300" s="13"/>
+      <c r="H300" s="16"/>
       <c r="I300" s="11"/>
       <c r="J300" s="11"/>
       <c r="K300" s="11"/>
@@ -4729,7 +4670,7 @@
       <c r="E301" s="9"/>
       <c r="F301" s="9"/>
       <c r="G301" s="11"/>
-      <c r="H301" s="13"/>
+      <c r="H301" s="16"/>
       <c r="I301" s="11"/>
       <c r="J301" s="11"/>
       <c r="K301" s="11"/>
@@ -4742,7 +4683,7 @@
       <c r="E302" s="9"/>
       <c r="F302" s="9"/>
       <c r="G302" s="11"/>
-      <c r="H302" s="13"/>
+      <c r="H302" s="16"/>
       <c r="I302" s="11"/>
       <c r="J302" s="11"/>
       <c r="K302" s="11"/>
@@ -4755,7 +4696,7 @@
       <c r="E303" s="9"/>
       <c r="F303" s="9"/>
       <c r="G303" s="11"/>
-      <c r="H303" s="13"/>
+      <c r="H303" s="16"/>
       <c r="I303" s="11"/>
       <c r="J303" s="11"/>
       <c r="K303" s="11"/>
@@ -4768,7 +4709,7 @@
       <c r="E304" s="9"/>
       <c r="F304" s="9"/>
       <c r="G304" s="11"/>
-      <c r="H304" s="13"/>
+      <c r="H304" s="16"/>
       <c r="I304" s="11"/>
       <c r="J304" s="11"/>
       <c r="K304" s="11"/>
@@ -4781,7 +4722,7 @@
       <c r="E305" s="9"/>
       <c r="F305" s="9"/>
       <c r="G305" s="11"/>
-      <c r="H305" s="13"/>
+      <c r="H305" s="16"/>
       <c r="I305" s="11"/>
       <c r="J305" s="11"/>
       <c r="K305" s="11"/>
@@ -4794,7 +4735,7 @@
       <c r="E306" s="9"/>
       <c r="F306" s="9"/>
       <c r="G306" s="11"/>
-      <c r="H306" s="13"/>
+      <c r="H306" s="16"/>
       <c r="I306" s="11"/>
       <c r="J306" s="11"/>
       <c r="K306" s="11"/>
@@ -4807,7 +4748,7 @@
       <c r="E307" s="9"/>
       <c r="F307" s="9"/>
       <c r="G307" s="11"/>
-      <c r="H307" s="13"/>
+      <c r="H307" s="16"/>
       <c r="I307" s="11"/>
       <c r="J307" s="11"/>
       <c r="K307" s="11"/>
@@ -4820,7 +4761,7 @@
       <c r="E308" s="9"/>
       <c r="F308" s="9"/>
       <c r="G308" s="11"/>
-      <c r="H308" s="13"/>
+      <c r="H308" s="16"/>
       <c r="I308" s="11"/>
       <c r="J308" s="11"/>
       <c r="K308" s="11"/>
@@ -4833,7 +4774,7 @@
       <c r="E309" s="9"/>
       <c r="F309" s="9"/>
       <c r="G309" s="11"/>
-      <c r="H309" s="13"/>
+      <c r="H309" s="16"/>
       <c r="I309" s="11"/>
       <c r="J309" s="11"/>
       <c r="K309" s="11"/>
@@ -4846,7 +4787,7 @@
       <c r="E310" s="9"/>
       <c r="F310" s="9"/>
       <c r="G310" s="11"/>
-      <c r="H310" s="13"/>
+      <c r="H310" s="16"/>
       <c r="I310" s="11"/>
       <c r="J310" s="11"/>
       <c r="K310" s="11"/>
@@ -4859,7 +4800,7 @@
       <c r="E311" s="9"/>
       <c r="F311" s="9"/>
       <c r="G311" s="11"/>
-      <c r="H311" s="13"/>
+      <c r="H311" s="16"/>
       <c r="I311" s="11"/>
       <c r="J311" s="11"/>
       <c r="K311" s="11"/>
@@ -4872,7 +4813,7 @@
       <c r="E312" s="9"/>
       <c r="F312" s="9"/>
       <c r="G312" s="11"/>
-      <c r="H312" s="13"/>
+      <c r="H312" s="16"/>
       <c r="I312" s="11"/>
       <c r="J312" s="11"/>
       <c r="K312" s="11"/>
@@ -4885,7 +4826,7 @@
       <c r="E313" s="9"/>
       <c r="F313" s="9"/>
       <c r="G313" s="11"/>
-      <c r="H313" s="13"/>
+      <c r="H313" s="16"/>
       <c r="I313" s="11"/>
       <c r="J313" s="11"/>
       <c r="K313" s="11"/>
@@ -4898,7 +4839,7 @@
       <c r="E314" s="9"/>
       <c r="F314" s="9"/>
       <c r="G314" s="11"/>
-      <c r="H314" s="13"/>
+      <c r="H314" s="16"/>
       <c r="I314" s="11"/>
       <c r="J314" s="11"/>
       <c r="K314" s="11"/>
@@ -4911,7 +4852,7 @@
       <c r="E315" s="9"/>
       <c r="F315" s="9"/>
       <c r="G315" s="11"/>
-      <c r="H315" s="13"/>
+      <c r="H315" s="16"/>
       <c r="I315" s="11"/>
       <c r="J315" s="11"/>
       <c r="K315" s="11"/>
@@ -4924,7 +4865,7 @@
       <c r="E316" s="9"/>
       <c r="F316" s="9"/>
       <c r="G316" s="11"/>
-      <c r="H316" s="13"/>
+      <c r="H316" s="16"/>
       <c r="I316" s="11"/>
       <c r="J316" s="11"/>
       <c r="K316" s="11"/>
@@ -4937,7 +4878,7 @@
       <c r="E317" s="9"/>
       <c r="F317" s="9"/>
       <c r="G317" s="11"/>
-      <c r="H317" s="13"/>
+      <c r="H317" s="16"/>
       <c r="I317" s="11"/>
       <c r="J317" s="11"/>
       <c r="K317" s="11"/>
@@ -4950,7 +4891,7 @@
       <c r="E318" s="9"/>
       <c r="F318" s="9"/>
       <c r="G318" s="11"/>
-      <c r="H318" s="13"/>
+      <c r="H318" s="16"/>
       <c r="I318" s="11"/>
       <c r="J318" s="11"/>
       <c r="K318" s="11"/>
@@ -4963,7 +4904,7 @@
       <c r="E319" s="9"/>
       <c r="F319" s="9"/>
       <c r="G319" s="11"/>
-      <c r="H319" s="13"/>
+      <c r="H319" s="16"/>
       <c r="I319" s="11"/>
       <c r="J319" s="11"/>
       <c r="K319" s="11"/>
@@ -4976,7 +4917,7 @@
       <c r="E320" s="9"/>
       <c r="F320" s="9"/>
       <c r="G320" s="11"/>
-      <c r="H320" s="13"/>
+      <c r="H320" s="16"/>
       <c r="I320" s="11"/>
       <c r="J320" s="11"/>
       <c r="K320" s="11"/>
@@ -4989,7 +4930,7 @@
       <c r="E321" s="9"/>
       <c r="F321" s="9"/>
       <c r="G321" s="11"/>
-      <c r="H321" s="13"/>
+      <c r="H321" s="16"/>
       <c r="I321" s="11"/>
       <c r="J321" s="11"/>
       <c r="K321" s="11"/>
@@ -5002,7 +4943,7 @@
       <c r="E322" s="9"/>
       <c r="F322" s="9"/>
       <c r="G322" s="11"/>
-      <c r="H322" s="13"/>
+      <c r="H322" s="16"/>
       <c r="I322" s="11"/>
       <c r="J322" s="11"/>
       <c r="K322" s="11"/>
@@ -5015,7 +4956,7 @@
       <c r="E323" s="9"/>
       <c r="F323" s="9"/>
       <c r="G323" s="11"/>
-      <c r="H323" s="13"/>
+      <c r="H323" s="16"/>
       <c r="I323" s="11"/>
       <c r="J323" s="11"/>
       <c r="K323" s="11"/>
@@ -5028,7 +4969,7 @@
       <c r="E324" s="9"/>
       <c r="F324" s="9"/>
       <c r="G324" s="11"/>
-      <c r="H324" s="13"/>
+      <c r="H324" s="16"/>
       <c r="I324" s="11"/>
       <c r="J324" s="11"/>
       <c r="K324" s="11"/>
@@ -5041,7 +4982,7 @@
       <c r="E325" s="9"/>
       <c r="F325" s="9"/>
       <c r="G325" s="11"/>
-      <c r="H325" s="13"/>
+      <c r="H325" s="16"/>
       <c r="I325" s="11"/>
       <c r="J325" s="11"/>
       <c r="K325" s="11"/>
@@ -5054,7 +4995,7 @@
       <c r="E326" s="9"/>
       <c r="F326" s="9"/>
       <c r="G326" s="11"/>
-      <c r="H326" s="13"/>
+      <c r="H326" s="16"/>
       <c r="I326" s="11"/>
       <c r="J326" s="11"/>
       <c r="K326" s="11"/>
@@ -5067,7 +5008,7 @@
       <c r="E327" s="9"/>
       <c r="F327" s="9"/>
       <c r="G327" s="11"/>
-      <c r="H327" s="13"/>
+      <c r="H327" s="16"/>
       <c r="I327" s="11"/>
       <c r="J327" s="11"/>
       <c r="K327" s="11"/>
@@ -5080,7 +5021,7 @@
       <c r="E328" s="9"/>
       <c r="F328" s="9"/>
       <c r="G328" s="11"/>
-      <c r="H328" s="13"/>
+      <c r="H328" s="16"/>
       <c r="I328" s="11"/>
       <c r="J328" s="11"/>
       <c r="K328" s="11"/>
@@ -5093,7 +5034,7 @@
       <c r="E329" s="9"/>
       <c r="F329" s="9"/>
       <c r="G329" s="11"/>
-      <c r="H329" s="13"/>
+      <c r="H329" s="16"/>
       <c r="I329" s="11"/>
       <c r="J329" s="11"/>
       <c r="K329" s="11"/>
@@ -5106,7 +5047,7 @@
       <c r="E330" s="9"/>
       <c r="F330" s="9"/>
       <c r="G330" s="11"/>
-      <c r="H330" s="13"/>
+      <c r="H330" s="16"/>
       <c r="I330" s="11"/>
       <c r="J330" s="11"/>
       <c r="K330" s="11"/>
@@ -5119,7 +5060,7 @@
       <c r="E331" s="9"/>
       <c r="F331" s="9"/>
       <c r="G331" s="11"/>
-      <c r="H331" s="13"/>
+      <c r="H331" s="16"/>
       <c r="I331" s="11"/>
       <c r="J331" s="11"/>
       <c r="K331" s="11"/>
@@ -5132,7 +5073,7 @@
       <c r="E332" s="9"/>
       <c r="F332" s="9"/>
       <c r="G332" s="11"/>
-      <c r="H332" s="13"/>
+      <c r="H332" s="16"/>
       <c r="I332" s="11"/>
       <c r="J332" s="11"/>
       <c r="K332" s="11"/>
@@ -5145,7 +5086,7 @@
       <c r="E333" s="9"/>
       <c r="F333" s="9"/>
       <c r="G333" s="11"/>
-      <c r="H333" s="13"/>
+      <c r="H333" s="16"/>
       <c r="I333" s="11"/>
       <c r="J333" s="11"/>
       <c r="K333" s="11"/>
@@ -5158,7 +5099,7 @@
       <c r="E334" s="9"/>
       <c r="F334" s="9"/>
       <c r="G334" s="11"/>
-      <c r="H334" s="13"/>
+      <c r="H334" s="16"/>
       <c r="I334" s="11"/>
       <c r="J334" s="11"/>
       <c r="K334" s="11"/>
@@ -5171,7 +5112,7 @@
       <c r="E335" s="9"/>
       <c r="F335" s="9"/>
       <c r="G335" s="11"/>
-      <c r="H335" s="13"/>
+      <c r="H335" s="16"/>
       <c r="I335" s="11"/>
       <c r="J335" s="11"/>
       <c r="K335" s="11"/>
@@ -5184,7 +5125,7 @@
       <c r="E336" s="9"/>
       <c r="F336" s="9"/>
       <c r="G336" s="11"/>
-      <c r="H336" s="13"/>
+      <c r="H336" s="16"/>
       <c r="I336" s="11"/>
       <c r="J336" s="11"/>
       <c r="K336" s="11"/>
@@ -5197,7 +5138,7 @@
       <c r="E337" s="9"/>
       <c r="F337" s="9"/>
       <c r="G337" s="11"/>
-      <c r="H337" s="13"/>
+      <c r="H337" s="16"/>
       <c r="I337" s="11"/>
       <c r="J337" s="11"/>
       <c r="K337" s="11"/>
@@ -5210,7 +5151,7 @@
       <c r="E338" s="9"/>
       <c r="F338" s="9"/>
       <c r="G338" s="11"/>
-      <c r="H338" s="13"/>
+      <c r="H338" s="16"/>
       <c r="I338" s="11"/>
       <c r="J338" s="11"/>
       <c r="K338" s="11"/>
@@ -5223,7 +5164,7 @@
       <c r="E339" s="9"/>
       <c r="F339" s="9"/>
       <c r="G339" s="11"/>
-      <c r="H339" s="13"/>
+      <c r="H339" s="16"/>
       <c r="I339" s="11"/>
       <c r="J339" s="11"/>
       <c r="K339" s="11"/>
@@ -5236,7 +5177,7 @@
       <c r="E340" s="9"/>
       <c r="F340" s="9"/>
       <c r="G340" s="11"/>
-      <c r="H340" s="13"/>
+      <c r="H340" s="16"/>
       <c r="I340" s="11"/>
       <c r="J340" s="11"/>
       <c r="K340" s="11"/>
@@ -5249,7 +5190,7 @@
       <c r="E341" s="9"/>
       <c r="F341" s="9"/>
       <c r="G341" s="11"/>
-      <c r="H341" s="13"/>
+      <c r="H341" s="16"/>
       <c r="I341" s="11"/>
       <c r="J341" s="11"/>
       <c r="K341" s="11"/>
@@ -5262,7 +5203,7 @@
       <c r="E342" s="9"/>
       <c r="F342" s="9"/>
       <c r="G342" s="11"/>
-      <c r="H342" s="13"/>
+      <c r="H342" s="16"/>
       <c r="I342" s="11"/>
       <c r="J342" s="11"/>
       <c r="K342" s="11"/>
@@ -5275,7 +5216,7 @@
       <c r="E343" s="9"/>
       <c r="F343" s="9"/>
       <c r="G343" s="11"/>
-      <c r="H343" s="13"/>
+      <c r="H343" s="16"/>
       <c r="I343" s="11"/>
       <c r="J343" s="11"/>
       <c r="K343" s="11"/>
@@ -5288,7 +5229,7 @@
       <c r="E344" s="9"/>
       <c r="F344" s="9"/>
       <c r="G344" s="11"/>
-      <c r="H344" s="13"/>
+      <c r="H344" s="16"/>
       <c r="I344" s="11"/>
       <c r="J344" s="11"/>
       <c r="K344" s="11"/>
@@ -5301,7 +5242,7 @@
       <c r="E345" s="9"/>
       <c r="F345" s="9"/>
       <c r="G345" s="11"/>
-      <c r="H345" s="13"/>
+      <c r="H345" s="16"/>
       <c r="I345" s="11"/>
       <c r="J345" s="11"/>
       <c r="K345" s="11"/>
@@ -5314,7 +5255,7 @@
       <c r="E346" s="9"/>
       <c r="F346" s="9"/>
       <c r="G346" s="11"/>
-      <c r="H346" s="13"/>
+      <c r="H346" s="16"/>
       <c r="I346" s="11"/>
       <c r="J346" s="11"/>
       <c r="K346" s="11"/>
@@ -5327,7 +5268,7 @@
       <c r="E347" s="9"/>
       <c r="F347" s="9"/>
       <c r="G347" s="11"/>
-      <c r="H347" s="13"/>
+      <c r="H347" s="16"/>
       <c r="I347" s="11"/>
       <c r="J347" s="11"/>
       <c r="K347" s="11"/>
@@ -5340,7 +5281,7 @@
       <c r="E348" s="9"/>
       <c r="F348" s="9"/>
       <c r="G348" s="11"/>
-      <c r="H348" s="13"/>
+      <c r="H348" s="16"/>
       <c r="I348" s="11"/>
       <c r="J348" s="11"/>
       <c r="K348" s="11"/>
@@ -5353,7 +5294,7 @@
       <c r="E349" s="9"/>
       <c r="F349" s="9"/>
       <c r="G349" s="11"/>
-      <c r="H349" s="13"/>
+      <c r="H349" s="16"/>
       <c r="I349" s="11"/>
       <c r="J349" s="11"/>
       <c r="K349" s="11"/>
@@ -5366,7 +5307,7 @@
       <c r="E350" s="9"/>
       <c r="F350" s="9"/>
       <c r="G350" s="11"/>
-      <c r="H350" s="13"/>
+      <c r="H350" s="16"/>
       <c r="I350" s="11"/>
       <c r="J350" s="11"/>
       <c r="K350" s="11"/>
@@ -5379,7 +5320,7 @@
       <c r="E351" s="9"/>
       <c r="F351" s="9"/>
       <c r="G351" s="11"/>
-      <c r="H351" s="13"/>
+      <c r="H351" s="16"/>
       <c r="I351" s="11"/>
       <c r="J351" s="11"/>
       <c r="K351" s="11"/>
@@ -5392,7 +5333,7 @@
       <c r="E352" s="9"/>
       <c r="F352" s="9"/>
       <c r="G352" s="11"/>
-      <c r="H352" s="13"/>
+      <c r="H352" s="16"/>
       <c r="I352" s="11"/>
       <c r="J352" s="11"/>
       <c r="K352" s="11"/>
@@ -5405,7 +5346,7 @@
       <c r="E353" s="9"/>
       <c r="F353" s="9"/>
       <c r="G353" s="11"/>
-      <c r="H353" s="13"/>
+      <c r="H353" s="16"/>
       <c r="I353" s="11"/>
       <c r="J353" s="11"/>
       <c r="K353" s="11"/>
@@ -5418,7 +5359,7 @@
       <c r="E354" s="9"/>
       <c r="F354" s="9"/>
       <c r="G354" s="11"/>
-      <c r="H354" s="13"/>
+      <c r="H354" s="16"/>
       <c r="I354" s="11"/>
       <c r="J354" s="11"/>
       <c r="K354" s="11"/>
@@ -5431,7 +5372,7 @@
       <c r="E355" s="9"/>
       <c r="F355" s="9"/>
       <c r="G355" s="11"/>
-      <c r="H355" s="13"/>
+      <c r="H355" s="16"/>
       <c r="I355" s="11"/>
       <c r="J355" s="11"/>
       <c r="K355" s="11"/>
@@ -5444,7 +5385,7 @@
       <c r="E356" s="9"/>
       <c r="F356" s="9"/>
       <c r="G356" s="11"/>
-      <c r="H356" s="13"/>
+      <c r="H356" s="16"/>
       <c r="I356" s="11"/>
       <c r="J356" s="11"/>
       <c r="K356" s="11"/>
@@ -5457,7 +5398,7 @@
       <c r="E357" s="9"/>
       <c r="F357" s="9"/>
       <c r="G357" s="11"/>
-      <c r="H357" s="13"/>
+      <c r="H357" s="16"/>
       <c r="I357" s="11"/>
       <c r="J357" s="11"/>
       <c r="K357" s="11"/>
@@ -5470,7 +5411,7 @@
       <c r="E358" s="9"/>
       <c r="F358" s="9"/>
       <c r="G358" s="11"/>
-      <c r="H358" s="13"/>
+      <c r="H358" s="16"/>
       <c r="I358" s="11"/>
       <c r="J358" s="11"/>
       <c r="K358" s="11"/>
@@ -5483,7 +5424,7 @@
       <c r="E359" s="9"/>
       <c r="F359" s="9"/>
       <c r="G359" s="11"/>
-      <c r="H359" s="13"/>
+      <c r="H359" s="16"/>
       <c r="I359" s="11"/>
       <c r="J359" s="11"/>
       <c r="K359" s="11"/>
@@ -5496,7 +5437,7 @@
       <c r="E360" s="9"/>
       <c r="F360" s="9"/>
       <c r="G360" s="11"/>
-      <c r="H360" s="13"/>
+      <c r="H360" s="16"/>
       <c r="I360" s="11"/>
       <c r="J360" s="11"/>
       <c r="K360" s="11"/>
@@ -5509,7 +5450,7 @@
       <c r="E361" s="9"/>
       <c r="F361" s="9"/>
       <c r="G361" s="11"/>
-      <c r="H361" s="13"/>
+      <c r="H361" s="16"/>
       <c r="I361" s="11"/>
       <c r="J361" s="11"/>
       <c r="K361" s="11"/>
@@ -5522,7 +5463,7 @@
       <c r="E362" s="9"/>
       <c r="F362" s="9"/>
       <c r="G362" s="11"/>
-      <c r="H362" s="13"/>
+      <c r="H362" s="16"/>
       <c r="I362" s="11"/>
       <c r="J362" s="11"/>
       <c r="K362" s="11"/>
@@ -5535,7 +5476,7 @@
       <c r="E363" s="9"/>
       <c r="F363" s="9"/>
       <c r="G363" s="11"/>
-      <c r="H363" s="13"/>
+      <c r="H363" s="16"/>
       <c r="I363" s="11"/>
       <c r="J363" s="11"/>
       <c r="K363" s="11"/>
@@ -5548,7 +5489,7 @@
       <c r="E364" s="9"/>
       <c r="F364" s="9"/>
       <c r="G364" s="11"/>
-      <c r="H364" s="13"/>
+      <c r="H364" s="16"/>
       <c r="I364" s="11"/>
       <c r="J364" s="11"/>
       <c r="K364" s="11"/>
@@ -5561,7 +5502,7 @@
       <c r="E365" s="9"/>
       <c r="F365" s="9"/>
       <c r="G365" s="11"/>
-      <c r="H365" s="13"/>
+      <c r="H365" s="16"/>
       <c r="I365" s="11"/>
       <c r="J365" s="11"/>
       <c r="K365" s="11"/>
@@ -5574,7 +5515,7 @@
       <c r="E366" s="9"/>
       <c r="F366" s="9"/>
       <c r="G366" s="11"/>
-      <c r="H366" s="13"/>
+      <c r="H366" s="16"/>
       <c r="I366" s="11"/>
       <c r="J366" s="11"/>
       <c r="K366" s="11"/>
@@ -5587,7 +5528,7 @@
       <c r="E367" s="9"/>
       <c r="F367" s="9"/>
       <c r="G367" s="11"/>
-      <c r="H367" s="13"/>
+      <c r="H367" s="16"/>
       <c r="I367" s="11"/>
       <c r="J367" s="11"/>
       <c r="K367" s="11"/>
@@ -5600,7 +5541,7 @@
       <c r="E368" s="9"/>
       <c r="F368" s="9"/>
       <c r="G368" s="11"/>
-      <c r="H368" s="13"/>
+      <c r="H368" s="16"/>
       <c r="I368" s="11"/>
       <c r="J368" s="11"/>
       <c r="K368" s="11"/>
@@ -5613,7 +5554,7 @@
       <c r="E369" s="9"/>
       <c r="F369" s="9"/>
       <c r="G369" s="11"/>
-      <c r="H369" s="13"/>
+      <c r="H369" s="16"/>
       <c r="I369" s="11"/>
       <c r="J369" s="11"/>
       <c r="K369" s="11"/>
@@ -5626,7 +5567,7 @@
       <c r="E370" s="9"/>
       <c r="F370" s="9"/>
       <c r="G370" s="11"/>
-      <c r="H370" s="13"/>
+      <c r="H370" s="16"/>
       <c r="I370" s="11"/>
       <c r="J370" s="11"/>
       <c r="K370" s="11"/>
@@ -5639,7 +5580,7 @@
       <c r="E371" s="9"/>
       <c r="F371" s="9"/>
       <c r="G371" s="11"/>
-      <c r="H371" s="13"/>
+      <c r="H371" s="16"/>
       <c r="I371" s="11"/>
       <c r="J371" s="11"/>
       <c r="K371" s="11"/>
@@ -5652,7 +5593,7 @@
       <c r="E372" s="9"/>
       <c r="F372" s="9"/>
       <c r="G372" s="11"/>
-      <c r="H372" s="13"/>
+      <c r="H372" s="16"/>
       <c r="I372" s="11"/>
       <c r="J372" s="11"/>
       <c r="K372" s="11"/>
@@ -5665,7 +5606,7 @@
       <c r="E373" s="9"/>
       <c r="F373" s="9"/>
       <c r="G373" s="11"/>
-      <c r="H373" s="13"/>
+      <c r="H373" s="16"/>
       <c r="I373" s="11"/>
       <c r="J373" s="11"/>
       <c r="K373" s="11"/>
@@ -5678,7 +5619,7 @@
       <c r="E374" s="9"/>
       <c r="F374" s="9"/>
       <c r="G374" s="11"/>
-      <c r="H374" s="13"/>
+      <c r="H374" s="16"/>
       <c r="I374" s="11"/>
       <c r="J374" s="11"/>
       <c r="K374" s="11"/>
@@ -5691,7 +5632,7 @@
       <c r="E375" s="9"/>
       <c r="F375" s="9"/>
       <c r="G375" s="11"/>
-      <c r="H375" s="13"/>
+      <c r="H375" s="16"/>
       <c r="I375" s="11"/>
       <c r="J375" s="11"/>
       <c r="K375" s="11"/>
@@ -5704,7 +5645,7 @@
       <c r="E376" s="9"/>
       <c r="F376" s="9"/>
       <c r="G376" s="11"/>
-      <c r="H376" s="13"/>
+      <c r="H376" s="16"/>
       <c r="I376" s="11"/>
       <c r="J376" s="11"/>
       <c r="K376" s="11"/>
@@ -5717,7 +5658,7 @@
       <c r="E377" s="9"/>
       <c r="F377" s="9"/>
       <c r="G377" s="11"/>
-      <c r="H377" s="13"/>
+      <c r="H377" s="16"/>
       <c r="I377" s="11"/>
       <c r="J377" s="11"/>
       <c r="K377" s="11"/>
@@ -5730,7 +5671,7 @@
       <c r="E378" s="9"/>
       <c r="F378" s="9"/>
       <c r="G378" s="11"/>
-      <c r="H378" s="13"/>
+      <c r="H378" s="16"/>
       <c r="I378" s="11"/>
       <c r="J378" s="11"/>
       <c r="K378" s="11"/>
@@ -5743,7 +5684,7 @@
       <c r="E379" s="9"/>
       <c r="F379" s="9"/>
       <c r="G379" s="11"/>
-      <c r="H379" s="13"/>
+      <c r="H379" s="16"/>
       <c r="I379" s="11"/>
       <c r="J379" s="11"/>
       <c r="K379" s="11"/>
@@ -5756,7 +5697,7 @@
       <c r="E380" s="9"/>
       <c r="F380" s="9"/>
       <c r="G380" s="11"/>
-      <c r="H380" s="13"/>
+      <c r="H380" s="16"/>
       <c r="I380" s="11"/>
       <c r="J380" s="11"/>
       <c r="K380" s="11"/>
@@ -5769,7 +5710,7 @@
       <c r="E381" s="9"/>
       <c r="F381" s="9"/>
       <c r="G381" s="11"/>
-      <c r="H381" s="13"/>
+      <c r="H381" s="16"/>
       <c r="I381" s="11"/>
       <c r="J381" s="11"/>
       <c r="K381" s="11"/>
@@ -5782,7 +5723,7 @@
       <c r="E382" s="9"/>
       <c r="F382" s="9"/>
       <c r="G382" s="11"/>
-      <c r="H382" s="13"/>
+      <c r="H382" s="16"/>
       <c r="I382" s="11"/>
       <c r="J382" s="11"/>
       <c r="K382" s="11"/>
@@ -5795,7 +5736,7 @@
       <c r="E383" s="9"/>
       <c r="F383" s="9"/>
       <c r="G383" s="11"/>
-      <c r="H383" s="13"/>
+      <c r="H383" s="16"/>
       <c r="I383" s="11"/>
       <c r="J383" s="11"/>
       <c r="K383" s="11"/>
@@ -5808,7 +5749,7 @@
       <c r="E384" s="9"/>
       <c r="F384" s="9"/>
       <c r="G384" s="11"/>
-      <c r="H384" s="13"/>
+      <c r="H384" s="16"/>
       <c r="I384" s="11"/>
       <c r="J384" s="11"/>
       <c r="K384" s="11"/>
@@ -5821,7 +5762,7 @@
       <c r="E385" s="9"/>
       <c r="F385" s="9"/>
       <c r="G385" s="11"/>
-      <c r="H385" s="13"/>
+      <c r="H385" s="16"/>
       <c r="I385" s="11"/>
       <c r="J385" s="11"/>
       <c r="K385" s="11"/>
@@ -5834,7 +5775,7 @@
       <c r="E386" s="9"/>
       <c r="F386" s="9"/>
       <c r="G386" s="11"/>
-      <c r="H386" s="13"/>
+      <c r="H386" s="16"/>
       <c r="I386" s="11"/>
       <c r="J386" s="11"/>
       <c r="K386" s="11"/>
@@ -5847,7 +5788,7 @@
       <c r="E387" s="9"/>
       <c r="F387" s="9"/>
       <c r="G387" s="11"/>
-      <c r="H387" s="13"/>
+      <c r="H387" s="16"/>
       <c r="I387" s="11"/>
       <c r="J387" s="11"/>
       <c r="K387" s="11"/>
@@ -5860,7 +5801,7 @@
       <c r="E388" s="9"/>
       <c r="F388" s="9"/>
       <c r="G388" s="11"/>
-      <c r="H388" s="13"/>
+      <c r="H388" s="16"/>
       <c r="I388" s="11"/>
       <c r="J388" s="11"/>
       <c r="K388" s="11"/>
@@ -5873,7 +5814,7 @@
       <c r="E389" s="9"/>
       <c r="F389" s="9"/>
       <c r="G389" s="11"/>
-      <c r="H389" s="13"/>
+      <c r="H389" s="16"/>
       <c r="I389" s="11"/>
       <c r="J389" s="11"/>
       <c r="K389" s="11"/>
@@ -5886,7 +5827,7 @@
       <c r="E390" s="9"/>
       <c r="F390" s="9"/>
       <c r="G390" s="11"/>
-      <c r="H390" s="13"/>
+      <c r="H390" s="16"/>
       <c r="I390" s="11"/>
       <c r="J390" s="11"/>
       <c r="K390" s="11"/>
@@ -5899,7 +5840,7 @@
       <c r="E391" s="9"/>
       <c r="F391" s="9"/>
       <c r="G391" s="11"/>
-      <c r="H391" s="13"/>
+      <c r="H391" s="16"/>
       <c r="I391" s="11"/>
       <c r="J391" s="11"/>
       <c r="K391" s="11"/>
@@ -5912,7 +5853,7 @@
       <c r="E392" s="9"/>
       <c r="F392" s="9"/>
       <c r="G392" s="11"/>
-      <c r="H392" s="13"/>
+      <c r="H392" s="16"/>
       <c r="I392" s="11"/>
       <c r="J392" s="11"/>
       <c r="K392" s="11"/>
@@ -5925,7 +5866,7 @@
       <c r="E393" s="9"/>
       <c r="F393" s="9"/>
       <c r="G393" s="11"/>
-      <c r="H393" s="13"/>
+      <c r="H393" s="16"/>
       <c r="I393" s="11"/>
       <c r="J393" s="11"/>
       <c r="K393" s="11"/>
@@ -5938,7 +5879,7 @@
       <c r="E394" s="9"/>
       <c r="F394" s="9"/>
       <c r="G394" s="11"/>
-      <c r="H394" s="13"/>
+      <c r="H394" s="16"/>
       <c r="I394" s="11"/>
       <c r="J394" s="11"/>
       <c r="K394" s="11"/>
@@ -5951,7 +5892,7 @@
       <c r="E395" s="9"/>
       <c r="F395" s="9"/>
       <c r="G395" s="11"/>
-      <c r="H395" s="13"/>
+      <c r="H395" s="16"/>
       <c r="I395" s="11"/>
       <c r="J395" s="11"/>
       <c r="K395" s="11"/>
@@ -5964,7 +5905,7 @@
       <c r="E396" s="9"/>
       <c r="F396" s="9"/>
       <c r="G396" s="11"/>
-      <c r="H396" s="13"/>
+      <c r="H396" s="16"/>
       <c r="I396" s="11"/>
       <c r="J396" s="11"/>
       <c r="K396" s="11"/>
@@ -5977,7 +5918,7 @@
       <c r="E397" s="9"/>
       <c r="F397" s="9"/>
       <c r="G397" s="11"/>
-      <c r="H397" s="13"/>
+      <c r="H397" s="16"/>
       <c r="I397" s="11"/>
       <c r="J397" s="11"/>
       <c r="K397" s="11"/>
@@ -5990,7 +5931,7 @@
       <c r="E398" s="9"/>
       <c r="F398" s="9"/>
       <c r="G398" s="11"/>
-      <c r="H398" s="13"/>
+      <c r="H398" s="16"/>
       <c r="I398" s="11"/>
       <c r="J398" s="11"/>
       <c r="K398" s="11"/>
@@ -6003,7 +5944,7 @@
       <c r="E399" s="9"/>
       <c r="F399" s="9"/>
       <c r="G399" s="11"/>
-      <c r="H399" s="13"/>
+      <c r="H399" s="16"/>
       <c r="I399" s="11"/>
       <c r="J399" s="11"/>
       <c r="K399" s="11"/>
@@ -6016,7 +5957,7 @@
       <c r="E400" s="9"/>
       <c r="F400" s="9"/>
       <c r="G400" s="11"/>
-      <c r="H400" s="13"/>
+      <c r="H400" s="16"/>
       <c r="I400" s="11"/>
       <c r="J400" s="11"/>
       <c r="K400" s="11"/>
@@ -6029,7 +5970,7 @@
       <c r="E401" s="9"/>
       <c r="F401" s="9"/>
       <c r="G401" s="11"/>
-      <c r="H401" s="13"/>
+      <c r="H401" s="16"/>
       <c r="I401" s="11"/>
       <c r="J401" s="11"/>
       <c r="K401" s="11"/>
@@ -6042,7 +5983,7 @@
       <c r="E402" s="9"/>
       <c r="F402" s="9"/>
       <c r="G402" s="11"/>
-      <c r="H402" s="13"/>
+      <c r="H402" s="16"/>
       <c r="I402" s="11"/>
       <c r="J402" s="11"/>
       <c r="K402" s="11"/>
@@ -6055,7 +5996,7 @@
       <c r="E403" s="9"/>
       <c r="F403" s="9"/>
       <c r="G403" s="11"/>
-      <c r="H403" s="13"/>
+      <c r="H403" s="16"/>
       <c r="I403" s="11"/>
       <c r="J403" s="11"/>
       <c r="K403" s="11"/>
@@ -6068,7 +6009,7 @@
       <c r="E404" s="9"/>
       <c r="F404" s="9"/>
       <c r="G404" s="11"/>
-      <c r="H404" s="13"/>
+      <c r="H404" s="16"/>
       <c r="I404" s="11"/>
       <c r="J404" s="11"/>
       <c r="K404" s="11"/>
@@ -6081,7 +6022,7 @@
       <c r="E405" s="9"/>
       <c r="F405" s="9"/>
       <c r="G405" s="11"/>
-      <c r="H405" s="13"/>
+      <c r="H405" s="16"/>
       <c r="I405" s="11"/>
       <c r="J405" s="11"/>
       <c r="K405" s="11"/>
@@ -6094,7 +6035,7 @@
       <c r="E406" s="9"/>
       <c r="F406" s="9"/>
       <c r="G406" s="11"/>
-      <c r="H406" s="13"/>
+      <c r="H406" s="16"/>
       <c r="I406" s="11"/>
       <c r="J406" s="11"/>
       <c r="K406" s="11"/>
@@ -6107,7 +6048,7 @@
       <c r="E407" s="9"/>
       <c r="F407" s="9"/>
       <c r="G407" s="11"/>
-      <c r="H407" s="13"/>
+      <c r="H407" s="16"/>
       <c r="I407" s="11"/>
       <c r="J407" s="11"/>
       <c r="K407" s="11"/>
@@ -6120,7 +6061,7 @@
       <c r="E408" s="9"/>
       <c r="F408" s="9"/>
       <c r="G408" s="11"/>
-      <c r="H408" s="13"/>
+      <c r="H408" s="16"/>
       <c r="I408" s="11"/>
       <c r="J408" s="11"/>
       <c r="K408" s="11"/>
@@ -6133,7 +6074,7 @@
       <c r="E409" s="9"/>
       <c r="F409" s="9"/>
       <c r="G409" s="11"/>
-      <c r="H409" s="13"/>
+      <c r="H409" s="16"/>
       <c r="I409" s="11"/>
       <c r="J409" s="11"/>
       <c r="K409" s="11"/>
@@ -6146,7 +6087,7 @@
       <c r="E410" s="9"/>
       <c r="F410" s="9"/>
       <c r="G410" s="11"/>
-      <c r="H410" s="13"/>
+      <c r="H410" s="16"/>
       <c r="I410" s="11"/>
       <c r="J410" s="11"/>
       <c r="K410" s="11"/>
@@ -6159,7 +6100,7 @@
       <c r="E411" s="9"/>
       <c r="F411" s="9"/>
       <c r="G411" s="11"/>
-      <c r="H411" s="13"/>
+      <c r="H411" s="16"/>
       <c r="I411" s="11"/>
       <c r="J411" s="11"/>
       <c r="K411" s="11"/>
@@ -6172,7 +6113,7 @@
       <c r="E412" s="9"/>
       <c r="F412" s="9"/>
       <c r="G412" s="11"/>
-      <c r="H412" s="13"/>
+      <c r="H412" s="16"/>
       <c r="I412" s="11"/>
       <c r="J412" s="11"/>
       <c r="K412" s="11"/>
@@ -6185,7 +6126,7 @@
       <c r="E413" s="9"/>
       <c r="F413" s="9"/>
       <c r="G413" s="11"/>
-      <c r="H413" s="13"/>
+      <c r="H413" s="16"/>
       <c r="I413" s="11"/>
       <c r="J413" s="11"/>
       <c r="K413" s="11"/>
@@ -6198,7 +6139,7 @@
       <c r="E414" s="9"/>
       <c r="F414" s="9"/>
       <c r="G414" s="11"/>
-      <c r="H414" s="13"/>
+      <c r="H414" s="16"/>
       <c r="I414" s="11"/>
       <c r="J414" s="11"/>
       <c r="K414" s="11"/>
@@ -6211,7 +6152,7 @@
       <c r="E415" s="9"/>
       <c r="F415" s="9"/>
       <c r="G415" s="11"/>
-      <c r="H415" s="13"/>
+      <c r="H415" s="16"/>
       <c r="I415" s="11"/>
       <c r="J415" s="11"/>
       <c r="K415" s="11"/>
@@ -6224,7 +6165,7 @@
       <c r="E416" s="9"/>
       <c r="F416" s="9"/>
       <c r="G416" s="11"/>
-      <c r="H416" s="13"/>
+      <c r="H416" s="16"/>
       <c r="I416" s="11"/>
       <c r="J416" s="11"/>
       <c r="K416" s="11"/>
@@ -6237,7 +6178,7 @@
       <c r="E417" s="9"/>
       <c r="F417" s="9"/>
       <c r="G417" s="11"/>
-      <c r="H417" s="13"/>
+      <c r="H417" s="16"/>
       <c r="I417" s="11"/>
       <c r="J417" s="11"/>
       <c r="K417" s="11"/>
@@ -6250,7 +6191,7 @@
       <c r="E418" s="9"/>
       <c r="F418" s="9"/>
       <c r="G418" s="11"/>
-      <c r="H418" s="13"/>
+      <c r="H418" s="16"/>
       <c r="I418" s="11"/>
       <c r="J418" s="11"/>
       <c r="K418" s="11"/>
@@ -6263,7 +6204,7 @@
       <c r="E419" s="9"/>
       <c r="F419" s="9"/>
       <c r="G419" s="11"/>
-      <c r="H419" s="13"/>
+      <c r="H419" s="16"/>
       <c r="I419" s="11"/>
       <c r="J419" s="11"/>
       <c r="K419" s="11"/>
@@ -6276,7 +6217,7 @@
       <c r="E420" s="9"/>
       <c r="F420" s="9"/>
       <c r="G420" s="11"/>
-      <c r="H420" s="13"/>
+      <c r="H420" s="16"/>
       <c r="I420" s="11"/>
       <c r="J420" s="11"/>
       <c r="K420" s="11"/>
@@ -6289,7 +6230,7 @@
       <c r="E421" s="9"/>
       <c r="F421" s="9"/>
       <c r="G421" s="11"/>
-      <c r="H421" s="13"/>
+      <c r="H421" s="16"/>
       <c r="I421" s="11"/>
       <c r="J421" s="11"/>
       <c r="K421" s="11"/>
@@ -6302,7 +6243,7 @@
       <c r="E422" s="9"/>
       <c r="F422" s="9"/>
       <c r="G422" s="11"/>
-      <c r="H422" s="13"/>
+      <c r="H422" s="16"/>
       <c r="I422" s="11"/>
       <c r="J422" s="11"/>
       <c r="K422" s="11"/>
@@ -6315,7 +6256,7 @@
       <c r="E423" s="9"/>
       <c r="F423" s="9"/>
       <c r="G423" s="11"/>
-      <c r="H423" s="13"/>
+      <c r="H423" s="16"/>
       <c r="I423" s="11"/>
       <c r="J423" s="11"/>
       <c r="K423" s="11"/>
@@ -6328,7 +6269,7 @@
       <c r="E424" s="9"/>
       <c r="F424" s="9"/>
       <c r="G424" s="11"/>
-      <c r="H424" s="13"/>
+      <c r="H424" s="16"/>
       <c r="I424" s="11"/>
       <c r="J424" s="11"/>
       <c r="K424" s="11"/>
@@ -6341,7 +6282,7 @@
       <c r="E425" s="9"/>
       <c r="F425" s="9"/>
       <c r="G425" s="11"/>
-      <c r="H425" s="13"/>
+      <c r="H425" s="16"/>
       <c r="I425" s="11"/>
       <c r="J425" s="11"/>
       <c r="K425" s="11"/>
@@ -6354,7 +6295,7 @@
       <c r="E426" s="9"/>
       <c r="F426" s="9"/>
       <c r="G426" s="11"/>
-      <c r="H426" s="13"/>
+      <c r="H426" s="16"/>
       <c r="I426" s="11"/>
       <c r="J426" s="11"/>
       <c r="K426" s="11"/>
@@ -6367,7 +6308,7 @@
       <c r="E427" s="9"/>
       <c r="F427" s="9"/>
       <c r="G427" s="11"/>
-      <c r="H427" s="13"/>
+      <c r="H427" s="16"/>
       <c r="I427" s="11"/>
       <c r="J427" s="11"/>
       <c r="K427" s="11"/>
@@ -6380,7 +6321,7 @@
       <c r="E428" s="9"/>
       <c r="F428" s="9"/>
       <c r="G428" s="11"/>
-      <c r="H428" s="13"/>
+      <c r="H428" s="16"/>
       <c r="I428" s="11"/>
       <c r="J428" s="11"/>
       <c r="K428" s="11"/>
@@ -6393,7 +6334,7 @@
       <c r="E429" s="9"/>
       <c r="F429" s="9"/>
       <c r="G429" s="11"/>
-      <c r="H429" s="13"/>
+      <c r="H429" s="16"/>
       <c r="I429" s="11"/>
       <c r="J429" s="11"/>
       <c r="K429" s="11"/>
@@ -6406,7 +6347,7 @@
       <c r="E430" s="9"/>
       <c r="F430" s="9"/>
       <c r="G430" s="11"/>
-      <c r="H430" s="13"/>
+      <c r="H430" s="16"/>
       <c r="I430" s="11"/>
       <c r="J430" s="11"/>
       <c r="K430" s="11"/>
@@ -6419,7 +6360,7 @@
       <c r="E431" s="9"/>
       <c r="F431" s="9"/>
       <c r="G431" s="11"/>
-      <c r="H431" s="13"/>
+      <c r="H431" s="16"/>
       <c r="I431" s="11"/>
       <c r="J431" s="11"/>
       <c r="K431" s="11"/>
@@ -6432,7 +6373,7 @@
       <c r="E432" s="9"/>
       <c r="F432" s="9"/>
       <c r="G432" s="11"/>
-      <c r="H432" s="13"/>
+      <c r="H432" s="16"/>
       <c r="I432" s="11"/>
       <c r="J432" s="11"/>
       <c r="K432" s="11"/>
@@ -6445,7 +6386,7 @@
       <c r="E433" s="9"/>
       <c r="F433" s="9"/>
       <c r="G433" s="11"/>
-      <c r="H433" s="13"/>
+      <c r="H433" s="16"/>
       <c r="I433" s="11"/>
       <c r="J433" s="11"/>
       <c r="K433" s="11"/>
@@ -6458,7 +6399,7 @@
       <c r="E434" s="9"/>
       <c r="F434" s="9"/>
       <c r="G434" s="11"/>
-      <c r="H434" s="13"/>
+      <c r="H434" s="16"/>
       <c r="I434" s="11"/>
       <c r="J434" s="11"/>
       <c r="K434" s="11"/>
@@ -6471,7 +6412,7 @@
       <c r="E435" s="9"/>
       <c r="F435" s="9"/>
       <c r="G435" s="11"/>
-      <c r="H435" s="13"/>
+      <c r="H435" s="16"/>
       <c r="I435" s="11"/>
       <c r="J435" s="11"/>
       <c r="K435" s="11"/>
@@ -6484,7 +6425,7 @@
       <c r="E436" s="9"/>
       <c r="F436" s="9"/>
       <c r="G436" s="11"/>
-      <c r="H436" s="13"/>
+      <c r="H436" s="16"/>
       <c r="I436" s="11"/>
       <c r="J436" s="11"/>
       <c r="K436" s="11"/>
@@ -6497,7 +6438,7 @@
       <c r="E437" s="9"/>
       <c r="F437" s="9"/>
       <c r="G437" s="11"/>
-      <c r="H437" s="13"/>
+      <c r="H437" s="16"/>
       <c r="I437" s="11"/>
       <c r="J437" s="11"/>
       <c r="K437" s="11"/>
@@ -6510,7 +6451,7 @@
       <c r="E438" s="9"/>
       <c r="F438" s="9"/>
       <c r="G438" s="11"/>
-      <c r="H438" s="13"/>
+      <c r="H438" s="16"/>
       <c r="I438" s="11"/>
       <c r="J438" s="11"/>
       <c r="K438" s="11"/>
@@ -6523,7 +6464,7 @@
       <c r="E439" s="9"/>
       <c r="F439" s="9"/>
       <c r="G439" s="11"/>
-      <c r="H439" s="13"/>
+      <c r="H439" s="16"/>
       <c r="I439" s="11"/>
       <c r="J439" s="11"/>
       <c r="K439" s="11"/>
@@ -6536,7 +6477,7 @@
       <c r="E440" s="9"/>
       <c r="F440" s="9"/>
       <c r="G440" s="11"/>
-      <c r="H440" s="13"/>
+      <c r="H440" s="16"/>
       <c r="I440" s="11"/>
       <c r="J440" s="11"/>
       <c r="K440" s="11"/>
@@ -6549,7 +6490,7 @@
       <c r="E441" s="9"/>
       <c r="F441" s="9"/>
       <c r="G441" s="11"/>
-      <c r="H441" s="13"/>
+      <c r="H441" s="16"/>
       <c r="I441" s="11"/>
       <c r="J441" s="11"/>
       <c r="K441" s="11"/>
@@ -6562,7 +6503,7 @@
       <c r="E442" s="9"/>
       <c r="F442" s="9"/>
       <c r="G442" s="11"/>
-      <c r="H442" s="13"/>
+      <c r="H442" s="16"/>
       <c r="I442" s="11"/>
       <c r="J442" s="11"/>
       <c r="K442" s="11"/>
@@ -6575,7 +6516,7 @@
       <c r="E443" s="9"/>
       <c r="F443" s="9"/>
       <c r="G443" s="11"/>
-      <c r="H443" s="13"/>
+      <c r="H443" s="16"/>
       <c r="I443" s="11"/>
       <c r="J443" s="11"/>
       <c r="K443" s="11"/>
@@ -6588,7 +6529,7 @@
       <c r="E444" s="9"/>
       <c r="F444" s="9"/>
       <c r="G444" s="11"/>
-      <c r="H444" s="13"/>
+      <c r="H444" s="16"/>
       <c r="I444" s="11"/>
       <c r="J444" s="11"/>
       <c r="K444" s="11"/>
@@ -6601,7 +6542,7 @@
       <c r="E445" s="9"/>
       <c r="F445" s="9"/>
       <c r="G445" s="11"/>
-      <c r="H445" s="13"/>
+      <c r="H445" s="16"/>
       <c r="I445" s="11"/>
       <c r="J445" s="11"/>
       <c r="K445" s="11"/>
@@ -6614,7 +6555,7 @@
       <c r="E446" s="9"/>
       <c r="F446" s="9"/>
       <c r="G446" s="11"/>
-      <c r="H446" s="13"/>
+      <c r="H446" s="16"/>
       <c r="I446" s="11"/>
       <c r="J446" s="11"/>
       <c r="K446" s="11"/>
@@ -6627,7 +6568,7 @@
       <c r="E447" s="9"/>
       <c r="F447" s="9"/>
       <c r="G447" s="11"/>
-      <c r="H447" s="13"/>
+      <c r="H447" s="16"/>
       <c r="I447" s="11"/>
       <c r="J447" s="11"/>
       <c r="K447" s="11"/>
@@ -6640,7 +6581,7 @@
       <c r="E448" s="9"/>
       <c r="F448" s="9"/>
       <c r="G448" s="11"/>
-      <c r="H448" s="13"/>
+      <c r="H448" s="16"/>
       <c r="I448" s="11"/>
       <c r="J448" s="11"/>
       <c r="K448" s="11"/>
@@ -6653,7 +6594,7 @@
       <c r="E449" s="9"/>
       <c r="F449" s="9"/>
       <c r="G449" s="11"/>
-      <c r="H449" s="13"/>
+      <c r="H449" s="16"/>
       <c r="I449" s="11"/>
       <c r="J449" s="11"/>
       <c r="K449" s="11"/>
@@ -6666,7 +6607,7 @@
       <c r="E450" s="9"/>
       <c r="F450" s="9"/>
       <c r="G450" s="11"/>
-      <c r="H450" s="13"/>
+      <c r="H450" s="16"/>
       <c r="I450" s="11"/>
       <c r="J450" s="11"/>
       <c r="K450" s="11"/>
@@ -6679,7 +6620,7 @@
       <c r="E451" s="9"/>
       <c r="F451" s="9"/>
       <c r="G451" s="11"/>
-      <c r="H451" s="13"/>
+      <c r="H451" s="16"/>
       <c r="I451" s="11"/>
       <c r="J451" s="11"/>
       <c r="K451" s="11"/>
@@ -6692,7 +6633,7 @@
       <c r="E452" s="9"/>
       <c r="F452" s="9"/>
       <c r="G452" s="11"/>
-      <c r="H452" s="13"/>
+      <c r="H452" s="16"/>
       <c r="I452" s="11"/>
       <c r="J452" s="11"/>
       <c r="K452" s="11"/>
@@ -6705,7 +6646,7 @@
       <c r="E453" s="9"/>
       <c r="F453" s="9"/>
       <c r="G453" s="11"/>
-      <c r="H453" s="13"/>
+      <c r="H453" s="16"/>
       <c r="I453" s="11"/>
       <c r="J453" s="11"/>
       <c r="K453" s="11"/>
@@ -6718,7 +6659,7 @@
       <c r="E454" s="9"/>
       <c r="F454" s="9"/>
       <c r="G454" s="11"/>
-      <c r="H454" s="13"/>
+      <c r="H454" s="16"/>
       <c r="I454" s="11"/>
       <c r="J454" s="11"/>
       <c r="K454" s="11"/>
@@ -6731,7 +6672,7 @@
       <c r="E455" s="9"/>
       <c r="F455" s="9"/>
       <c r="G455" s="11"/>
-      <c r="H455" s="13"/>
+      <c r="H455" s="16"/>
       <c r="I455" s="11"/>
       <c r="J455" s="11"/>
       <c r="K455" s="11"/>
@@ -6744,7 +6685,7 @@
       <c r="E456" s="9"/>
       <c r="F456" s="9"/>
       <c r="G456" s="11"/>
-      <c r="H456" s="13"/>
+      <c r="H456" s="16"/>
       <c r="I456" s="11"/>
       <c r="J456" s="11"/>
       <c r="K456" s="11"/>
@@ -6757,7 +6698,7 @@
       <c r="E457" s="9"/>
       <c r="F457" s="9"/>
       <c r="G457" s="11"/>
-      <c r="H457" s="13"/>
+      <c r="H457" s="16"/>
       <c r="I457" s="11"/>
       <c r="J457" s="11"/>
       <c r="K457" s="11"/>
@@ -6770,7 +6711,7 @@
       <c r="E458" s="9"/>
       <c r="F458" s="9"/>
       <c r="G458" s="11"/>
-      <c r="H458" s="13"/>
+      <c r="H458" s="16"/>
       <c r="I458" s="11"/>
       <c r="J458" s="11"/>
       <c r="K458" s="11"/>
@@ -6783,7 +6724,7 @@
       <c r="E459" s="9"/>
       <c r="F459" s="9"/>
       <c r="G459" s="11"/>
-      <c r="H459" s="13"/>
+      <c r="H459" s="16"/>
       <c r="I459" s="11"/>
       <c r="J459" s="11"/>
       <c r="K459" s="11"/>
@@ -6796,7 +6737,7 @@
       <c r="E460" s="9"/>
       <c r="F460" s="9"/>
       <c r="G460" s="11"/>
-      <c r="H460" s="13"/>
+      <c r="H460" s="16"/>
       <c r="I460" s="11"/>
       <c r="J460" s="11"/>
       <c r="K460" s="11"/>
@@ -6809,7 +6750,7 @@
       <c r="E461" s="9"/>
       <c r="F461" s="9"/>
       <c r="G461" s="11"/>
-      <c r="H461" s="13"/>
+      <c r="H461" s="16"/>
       <c r="I461" s="11"/>
       <c r="J461" s="11"/>
       <c r="K461" s="11"/>
@@ -6822,7 +6763,7 @@
       <c r="E462" s="9"/>
       <c r="F462" s="9"/>
       <c r="G462" s="11"/>
-      <c r="H462" s="13"/>
+      <c r="H462" s="16"/>
       <c r="I462" s="11"/>
       <c r="J462" s="11"/>
       <c r="K462" s="11"/>
@@ -6835,7 +6776,7 @@
       <c r="E463" s="9"/>
       <c r="F463" s="9"/>
       <c r="G463" s="11"/>
-      <c r="H463" s="13"/>
+      <c r="H463" s="16"/>
       <c r="I463" s="11"/>
       <c r="J463" s="11"/>
       <c r="K463" s="11"/>
@@ -6848,7 +6789,7 @@
       <c r="E464" s="9"/>
       <c r="F464" s="9"/>
       <c r="G464" s="11"/>
-      <c r="H464" s="13"/>
+      <c r="H464" s="16"/>
       <c r="I464" s="11"/>
       <c r="J464" s="11"/>
       <c r="K464" s="11"/>
@@ -6861,7 +6802,7 @@
       <c r="E465" s="9"/>
       <c r="F465" s="9"/>
       <c r="G465" s="11"/>
-      <c r="H465" s="13"/>
+      <c r="H465" s="16"/>
       <c r="I465" s="11"/>
       <c r="J465" s="11"/>
       <c r="K465" s="11"/>
@@ -6874,7 +6815,7 @@
       <c r="E466" s="9"/>
       <c r="F466" s="9"/>
       <c r="G466" s="11"/>
-      <c r="H466" s="13"/>
+      <c r="H466" s="16"/>
       <c r="I466" s="11"/>
       <c r="J466" s="11"/>
       <c r="K466" s="11"/>
@@ -6887,7 +6828,7 @@
       <c r="E467" s="9"/>
       <c r="F467" s="9"/>
       <c r="G467" s="11"/>
-      <c r="H467" s="13"/>
+      <c r="H467" s="16"/>
       <c r="I467" s="11"/>
       <c r="J467" s="11"/>
       <c r="K467" s="11"/>
@@ -6900,7 +6841,7 @@
       <c r="E468" s="9"/>
       <c r="F468" s="9"/>
       <c r="G468" s="11"/>
-      <c r="H468" s="13"/>
+      <c r="H468" s="16"/>
       <c r="I468" s="11"/>
       <c r="J468" s="11"/>
       <c r="K468" s="11"/>
@@ -6913,7 +6854,7 @@
       <c r="E469" s="9"/>
       <c r="F469" s="9"/>
       <c r="G469" s="11"/>
-      <c r="H469" s="13"/>
+      <c r="H469" s="16"/>
       <c r="I469" s="11"/>
       <c r="J469" s="11"/>
       <c r="K469" s="11"/>
@@ -6926,7 +6867,7 @@
       <c r="E470" s="9"/>
       <c r="F470" s="9"/>
       <c r="G470" s="11"/>
-      <c r="H470" s="13"/>
+      <c r="H470" s="16"/>
       <c r="I470" s="11"/>
       <c r="J470" s="11"/>
       <c r="K470" s="11"/>
@@ -6939,7 +6880,7 @@
       <c r="E471" s="9"/>
       <c r="F471" s="9"/>
       <c r="G471" s="11"/>
-      <c r="H471" s="13"/>
+      <c r="H471" s="16"/>
       <c r="I471" s="11"/>
       <c r="J471" s="11"/>
       <c r="K471" s="11"/>
@@ -6952,7 +6893,7 @@
       <c r="E472" s="9"/>
       <c r="F472" s="9"/>
       <c r="G472" s="11"/>
-      <c r="H472" s="13"/>
+      <c r="H472" s="16"/>
       <c r="I472" s="11"/>
       <c r="J472" s="11"/>
       <c r="K472" s="11"/>
@@ -6965,7 +6906,7 @@
       <c r="E473" s="9"/>
       <c r="F473" s="9"/>
       <c r="G473" s="11"/>
-      <c r="H473" s="13"/>
+      <c r="H473" s="16"/>
       <c r="I473" s="11"/>
       <c r="J473" s="11"/>
       <c r="K473" s="11"/>
@@ -6978,7 +6919,7 @@
       <c r="E474" s="9"/>
       <c r="F474" s="9"/>
       <c r="G474" s="11"/>
-      <c r="H474" s="13"/>
+      <c r="H474" s="16"/>
       <c r="I474" s="11"/>
       <c r="J474" s="11"/>
       <c r="K474" s="11"/>
@@ -6991,7 +6932,7 @@
       <c r="E475" s="9"/>
       <c r="F475" s="9"/>
       <c r="G475" s="11"/>
-      <c r="H475" s="13"/>
+      <c r="H475" s="16"/>
       <c r="I475" s="11"/>
       <c r="J475" s="11"/>
       <c r="K475" s="11"/>
@@ -7004,7 +6945,7 @@
       <c r="E476" s="9"/>
       <c r="F476" s="9"/>
       <c r="G476" s="11"/>
-      <c r="H476" s="13"/>
+      <c r="H476" s="16"/>
       <c r="I476" s="11"/>
       <c r="J476" s="11"/>
       <c r="K476" s="11"/>
@@ -7017,7 +6958,7 @@
       <c r="E477" s="9"/>
       <c r="F477" s="9"/>
       <c r="G477" s="11"/>
-      <c r="H477" s="13"/>
+      <c r="H477" s="16"/>
       <c r="I477" s="11"/>
       <c r="J477" s="11"/>
       <c r="K477" s="11"/>
@@ -7030,7 +6971,7 @@
       <c r="E478" s="9"/>
       <c r="F478" s="9"/>
       <c r="G478" s="11"/>
-      <c r="H478" s="13"/>
+      <c r="H478" s="16"/>
       <c r="I478" s="11"/>
       <c r="J478" s="11"/>
       <c r="K478" s="11"/>
@@ -7043,7 +6984,7 @@
       <c r="E479" s="9"/>
       <c r="F479" s="9"/>
       <c r="G479" s="11"/>
-      <c r="H479" s="13"/>
+      <c r="H479" s="16"/>
       <c r="I479" s="11"/>
       <c r="J479" s="11"/>
       <c r="K479" s="11"/>
@@ -7056,7 +6997,7 @@
       <c r="E480" s="9"/>
       <c r="F480" s="9"/>
       <c r="G480" s="11"/>
-      <c r="H480" s="13"/>
+      <c r="H480" s="16"/>
       <c r="I480" s="11"/>
       <c r="J480" s="11"/>
       <c r="K480" s="11"/>
@@ -7069,7 +7010,7 @@
       <c r="E481" s="9"/>
       <c r="F481" s="9"/>
       <c r="G481" s="11"/>
-      <c r="H481" s="13"/>
+      <c r="H481" s="16"/>
       <c r="I481" s="11"/>
       <c r="J481" s="11"/>
       <c r="K481" s="11"/>
@@ -7082,7 +7023,7 @@
       <c r="E482" s="9"/>
       <c r="F482" s="9"/>
       <c r="G482" s="11"/>
-      <c r="H482" s="13"/>
+      <c r="H482" s="16"/>
       <c r="I482" s="11"/>
       <c r="J482" s="11"/>
       <c r="K482" s="11"/>
@@ -7095,7 +7036,7 @@
       <c r="E483" s="9"/>
       <c r="F483" s="9"/>
       <c r="G483" s="11"/>
-      <c r="H483" s="13"/>
+      <c r="H483" s="16"/>
       <c r="I483" s="11"/>
       <c r="J483" s="11"/>
       <c r="K483" s="11"/>
@@ -7108,7 +7049,7 @@
       <c r="E484" s="9"/>
       <c r="F484" s="9"/>
       <c r="G484" s="11"/>
-      <c r="H484" s="13"/>
+      <c r="H484" s="16"/>
       <c r="I484" s="11"/>
       <c r="J484" s="11"/>
       <c r="K484" s="11"/>
@@ -7121,7 +7062,7 @@
       <c r="E485" s="9"/>
       <c r="F485" s="9"/>
       <c r="G485" s="11"/>
-      <c r="H485" s="13"/>
+      <c r="H485" s="16"/>
       <c r="I485" s="11"/>
       <c r="J485" s="11"/>
       <c r="K485" s="11"/>
@@ -7134,7 +7075,7 @@
       <c r="E486" s="9"/>
       <c r="F486" s="9"/>
       <c r="G486" s="11"/>
-      <c r="H486" s="13"/>
+      <c r="H486" s="16"/>
       <c r="I486" s="11"/>
       <c r="J486" s="11"/>
       <c r="K486" s="11"/>
@@ -7147,7 +7088,7 @@
       <c r="E487" s="9"/>
       <c r="F487" s="9"/>
       <c r="G487" s="11"/>
-      <c r="H487" s="13"/>
+      <c r="H487" s="16"/>
       <c r="I487" s="11"/>
       <c r="J487" s="11"/>
       <c r="K487" s="11"/>
@@ -7160,7 +7101,7 @@
       <c r="E488" s="9"/>
       <c r="F488" s="9"/>
       <c r="G488" s="11"/>
-      <c r="H488" s="13"/>
+      <c r="H488" s="16"/>
       <c r="I488" s="11"/>
       <c r="J488" s="11"/>
       <c r="K488" s="11"/>
@@ -7173,7 +7114,7 @@
       <c r="E489" s="9"/>
       <c r="F489" s="9"/>
       <c r="G489" s="11"/>
-      <c r="H489" s="13"/>
+      <c r="H489" s="16"/>
       <c r="I489" s="11"/>
       <c r="J489" s="11"/>
       <c r="K489" s="11"/>
@@ -7186,7 +7127,7 @@
       <c r="E490" s="9"/>
       <c r="F490" s="9"/>
       <c r="G490" s="11"/>
-      <c r="H490" s="13"/>
+      <c r="H490" s="16"/>
       <c r="I490" s="11"/>
       <c r="J490" s="11"/>
       <c r="K490" s="11"/>
@@ -7199,7 +7140,7 @@
       <c r="E491" s="9"/>
       <c r="F491" s="9"/>
       <c r="G491" s="11"/>
-      <c r="H491" s="13"/>
+      <c r="H491" s="16"/>
       <c r="I491" s="11"/>
       <c r="J491" s="11"/>
       <c r="K491" s="11"/>
@@ -7212,7 +7153,7 @@
       <c r="E492" s="9"/>
       <c r="F492" s="9"/>
       <c r="G492" s="11"/>
-      <c r="H492" s="13"/>
+      <c r="H492" s="16"/>
       <c r="I492" s="11"/>
       <c r="J492" s="11"/>
       <c r="K492" s="11"/>
@@ -7225,7 +7166,7 @@
       <c r="E493" s="9"/>
       <c r="F493" s="9"/>
       <c r="G493" s="11"/>
-      <c r="H493" s="13"/>
+      <c r="H493" s="16"/>
       <c r="I493" s="11"/>
       <c r="J493" s="11"/>
       <c r="K493" s="11"/>
@@ -7238,7 +7179,7 @@
       <c r="E494" s="9"/>
       <c r="F494" s="9"/>
       <c r="G494" s="11"/>
-      <c r="H494" s="13"/>
+      <c r="H494" s="16"/>
       <c r="I494" s="11"/>
       <c r="J494" s="11"/>
       <c r="K494" s="11"/>
@@ -7251,7 +7192,7 @@
       <c r="E495" s="9"/>
       <c r="F495" s="9"/>
       <c r="G495" s="11"/>
-      <c r="H495" s="13"/>
+      <c r="H495" s="16"/>
       <c r="I495" s="11"/>
       <c r="J495" s="11"/>
       <c r="K495" s="11"/>
@@ -7264,7 +7205,7 @@
       <c r="E496" s="9"/>
       <c r="F496" s="9"/>
       <c r="G496" s="11"/>
-      <c r="H496" s="13"/>
+      <c r="H496" s="16"/>
       <c r="I496" s="11"/>
       <c r="J496" s="11"/>
       <c r="K496" s="11"/>
@@ -7277,7 +7218,7 @@
       <c r="E497" s="9"/>
       <c r="F497" s="9"/>
       <c r="G497" s="11"/>
-      <c r="H497" s="13"/>
+      <c r="H497" s="16"/>
       <c r="I497" s="11"/>
       <c r="J497" s="11"/>
       <c r="K497" s="11"/>
@@ -7290,7 +7231,7 @@
       <c r="E498" s="9"/>
       <c r="F498" s="9"/>
       <c r="G498" s="11"/>
-      <c r="H498" s="13"/>
+      <c r="H498" s="16"/>
       <c r="I498" s="11"/>
       <c r="J498" s="11"/>
       <c r="K498" s="11"/>
@@ -7303,7 +7244,7 @@
       <c r="E499" s="9"/>
       <c r="F499" s="9"/>
       <c r="G499" s="11"/>
-      <c r="H499" s="13"/>
+      <c r="H499" s="16"/>
       <c r="I499" s="11"/>
       <c r="J499" s="11"/>
       <c r="K499" s="11"/>
@@ -7316,7 +7257,7 @@
       <c r="E500" s="9"/>
       <c r="F500" s="9"/>
       <c r="G500" s="11"/>
-      <c r="H500" s="13"/>
+      <c r="H500" s="16"/>
       <c r="I500" s="11"/>
       <c r="J500" s="11"/>
       <c r="K500" s="11"/>
@@ -7329,7 +7270,7 @@
       <c r="E501" s="9"/>
       <c r="F501" s="9"/>
       <c r="G501" s="11"/>
-      <c r="H501" s="13"/>
+      <c r="H501" s="16"/>
       <c r="I501" s="11"/>
       <c r="J501" s="11"/>
       <c r="K501" s="11"/>
@@ -7342,7 +7283,7 @@
       <c r="E502" s="9"/>
       <c r="F502" s="9"/>
       <c r="G502" s="11"/>
-      <c r="H502" s="13"/>
+      <c r="H502" s="16"/>
       <c r="I502" s="11"/>
       <c r="J502" s="11"/>
       <c r="K502" s="11"/>
@@ -7355,7 +7296,7 @@
       <c r="E503" s="9"/>
       <c r="F503" s="9"/>
       <c r="G503" s="11"/>
-      <c r="H503" s="13"/>
+      <c r="H503" s="16"/>
       <c r="I503" s="11"/>
       <c r="J503" s="11"/>
       <c r="K503" s="11"/>
@@ -7368,7 +7309,7 @@
       <c r="E504" s="9"/>
       <c r="F504" s="9"/>
       <c r="G504" s="11"/>
-      <c r="H504" s="13"/>
+      <c r="H504" s="16"/>
       <c r="I504" s="11"/>
       <c r="J504" s="11"/>
       <c r="K504" s="11"/>
@@ -7381,7 +7322,7 @@
       <c r="E505" s="9"/>
       <c r="F505" s="9"/>
       <c r="G505" s="11"/>
-      <c r="H505" s="13"/>
+      <c r="H505" s="16"/>
       <c r="I505" s="11"/>
       <c r="J505" s="11"/>
       <c r="K505" s="11"/>
@@ -7394,7 +7335,7 @@
       <c r="E506" s="9"/>
       <c r="F506" s="9"/>
       <c r="G506" s="11"/>
-      <c r="H506" s="13"/>
+      <c r="H506" s="16"/>
       <c r="I506" s="11"/>
       <c r="J506" s="11"/>
       <c r="K506" s="11"/>
@@ -7407,7 +7348,7 @@
       <c r="E507" s="9"/>
       <c r="F507" s="9"/>
       <c r="G507" s="11"/>
-      <c r="H507" s="13"/>
+      <c r="H507" s="16"/>
       <c r="I507" s="11"/>
       <c r="J507" s="11"/>
       <c r="K507" s="11"/>
@@ -7420,7 +7361,7 @@
       <c r="E508" s="9"/>
       <c r="F508" s="9"/>
       <c r="G508" s="11"/>
-      <c r="H508" s="13"/>
+      <c r="H508" s="16"/>
       <c r="I508" s="11"/>
       <c r="J508" s="11"/>
       <c r="K508" s="11"/>
@@ -7433,7 +7374,7 @@
       <c r="E509" s="9"/>
       <c r="F509" s="9"/>
       <c r="G509" s="11"/>
-      <c r="H509" s="13"/>
+      <c r="H509" s="16"/>
       <c r="I509" s="11"/>
       <c r="J509" s="11"/>
       <c r="K509" s="11"/>
@@ -7446,7 +7387,7 @@
       <c r="E510" s="9"/>
       <c r="F510" s="9"/>
       <c r="G510" s="11"/>
-      <c r="H510" s="13"/>
+      <c r="H510" s="16"/>
       <c r="I510" s="11"/>
       <c r="J510" s="11"/>
       <c r="K510" s="11"/>
@@ -7459,7 +7400,7 @@
       <c r="E511" s="9"/>
       <c r="F511" s="9"/>
       <c r="G511" s="11"/>
-      <c r="H511" s="13"/>
+      <c r="H511" s="16"/>
       <c r="I511" s="11"/>
       <c r="J511" s="11"/>
       <c r="K511" s="11"/>
@@ -7472,7 +7413,7 @@
       <c r="E512" s="9"/>
       <c r="F512" s="9"/>
       <c r="G512" s="11"/>
-      <c r="H512" s="13"/>
+      <c r="H512" s="16"/>
       <c r="I512" s="11"/>
       <c r="J512" s="11"/>
       <c r="K512" s="11"/>
@@ -7485,7 +7426,7 @@
       <c r="E513" s="9"/>
       <c r="F513" s="9"/>
       <c r="G513" s="11"/>
-      <c r="H513" s="13"/>
+      <c r="H513" s="16"/>
       <c r="I513" s="11"/>
       <c r="J513" s="11"/>
       <c r="K513" s="11"/>
@@ -7498,7 +7439,7 @@
       <c r="E514" s="9"/>
       <c r="F514" s="9"/>
       <c r="G514" s="11"/>
-      <c r="H514" s="13"/>
+      <c r="H514" s="16"/>
       <c r="I514" s="11"/>
       <c r="J514" s="11"/>
       <c r="K514" s="11"/>
@@ -7511,7 +7452,7 @@
       <c r="E515" s="9"/>
       <c r="F515" s="9"/>
       <c r="G515" s="11"/>
-      <c r="H515" s="13"/>
+      <c r="H515" s="16"/>
       <c r="I515" s="11"/>
       <c r="J515" s="11"/>
       <c r="K515" s="11"/>
@@ -7524,7 +7465,7 @@
       <c r="E516" s="9"/>
       <c r="F516" s="9"/>
       <c r="G516" s="11"/>
-      <c r="H516" s="13"/>
+      <c r="H516" s="16"/>
       <c r="I516" s="11"/>
       <c r="J516" s="11"/>
       <c r="K516" s="11"/>
@@ -7537,7 +7478,7 @@
       <c r="E517" s="9"/>
       <c r="F517" s="9"/>
       <c r="G517" s="11"/>
-      <c r="H517" s="13"/>
+      <c r="H517" s="16"/>
       <c r="I517" s="11"/>
       <c r="J517" s="11"/>
       <c r="K517" s="11"/>
@@ -7550,7 +7491,7 @@
       <c r="E518" s="9"/>
       <c r="F518" s="9"/>
       <c r="G518" s="11"/>
-      <c r="H518" s="13"/>
+      <c r="H518" s="16"/>
       <c r="I518" s="11"/>
       <c r="J518" s="11"/>
       <c r="K518" s="11"/>
@@ -7563,7 +7504,7 @@
       <c r="E519" s="9"/>
       <c r="F519" s="9"/>
       <c r="G519" s="11"/>
-      <c r="H519" s="13"/>
+      <c r="H519" s="16"/>
       <c r="I519" s="11"/>
       <c r="J519" s="11"/>
       <c r="K519" s="11"/>
@@ -7576,7 +7517,7 @@
       <c r="E520" s="9"/>
       <c r="F520" s="9"/>
       <c r="G520" s="11"/>
-      <c r="H520" s="13"/>
+      <c r="H520" s="16"/>
       <c r="I520" s="11"/>
       <c r="J520" s="11"/>
       <c r="K520" s="11"/>
@@ -7589,7 +7530,7 @@
       <c r="E521" s="9"/>
       <c r="F521" s="9"/>
       <c r="G521" s="11"/>
-      <c r="H521" s="13"/>
+      <c r="H521" s="16"/>
       <c r="I521" s="11"/>
       <c r="J521" s="11"/>
       <c r="K521" s="11"/>
@@ -7602,7 +7543,7 @@
       <c r="E522" s="9"/>
       <c r="F522" s="9"/>
       <c r="G522" s="11"/>
-      <c r="H522" s="13"/>
+      <c r="H522" s="16"/>
       <c r="I522" s="11"/>
       <c r="J522" s="11"/>
       <c r="K522" s="11"/>
@@ -7615,7 +7556,7 @@
       <c r="E523" s="9"/>
       <c r="F523" s="9"/>
       <c r="G523" s="11"/>
-      <c r="H523" s="13"/>
+      <c r="H523" s="16"/>
       <c r="I523" s="11"/>
       <c r="J523" s="11"/>
       <c r="K523" s="11"/>
@@ -7628,7 +7569,7 @@
       <c r="E524" s="9"/>
       <c r="F524" s="9"/>
       <c r="G524" s="11"/>
-      <c r="H524" s="13"/>
+      <c r="H524" s="16"/>
       <c r="I524" s="11"/>
       <c r="J524" s="11"/>
       <c r="K524" s="11"/>
@@ -7641,7 +7582,7 @@
       <c r="E525" s="9"/>
       <c r="F525" s="9"/>
       <c r="G525" s="11"/>
-      <c r="H525" s="13"/>
+      <c r="H525" s="16"/>
       <c r="I525" s="11"/>
       <c r="J525" s="11"/>
       <c r="K525" s="11"/>
@@ -7654,7 +7595,7 @@
       <c r="E526" s="9"/>
       <c r="F526" s="9"/>
       <c r="G526" s="11"/>
-      <c r="H526" s="13"/>
+      <c r="H526" s="16"/>
       <c r="I526" s="11"/>
       <c r="J526" s="11"/>
       <c r="K526" s="11"/>
@@ -7667,7 +7608,7 @@
       <c r="E527" s="9"/>
       <c r="F527" s="9"/>
       <c r="G527" s="11"/>
-      <c r="H527" s="13"/>
+      <c r="H527" s="16"/>
       <c r="I527" s="11"/>
       <c r="J527" s="11"/>
       <c r="K527" s="11"/>
@@ -7680,7 +7621,7 @@
       <c r="E528" s="9"/>
       <c r="F528" s="9"/>
       <c r="G528" s="11"/>
-      <c r="H528" s="13"/>
+      <c r="H528" s="16"/>
       <c r="I528" s="11"/>
       <c r="J528" s="11"/>
       <c r="K528" s="11"/>
@@ -7693,7 +7634,7 @@
       <c r="E529" s="9"/>
       <c r="F529" s="9"/>
       <c r="G529" s="11"/>
-      <c r="H529" s="13"/>
+      <c r="H529" s="16"/>
       <c r="I529" s="11"/>
       <c r="J529" s="11"/>
       <c r="K529" s="11"/>
@@ -7706,7 +7647,7 @@
       <c r="E530" s="9"/>
       <c r="F530" s="9"/>
       <c r="G530" s="11"/>
-      <c r="H530" s="13"/>
+      <c r="H530" s="16"/>
       <c r="I530" s="11"/>
       <c r="J530" s="11"/>
       <c r="K530" s="11"/>
@@ -7719,7 +7660,7 @@
       <c r="E531" s="9"/>
       <c r="F531" s="9"/>
       <c r="G531" s="11"/>
-      <c r="H531" s="13"/>
+      <c r="H531" s="16"/>
       <c r="I531" s="11"/>
       <c r="J531" s="11"/>
       <c r="K531" s="11"/>
@@ -7732,7 +7673,7 @@
       <c r="E532" s="9"/>
       <c r="F532" s="9"/>
       <c r="G532" s="11"/>
-      <c r="H532" s="13"/>
+      <c r="H532" s="16"/>
       <c r="I532" s="11"/>
       <c r="J532" s="11"/>
       <c r="K532" s="11"/>
@@ -7745,7 +7686,7 @@
       <c r="E533" s="9"/>
       <c r="F533" s="9"/>
       <c r="G533" s="11"/>
-      <c r="H533" s="13"/>
+      <c r="H533" s="16"/>
       <c r="I533" s="11"/>
       <c r="J533" s="11"/>
       <c r="K533" s="11"/>
@@ -7758,7 +7699,7 @@
       <c r="E534" s="9"/>
       <c r="F534" s="9"/>
       <c r="G534" s="11"/>
-      <c r="H534" s="13"/>
+      <c r="H534" s="16"/>
       <c r="I534" s="11"/>
       <c r="J534" s="11"/>
       <c r="K534" s="11"/>
@@ -7771,7 +7712,7 @@
       <c r="E535" s="9"/>
       <c r="F535" s="9"/>
       <c r="G535" s="11"/>
-      <c r="H535" s="13"/>
+      <c r="H535" s="16"/>
       <c r="I535" s="11"/>
       <c r="J535" s="11"/>
       <c r="K535" s="11"/>
@@ -7784,7 +7725,7 @@
       <c r="E536" s="9"/>
       <c r="F536" s="9"/>
       <c r="G536" s="11"/>
-      <c r="H536" s="13"/>
+      <c r="H536" s="16"/>
       <c r="I536" s="11"/>
       <c r="J536" s="11"/>
       <c r="K536" s="11"/>
@@ -7797,7 +7738,7 @@
       <c r="E537" s="9"/>
       <c r="F537" s="9"/>
       <c r="G537" s="11"/>
-      <c r="H537" s="13"/>
+      <c r="H537" s="16"/>
       <c r="I537" s="11"/>
       <c r="J537" s="11"/>
       <c r="K537" s="11"/>
@@ -7810,7 +7751,7 @@
       <c r="E538" s="9"/>
       <c r="F538" s="9"/>
       <c r="G538" s="11"/>
-      <c r="H538" s="13"/>
+      <c r="H538" s="16"/>
       <c r="I538" s="11"/>
       <c r="J538" s="11"/>
       <c r="K538" s="11"/>
@@ -7823,7 +7764,7 @@
       <c r="E539" s="9"/>
       <c r="F539" s="9"/>
       <c r="G539" s="11"/>
-      <c r="H539" s="13"/>
+      <c r="H539" s="16"/>
       <c r="I539" s="11"/>
       <c r="J539" s="11"/>
       <c r="K539" s="11"/>
@@ -7836,7 +7777,7 @@
       <c r="E540" s="9"/>
       <c r="F540" s="9"/>
       <c r="G540" s="11"/>
-      <c r="H540" s="13"/>
+      <c r="H540" s="16"/>
       <c r="I540" s="11"/>
       <c r="J540" s="11"/>
       <c r="K540" s="11"/>
@@ -7849,7 +7790,7 @@
       <c r="E541" s="9"/>
       <c r="F541" s="9"/>
       <c r="G541" s="11"/>
-      <c r="H541" s="13"/>
+      <c r="H541" s="16"/>
       <c r="I541" s="11"/>
       <c r="J541" s="11"/>
       <c r="K541" s="11"/>
@@ -7862,7 +7803,7 @@
       <c r="E542" s="9"/>
       <c r="F542" s="9"/>
       <c r="G542" s="11"/>
-      <c r="H542" s="13"/>
+      <c r="H542" s="16"/>
       <c r="I542" s="11"/>
       <c r="J542" s="11"/>
       <c r="K542" s="11"/>
@@ -7875,7 +7816,7 @@
       <c r="E543" s="9"/>
       <c r="F543" s="9"/>
       <c r="G543" s="11"/>
-      <c r="H543" s="13"/>
+      <c r="H543" s="16"/>
       <c r="I543" s="11"/>
       <c r="J543" s="11"/>
       <c r="K543" s="11"/>
@@ -7888,7 +7829,7 @@
       <c r="E544" s="9"/>
       <c r="F544" s="9"/>
       <c r="G544" s="11"/>
-      <c r="H544" s="13"/>
+      <c r="H544" s="16"/>
       <c r="I544" s="11"/>
       <c r="J544" s="11"/>
       <c r="K544" s="11"/>
@@ -7901,7 +7842,7 @@
       <c r="E545" s="9"/>
       <c r="F545" s="9"/>
       <c r="G545" s="11"/>
-      <c r="H545" s="13"/>
+      <c r="H545" s="16"/>
       <c r="I545" s="11"/>
       <c r="J545" s="11"/>
       <c r="K545" s="11"/>
@@ -7914,7 +7855,7 @@
       <c r="E546" s="9"/>
       <c r="F546" s="9"/>
       <c r="G546" s="11"/>
-      <c r="H546" s="13"/>
+      <c r="H546" s="16"/>
       <c r="I546" s="11"/>
       <c r="J546" s="11"/>
       <c r="K546" s="11"/>
@@ -7927,7 +7868,7 @@
       <c r="E547" s="9"/>
       <c r="F547" s="9"/>
       <c r="G547" s="11"/>
-      <c r="H547" s="13"/>
+      <c r="H547" s="16"/>
       <c r="I547" s="11"/>
       <c r="J547" s="11"/>
       <c r="K547" s="11"/>
@@ -7940,7 +7881,7 @@
       <c r="E548" s="9"/>
       <c r="F548" s="9"/>
       <c r="G548" s="11"/>
-      <c r="H548" s="13"/>
+      <c r="H548" s="16"/>
       <c r="I548" s="11"/>
       <c r="J548" s="11"/>
       <c r="K548" s="11"/>
@@ -7953,7 +7894,7 @@
       <c r="E549" s="9"/>
       <c r="F549" s="9"/>
       <c r="G549" s="11"/>
-      <c r="H549" s="13"/>
+      <c r="H549" s="16"/>
       <c r="I549" s="11"/>
       <c r="J549" s="11"/>
       <c r="K549" s="11"/>
@@ -7966,7 +7907,7 @@
       <c r="E550" s="9"/>
       <c r="F550" s="9"/>
       <c r="G550" s="11"/>
-      <c r="H550" s="13"/>
+      <c r="H550" s="16"/>
       <c r="I550" s="11"/>
       <c r="J550" s="11"/>
       <c r="K550" s="11"/>
@@ -7979,7 +7920,7 @@
       <c r="E551" s="9"/>
       <c r="F551" s="9"/>
       <c r="G551" s="11"/>
-      <c r="H551" s="13"/>
+      <c r="H551" s="16"/>
       <c r="I551" s="11"/>
       <c r="J551" s="11"/>
       <c r="K551" s="11"/>
@@ -7992,7 +7933,7 @@
       <c r="E552" s="9"/>
       <c r="F552" s="9"/>
       <c r="G552" s="11"/>
-      <c r="H552" s="13"/>
+      <c r="H552" s="16"/>
       <c r="I552" s="11"/>
       <c r="J552" s="11"/>
       <c r="K552" s="11"/>
@@ -8005,7 +7946,7 @@
       <c r="E553" s="9"/>
       <c r="F553" s="9"/>
       <c r="G553" s="11"/>
-      <c r="H553" s="13"/>
+      <c r="H553" s="16"/>
       <c r="I553" s="11"/>
       <c r="J553" s="11"/>
       <c r="K553" s="11"/>
@@ -8018,7 +7959,7 @@
       <c r="E554" s="9"/>
       <c r="F554" s="9"/>
       <c r="G554" s="11"/>
-      <c r="H554" s="13"/>
+      <c r="H554" s="16"/>
       <c r="I554" s="11"/>
       <c r="J554" s="11"/>
       <c r="K554" s="11"/>
@@ -8031,7 +7972,7 @@
       <c r="E555" s="9"/>
       <c r="F555" s="9"/>
       <c r="G555" s="11"/>
-      <c r="H555" s="13"/>
+      <c r="H555" s="16"/>
       <c r="I555" s="11"/>
       <c r="J555" s="11"/>
       <c r="K555" s="11"/>
@@ -8044,7 +7985,7 @@
       <c r="E556" s="9"/>
       <c r="F556" s="9"/>
       <c r="G556" s="11"/>
-      <c r="H556" s="13"/>
+      <c r="H556" s="16"/>
       <c r="I556" s="11"/>
       <c r="J556" s="11"/>
       <c r="K556" s="11"/>
@@ -8057,7 +7998,7 @@
       <c r="E557" s="9"/>
       <c r="F557" s="9"/>
       <c r="G557" s="11"/>
-      <c r="H557" s="13"/>
+      <c r="H557" s="16"/>
       <c r="I557" s="11"/>
       <c r="J557" s="11"/>
       <c r="K557" s="11"/>
@@ -8070,7 +8011,7 @@
       <c r="E558" s="9"/>
       <c r="F558" s="9"/>
       <c r="G558" s="11"/>
-      <c r="H558" s="13"/>
+      <c r="H558" s="16"/>
       <c r="I558" s="11"/>
       <c r="J558" s="11"/>
       <c r="K558" s="11"/>
@@ -8083,7 +8024,7 @@
       <c r="E559" s="9"/>
       <c r="F559" s="9"/>
       <c r="G559" s="11"/>
-      <c r="H559" s="13"/>
+      <c r="H559" s="16"/>
       <c r="I559" s="11"/>
       <c r="J559" s="11"/>
       <c r="K559" s="11"/>
@@ -8096,7 +8037,7 @@
       <c r="E560" s="9"/>
       <c r="F560" s="9"/>
       <c r="G560" s="11"/>
-      <c r="H560" s="13"/>
+      <c r="H560" s="16"/>
       <c r="I560" s="11"/>
       <c r="J560" s="11"/>
       <c r="K560" s="11"/>
@@ -8109,7 +8050,7 @@
       <c r="E561" s="9"/>
       <c r="F561" s="9"/>
       <c r="G561" s="11"/>
-      <c r="H561" s="13"/>
+      <c r="H561" s="16"/>
       <c r="I561" s="11"/>
       <c r="J561" s="11"/>
       <c r="K561" s="11"/>
@@ -8122,7 +8063,7 @@
       <c r="E562" s="9"/>
       <c r="F562" s="9"/>
       <c r="G562" s="11"/>
-      <c r="H562" s="13"/>
+      <c r="H562" s="16"/>
       <c r="I562" s="11"/>
       <c r="J562" s="11"/>
       <c r="K562" s="11"/>
@@ -8135,7 +8076,7 @@
       <c r="E563" s="9"/>
       <c r="F563" s="9"/>
       <c r="G563" s="11"/>
-      <c r="H563" s="13"/>
+      <c r="H563" s="16"/>
       <c r="I563" s="11"/>
       <c r="J563" s="11"/>
       <c r="K563" s="11"/>
@@ -8148,7 +8089,7 @@
       <c r="E564" s="9"/>
       <c r="F564" s="9"/>
       <c r="G564" s="11"/>
-      <c r="H564" s="13"/>
+      <c r="H564" s="16"/>
       <c r="I564" s="11"/>
       <c r="J564" s="11"/>
       <c r="K564" s="11"/>
@@ -8161,7 +8102,7 @@
       <c r="E565" s="9"/>
       <c r="F565" s="9"/>
       <c r="G565" s="11"/>
-      <c r="H565" s="13"/>
+      <c r="H565" s="16"/>
       <c r="I565" s="11"/>
       <c r="J565" s="11"/>
       <c r="K565" s="11"/>
@@ -8174,7 +8115,7 @@
       <c r="E566" s="9"/>
       <c r="F566" s="9"/>
       <c r="G566" s="11"/>
-      <c r="H566" s="13"/>
+      <c r="H566" s="16"/>
       <c r="I566" s="11"/>
       <c r="J566" s="11"/>
       <c r="K566" s="11"/>
@@ -8187,7 +8128,7 @@
       <c r="E567" s="9"/>
       <c r="F567" s="9"/>
       <c r="G567" s="11"/>
-      <c r="H567" s="13"/>
+      <c r="H567" s="16"/>
       <c r="I567" s="11"/>
       <c r="J567" s="11"/>
       <c r="K567" s="11"/>
@@ -8200,7 +8141,7 @@
       <c r="E568" s="9"/>
       <c r="F568" s="9"/>
       <c r="G568" s="11"/>
-      <c r="H568" s="13"/>
+      <c r="H568" s="16"/>
       <c r="I568" s="11"/>
       <c r="J568" s="11"/>
       <c r="K568" s="11"/>
@@ -8213,7 +8154,7 @@
       <c r="E569" s="9"/>
       <c r="F569" s="9"/>
       <c r="G569" s="11"/>
-      <c r="H569" s="13"/>
+      <c r="H569" s="16"/>
       <c r="I569" s="11"/>
       <c r="J569" s="11"/>
       <c r="K569" s="11"/>
@@ -8226,7 +8167,7 @@
       <c r="E570" s="9"/>
       <c r="F570" s="9"/>
       <c r="G570" s="11"/>
-      <c r="H570" s="13"/>
+      <c r="H570" s="16"/>
       <c r="I570" s="11"/>
       <c r="J570" s="11"/>
       <c r="K570" s="11"/>
@@ -8239,7 +8180,7 @@
       <c r="E571" s="9"/>
       <c r="F571" s="9"/>
       <c r="G571" s="11"/>
-      <c r="H571" s="13"/>
+      <c r="H571" s="16"/>
       <c r="I571" s="11"/>
       <c r="J571" s="11"/>
       <c r="K571" s="11"/>
@@ -8252,7 +8193,7 @@
       <c r="E572" s="9"/>
       <c r="F572" s="9"/>
       <c r="G572" s="11"/>
-      <c r="H572" s="13"/>
+      <c r="H572" s="16"/>
       <c r="I572" s="11"/>
       <c r="J572" s="11"/>
       <c r="K572" s="11"/>
@@ -8265,7 +8206,7 @@
       <c r="E573" s="9"/>
       <c r="F573" s="9"/>
       <c r="G573" s="11"/>
-      <c r="H573" s="13"/>
+      <c r="H573" s="16"/>
       <c r="I573" s="11"/>
       <c r="J573" s="11"/>
       <c r="K573" s="11"/>
@@ -8278,7 +8219,7 @@
       <c r="E574" s="9"/>
       <c r="F574" s="9"/>
       <c r="G574" s="11"/>
-      <c r="H574" s="13"/>
+      <c r="H574" s="16"/>
       <c r="I574" s="11"/>
       <c r="J574" s="11"/>
       <c r="K574" s="11"/>
@@ -8291,7 +8232,7 @@
       <c r="E575" s="9"/>
       <c r="F575" s="9"/>
       <c r="G575" s="11"/>
-      <c r="H575" s="13"/>
+      <c r="H575" s="16"/>
       <c r="I575" s="11"/>
       <c r="J575" s="11"/>
       <c r="K575" s="11"/>
@@ -8304,7 +8245,7 @@
       <c r="E576" s="9"/>
       <c r="F576" s="9"/>
       <c r="G576" s="11"/>
-      <c r="H576" s="13"/>
+      <c r="H576" s="16"/>
       <c r="I576" s="11"/>
       <c r="J576" s="11"/>
       <c r="K576" s="11"/>
@@ -8317,7 +8258,7 @@
       <c r="E577" s="9"/>
       <c r="F577" s="9"/>
       <c r="G577" s="11"/>
-      <c r="H577" s="13"/>
+      <c r="H577" s="16"/>
       <c r="I577" s="11"/>
       <c r="J577" s="11"/>
       <c r="K577" s="11"/>
@@ -8330,7 +8271,7 @@
       <c r="E578" s="9"/>
       <c r="F578" s="9"/>
       <c r="G578" s="11"/>
-      <c r="H578" s="13"/>
+      <c r="H578" s="16"/>
       <c r="I578" s="11"/>
       <c r="J578" s="11"/>
       <c r="K578" s="11"/>
@@ -8343,7 +8284,7 @@
       <c r="E579" s="9"/>
       <c r="F579" s="9"/>
       <c r="G579" s="11"/>
-      <c r="H579" s="13"/>
+      <c r="H579" s="16"/>
       <c r="I579" s="11"/>
       <c r="J579" s="11"/>
       <c r="K579" s="11"/>
@@ -8356,7 +8297,7 @@
       <c r="E580" s="9"/>
       <c r="F580" s="9"/>
       <c r="G580" s="11"/>
-      <c r="H580" s="13"/>
+      <c r="H580" s="16"/>
       <c r="I580" s="11"/>
       <c r="J580" s="11"/>
       <c r="K580" s="11"/>
@@ -8369,7 +8310,7 @@
       <c r="E581" s="9"/>
       <c r="F581" s="9"/>
       <c r="G581" s="11"/>
-      <c r="H581" s="13"/>
+      <c r="H581" s="16"/>
       <c r="I581" s="11"/>
       <c r="J581" s="11"/>
       <c r="K581" s="11"/>
@@ -8382,7 +8323,7 @@
       <c r="E582" s="9"/>
       <c r="F582" s="9"/>
       <c r="G582" s="11"/>
-      <c r="H582" s="13"/>
+      <c r="H582" s="16"/>
       <c r="I582" s="11"/>
       <c r="J582" s="11"/>
       <c r="K582" s="11"/>
@@ -8395,7 +8336,7 @@
       <c r="E583" s="9"/>
       <c r="F583" s="9"/>
       <c r="G583" s="11"/>
-      <c r="H583" s="13"/>
+      <c r="H583" s="16"/>
       <c r="I583" s="11"/>
       <c r="J583" s="11"/>
       <c r="K583" s="11"/>
@@ -8408,7 +8349,7 @@
       <c r="E584" s="9"/>
       <c r="F584" s="9"/>
       <c r="G584" s="11"/>
-      <c r="H584" s="13"/>
+      <c r="H584" s="16"/>
       <c r="I584" s="11"/>
       <c r="J584" s="11"/>
       <c r="K584" s="11"/>
@@ -8421,7 +8362,7 @@
       <c r="E585" s="9"/>
       <c r="F585" s="9"/>
       <c r="G585" s="11"/>
-      <c r="H585" s="13"/>
+      <c r="H585" s="16"/>
       <c r="I585" s="11"/>
       <c r="J585" s="11"/>
       <c r="K585" s="11"/>
@@ -8434,7 +8375,7 @@
       <c r="E586" s="9"/>
       <c r="F586" s="9"/>
       <c r="G586" s="11"/>
-      <c r="H586" s="13"/>
+      <c r="H586" s="16"/>
       <c r="I586" s="11"/>
       <c r="J586" s="11"/>
       <c r="K586" s="11"/>
@@ -8447,7 +8388,7 @@
       <c r="E587" s="9"/>
       <c r="F587" s="9"/>
       <c r="G587" s="11"/>
-      <c r="H587" s="13"/>
+      <c r="H587" s="16"/>
       <c r="I587" s="11"/>
       <c r="J587" s="11"/>
       <c r="K587" s="11"/>
@@ -8460,7 +8401,7 @@
       <c r="E588" s="9"/>
       <c r="F588" s="9"/>
       <c r="G588" s="11"/>
-      <c r="H588" s="13"/>
+      <c r="H588" s="16"/>
       <c r="I588" s="11"/>
       <c r="J588" s="11"/>
       <c r="K588" s="11"/>
@@ -8473,7 +8414,7 @@
       <c r="E589" s="9"/>
       <c r="F589" s="9"/>
       <c r="G589" s="11"/>
-      <c r="H589" s="13"/>
+      <c r="H589" s="16"/>
       <c r="I589" s="11"/>
       <c r="J589" s="11"/>
       <c r="K589" s="11"/>
@@ -8486,7 +8427,7 @@
       <c r="E590" s="9"/>
       <c r="F590" s="9"/>
       <c r="G590" s="11"/>
-      <c r="H590" s="13"/>
+      <c r="H590" s="16"/>
       <c r="I590" s="11"/>
       <c r="J590" s="11"/>
       <c r="K590" s="11"/>
@@ -8499,7 +8440,7 @@
       <c r="E591" s="9"/>
       <c r="F591" s="9"/>
       <c r="G591" s="11"/>
-      <c r="H591" s="13"/>
+      <c r="H591" s="16"/>
       <c r="I591" s="11"/>
       <c r="J591" s="11"/>
       <c r="K591" s="11"/>
@@ -8512,7 +8453,7 @@
       <c r="E592" s="9"/>
       <c r="F592" s="9"/>
       <c r="G592" s="11"/>
-      <c r="H592" s="13"/>
+      <c r="H592" s="16"/>
       <c r="I592" s="11"/>
       <c r="J592" s="11"/>
       <c r="K592" s="11"/>
@@ -8525,7 +8466,7 @@
       <c r="E593" s="9"/>
       <c r="F593" s="9"/>
       <c r="G593" s="11"/>
-      <c r="H593" s="13"/>
+      <c r="H593" s="16"/>
       <c r="I593" s="11"/>
       <c r="J593" s="11"/>
       <c r="K593" s="11"/>
@@ -8538,7 +8479,7 @@
       <c r="E594" s="9"/>
       <c r="F594" s="9"/>
       <c r="G594" s="11"/>
-      <c r="H594" s="13"/>
+      <c r="H594" s="16"/>
       <c r="I594" s="11"/>
       <c r="J594" s="11"/>
       <c r="K594" s="11"/>
@@ -8551,7 +8492,7 @@
       <c r="E595" s="9"/>
       <c r="F595" s="9"/>
       <c r="G595" s="11"/>
-      <c r="H595" s="13"/>
+      <c r="H595" s="16"/>
       <c r="I595" s="11"/>
       <c r="J595" s="11"/>
       <c r="K595" s="11"/>
@@ -8564,7 +8505,7 @@
       <c r="E596" s="9"/>
       <c r="F596" s="9"/>
       <c r="G596" s="11"/>
-      <c r="H596" s="13"/>
+      <c r="H596" s="16"/>
       <c r="I596" s="11"/>
       <c r="J596" s="11"/>
       <c r="K596" s="11"/>
@@ -8577,7 +8518,7 @@
       <c r="E597" s="9"/>
       <c r="F597" s="9"/>
       <c r="G597" s="11"/>
-      <c r="H597" s="13"/>
+      <c r="H597" s="16"/>
       <c r="I597" s="11"/>
       <c r="J597" s="11"/>
       <c r="K597" s="11"/>
@@ -8590,7 +8531,7 @@
       <c r="E598" s="9"/>
       <c r="F598" s="9"/>
       <c r="G598" s="11"/>
-      <c r="H598" s="13"/>
+      <c r="H598" s="16"/>
       <c r="I598" s="11"/>
       <c r="J598" s="11"/>
       <c r="K598" s="11"/>
@@ -8603,7 +8544,7 @@
       <c r="E599" s="9"/>
       <c r="F599" s="9"/>
       <c r="G599" s="11"/>
-      <c r="H599" s="13"/>
+      <c r="H599" s="16"/>
       <c r="I599" s="11"/>
       <c r="J599" s="11"/>
       <c r="K599" s="11"/>
@@ -8616,7 +8557,7 @@
       <c r="E600" s="9"/>
       <c r="F600" s="9"/>
       <c r="G600" s="11"/>
-      <c r="H600" s="13"/>
+      <c r="H600" s="16"/>
       <c r="I600" s="11"/>
       <c r="J600" s="11"/>
       <c r="K600" s="11"/>
@@ -8629,7 +8570,7 @@
       <c r="E601" s="9"/>
       <c r="F601" s="9"/>
       <c r="G601" s="11"/>
-      <c r="H601" s="13"/>
+      <c r="H601" s="16"/>
       <c r="I601" s="11"/>
       <c r="J601" s="11"/>
       <c r="K601" s="11"/>
@@ -8642,7 +8583,7 @@
       <c r="E602" s="9"/>
       <c r="F602" s="9"/>
       <c r="G602" s="11"/>
-      <c r="H602" s="13"/>
+      <c r="H602" s="16"/>
       <c r="I602" s="11"/>
       <c r="J602" s="11"/>
       <c r="K602" s="11"/>
@@ -8655,7 +8596,7 @@
       <c r="E603" s="9"/>
       <c r="F603" s="9"/>
       <c r="G603" s="11"/>
-      <c r="H603" s="13"/>
+      <c r="H603" s="16"/>
       <c r="I603" s="11"/>
       <c r="J603" s="11"/>
       <c r="K603" s="11"/>
@@ -8668,7 +8609,7 @@
       <c r="E604" s="9"/>
       <c r="F604" s="9"/>
       <c r="G604" s="11"/>
-      <c r="H604" s="13"/>
+      <c r="H604" s="16"/>
       <c r="I604" s="11"/>
       <c r="J604" s="11"/>
       <c r="K604" s="11"/>
@@ -8681,7 +8622,7 @@
       <c r="E605" s="9"/>
       <c r="F605" s="9"/>
       <c r="G605" s="11"/>
-      <c r="H605" s="13"/>
+      <c r="H605" s="16"/>
       <c r="I605" s="11"/>
       <c r="J605" s="11"/>
       <c r="K605" s="11"/>
@@ -8694,7 +8635,7 @@
       <c r="E606" s="9"/>
       <c r="F606" s="9"/>
       <c r="G606" s="11"/>
-      <c r="H606" s="13"/>
+      <c r="H606" s="16"/>
       <c r="I606" s="11"/>
       <c r="J606" s="11"/>
       <c r="K606" s="11"/>
@@ -8707,7 +8648,7 @@
       <c r="E607" s="9"/>
       <c r="F607" s="9"/>
       <c r="G607" s="11"/>
-      <c r="H607" s="13"/>
+      <c r="H607" s="16"/>
       <c r="I607" s="11"/>
       <c r="J607" s="11"/>
       <c r="K607" s="11"/>
@@ -8720,7 +8661,7 @@
       <c r="E608" s="9"/>
       <c r="F608" s="9"/>
       <c r="G608" s="11"/>
-      <c r="H608" s="13"/>
+      <c r="H608" s="16"/>
       <c r="I608" s="11"/>
       <c r="J608" s="11"/>
       <c r="K608" s="11"/>
@@ -8733,7 +8674,7 @@
       <c r="E609" s="9"/>
       <c r="F609" s="9"/>
       <c r="G609" s="11"/>
-      <c r="H609" s="13"/>
+      <c r="H609" s="16"/>
       <c r="I609" s="11"/>
       <c r="J609" s="11"/>
       <c r="K609" s="11"/>
@@ -8746,7 +8687,7 @@
       <c r="E610" s="9"/>
       <c r="F610" s="9"/>
       <c r="G610" s="11"/>
-      <c r="H610" s="13"/>
+      <c r="H610" s="16"/>
       <c r="I610" s="11"/>
       <c r="J610" s="11"/>
       <c r="K610" s="11"/>
@@ -8759,7 +8700,7 @@
       <c r="E611" s="9"/>
       <c r="F611" s="9"/>
       <c r="G611" s="11"/>
-      <c r="H611" s="13"/>
+      <c r="H611" s="16"/>
       <c r="I611" s="11"/>
       <c r="J611" s="11"/>
       <c r="K611" s="11"/>
@@ -8772,7 +8713,7 @@
       <c r="E612" s="9"/>
       <c r="F612" s="9"/>
       <c r="G612" s="11"/>
-      <c r="H612" s="13"/>
+      <c r="H612" s="16"/>
       <c r="I612" s="11"/>
       <c r="J612" s="11"/>
       <c r="K612" s="11"/>
@@ -8785,7 +8726,7 @@
       <c r="E613" s="9"/>
       <c r="F613" s="9"/>
       <c r="G613" s="11"/>
-      <c r="H613" s="13"/>
+      <c r="H613" s="16"/>
       <c r="I613" s="11"/>
       <c r="J613" s="11"/>
       <c r="K613" s="11"/>
@@ -8798,7 +8739,7 @@
       <c r="E614" s="9"/>
       <c r="F614" s="9"/>
       <c r="G614" s="11"/>
-      <c r="H614" s="13"/>
+      <c r="H614" s="16"/>
       <c r="I614" s="11"/>
       <c r="J614" s="11"/>
       <c r="K614" s="11"/>
@@ -8811,7 +8752,7 @@
       <c r="E615" s="9"/>
       <c r="F615" s="9"/>
       <c r="G615" s="11"/>
-      <c r="H615" s="13"/>
+      <c r="H615" s="16"/>
       <c r="I615" s="11"/>
       <c r="J615" s="11"/>
       <c r="K615" s="11"/>
@@ -8824,7 +8765,7 @@
       <c r="E616" s="9"/>
       <c r="F616" s="9"/>
       <c r="G616" s="11"/>
-      <c r="H616" s="13"/>
+      <c r="H616" s="16"/>
       <c r="I616" s="11"/>
       <c r="J616" s="11"/>
       <c r="K616" s="11"/>
@@ -8837,7 +8778,7 @@
       <c r="E617" s="9"/>
       <c r="F617" s="9"/>
       <c r="G617" s="11"/>
-      <c r="H617" s="13"/>
+      <c r="H617" s="16"/>
       <c r="I617" s="11"/>
       <c r="J617" s="11"/>
       <c r="K617" s="11"/>
@@ -8850,7 +8791,7 @@
       <c r="E618" s="9"/>
       <c r="F618" s="9"/>
       <c r="G618" s="11"/>
-      <c r="H618" s="13"/>
+      <c r="H618" s="16"/>
       <c r="I618" s="11"/>
       <c r="J618" s="11"/>
       <c r="K618" s="11"/>
@@ -8863,7 +8804,7 @@
       <c r="E619" s="9"/>
       <c r="F619" s="9"/>
       <c r="G619" s="11"/>
-      <c r="H619" s="13"/>
+      <c r="H619" s="16"/>
       <c r="I619" s="11"/>
       <c r="J619" s="11"/>
       <c r="K619" s="11"/>
@@ -8876,7 +8817,7 @@
       <c r="E620" s="9"/>
       <c r="F620" s="9"/>
       <c r="G620" s="11"/>
-      <c r="H620" s="13"/>
+      <c r="H620" s="16"/>
       <c r="I620" s="11"/>
       <c r="J620" s="11"/>
       <c r="K620" s="11"/>
@@ -8889,7 +8830,7 @@
       <c r="E621" s="9"/>
       <c r="F621" s="9"/>
       <c r="G621" s="11"/>
-      <c r="H621" s="13"/>
+      <c r="H621" s="16"/>
       <c r="I621" s="11"/>
       <c r="J621" s="11"/>
       <c r="K621" s="11"/>
@@ -8902,7 +8843,7 @@
       <c r="E622" s="9"/>
       <c r="F622" s="9"/>
       <c r="G622" s="11"/>
-      <c r="H622" s="13"/>
+      <c r="H622" s="16"/>
       <c r="I622" s="11"/>
       <c r="J622" s="11"/>
       <c r="K622" s="11"/>
@@ -8915,7 +8856,7 @@
       <c r="E623" s="9"/>
       <c r="F623" s="9"/>
       <c r="G623" s="11"/>
-      <c r="H623" s="13"/>
+      <c r="H623" s="16"/>
       <c r="I623" s="11"/>
       <c r="J623" s="11"/>
       <c r="K623" s="11"/>
@@ -8928,7 +8869,7 @@
       <c r="E624" s="9"/>
       <c r="F624" s="9"/>
       <c r="G624" s="11"/>
-      <c r="H624" s="13"/>
+      <c r="H624" s="16"/>
       <c r="I624" s="11"/>
       <c r="J624" s="11"/>
       <c r="K624" s="11"/>
@@ -8941,7 +8882,7 @@
       <c r="E625" s="9"/>
       <c r="F625" s="9"/>
       <c r="G625" s="11"/>
-      <c r="H625" s="13"/>
+      <c r="H625" s="16"/>
       <c r="I625" s="11"/>
       <c r="J625" s="11"/>
       <c r="K625" s="11"/>
@@ -8954,7 +8895,7 @@
       <c r="E626" s="9"/>
       <c r="F626" s="9"/>
       <c r="G626" s="11"/>
-      <c r="H626" s="13"/>
+      <c r="H626" s="16"/>
       <c r="I626" s="11"/>
       <c r="J626" s="11"/>
       <c r="K626" s="11"/>
@@ -8967,7 +8908,7 @@
       <c r="E627" s="9"/>
       <c r="F627" s="9"/>
       <c r="G627" s="11"/>
-      <c r="H627" s="13"/>
+      <c r="H627" s="16"/>
       <c r="I627" s="11"/>
       <c r="J627" s="11"/>
       <c r="K627" s="11"/>
@@ -8980,7 +8921,7 @@
       <c r="E628" s="9"/>
       <c r="F628" s="9"/>
       <c r="G628" s="11"/>
-      <c r="H628" s="13"/>
+      <c r="H628" s="16"/>
       <c r="I628" s="11"/>
       <c r="J628" s="11"/>
       <c r="K628" s="11"/>
@@ -8993,7 +8934,7 @@
       <c r="E629" s="9"/>
       <c r="F629" s="9"/>
       <c r="G629" s="11"/>
-      <c r="H629" s="13"/>
+      <c r="H629" s="16"/>
       <c r="I629" s="11"/>
       <c r="J629" s="11"/>
       <c r="K629" s="11"/>
@@ -9006,7 +8947,7 @@
       <c r="E630" s="9"/>
       <c r="F630" s="9"/>
       <c r="G630" s="11"/>
-      <c r="H630" s="13"/>
+      <c r="H630" s="16"/>
       <c r="I630" s="11"/>
       <c r="J630" s="11"/>
       <c r="K630" s="11"/>
@@ -9019,7 +8960,7 @@
       <c r="E631" s="9"/>
       <c r="F631" s="9"/>
       <c r="G631" s="11"/>
-      <c r="H631" s="13"/>
+      <c r="H631" s="16"/>
       <c r="I631" s="11"/>
       <c r="J631" s="11"/>
       <c r="K631" s="11"/>
@@ -9032,7 +8973,7 @@
       <c r="E632" s="9"/>
       <c r="F632" s="9"/>
       <c r="G632" s="11"/>
-      <c r="H632" s="13"/>
+      <c r="H632" s="16"/>
       <c r="I632" s="11"/>
       <c r="J632" s="11"/>
       <c r="K632" s="11"/>
@@ -9045,7 +8986,7 @@
       <c r="E633" s="9"/>
       <c r="F633" s="9"/>
       <c r="G633" s="11"/>
-      <c r="H633" s="13"/>
+      <c r="H633" s="16"/>
       <c r="I633" s="11"/>
       <c r="J633" s="11"/>
       <c r="K633" s="11"/>
@@ -9058,7 +8999,7 @@
       <c r="E634" s="9"/>
       <c r="F634" s="9"/>
       <c r="G634" s="11"/>
-      <c r="H634" s="13"/>
+      <c r="H634" s="16"/>
       <c r="I634" s="11"/>
       <c r="J634" s="11"/>
       <c r="K634" s="11"/>
@@ -9071,7 +9012,7 @@
       <c r="E635" s="9"/>
       <c r="F635" s="9"/>
       <c r="G635" s="11"/>
-      <c r="H635" s="13"/>
+      <c r="H635" s="16"/>
       <c r="I635" s="11"/>
       <c r="J635" s="11"/>
       <c r="K635" s="11"/>
@@ -9084,7 +9025,7 @@
       <c r="E636" s="9"/>
       <c r="F636" s="9"/>
       <c r="G636" s="11"/>
-      <c r="H636" s="13"/>
+      <c r="H636" s="16"/>
       <c r="I636" s="11"/>
       <c r="J636" s="11"/>
       <c r="K636" s="11"/>
@@ -9097,7 +9038,7 @@
       <c r="E637" s="9"/>
       <c r="F637" s="9"/>
       <c r="G637" s="11"/>
-      <c r="H637" s="13"/>
+      <c r="H637" s="16"/>
       <c r="I637" s="11"/>
       <c r="J637" s="11"/>
       <c r="K637" s="11"/>
@@ -9110,7 +9051,7 @@
       <c r="E638" s="9"/>
       <c r="F638" s="9"/>
       <c r="G638" s="11"/>
-      <c r="H638" s="13"/>
+      <c r="H638" s="16"/>
       <c r="I638" s="11"/>
       <c r="J638" s="11"/>
       <c r="K638" s="11"/>
@@ -9123,7 +9064,7 @@
       <c r="E639" s="9"/>
       <c r="F639" s="9"/>
       <c r="G639" s="11"/>
-      <c r="H639" s="13"/>
+      <c r="H639" s="16"/>
       <c r="I639" s="11"/>
       <c r="J639" s="11"/>
       <c r="K639" s="11"/>
@@ -9136,7 +9077,7 @@
       <c r="E640" s="9"/>
       <c r="F640" s="9"/>
       <c r="G640" s="11"/>
-      <c r="H640" s="13"/>
+      <c r="H640" s="16"/>
       <c r="I640" s="11"/>
       <c r="J640" s="11"/>
       <c r="K640" s="11"/>
@@ -9149,7 +9090,7 @@
       <c r="E641" s="9"/>
       <c r="F641" s="9"/>
       <c r="G641" s="11"/>
-      <c r="H641" s="13"/>
+      <c r="H641" s="16"/>
       <c r="I641" s="11"/>
       <c r="J641" s="11"/>
       <c r="K641" s="11"/>
@@ -9162,7 +9103,7 @@
       <c r="E642" s="9"/>
       <c r="F642" s="9"/>
       <c r="G642" s="11"/>
-      <c r="H642" s="13"/>
+      <c r="H642" s="16"/>
       <c r="I642" s="11"/>
       <c r="J642" s="11"/>
       <c r="K642" s="11"/>
@@ -9175,7 +9116,7 @@
       <c r="E643" s="9"/>
       <c r="F643" s="9"/>
       <c r="G643" s="11"/>
-      <c r="H643" s="13"/>
+      <c r="H643" s="16"/>
       <c r="I643" s="11"/>
       <c r="J643" s="11"/>
       <c r="K643" s="11"/>
@@ -9188,7 +9129,7 @@
       <c r="E644" s="9"/>
       <c r="F644" s="9"/>
       <c r="G644" s="11"/>
-      <c r="H644" s="13"/>
+      <c r="H644" s="16"/>
       <c r="I644" s="11"/>
       <c r="J644" s="11"/>
       <c r="K644" s="11"/>
@@ -9201,7 +9142,7 @@
       <c r="E645" s="9"/>
       <c r="F645" s="9"/>
       <c r="G645" s="11"/>
-      <c r="H645" s="13"/>
+      <c r="H645" s="16"/>
       <c r="I645" s="11"/>
       <c r="J645" s="11"/>
       <c r="K645" s="11"/>
@@ -9214,7 +9155,7 @@
       <c r="E646" s="9"/>
       <c r="F646" s="9"/>
       <c r="G646" s="11"/>
-      <c r="H646" s="13"/>
+      <c r="H646" s="16"/>
       <c r="I646" s="11"/>
       <c r="J646" s="11"/>
       <c r="K646" s="11"/>
@@ -9227,7 +9168,7 @@
       <c r="E647" s="9"/>
       <c r="F647" s="9"/>
       <c r="G647" s="11"/>
-      <c r="H647" s="13"/>
+      <c r="H647" s="16"/>
       <c r="I647" s="11"/>
       <c r="J647" s="11"/>
       <c r="K647" s="11"/>
@@ -9240,7 +9181,7 @@
       <c r="E648" s="9"/>
       <c r="F648" s="9"/>
       <c r="G648" s="11"/>
-      <c r="H648" s="13"/>
+      <c r="H648" s="16"/>
       <c r="I648" s="11"/>
       <c r="J648" s="11"/>
       <c r="K648" s="11"/>
@@ -9253,7 +9194,7 @@
       <c r="E649" s="9"/>
       <c r="F649" s="9"/>
       <c r="G649" s="11"/>
-      <c r="H649" s="13"/>
+      <c r="H649" s="16"/>
       <c r="I649" s="11"/>
       <c r="J649" s="11"/>
       <c r="K649" s="11"/>
@@ -9266,7 +9207,7 @@
       <c r="E650" s="9"/>
       <c r="F650" s="9"/>
       <c r="G650" s="11"/>
-      <c r="H650" s="13"/>
+      <c r="H650" s="16"/>
       <c r="I650" s="11"/>
       <c r="J650" s="11"/>
       <c r="K650" s="11"/>
@@ -9279,7 +9220,7 @@
       <c r="E651" s="9"/>
       <c r="F651" s="9"/>
       <c r="G651" s="11"/>
-      <c r="H651" s="13"/>
+      <c r="H651" s="16"/>
       <c r="I651" s="11"/>
       <c r="J651" s="11"/>
       <c r="K651" s="11"/>
@@ -9292,7 +9233,7 @@
       <c r="E652" s="9"/>
       <c r="F652" s="9"/>
       <c r="G652" s="11"/>
-      <c r="H652" s="13"/>
+      <c r="H652" s="16"/>
       <c r="I652" s="11"/>
       <c r="J652" s="11"/>
       <c r="K652" s="11"/>
@@ -9305,7 +9246,7 @@
       <c r="E653" s="9"/>
       <c r="F653" s="9"/>
       <c r="G653" s="11"/>
-      <c r="H653" s="13"/>
+      <c r="H653" s="16"/>
       <c r="I653" s="11"/>
       <c r="J653" s="11"/>
       <c r="K653" s="11"/>
@@ -9318,7 +9259,7 @@
       <c r="E654" s="9"/>
       <c r="F654" s="9"/>
       <c r="G654" s="11"/>
-      <c r="H654" s="13"/>
+      <c r="H654" s="16"/>
       <c r="I654" s="11"/>
       <c r="J654" s="11"/>
       <c r="K654" s="11"/>
@@ -9331,7 +9272,7 @@
       <c r="E655" s="9"/>
       <c r="F655" s="9"/>
       <c r="G655" s="11"/>
-      <c r="H655" s="13"/>
+      <c r="H655" s="16"/>
       <c r="I655" s="11"/>
       <c r="J655" s="11"/>
       <c r="K655" s="11"/>
@@ -9344,7 +9285,7 @@
       <c r="E656" s="9"/>
       <c r="F656" s="9"/>
       <c r="G656" s="11"/>
-      <c r="H656" s="13"/>
+      <c r="H656" s="16"/>
       <c r="I656" s="11"/>
       <c r="J656" s="11"/>
       <c r="K656" s="11"/>
@@ -9357,7 +9298,7 @@
       <c r="E657" s="9"/>
       <c r="F657" s="9"/>
       <c r="G657" s="11"/>
-      <c r="H657" s="13"/>
+      <c r="H657" s="16"/>
       <c r="I657" s="11"/>
       <c r="J657" s="11"/>
       <c r="K657" s="11"/>
@@ -9370,7 +9311,7 @@
       <c r="E658" s="9"/>
       <c r="F658" s="9"/>
       <c r="G658" s="11"/>
-      <c r="H658" s="13"/>
+      <c r="H658" s="16"/>
       <c r="I658" s="11"/>
       <c r="J658" s="11"/>
       <c r="K658" s="11"/>
@@ -9383,7 +9324,7 @@
       <c r="E659" s="9"/>
       <c r="F659" s="9"/>
       <c r="G659" s="11"/>
-      <c r="H659" s="13"/>
+      <c r="H659" s="16"/>
       <c r="I659" s="11"/>
       <c r="J659" s="11"/>
       <c r="K659" s="11"/>
@@ -9396,7 +9337,7 @@
       <c r="E660" s="9"/>
       <c r="F660" s="9"/>
       <c r="G660" s="11"/>
-      <c r="H660" s="13"/>
+      <c r="H660" s="16"/>
       <c r="I660" s="11"/>
       <c r="J660" s="11"/>
       <c r="K660" s="11"/>
@@ -9409,7 +9350,7 @@
       <c r="E661" s="9"/>
       <c r="F661" s="9"/>
       <c r="G661" s="11"/>
-      <c r="H661" s="13"/>
+      <c r="H661" s="16"/>
       <c r="I661" s="11"/>
       <c r="J661" s="11"/>
       <c r="K661" s="11"/>
@@ -9422,7 +9363,7 @@
       <c r="E662" s="9"/>
       <c r="F662" s="9"/>
       <c r="G662" s="11"/>
-      <c r="H662" s="13"/>
+      <c r="H662" s="16"/>
       <c r="I662" s="11"/>
       <c r="J662" s="11"/>
       <c r="K662" s="11"/>
@@ -9435,7 +9376,7 @@
       <c r="E663" s="9"/>
       <c r="F663" s="9"/>
       <c r="G663" s="11"/>
-      <c r="H663" s="13"/>
+      <c r="H663" s="16"/>
       <c r="I663" s="11"/>
       <c r="J663" s="11"/>
       <c r="K663" s="11"/>
@@ -9448,7 +9389,7 @@
       <c r="E664" s="9"/>
       <c r="F664" s="9"/>
       <c r="G664" s="11"/>
-      <c r="H664" s="13"/>
+      <c r="H664" s="16"/>
       <c r="I664" s="11"/>
       <c r="J664" s="11"/>
       <c r="K664" s="11"/>
@@ -9461,7 +9402,7 @@
       <c r="E665" s="9"/>
       <c r="F665" s="9"/>
       <c r="G665" s="11"/>
-      <c r="H665" s="13"/>
+      <c r="H665" s="16"/>
       <c r="I665" s="11"/>
       <c r="J665" s="11"/>
       <c r="K665" s="11"/>
@@ -9474,7 +9415,7 @@
       <c r="E666" s="9"/>
       <c r="F666" s="9"/>
       <c r="G666" s="11"/>
-      <c r="H666" s="13"/>
+      <c r="H666" s="16"/>
       <c r="I666" s="11"/>
       <c r="J666" s="11"/>
       <c r="K666" s="11"/>
@@ -9487,7 +9428,7 @@
       <c r="E667" s="9"/>
       <c r="F667" s="9"/>
       <c r="G667" s="11"/>
-      <c r="H667" s="13"/>
+      <c r="H667" s="16"/>
       <c r="I667" s="11"/>
       <c r="J667" s="11"/>
       <c r="K667" s="11"/>
@@ -9500,7 +9441,7 @@
       <c r="E668" s="9"/>
       <c r="F668" s="9"/>
       <c r="G668" s="11"/>
-      <c r="H668" s="13"/>
+      <c r="H668" s="16"/>
       <c r="I668" s="11"/>
       <c r="J668" s="11"/>
       <c r="K668" s="11"/>
@@ -9513,7 +9454,7 @@
       <c r="E669" s="9"/>
       <c r="F669" s="9"/>
       <c r="G669" s="11"/>
-      <c r="H669" s="13"/>
+      <c r="H669" s="16"/>
       <c r="I669" s="11"/>
       <c r="J669" s="11"/>
       <c r="K669" s="11"/>
@@ -9526,7 +9467,7 @@
       <c r="E670" s="9"/>
       <c r="F670" s="9"/>
       <c r="G670" s="11"/>
-      <c r="H670" s="13"/>
+      <c r="H670" s="16"/>
       <c r="I670" s="11"/>
       <c r="J670" s="11"/>
       <c r="K670" s="11"/>
@@ -9539,7 +9480,7 @@
       <c r="E671" s="9"/>
       <c r="F671" s="9"/>
       <c r="G671" s="11"/>
-      <c r="H671" s="13"/>
+      <c r="H671" s="16"/>
       <c r="I671" s="11"/>
       <c r="J671" s="11"/>
       <c r="K671" s="11"/>
@@ -9552,7 +9493,7 @@
       <c r="E672" s="9"/>
       <c r="F672" s="9"/>
       <c r="G672" s="11"/>
-      <c r="H672" s="13"/>
+      <c r="H672" s="16"/>
       <c r="I672" s="11"/>
       <c r="J672" s="11"/>
       <c r="K672" s="11"/>
@@ -9565,7 +9506,7 @@
       <c r="E673" s="9"/>
       <c r="F673" s="9"/>
       <c r="G673" s="11"/>
-      <c r="H673" s="13"/>
+      <c r="H673" s="16"/>
       <c r="I673" s="11"/>
       <c r="J673" s="11"/>
       <c r="K673" s="11"/>
@@ -9578,7 +9519,7 @@
       <c r="E674" s="9"/>
       <c r="F674" s="9"/>
       <c r="G674" s="11"/>
-      <c r="H674" s="13"/>
+      <c r="H674" s="16"/>
       <c r="I674" s="11"/>
       <c r="J674" s="11"/>
       <c r="K674" s="11"/>
@@ -9591,7 +9532,7 @@
       <c r="E675" s="9"/>
       <c r="F675" s="9"/>
       <c r="G675" s="11"/>
-      <c r="H675" s="13"/>
+      <c r="H675" s="16"/>
       <c r="I675" s="11"/>
       <c r="J675" s="11"/>
       <c r="K675" s="11"/>
@@ -9604,7 +9545,7 @@
       <c r="E676" s="9"/>
       <c r="F676" s="9"/>
       <c r="G676" s="11"/>
-      <c r="H676" s="13"/>
+      <c r="H676" s="16"/>
       <c r="I676" s="11"/>
       <c r="J676" s="11"/>
       <c r="K676" s="11"/>
@@ -9617,7 +9558,7 @@
       <c r="E677" s="9"/>
       <c r="F677" s="9"/>
       <c r="G677" s="11"/>
-      <c r="H677" s="13"/>
+      <c r="H677" s="16"/>
       <c r="I677" s="11"/>
       <c r="J677" s="11"/>
       <c r="K677" s="11"/>
@@ -9630,7 +9571,7 @@
       <c r="E678" s="9"/>
       <c r="F678" s="9"/>
       <c r="G678" s="11"/>
-      <c r="H678" s="13"/>
+      <c r="H678" s="16"/>
       <c r="I678" s="11"/>
       <c r="J678" s="11"/>
       <c r="K678" s="11"/>
@@ -9643,7 +9584,7 @@
       <c r="E679" s="9"/>
       <c r="F679" s="9"/>
       <c r="G679" s="11"/>
-      <c r="H679" s="13"/>
+      <c r="H679" s="16"/>
       <c r="I679" s="11"/>
       <c r="J679" s="11"/>
       <c r="K679" s="11"/>
@@ -9656,7 +9597,7 @@
       <c r="E680" s="9"/>
       <c r="F680" s="9"/>
       <c r="G680" s="11"/>
-      <c r="H680" s="13"/>
+      <c r="H680" s="16"/>
       <c r="I680" s="11"/>
       <c r="J680" s="11"/>
       <c r="K680" s="11"/>
@@ -9669,7 +9610,7 @@
       <c r="E681" s="9"/>
       <c r="F681" s="9"/>
       <c r="G681" s="11"/>
-      <c r="H681" s="13"/>
+      <c r="H681" s="16"/>
       <c r="I681" s="11"/>
       <c r="J681" s="11"/>
       <c r="K681" s="11"/>
@@ -9682,7 +9623,7 @@
       <c r="E682" s="9"/>
       <c r="F682" s="9"/>
       <c r="G682" s="11"/>
-      <c r="H682" s="13"/>
+      <c r="H682" s="16"/>
       <c r="I682" s="11"/>
       <c r="J682" s="11"/>
       <c r="K682" s="11"/>
@@ -9695,7 +9636,7 @@
       <c r="E683" s="9"/>
       <c r="F683" s="9"/>
       <c r="G683" s="11"/>
-      <c r="H683" s="13"/>
+      <c r="H683" s="16"/>
       <c r="I683" s="11"/>
       <c r="J683" s="11"/>
       <c r="K683" s="11"/>
@@ -9708,7 +9649,7 @@
       <c r="E684" s="9"/>
       <c r="F684" s="9"/>
       <c r="G684" s="11"/>
-      <c r="H684" s="13"/>
+      <c r="H684" s="16"/>
       <c r="I684" s="11"/>
       <c r="J684" s="11"/>
       <c r="K684" s="11"/>
@@ -9721,7 +9662,7 @@
       <c r="E685" s="9"/>
       <c r="F685" s="9"/>
       <c r="G685" s="11"/>
-      <c r="H685" s="13"/>
+      <c r="H685" s="16"/>
       <c r="I685" s="11"/>
       <c r="J685" s="11"/>
       <c r="K685" s="11"/>
@@ -9734,7 +9675,7 @@
       <c r="E686" s="9"/>
       <c r="F686" s="9"/>
       <c r="G686" s="11"/>
-      <c r="H686" s="13"/>
+      <c r="H686" s="16"/>
       <c r="I686" s="11"/>
       <c r="J686" s="11"/>
       <c r="K686" s="11"/>
@@ -9747,7 +9688,7 @@
       <c r="E687" s="9"/>
       <c r="F687" s="9"/>
       <c r="G687" s="11"/>
-      <c r="H687" s="13"/>
+      <c r="H687" s="16"/>
       <c r="I687" s="11"/>
       <c r="J687" s="11"/>
       <c r="K687" s="11"/>
@@ -9760,7 +9701,7 @@
       <c r="E688" s="9"/>
       <c r="F688" s="9"/>
       <c r="G688" s="11"/>
-      <c r="H688" s="13"/>
+      <c r="H688" s="16"/>
       <c r="I688" s="11"/>
       <c r="J688" s="11"/>
       <c r="K688" s="11"/>
@@ -9773,7 +9714,7 @@
       <c r="E689" s="9"/>
       <c r="F689" s="9"/>
       <c r="G689" s="11"/>
-      <c r="H689" s="13"/>
+      <c r="H689" s="16"/>
       <c r="I689" s="11"/>
       <c r="J689" s="11"/>
       <c r="K689" s="11"/>
@@ -9786,7 +9727,7 @@
       <c r="E690" s="9"/>
       <c r="F690" s="9"/>
       <c r="G690" s="11"/>
-      <c r="H690" s="13"/>
+      <c r="H690" s="16"/>
       <c r="I690" s="11"/>
       <c r="J690" s="11"/>
       <c r="K690" s="11"/>
@@ -9799,7 +9740,7 @@
       <c r="E691" s="9"/>
       <c r="F691" s="9"/>
       <c r="G691" s="11"/>
-      <c r="H691" s="13"/>
+      <c r="H691" s="16"/>
       <c r="I691" s="11"/>
       <c r="J691" s="11"/>
       <c r="K691" s="11"/>
@@ -9812,7 +9753,7 @@
       <c r="E692" s="9"/>
       <c r="F692" s="9"/>
       <c r="G692" s="11"/>
-      <c r="H692" s="13"/>
+      <c r="H692" s="16"/>
       <c r="I692" s="11"/>
       <c r="J692" s="11"/>
       <c r="K692" s="11"/>
@@ -9825,7 +9766,7 @@
       <c r="E693" s="9"/>
       <c r="F693" s="9"/>
       <c r="G693" s="11"/>
-      <c r="H693" s="13"/>
+      <c r="H693" s="16"/>
       <c r="I693" s="11"/>
       <c r="J693" s="11"/>
       <c r="K693" s="11"/>
@@ -9838,7 +9779,7 @@
       <c r="E694" s="9"/>
       <c r="F694" s="9"/>
       <c r="G694" s="11"/>
-      <c r="H694" s="13"/>
+      <c r="H694" s="16"/>
       <c r="I694" s="11"/>
       <c r="J694" s="11"/>
       <c r="K694" s="11"/>
@@ -9851,7 +9792,7 @@
       <c r="E695" s="9"/>
       <c r="F695" s="9"/>
       <c r="G695" s="11"/>
-      <c r="H695" s="13"/>
+      <c r="H695" s="16"/>
       <c r="I695" s="11"/>
       <c r="J695" s="11"/>
       <c r="K695" s="11"/>
@@ -9864,7 +9805,7 @@
       <c r="E696" s="9"/>
       <c r="F696" s="9"/>
       <c r="G696" s="11"/>
-      <c r="H696" s="13"/>
+      <c r="H696" s="16"/>
       <c r="I696" s="11"/>
       <c r="J696" s="11"/>
       <c r="K696" s="11"/>
@@ -9877,7 +9818,7 @@
       <c r="E697" s="9"/>
       <c r="F697" s="9"/>
       <c r="G697" s="11"/>
-      <c r="H697" s="13"/>
+      <c r="H697" s="16"/>
       <c r="I697" s="11"/>
       <c r="J697" s="11"/>
       <c r="K697" s="11"/>
@@ -9890,7 +9831,7 @@
       <c r="E698" s="9"/>
       <c r="F698" s="9"/>
       <c r="G698" s="11"/>
-      <c r="H698" s="13"/>
+      <c r="H698" s="16"/>
       <c r="I698" s="11"/>
       <c r="J698" s="11"/>
       <c r="K698" s="11"/>
@@ -9903,7 +9844,7 @@
       <c r="E699" s="9"/>
       <c r="F699" s="9"/>
       <c r="G699" s="11"/>
-      <c r="H699" s="13"/>
+      <c r="H699" s="16"/>
       <c r="I699" s="11"/>
       <c r="J699" s="11"/>
       <c r="K699" s="11"/>
@@ -9916,7 +9857,7 @@
       <c r="E700" s="9"/>
       <c r="F700" s="9"/>
       <c r="G700" s="11"/>
-      <c r="H700" s="13"/>
+      <c r="H700" s="16"/>
       <c r="I700" s="11"/>
       <c r="J700" s="11"/>
       <c r="K700" s="11"/>
@@ -9929,7 +9870,7 @@
       <c r="E701" s="9"/>
       <c r="F701" s="9"/>
       <c r="G701" s="11"/>
-      <c r="H701" s="13"/>
+      <c r="H701" s="16"/>
       <c r="I701" s="11"/>
       <c r="J701" s="11"/>
       <c r="K701" s="11"/>
@@ -9942,7 +9883,7 @@
       <c r="E702" s="9"/>
       <c r="F702" s="9"/>
       <c r="G702" s="11"/>
-      <c r="H702" s="13"/>
+      <c r="H702" s="16"/>
       <c r="I702" s="11"/>
       <c r="J702" s="11"/>
       <c r="K702" s="11"/>
@@ -9955,7 +9896,7 @@
       <c r="E703" s="9"/>
       <c r="F703" s="9"/>
       <c r="G703" s="11"/>
-      <c r="H703" s="13"/>
+      <c r="H703" s="16"/>
       <c r="I703" s="11"/>
       <c r="J703" s="11"/>
       <c r="K703" s="11"/>
@@ -9968,7 +9909,7 @@
       <c r="E704" s="9"/>
       <c r="F704" s="9"/>
       <c r="G704" s="11"/>
-      <c r="H704" s="13"/>
+      <c r="H704" s="16"/>
       <c r="I704" s="11"/>
       <c r="J704" s="11"/>
       <c r="K704" s="11"/>
@@ -9981,7 +9922,7 @@
       <c r="E705" s="9"/>
       <c r="F705" s="9"/>
       <c r="G705" s="11"/>
-      <c r="H705" s="13"/>
+      <c r="H705" s="16"/>
       <c r="I705" s="11"/>
       <c r="J705" s="11"/>
       <c r="K705" s="11"/>
@@ -9994,7 +9935,7 @@
       <c r="E706" s="9"/>
       <c r="F706" s="9"/>
       <c r="G706" s="11"/>
-      <c r="H706" s="13"/>
+      <c r="H706" s="16"/>
       <c r="I706" s="11"/>
       <c r="J706" s="11"/>
       <c r="K706" s="11"/>
@@ -10007,7 +9948,7 @@
       <c r="E707" s="9"/>
       <c r="F707" s="9"/>
       <c r="G707" s="11"/>
-      <c r="H707" s="13"/>
+      <c r="H707" s="16"/>
       <c r="I707" s="11"/>
       <c r="J707" s="11"/>
       <c r="K707" s="11"/>
@@ -10020,7 +9961,7 @@
       <c r="E708" s="9"/>
       <c r="F708" s="9"/>
       <c r="G708" s="11"/>
-      <c r="H708" s="13"/>
+      <c r="H708" s="16"/>
       <c r="I708" s="11"/>
       <c r="J708" s="11"/>
       <c r="K708" s="11"/>
@@ -10033,7 +9974,7 @@
       <c r="E709" s="9"/>
       <c r="F709" s="9"/>
       <c r="G709" s="11"/>
-      <c r="H709" s="13"/>
+      <c r="H709" s="16"/>
       <c r="I709" s="11"/>
       <c r="J709" s="11"/>
       <c r="K709" s="11"/>
@@ -10046,7 +9987,7 @@
       <c r="E710" s="9"/>
       <c r="F710" s="9"/>
       <c r="G710" s="11"/>
-      <c r="H710" s="13"/>
+      <c r="H710" s="16"/>
       <c r="I710" s="11"/>
       <c r="J710" s="11"/>
       <c r="K710" s="11"/>
@@ -10059,7 +10000,7 @@
       <c r="E711" s="9"/>
       <c r="F711" s="9"/>
       <c r="G711" s="11"/>
-      <c r="H711" s="13"/>
+      <c r="H711" s="16"/>
       <c r="I711" s="11"/>
       <c r="J711" s="11"/>
       <c r="K711" s="11"/>
@@ -10072,7 +10013,7 @@
       <c r="E712" s="9"/>
       <c r="F712" s="9"/>
       <c r="G712" s="11"/>
-      <c r="H712" s="13"/>
+      <c r="H712" s="16"/>
       <c r="I712" s="11"/>
       <c r="J712" s="11"/>
       <c r="K712" s="11"/>
@@ -10085,7 +10026,7 @@
       <c r="E713" s="9"/>
       <c r="F713" s="9"/>
       <c r="G713" s="11"/>
-      <c r="H713" s="13"/>
+      <c r="H713" s="16"/>
       <c r="I713" s="11"/>
       <c r="J713" s="11"/>
       <c r="K713" s="11"/>
@@ -10098,7 +10039,7 @@
       <c r="E714" s="9"/>
       <c r="F714" s="9"/>
       <c r="G714" s="11"/>
-      <c r="H714" s="13"/>
+      <c r="H714" s="16"/>
       <c r="I714" s="11"/>
       <c r="J714" s="11"/>
       <c r="K714" s="11"/>
@@ -10111,7 +10052,7 @@
       <c r="E715" s="9"/>
       <c r="F715" s="9"/>
       <c r="G715" s="11"/>
-      <c r="H715" s="13"/>
+      <c r="H715" s="16"/>
       <c r="I715" s="11"/>
       <c r="J715" s="11"/>
       <c r="K715" s="11"/>
@@ -10124,7 +10065,7 @@
       <c r="E716" s="9"/>
       <c r="F716" s="9"/>
       <c r="G716" s="11"/>
-      <c r="H716" s="13"/>
+      <c r="H716" s="16"/>
       <c r="I716" s="11"/>
       <c r="J716" s="11"/>
       <c r="K716" s="11"/>
@@ -10137,7 +10078,7 @@
       <c r="E717" s="9"/>
       <c r="F717" s="9"/>
       <c r="G717" s="11"/>
-      <c r="H717" s="13"/>
+      <c r="H717" s="16"/>
       <c r="I717" s="11"/>
       <c r="J717" s="11"/>
       <c r="K717" s="11"/>
@@ -10150,7 +10091,7 @@
       <c r="E718" s="9"/>
       <c r="F718" s="9"/>
       <c r="G718" s="11"/>
-      <c r="H718" s="13"/>
+      <c r="H718" s="16"/>
       <c r="I718" s="11"/>
       <c r="J718" s="11"/>
       <c r="K718" s="11"/>
@@ -10163,7 +10104,7 @@
       <c r="E719" s="9"/>
       <c r="F719" s="9"/>
       <c r="G719" s="11"/>
-      <c r="H719" s="13"/>
+      <c r="H719" s="16"/>
       <c r="I719" s="11"/>
       <c r="J719" s="11"/>
       <c r="K719" s="11"/>
@@ -10176,7 +10117,7 @@
       <c r="E720" s="9"/>
       <c r="F720" s="9"/>
       <c r="G720" s="11"/>
-      <c r="H720" s="13"/>
+      <c r="H720" s="16"/>
       <c r="I720" s="11"/>
       <c r="J720" s="11"/>
       <c r="K720" s="11"/>
@@ -10189,7 +10130,7 @@
       <c r="E721" s="9"/>
       <c r="F721" s="9"/>
       <c r="G721" s="11"/>
-      <c r="H721" s="13"/>
+      <c r="H721" s="16"/>
       <c r="I721" s="11"/>
       <c r="J721" s="11"/>
       <c r="K721" s="11"/>
@@ -10202,7 +10143,7 @@
       <c r="E722" s="9"/>
       <c r="F722" s="9"/>
       <c r="G722" s="11"/>
-      <c r="H722" s="13"/>
+      <c r="H722" s="16"/>
       <c r="I722" s="11"/>
       <c r="J722" s="11"/>
       <c r="K722" s="11"/>
@@ -10215,7 +10156,7 @@
       <c r="E723" s="9"/>
       <c r="F723" s="9"/>
       <c r="G723" s="11"/>
-      <c r="H723" s="13"/>
+      <c r="H723" s="16"/>
       <c r="I723" s="11"/>
       <c r="J723" s="11"/>
       <c r="K723" s="11"/>
@@ -10228,7 +10169,7 @@
       <c r="E724" s="9"/>
       <c r="F724" s="9"/>
       <c r="G724" s="11"/>
-      <c r="H724" s="13"/>
+      <c r="H724" s="16"/>
       <c r="I724" s="11"/>
       <c r="J724" s="11"/>
       <c r="K724" s="11"/>
@@ -10241,7 +10182,7 @@
       <c r="E725" s="9"/>
       <c r="F725" s="9"/>
       <c r="G725" s="11"/>
-      <c r="H725" s="13"/>
+      <c r="H725" s="16"/>
       <c r="I725" s="11"/>
       <c r="J725" s="11"/>
       <c r="K725" s="11"/>
@@ -10254,7 +10195,7 @@
       <c r="E726" s="9"/>
       <c r="F726" s="9"/>
       <c r="G726" s="11"/>
-      <c r="H726" s="13"/>
+      <c r="H726" s="16"/>
       <c r="I726" s="11"/>
       <c r="J726" s="11"/>
       <c r="K726" s="11"/>
@@ -10267,7 +10208,7 @@
       <c r="E727" s="9"/>
       <c r="F727" s="9"/>
       <c r="G727" s="11"/>
-      <c r="H727" s="13"/>
+      <c r="H727" s="16"/>
       <c r="I727" s="11"/>
       <c r="J727" s="11"/>
       <c r="K727" s="11"/>
@@ -10280,7 +10221,7 @@
       <c r="E728" s="9"/>
       <c r="F728" s="9"/>
       <c r="G728" s="11"/>
-      <c r="H728" s="13"/>
+      <c r="H728" s="16"/>
       <c r="I728" s="11"/>
       <c r="J728" s="11"/>
       <c r="K728" s="11"/>
@@ -10293,7 +10234,7 @@
       <c r="E729" s="9"/>
       <c r="F729" s="9"/>
       <c r="G729" s="11"/>
-      <c r="H729" s="13"/>
+      <c r="H729" s="16"/>
       <c r="I729" s="11"/>
       <c r="J729" s="11"/>
       <c r="K729" s="11"/>
@@ -10306,7 +10247,7 @@
       <c r="E730" s="9"/>
       <c r="F730" s="9"/>
       <c r="G730" s="11"/>
-      <c r="H730" s="13"/>
+      <c r="H730" s="16"/>
       <c r="I730" s="11"/>
       <c r="J730" s="11"/>
       <c r="K730" s="11"/>
@@ -10319,7 +10260,7 @@
       <c r="E731" s="9"/>
       <c r="F731" s="9"/>
       <c r="G731" s="11"/>
-      <c r="H731" s="13"/>
+      <c r="H731" s="16"/>
       <c r="I731" s="11"/>
       <c r="J731" s="11"/>
       <c r="K731" s="11"/>
@@ -10332,7 +10273,7 @@
       <c r="E732" s="9"/>
       <c r="F732" s="9"/>
       <c r="G732" s="11"/>
-      <c r="H732" s="13"/>
+      <c r="H732" s="16"/>
       <c r="I732" s="11"/>
       <c r="J732" s="11"/>
       <c r="K732" s="11"/>
@@ -10345,7 +10286,7 @@
       <c r="E733" s="9"/>
       <c r="F733" s="9"/>
       <c r="G733" s="11"/>
-      <c r="H733" s="13"/>
+      <c r="H733" s="16"/>
       <c r="I733" s="11"/>
       <c r="J733" s="11"/>
       <c r="K733" s="11"/>
@@ -10358,7 +10299,7 @@
       <c r="E734" s="9"/>
       <c r="F734" s="9"/>
       <c r="G734" s="11"/>
-      <c r="H734" s="13"/>
+      <c r="H734" s="16"/>
       <c r="I734" s="11"/>
       <c r="J734" s="11"/>
       <c r="K734" s="11"/>
@@ -10371,7 +10312,7 @@
       <c r="E735" s="9"/>
       <c r="F735" s="9"/>
       <c r="G735" s="11"/>
-      <c r="H735" s="13"/>
+      <c r="H735" s="16"/>
       <c r="I735" s="11"/>
       <c r="J735" s="11"/>
       <c r="K735" s="11"/>
@@ -10384,7 +10325,7 @@
       <c r="E736" s="9"/>
       <c r="F736" s="9"/>
       <c r="G736" s="11"/>
-      <c r="H736" s="13"/>
+      <c r="H736" s="16"/>
       <c r="I736" s="11"/>
       <c r="J736" s="11"/>
       <c r="K736" s="11"/>
@@ -10397,7 +10338,7 @@
       <c r="E737" s="9"/>
       <c r="F737" s="9"/>
       <c r="G737" s="11"/>
-      <c r="H737" s="13"/>
+      <c r="H737" s="16"/>
       <c r="I737" s="11"/>
       <c r="J737" s="11"/>
       <c r="K737" s="11"/>
@@ -10410,7 +10351,7 @@
       <c r="E738" s="9"/>
       <c r="F738" s="9"/>
       <c r="G738" s="11"/>
-      <c r="H738" s="13"/>
+      <c r="H738" s="16"/>
       <c r="I738" s="11"/>
       <c r="J738" s="11"/>
       <c r="K738" s="11"/>
@@ -10423,7 +10364,7 @@
       <c r="E739" s="9"/>
       <c r="F739" s="9"/>
       <c r="G739" s="11"/>
-      <c r="H739" s="13"/>
+      <c r="H739" s="16"/>
       <c r="I739" s="11"/>
       <c r="J739" s="11"/>
       <c r="K739" s="11"/>
@@ -10436,7 +10377,7 @@
       <c r="E740" s="9"/>
       <c r="F740" s="9"/>
       <c r="G740" s="11"/>
-      <c r="H740" s="13"/>
+      <c r="H740" s="16"/>
       <c r="I740" s="11"/>
       <c r="J740" s="11"/>
       <c r="K740" s="11"/>
@@ -10449,7 +10390,7 @@
       <c r="E741" s="9"/>
       <c r="F741" s="9"/>
       <c r="G741" s="11"/>
-      <c r="H741" s="13"/>
+      <c r="H741" s="16"/>
       <c r="I741" s="11"/>
       <c r="J741" s="11"/>
       <c r="K741" s="11"/>
@@ -10462,7 +10403,7 @@
       <c r="E742" s="9"/>
       <c r="F742" s="9"/>
       <c r="G742" s="11"/>
-      <c r="H742" s="13"/>
+      <c r="H742" s="16"/>
       <c r="I742" s="11"/>
       <c r="J742" s="11"/>
       <c r="K742" s="11"/>
@@ -10475,7 +10416,7 @@
       <c r="E743" s="9"/>
       <c r="F743" s="9"/>
       <c r="G743" s="11"/>
-      <c r="H743" s="13"/>
+      <c r="H743" s="16"/>
       <c r="I743" s="11"/>
       <c r="J743" s="11"/>
       <c r="K743" s="11"/>
@@ -10488,7 +10429,7 @@
       <c r="E744" s="9"/>
       <c r="F744" s="9"/>
       <c r="G744" s="11"/>
-      <c r="H744" s="13"/>
+      <c r="H744" s="16"/>
       <c r="I744" s="11"/>
       <c r="J744" s="11"/>
       <c r="K744" s="11"/>
@@ -10501,7 +10442,7 @@
       <c r="E745" s="9"/>
       <c r="F745" s="9"/>
       <c r="G745" s="11"/>
-      <c r="H745" s="13"/>
+      <c r="H745" s="16"/>
       <c r="I745" s="11"/>
       <c r="J745" s="11"/>
       <c r="K745" s="11"/>
@@ -10514,7 +10455,7 @@
       <c r="E746" s="9"/>
       <c r="F746" s="9"/>
       <c r="G746" s="11"/>
-      <c r="H746" s="13"/>
+      <c r="H746" s="16"/>
       <c r="I746" s="11"/>
       <c r="J746" s="11"/>
       <c r="K746" s="11"/>
@@ -10527,7 +10468,7 @@
       <c r="E747" s="9"/>
       <c r="F747" s="9"/>
       <c r="G747" s="11"/>
-      <c r="H747" s="13"/>
+      <c r="H747" s="16"/>
       <c r="I747" s="11"/>
       <c r="J747" s="11"/>
       <c r="K747" s="11"/>
@@ -10540,7 +10481,7 @@
       <c r="E748" s="9"/>
       <c r="F748" s="9"/>
       <c r="G748" s="11"/>
-      <c r="H748" s="13"/>
+      <c r="H748" s="16"/>
       <c r="I748" s="11"/>
       <c r="J748" s="11"/>
       <c r="K748" s="11"/>
@@ -10553,7 +10494,7 @@
       <c r="E749" s="9"/>
       <c r="F749" s="9"/>
       <c r="G749" s="11"/>
-      <c r="H749" s="13"/>
+      <c r="H749" s="16"/>
       <c r="I749" s="11"/>
       <c r="J749" s="11"/>
       <c r="K749" s="11"/>
@@ -10566,7 +10507,7 @@
       <c r="E750" s="9"/>
       <c r="F750" s="9"/>
       <c r="G750" s="11"/>
-      <c r="H750" s="13"/>
+      <c r="H750" s="16"/>
       <c r="I750" s="11"/>
       <c r="J750" s="11"/>
       <c r="K750" s="11"/>
@@ -10579,7 +10520,7 @@
       <c r="E751" s="9"/>
       <c r="F751" s="9"/>
       <c r="G751" s="11"/>
-      <c r="H751" s="13"/>
+      <c r="H751" s="16"/>
       <c r="I751" s="11"/>
       <c r="J751" s="11"/>
       <c r="K751" s="11"/>
@@ -10592,7 +10533,7 @@
       <c r="E752" s="9"/>
       <c r="F752" s="9"/>
       <c r="G752" s="11"/>
-      <c r="H752" s="13"/>
+      <c r="H752" s="16"/>
       <c r="I752" s="11"/>
       <c r="J752" s="11"/>
       <c r="K752" s="11"/>
@@ -10605,7 +10546,7 @@
       <c r="E753" s="9"/>
       <c r="F753" s="9"/>
       <c r="G753" s="11"/>
-      <c r="H753" s="13"/>
+      <c r="H753" s="16"/>
       <c r="I753" s="11"/>
       <c r="J753" s="11"/>
       <c r="K753" s="11"/>
@@ -10618,7 +10559,7 @@
       <c r="E754" s="9"/>
       <c r="F754" s="9"/>
       <c r="G754" s="11"/>
-      <c r="H754" s="13"/>
+      <c r="H754" s="16"/>
       <c r="I754" s="11"/>
       <c r="J754" s="11"/>
       <c r="K754" s="11"/>
@@ -10631,7 +10572,7 @@
       <c r="E755" s="9"/>
       <c r="F755" s="9"/>
       <c r="G755" s="11"/>
-      <c r="H755" s="13"/>
+      <c r="H755" s="16"/>
       <c r="I755" s="11"/>
       <c r="J755" s="11"/>
       <c r="K755" s="11"/>
@@ -10644,7 +10585,7 @@
       <c r="E756" s="9"/>
       <c r="F756" s="9"/>
       <c r="G756" s="11"/>
-      <c r="H756" s="13"/>
+      <c r="H756" s="16"/>
       <c r="I756" s="11"/>
       <c r="J756" s="11"/>
       <c r="K756" s="11"/>
@@ -10657,7 +10598,7 @@
       <c r="E757" s="9"/>
       <c r="F757" s="9"/>
       <c r="G757" s="11"/>
-      <c r="H757" s="13"/>
+      <c r="H757" s="16"/>
       <c r="I757" s="11"/>
       <c r="J757" s="11"/>
       <c r="K757" s="11"/>
@@ -10670,7 +10611,7 @@
       <c r="E758" s="9"/>
       <c r="F758" s="9"/>
       <c r="G758" s="11"/>
-      <c r="H758" s="13"/>
+      <c r="H758" s="16"/>
       <c r="I758" s="11"/>
       <c r="J758" s="11"/>
       <c r="K758" s="11"/>
@@ -10683,7 +10624,7 @@
       <c r="E759" s="9"/>
       <c r="F759" s="9"/>
       <c r="G759" s="11"/>
-      <c r="H759" s="13"/>
+      <c r="H759" s="16"/>
       <c r="I759" s="11"/>
       <c r="J759" s="11"/>
       <c r="K759" s="11"/>
@@ -10696,7 +10637,7 @@
       <c r="E760" s="9"/>
       <c r="F760" s="9"/>
       <c r="G760" s="11"/>
-      <c r="H760" s="13"/>
+      <c r="H760" s="16"/>
       <c r="I760" s="11"/>
       <c r="J760" s="11"/>
       <c r="K760" s="11"/>
@@ -10709,7 +10650,7 @@
       <c r="E761" s="9"/>
       <c r="F761" s="9"/>
       <c r="G761" s="11"/>
-      <c r="H761" s="13"/>
+      <c r="H761" s="16"/>
       <c r="I761" s="11"/>
       <c r="J761" s="11"/>
       <c r="K761" s="11"/>
@@ -10722,7 +10663,7 @@
       <c r="E762" s="9"/>
       <c r="F762" s="9"/>
       <c r="G762" s="11"/>
-      <c r="H762" s="13"/>
+      <c r="H762" s="16"/>
       <c r="I762" s="11"/>
       <c r="J762" s="11"/>
       <c r="K762" s="11"/>
@@ -10735,7 +10676,7 @@
       <c r="E763" s="9"/>
       <c r="F763" s="9"/>
       <c r="G763" s="11"/>
-      <c r="H763" s="13"/>
+      <c r="H763" s="16"/>
       <c r="I763" s="11"/>
       <c r="J763" s="11"/>
       <c r="K763" s="11"/>
@@ -10748,7 +10689,7 @@
       <c r="E764" s="9"/>
       <c r="F764" s="9"/>
       <c r="G764" s="11"/>
-      <c r="H764" s="13"/>
+      <c r="H764" s="16"/>
       <c r="I764" s="11"/>
       <c r="J764" s="11"/>
       <c r="K764" s="11"/>
@@ -10761,7 +10702,7 @@
       <c r="E765" s="9"/>
       <c r="F765" s="9"/>
       <c r="G765" s="11"/>
-      <c r="H765" s="13"/>
+      <c r="H765" s="16"/>
       <c r="I765" s="11"/>
       <c r="J765" s="11"/>
       <c r="K765" s="11"/>
@@ -10774,7 +10715,7 @@
       <c r="E766" s="9"/>
       <c r="F766" s="9"/>
       <c r="G766" s="11"/>
-      <c r="H766" s="13"/>
+      <c r="H766" s="16"/>
       <c r="I766" s="11"/>
       <c r="J766" s="11"/>
       <c r="K766" s="11"/>
@@ -10787,7 +10728,7 @@
       <c r="E767" s="9"/>
       <c r="F767" s="9"/>
       <c r="G767" s="11"/>
-      <c r="H767" s="13"/>
+      <c r="H767" s="16"/>
       <c r="I767" s="11"/>
       <c r="J767" s="11"/>
       <c r="K767" s="11"/>
@@ -10800,7 +10741,7 @@
       <c r="E768" s="9"/>
       <c r="F768" s="9"/>
       <c r="G768" s="11"/>
-      <c r="H768" s="13"/>
+      <c r="H768" s="16"/>
       <c r="I768" s="11"/>
       <c r="J768" s="11"/>
       <c r="K768" s="11"/>
@@ -10813,7 +10754,7 @@
       <c r="E769" s="9"/>
       <c r="F769" s="9"/>
       <c r="G769" s="11"/>
-      <c r="H769" s="13"/>
+      <c r="H769" s="16"/>
       <c r="I769" s="11"/>
       <c r="J769" s="11"/>
       <c r="K769" s="11"/>
@@ -10826,7 +10767,7 @@
       <c r="E770" s="9"/>
       <c r="F770" s="9"/>
       <c r="G770" s="11"/>
-      <c r="H770" s="13"/>
+      <c r="H770" s="16"/>
       <c r="I770" s="11"/>
       <c r="J770" s="11"/>
       <c r="K770" s="11"/>
@@ -10839,7 +10780,7 @@
       <c r="E771" s="9"/>
       <c r="F771" s="9"/>
       <c r="G771" s="11"/>
-      <c r="H771" s="13"/>
+      <c r="H771" s="16"/>
       <c r="I771" s="11"/>
       <c r="J771" s="11"/>
       <c r="K771" s="11"/>
@@ -10852,7 +10793,7 @@
       <c r="E772" s="9"/>
       <c r="F772" s="9"/>
       <c r="G772" s="11"/>
-      <c r="H772" s="13"/>
+      <c r="H772" s="16"/>
       <c r="I772" s="11"/>
       <c r="J772" s="11"/>
       <c r="K772" s="11"/>
@@ -10865,7 +10806,7 @@
       <c r="E773" s="9"/>
       <c r="F773" s="9"/>
       <c r="G773" s="11"/>
-      <c r="H773" s="13"/>
+      <c r="H773" s="16"/>
       <c r="I773" s="11"/>
       <c r="J773" s="11"/>
       <c r="K773" s="11"/>
@@ -10878,7 +10819,7 @@
       <c r="E774" s="9"/>
       <c r="F774" s="9"/>
       <c r="G774" s="11"/>
-      <c r="H774" s="13"/>
+      <c r="H774" s="16"/>
       <c r="I774" s="11"/>
       <c r="J774" s="11"/>
       <c r="K774" s="11"/>
@@ -10891,7 +10832,7 @@
       <c r="E775" s="9"/>
       <c r="F775" s="9"/>
       <c r="G775" s="11"/>
-      <c r="H775" s="13"/>
+      <c r="H775" s="16"/>
       <c r="I775" s="11"/>
       <c r="J775" s="11"/>
       <c r="K775" s="11"/>
@@ -10904,7 +10845,7 @@
       <c r="E776" s="9"/>
       <c r="F776" s="9"/>
       <c r="G776" s="11"/>
-      <c r="H776" s="13"/>
+      <c r="H776" s="16"/>
       <c r="I776" s="11"/>
       <c r="J776" s="11"/>
       <c r="K776" s="11"/>
@@ -10917,7 +10858,7 @@
       <c r="E777" s="9"/>
       <c r="F777" s="9"/>
       <c r="G777" s="11"/>
-      <c r="H777" s="13"/>
+      <c r="H777" s="16"/>
       <c r="I777" s="11"/>
       <c r="J777" s="11"/>
       <c r="K777" s="11"/>
@@ -10930,7 +10871,7 @@
       <c r="E778" s="9"/>
       <c r="F778" s="9"/>
       <c r="G778" s="11"/>
-      <c r="H778" s="13"/>
+      <c r="H778" s="16"/>
       <c r="I778" s="11"/>
       <c r="J778" s="11"/>
       <c r="K778" s="11"/>
@@ -10943,7 +10884,7 @@
       <c r="E779" s="9"/>
       <c r="F779" s="9"/>
       <c r="G779" s="11"/>
-      <c r="H779" s="13"/>
+      <c r="H779" s="16"/>
       <c r="I779" s="11"/>
       <c r="J779" s="11"/>
       <c r="K779" s="11"/>
@@ -10956,7 +10897,7 @@
       <c r="E780" s="9"/>
       <c r="F780" s="9"/>
       <c r="G780" s="11"/>
-      <c r="H780" s="13"/>
+      <c r="H780" s="16"/>
       <c r="I780" s="11"/>
       <c r="J780" s="11"/>
       <c r="K780" s="11"/>
@@ -10969,7 +10910,7 @@
       <c r="E781" s="9"/>
       <c r="F781" s="9"/>
       <c r="G781" s="11"/>
-      <c r="H781" s="13"/>
+      <c r="H781" s="16"/>
       <c r="I781" s="11"/>
       <c r="J781" s="11"/>
       <c r="K781" s="11"/>
@@ -10982,7 +10923,7 @@
       <c r="E782" s="9"/>
       <c r="F782" s="9"/>
       <c r="G782" s="11"/>
-      <c r="H782" s="13"/>
+      <c r="H782" s="16"/>
       <c r="I782" s="11"/>
       <c r="J782" s="11"/>
       <c r="K782" s="11"/>
@@ -10995,7 +10936,7 @@
       <c r="E783" s="9"/>
       <c r="F783" s="9"/>
       <c r="G783" s="11"/>
-      <c r="H783" s="13"/>
+      <c r="H783" s="16"/>
       <c r="I783" s="11"/>
       <c r="J783" s="11"/>
       <c r="K783" s="11"/>
@@ -11008,7 +10949,7 @@
       <c r="E784" s="9"/>
       <c r="F784" s="9"/>
       <c r="G784" s="11"/>
-      <c r="H784" s="13"/>
+      <c r="H784" s="16"/>
       <c r="I784" s="11"/>
       <c r="J784" s="11"/>
       <c r="K784" s="11"/>
@@ -11021,7 +10962,7 @@
       <c r="E785" s="9"/>
       <c r="F785" s="9"/>
       <c r="G785" s="11"/>
-      <c r="H785" s="13"/>
+      <c r="H785" s="16"/>
       <c r="I785" s="11"/>
       <c r="J785" s="11"/>
       <c r="K785" s="11"/>
@@ -11034,7 +10975,7 @@
       <c r="E786" s="9"/>
       <c r="F786" s="9"/>
       <c r="G786" s="11"/>
-      <c r="H786" s="13"/>
+      <c r="H786" s="16"/>
       <c r="I786" s="11"/>
       <c r="J786" s="11"/>
       <c r="K786" s="11"/>
@@ -11047,7 +10988,7 @@
       <c r="E787" s="9"/>
       <c r="F787" s="9"/>
       <c r="G787" s="11"/>
-      <c r="H787" s="13"/>
+      <c r="H787" s="16"/>
       <c r="I787" s="11"/>
       <c r="J787" s="11"/>
       <c r="K787" s="11"/>
@@ -11060,7 +11001,7 @@
       <c r="E788" s="9"/>
       <c r="F788" s="9"/>
       <c r="G788" s="11"/>
-      <c r="H788" s="13"/>
+      <c r="H788" s="16"/>
       <c r="I788" s="11"/>
       <c r="J788" s="11"/>
       <c r="K788" s="11"/>
@@ -11073,7 +11014,7 @@
       <c r="E789" s="9"/>
       <c r="F789" s="9"/>
       <c r="G789" s="11"/>
-      <c r="H789" s="13"/>
+      <c r="H789" s="16"/>
       <c r="I789" s="11"/>
       <c r="J789" s="11"/>
       <c r="K789" s="11"/>
@@ -11086,7 +11027,7 @@
       <c r="E790" s="9"/>
       <c r="F790" s="9"/>
       <c r="G790" s="11"/>
-      <c r="H790" s="13"/>
+      <c r="H790" s="16"/>
       <c r="I790" s="11"/>
       <c r="J790" s="11"/>
       <c r="K790" s="11"/>
@@ -11099,7 +11040,7 @@
       <c r="E791" s="9"/>
       <c r="F791" s="9"/>
       <c r="G791" s="11"/>
-      <c r="H791" s="13"/>
+      <c r="H791" s="16"/>
       <c r="I791" s="11"/>
       <c r="J791" s="11"/>
       <c r="K791" s="11"/>
@@ -11112,7 +11053,7 @@
       <c r="E792" s="9"/>
       <c r="F792" s="9"/>
       <c r="G792" s="11"/>
-      <c r="H792" s="13"/>
+      <c r="H792" s="16"/>
       <c r="I792" s="11"/>
       <c r="J792" s="11"/>
       <c r="K792" s="11"/>
@@ -11125,7 +11066,7 @@
       <c r="E793" s="9"/>
       <c r="F793" s="9"/>
       <c r="G793" s="11"/>
-      <c r="H793" s="13"/>
+      <c r="H793" s="16"/>
       <c r="I793" s="11"/>
       <c r="J793" s="11"/>
       <c r="K793" s="11"/>
@@ -11138,7 +11079,7 @@
       <c r="E794" s="9"/>
       <c r="F794" s="9"/>
       <c r="G794" s="11"/>
-      <c r="H794" s="13"/>
+      <c r="H794" s="16"/>
       <c r="I794" s="11"/>
       <c r="J794" s="11"/>
       <c r="K794" s="11"/>
@@ -11151,7 +11092,7 @@
       <c r="E795" s="9"/>
       <c r="F795" s="9"/>
       <c r="G795" s="11"/>
-      <c r="H795" s="13"/>
+      <c r="H795" s="16"/>
       <c r="I795" s="11"/>
       <c r="J795" s="11"/>
       <c r="K795" s="11"/>
@@ -11164,7 +11105,7 @@
       <c r="E796" s="9"/>
       <c r="F796" s="9"/>
       <c r="G796" s="11"/>
-      <c r="H796" s="13"/>
+      <c r="H796" s="16"/>
       <c r="I796" s="11"/>
       <c r="J796" s="11"/>
       <c r="K796" s="11"/>
@@ -11177,7 +11118,7 @@
       <c r="E797" s="9"/>
       <c r="F797" s="9"/>
       <c r="G797" s="11"/>
-      <c r="H797" s="13"/>
+      <c r="H797" s="16"/>
       <c r="I797" s="11"/>
       <c r="J797" s="11"/>
       <c r="K797" s="11"/>
@@ -11190,7 +11131,7 @@
       <c r="E798" s="9"/>
       <c r="F798" s="9"/>
       <c r="G798" s="11"/>
-      <c r="H798" s="13"/>
+      <c r="H798" s="16"/>
       <c r="I798" s="11"/>
       <c r="J798" s="11"/>
       <c r="K798" s="11"/>
@@ -11203,7 +11144,7 @@
       <c r="E799" s="9"/>
       <c r="F799" s="9"/>
       <c r="G799" s="11"/>
-      <c r="H799" s="13"/>
+      <c r="H799" s="16"/>
       <c r="I799" s="11"/>
       <c r="J799" s="11"/>
       <c r="K799" s="11"/>
@@ -11216,7 +11157,7 @@
       <c r="E800" s="9"/>
       <c r="F800" s="9"/>
       <c r="G800" s="11"/>
-      <c r="H800" s="13"/>
+      <c r="H800" s="16"/>
       <c r="I800" s="11"/>
       <c r="J800" s="11"/>
       <c r="K800" s="11"/>
@@ -11229,7 +11170,7 @@
       <c r="E801" s="9"/>
       <c r="F801" s="9"/>
       <c r="G801" s="11"/>
-      <c r="H801" s="13"/>
+      <c r="H801" s="16"/>
       <c r="I801" s="11"/>
       <c r="J801" s="11"/>
       <c r="K801" s="11"/>
@@ -11242,7 +11183,7 @@
       <c r="E802" s="9"/>
       <c r="F802" s="9"/>
       <c r="G802" s="11"/>
-      <c r="H802" s="13"/>
+      <c r="H802" s="16"/>
       <c r="I802" s="11"/>
       <c r="J802" s="11"/>
       <c r="K802" s="11"/>
@@ -11255,7 +11196,7 @@
       <c r="E803" s="9"/>
       <c r="F803" s="9"/>
       <c r="G803" s="11"/>
-      <c r="H803" s="13"/>
+      <c r="H803" s="16"/>
       <c r="I803" s="11"/>
       <c r="J803" s="11"/>
       <c r="K803" s="11"/>
@@ -11268,7 +11209,7 @@
       <c r="E804" s="9"/>
       <c r="F804" s="9"/>
       <c r="G804" s="11"/>
-      <c r="H804" s="13"/>
+      <c r="H804" s="16"/>
       <c r="I804" s="11"/>
       <c r="J804" s="11"/>
       <c r="K804" s="11"/>
@@ -11281,7 +11222,7 @@
       <c r="E805" s="9"/>
       <c r="F805" s="9"/>
       <c r="G805" s="11"/>
-      <c r="H805" s="13"/>
+      <c r="H805" s="16"/>
       <c r="I805" s="11"/>
       <c r="J805" s="11"/>
       <c r="K805" s="11"/>
@@ -11294,7 +11235,7 @@
       <c r="E806" s="9"/>
       <c r="F806" s="9"/>
       <c r="G806" s="11"/>
-      <c r="H806" s="13"/>
+      <c r="H806" s="16"/>
       <c r="I806" s="11"/>
       <c r="J806" s="11"/>
       <c r="K806" s="11"/>
@@ -11307,7 +11248,7 @@
       <c r="E807" s="9"/>
       <c r="F807" s="9"/>
       <c r="G807" s="11"/>
-      <c r="H807" s="13"/>
+      <c r="H807" s="16"/>
       <c r="I807" s="11"/>
       <c r="J807" s="11"/>
       <c r="K807" s="11"/>
@@ -11320,7 +11261,7 @@
       <c r="E808" s="9"/>
       <c r="F808" s="9"/>
       <c r="G808" s="11"/>
-      <c r="H808" s="13"/>
+      <c r="H808" s="16"/>
       <c r="I808" s="11"/>
       <c r="J808" s="11"/>
       <c r="K808" s="11"/>
@@ -11333,7 +11274,7 @@
       <c r="E809" s="9"/>
       <c r="F809" s="9"/>
       <c r="G809" s="11"/>
-      <c r="H809" s="13"/>
+      <c r="H809" s="16"/>
       <c r="I809" s="11"/>
       <c r="J809" s="11"/>
       <c r="K809" s="11"/>
@@ -11346,7 +11287,7 @@
       <c r="E810" s="9"/>
       <c r="F810" s="9"/>
       <c r="G810" s="11"/>
-      <c r="H810" s="13"/>
+      <c r="H810" s="16"/>
       <c r="I810" s="11"/>
       <c r="J810" s="11"/>
       <c r="K810" s="11"/>
@@ -11359,7 +11300,7 @@
       <c r="E811" s="9"/>
       <c r="F811" s="9"/>
       <c r="G811" s="11"/>
-      <c r="H811" s="13"/>
+      <c r="H811" s="16"/>
       <c r="I811" s="11"/>
       <c r="J811" s="11"/>
       <c r="K811" s="11"/>
@@ -11372,7 +11313,7 @@
       <c r="E812" s="9"/>
       <c r="F812" s="9"/>
       <c r="G812" s="11"/>
-      <c r="H812" s="13"/>
+      <c r="H812" s="16"/>
       <c r="I812" s="11"/>
       <c r="J812" s="11"/>
       <c r="K812" s="11"/>
@@ -11385,7 +11326,7 @@
       <c r="E813" s="9"/>
       <c r="F813" s="9"/>
       <c r="G813" s="11"/>
-      <c r="H813" s="13"/>
+      <c r="H813" s="16"/>
       <c r="I813" s="11"/>
       <c r="J813" s="11"/>
       <c r="K813" s="11"/>
@@ -11398,7 +11339,7 @@
       <c r="E814" s="9"/>
       <c r="F814" s="9"/>
       <c r="G814" s="11"/>
-      <c r="H814" s="13"/>
+      <c r="H814" s="16"/>
       <c r="I814" s="11"/>
       <c r="J814" s="11"/>
       <c r="K814" s="11"/>
@@ -11411,7 +11352,7 @@
       <c r="E815" s="9"/>
       <c r="F815" s="9"/>
       <c r="G815" s="11"/>
-      <c r="H815" s="13"/>
+      <c r="H815" s="16"/>
       <c r="I815" s="11"/>
       <c r="J815" s="11"/>
       <c r="K815" s="11"/>
@@ -11424,7 +11365,7 @@
       <c r="E816" s="9"/>
       <c r="F816" s="9"/>
       <c r="G816" s="11"/>
-      <c r="H816" s="13"/>
+      <c r="H816" s="16"/>
       <c r="I816" s="11"/>
       <c r="J816" s="11"/>
       <c r="K816" s="11"/>
@@ -11437,7 +11378,7 @@
       <c r="E817" s="9"/>
       <c r="F817" s="9"/>
       <c r="G817" s="11"/>
-      <c r="H817" s="13"/>
+      <c r="H817" s="16"/>
       <c r="I817" s="11"/>
       <c r="J817" s="11"/>
       <c r="K817" s="11"/>
@@ -11450,7 +11391,7 @@
       <c r="E818" s="9"/>
       <c r="F818" s="9"/>
       <c r="G818" s="11"/>
-      <c r="H818" s="13"/>
+      <c r="H818" s="16"/>
       <c r="I818" s="11"/>
       <c r="J818" s="11"/>
       <c r="K818" s="11"/>
@@ -11463,7 +11404,7 @@
       <c r="E819" s="9"/>
       <c r="F819" s="9"/>
       <c r="G819" s="11"/>
-      <c r="H819" s="13"/>
+      <c r="H819" s="16"/>
       <c r="I819" s="11"/>
       <c r="J819" s="11"/>
       <c r="K819" s="11"/>
@@ -11476,7 +11417,7 @@
       <c r="E820" s="9"/>
       <c r="F820" s="9"/>
       <c r="G820" s="11"/>
-      <c r="H820" s="13"/>
+      <c r="H820" s="16"/>
       <c r="I820" s="11"/>
       <c r="J820" s="11"/>
       <c r="K820" s="11"/>
@@ -11489,7 +11430,7 @@
       <c r="E821" s="9"/>
       <c r="F821" s="9"/>
       <c r="G821" s="11"/>
-      <c r="H821" s="13"/>
+      <c r="H821" s="16"/>
       <c r="I821" s="11"/>
       <c r="J821" s="11"/>
       <c r="K821" s="11"/>
@@ -11502,7 +11443,7 @@
       <c r="E822" s="9"/>
       <c r="F822" s="9"/>
       <c r="G822" s="11"/>
-      <c r="H822" s="13"/>
+      <c r="H822" s="16"/>
       <c r="I822" s="11"/>
       <c r="J822" s="11"/>
       <c r="K822" s="11"/>
@@ -11515,7 +11456,7 @@
       <c r="E823" s="9"/>
       <c r="F823" s="9"/>
       <c r="G823" s="11"/>
-      <c r="H823" s="13"/>
+      <c r="H823" s="16"/>
       <c r="I823" s="11"/>
       <c r="J823" s="11"/>
       <c r="K823" s="11"/>
@@ -11528,7 +11469,7 @@
       <c r="E824" s="9"/>
       <c r="F824" s="9"/>
       <c r="G824" s="11"/>
-      <c r="H824" s="13"/>
+      <c r="H824" s="16"/>
       <c r="I824" s="11"/>
       <c r="J824" s="11"/>
       <c r="K824" s="11"/>
@@ -11541,7 +11482,7 @@
       <c r="E825" s="9"/>
       <c r="F825" s="9"/>
       <c r="G825" s="11"/>
-      <c r="H825" s="13"/>
+      <c r="H825" s="16"/>
       <c r="I825" s="11"/>
       <c r="J825" s="11"/>
       <c r="K825" s="11"/>
@@ -11554,7 +11495,7 @@
       <c r="E826" s="9"/>
       <c r="F826" s="9"/>
       <c r="G826" s="11"/>
-      <c r="H826" s="13"/>
+      <c r="H826" s="16"/>
       <c r="I826" s="11"/>
       <c r="J826" s="11"/>
       <c r="K826" s="11"/>
@@ -11567,7 +11508,7 @@
       <c r="E827" s="9"/>
       <c r="F827" s="9"/>
       <c r="G827" s="11"/>
-      <c r="H827" s="13"/>
+      <c r="H827" s="16"/>
       <c r="I827" s="11"/>
       <c r="J827" s="11"/>
       <c r="K827" s="11"/>
@@ -11580,7 +11521,7 @@
       <c r="E828" s="9"/>
       <c r="F828" s="9"/>
       <c r="G828" s="11"/>
-      <c r="H828" s="13"/>
+      <c r="H828" s="16"/>
       <c r="I828" s="11"/>
       <c r="J828" s="11"/>
       <c r="K828" s="11"/>
@@ -11593,7 +11534,7 @@
       <c r="E829" s="9"/>
       <c r="F829" s="9"/>
       <c r="G829" s="11"/>
-      <c r="H829" s="13"/>
+      <c r="H829" s="16"/>
       <c r="I829" s="11"/>
       <c r="J829" s="11"/>
       <c r="K829" s="11"/>
@@ -11606,7 +11547,7 @@
       <c r="E830" s="9"/>
       <c r="F830" s="9"/>
       <c r="G830" s="11"/>
-      <c r="H830" s="13"/>
+      <c r="H830" s="16"/>
       <c r="I830" s="11"/>
       <c r="J830" s="11"/>
       <c r="K830" s="11"/>
@@ -11619,7 +11560,7 @@
       <c r="E831" s="9"/>
       <c r="F831" s="9"/>
       <c r="G831" s="11"/>
-      <c r="H831" s="13"/>
+      <c r="H831" s="16"/>
       <c r="I831" s="11"/>
       <c r="J831" s="11"/>
       <c r="K831" s="11"/>
@@ -11632,7 +11573,7 @@
       <c r="E832" s="9"/>
       <c r="F832" s="9"/>
       <c r="G832" s="11"/>
-      <c r="H832" s="13"/>
+      <c r="H832" s="16"/>
       <c r="I832" s="11"/>
       <c r="J832" s="11"/>
       <c r="K832" s="11"/>
@@ -11645,7 +11586,7 @@
       <c r="E833" s="9"/>
       <c r="F833" s="9"/>
       <c r="G833" s="11"/>
-      <c r="H833" s="13"/>
+      <c r="H833" s="16"/>
       <c r="I833" s="11"/>
       <c r="J833" s="11"/>
       <c r="K833" s="11"/>
@@ -11658,7 +11599,7 @@
       <c r="E834" s="9"/>
       <c r="F834" s="9"/>
       <c r="G834" s="11"/>
-      <c r="H834" s="13"/>
+      <c r="H834" s="16"/>
       <c r="I834" s="11"/>
       <c r="J834" s="11"/>
       <c r="K834" s="11"/>
@@ -11671,7 +11612,7 @@
       <c r="E835" s="9"/>
       <c r="F835" s="9"/>
       <c r="G835" s="11"/>
-      <c r="H835" s="13"/>
+      <c r="H835" s="16"/>
       <c r="I835" s="11"/>
       <c r="J835" s="11"/>
       <c r="K835" s="11"/>
@@ -11684,7 +11625,7 @@
       <c r="E836" s="9"/>
       <c r="F836" s="9"/>
       <c r="G836" s="11"/>
-      <c r="H836" s="13"/>
+      <c r="H836" s="16"/>
       <c r="I836" s="11"/>
       <c r="J836" s="11"/>
       <c r="K836" s="11"/>
@@ -11697,7 +11638,7 @@
       <c r="E837" s="9"/>
       <c r="F837" s="9"/>
       <c r="G837" s="11"/>
-      <c r="H837" s="13"/>
+      <c r="H837" s="16"/>
       <c r="I837" s="11"/>
       <c r="J837" s="11"/>
       <c r="K837" s="11"/>
@@ -11710,7 +11651,7 @@
       <c r="E838" s="9"/>
       <c r="F838" s="9"/>
       <c r="G838" s="11"/>
-      <c r="H838" s="13"/>
+      <c r="H838" s="16"/>
       <c r="I838" s="11"/>
       <c r="J838" s="11"/>
       <c r="K838" s="11"/>
@@ -11723,7 +11664,7 @@
       <c r="E839" s="9"/>
       <c r="F839" s="9"/>
       <c r="G839" s="11"/>
-      <c r="H839" s="13"/>
+      <c r="H839" s="16"/>
       <c r="I839" s="11"/>
       <c r="J839" s="11"/>
       <c r="K839" s="11"/>
@@ -11736,7 +11677,7 @@
       <c r="E840" s="9"/>
       <c r="F840" s="9"/>
       <c r="G840" s="11"/>
-      <c r="H840" s="13"/>
+      <c r="H840" s="16"/>
       <c r="I840" s="11"/>
       <c r="J840" s="11"/>
       <c r="K840" s="11"/>
@@ -11749,7 +11690,7 @@
       <c r="E841" s="9"/>
       <c r="F841" s="9"/>
       <c r="G841" s="11"/>
-      <c r="H841" s="13"/>
+      <c r="H841" s="16"/>
       <c r="I841" s="11"/>
       <c r="J841" s="11"/>
       <c r="K841" s="11"/>
@@ -11762,7 +11703,7 @@
       <c r="E842" s="9"/>
       <c r="F842" s="9"/>
       <c r="G842" s="11"/>
-      <c r="H842" s="13"/>
+      <c r="H842" s="16"/>
       <c r="I842" s="11"/>
       <c r="J842" s="11"/>
       <c r="K842" s="11"/>
@@ -11775,7 +11716,7 @@
       <c r="E843" s="9"/>
       <c r="F843" s="9"/>
       <c r="G843" s="11"/>
-      <c r="H843" s="13"/>
+      <c r="H843" s="16"/>
       <c r="I843" s="11"/>
       <c r="J843" s="11"/>
       <c r="K843" s="11"/>
@@ -11788,7 +11729,7 @@
       <c r="E844" s="9"/>
       <c r="F844" s="9"/>
       <c r="G844" s="11"/>
-      <c r="H844" s="13"/>
+      <c r="H844" s="16"/>
       <c r="I844" s="11"/>
       <c r="J844" s="11"/>
       <c r="K844" s="11"/>
@@ -11801,7 +11742,7 @@
       <c r="E845" s="9"/>
       <c r="F845" s="9"/>
       <c r="G845" s="11"/>
-      <c r="H845" s="13"/>
+      <c r="H845" s="16"/>
       <c r="I845" s="11"/>
       <c r="J845" s="11"/>
       <c r="K845" s="11"/>
@@ -11814,7 +11755,7 @@
       <c r="E846" s="9"/>
       <c r="F846" s="9"/>
       <c r="G846" s="11"/>
-      <c r="H846" s="13"/>
+      <c r="H846" s="16"/>
       <c r="I846" s="11"/>
       <c r="J846" s="11"/>
       <c r="K846" s="11"/>
@@ -11827,7 +11768,7 @@
       <c r="E847" s="9"/>
       <c r="F847" s="9"/>
       <c r="G847" s="11"/>
-      <c r="H847" s="13"/>
+      <c r="H847" s="16"/>
       <c r="I847" s="11"/>
       <c r="J847" s="11"/>
       <c r="K847" s="11"/>
@@ -11840,7 +11781,7 @@
       <c r="E848" s="9"/>
       <c r="F848" s="9"/>
       <c r="G848" s="11"/>
-      <c r="H848" s="13"/>
+      <c r="H848" s="16"/>
       <c r="I848" s="11"/>
       <c r="J848" s="11"/>
       <c r="K848" s="11"/>
@@ -11853,7 +11794,7 @@
       <c r="E849" s="9"/>
       <c r="F849" s="9"/>
       <c r="G849" s="11"/>
-      <c r="H849" s="13"/>
+      <c r="H849" s="16"/>
       <c r="I849" s="11"/>
       <c r="J849" s="11"/>
       <c r="K849" s="11"/>
@@ -11866,7 +11807,7 @@
       <c r="E850" s="9"/>
       <c r="F850" s="9"/>
       <c r="G850" s="11"/>
-      <c r="H850" s="13"/>
+      <c r="H850" s="16"/>
       <c r="I850" s="11"/>
       <c r="J850" s="11"/>
       <c r="K850" s="11"/>
@@ -11879,7 +11820,7 @@
       <c r="E851" s="9"/>
       <c r="F851" s="9"/>
       <c r="G851" s="11"/>
-      <c r="H851" s="13"/>
+      <c r="H851" s="16"/>
       <c r="I851" s="11"/>
       <c r="J851" s="11"/>
       <c r="K851" s="11"/>
@@ -11892,7 +11833,7 @@
       <c r="E852" s="9"/>
       <c r="F852" s="9"/>
       <c r="G852" s="11"/>
-      <c r="H852" s="13"/>
+      <c r="H852" s="16"/>
       <c r="I852" s="11"/>
       <c r="J852" s="11"/>
       <c r="K852" s="11"/>
@@ -11905,7 +11846,7 @@
       <c r="E853" s="9"/>
       <c r="F853" s="9"/>
       <c r="G853" s="11"/>
-      <c r="H853" s="13"/>
+      <c r="H853" s="16"/>
       <c r="I853" s="11"/>
       <c r="J853" s="11"/>
       <c r="K853" s="11"/>
@@ -11918,7 +11859,7 @@
       <c r="E854" s="9"/>
       <c r="F854" s="9"/>
       <c r="G854" s="11"/>
-      <c r="H854" s="13"/>
+      <c r="H854" s="16"/>
       <c r="I854" s="11"/>
       <c r="J854" s="11"/>
       <c r="K854" s="11"/>
@@ -11931,7 +11872,7 @@
       <c r="E855" s="9"/>
       <c r="F855" s="9"/>
       <c r="G855" s="11"/>
-      <c r="H855" s="13"/>
+      <c r="H855" s="16"/>
       <c r="I855" s="11"/>
       <c r="J855" s="11"/>
       <c r="K855" s="11"/>
@@ -11944,7 +11885,7 @@
       <c r="E856" s="9"/>
       <c r="F856" s="9"/>
       <c r="G856" s="11"/>
-      <c r="H856" s="13"/>
+      <c r="H856" s="16"/>
       <c r="I856" s="11"/>
       <c r="J856" s="11"/>
       <c r="K856" s="11"/>
@@ -11957,7 +11898,7 @@
       <c r="E857" s="9"/>
       <c r="F857" s="9"/>
       <c r="G857" s="11"/>
-      <c r="H857" s="13"/>
+      <c r="H857" s="16"/>
       <c r="I857" s="11"/>
       <c r="J857" s="11"/>
       <c r="K857" s="11"/>
@@ -11970,7 +11911,7 @@
       <c r="E858" s="9"/>
       <c r="F858" s="9"/>
       <c r="G858" s="11"/>
-      <c r="H858" s="13"/>
+      <c r="H858" s="16"/>
       <c r="I858" s="11"/>
       <c r="J858" s="11"/>
       <c r="K858" s="11"/>
@@ -11983,7 +11924,7 @@
       <c r="E859" s="9"/>
       <c r="F859" s="9"/>
       <c r="G859" s="11"/>
-      <c r="H859" s="13"/>
+      <c r="H859" s="16"/>
       <c r="I859" s="11"/>
       <c r="J859" s="11"/>
       <c r="K859" s="11"/>
@@ -11996,7 +11937,7 @@
       <c r="E860" s="9"/>
       <c r="F860" s="9"/>
       <c r="G860" s="11"/>
-      <c r="H860" s="13"/>
+      <c r="H860" s="16"/>
       <c r="I860" s="11"/>
       <c r="J860" s="11"/>
       <c r="K860" s="11"/>
@@ -12009,7 +11950,7 @@
       <c r="E861" s="9"/>
       <c r="F861" s="9"/>
       <c r="G861" s="11"/>
-      <c r="H861" s="13"/>
+      <c r="H861" s="16"/>
       <c r="I861" s="11"/>
       <c r="J861" s="11"/>
       <c r="K861" s="11"/>
@@ -12022,7 +11963,7 @@
       <c r="E862" s="9"/>
       <c r="F862" s="9"/>
       <c r="G862" s="11"/>
-      <c r="H862" s="13"/>
+      <c r="H862" s="16"/>
       <c r="I862" s="11"/>
       <c r="J862" s="11"/>
       <c r="K862" s="11"/>
@@ -12035,7 +11976,7 @@
       <c r="E863" s="9"/>
       <c r="F863" s="9"/>
       <c r="G863" s="11"/>
-      <c r="H863" s="13"/>
+      <c r="H863" s="16"/>
       <c r="I863" s="11"/>
       <c r="J863" s="11"/>
       <c r="K863" s="11"/>
@@ -12048,7 +11989,7 @@
       <c r="E864" s="9"/>
       <c r="F864" s="9"/>
       <c r="G864" s="11"/>
-      <c r="H864" s="13"/>
+      <c r="H864" s="16"/>
       <c r="I864" s="11"/>
       <c r="J864" s="11"/>
       <c r="K864" s="11"/>
@@ -12061,7 +12002,7 @@
       <c r="E865" s="9"/>
       <c r="F865" s="9"/>
       <c r="G865" s="11"/>
-      <c r="H865" s="13"/>
+      <c r="H865" s="16"/>
       <c r="I865" s="11"/>
       <c r="J865" s="11"/>
       <c r="K865" s="11"/>
@@ -12074,7 +12015,7 @@
       <c r="E866" s="9"/>
       <c r="F866" s="9"/>
       <c r="G866" s="11"/>
-      <c r="H866" s="13"/>
+      <c r="H866" s="16"/>
       <c r="I866" s="11"/>
       <c r="J866" s="11"/>
       <c r="K866" s="11"/>
@@ -12087,7 +12028,7 @@
       <c r="E867" s="9"/>
       <c r="F867" s="9"/>
       <c r="G867" s="11"/>
-      <c r="H867" s="13"/>
+      <c r="H867" s="16"/>
       <c r="I867" s="11"/>
       <c r="J867" s="11"/>
       <c r="K867" s="11"/>
@@ -12100,7 +12041,7 @@
       <c r="E868" s="9"/>
       <c r="F868" s="9"/>
       <c r="G868" s="11"/>
-      <c r="H868" s="13"/>
+      <c r="H868" s="16"/>
       <c r="I868" s="11"/>
       <c r="J868" s="11"/>
       <c r="K868" s="11"/>
@@ -12113,7 +12054,7 @@
       <c r="E869" s="9"/>
       <c r="F869" s="9"/>
       <c r="G869" s="11"/>
-      <c r="H869" s="13"/>
+      <c r="H869" s="16"/>
       <c r="I869" s="11"/>
       <c r="J869" s="11"/>
       <c r="K869" s="11"/>
@@ -12126,7 +12067,7 @@
       <c r="E870" s="9"/>
       <c r="F870" s="9"/>
       <c r="G870" s="11"/>
-      <c r="H870" s="13"/>
+      <c r="H870" s="16"/>
       <c r="I870" s="11"/>
       <c r="J870" s="11"/>
       <c r="K870" s="11"/>
@@ -12139,7 +12080,7 @@
       <c r="E871" s="9"/>
       <c r="F871" s="9"/>
       <c r="G871" s="11"/>
-      <c r="H871" s="13"/>
+      <c r="H871" s="16"/>
       <c r="I871" s="11"/>
       <c r="J871" s="11"/>
       <c r="K871" s="11"/>
@@ -12152,7 +12093,7 @@
       <c r="E872" s="9"/>
       <c r="F872" s="9"/>
       <c r="G872" s="11"/>
-      <c r="H872" s="13"/>
+      <c r="H872" s="16"/>
       <c r="I872" s="11"/>
       <c r="J872" s="11"/>
       <c r="K872" s="11"/>
@@ -12165,7 +12106,7 @@
       <c r="E873" s="9"/>
       <c r="F873" s="9"/>
       <c r="G873" s="11"/>
-      <c r="H873" s="13"/>
+      <c r="H873" s="16"/>
       <c r="I873" s="11"/>
       <c r="J873" s="11"/>
       <c r="K873" s="11"/>
@@ -12178,7 +12119,7 @@
       <c r="E874" s="9"/>
       <c r="F874" s="9"/>
       <c r="G874" s="11"/>
-      <c r="H874" s="13"/>
+      <c r="H874" s="16"/>
       <c r="I874" s="11"/>
       <c r="J874" s="11"/>
       <c r="K874" s="11"/>
@@ -12191,7 +12132,7 @@
       <c r="E875" s="9"/>
       <c r="F875" s="9"/>
       <c r="G875" s="11"/>
-      <c r="H875" s="13"/>
+      <c r="H875" s="16"/>
       <c r="I875" s="11"/>
       <c r="J875" s="11"/>
       <c r="K875" s="11"/>
@@ -12204,7 +12145,7 @@
       <c r="E876" s="9"/>
       <c r="F876" s="9"/>
       <c r="G876" s="11"/>
-      <c r="H876" s="13"/>
+      <c r="H876" s="16"/>
       <c r="I876" s="11"/>
       <c r="J876" s="11"/>
       <c r="K876" s="11"/>
@@ -12217,7 +12158,7 @@
       <c r="E877" s="9"/>
       <c r="F877" s="9"/>
       <c r="G877" s="11"/>
-      <c r="H877" s="13"/>
+      <c r="H877" s="16"/>
       <c r="I877" s="11"/>
       <c r="J877" s="11"/>
       <c r="K877" s="11"/>
@@ -12230,7 +12171,7 @@
       <c r="E878" s="9"/>
       <c r="F878" s="9"/>
       <c r="G878" s="11"/>
-      <c r="H878" s="13"/>
+      <c r="H878" s="16"/>
       <c r="I878" s="11"/>
       <c r="J878" s="11"/>
       <c r="K878" s="11"/>
@@ -12243,7 +12184,7 @@
       <c r="E879" s="9"/>
       <c r="F879" s="9"/>
       <c r="G879" s="11"/>
-      <c r="H879" s="13"/>
+      <c r="H879" s="16"/>
       <c r="I879" s="11"/>
       <c r="J879" s="11"/>
       <c r="K879" s="11"/>
@@ -12256,7 +12197,7 @@
       <c r="E880" s="9"/>
       <c r="F880" s="9"/>
       <c r="G880" s="11"/>
-      <c r="H880" s="13"/>
+      <c r="H880" s="16"/>
       <c r="I880" s="11"/>
       <c r="J880" s="11"/>
       <c r="K880" s="11"/>
@@ -12269,7 +12210,7 @@
       <c r="E881" s="9"/>
       <c r="F881" s="9"/>
       <c r="G881" s="11"/>
-      <c r="H881" s="13"/>
+      <c r="H881" s="16"/>
       <c r="I881" s="11"/>
       <c r="J881" s="11"/>
       <c r="K881" s="11"/>
@@ -12282,7 +12223,7 @@
       <c r="E882" s="9"/>
       <c r="F882" s="9"/>
       <c r="G882" s="11"/>
-      <c r="H882" s="13"/>
+      <c r="H882" s="16"/>
       <c r="I882" s="11"/>
       <c r="J882" s="11"/>
       <c r="K882" s="11"/>
@@ -12295,7 +12236,7 @@
       <c r="E883" s="9"/>
       <c r="F883" s="9"/>
       <c r="G883" s="11"/>
-      <c r="H883" s="13"/>
+      <c r="H883" s="16"/>
       <c r="I883" s="11"/>
       <c r="J883" s="11"/>
       <c r="K883" s="11"/>
@@ -12308,7 +12249,7 @@
       <c r="E884" s="9"/>
       <c r="F884" s="9"/>
       <c r="G884" s="11"/>
-      <c r="H884" s="13"/>
+      <c r="H884" s="16"/>
       <c r="I884" s="11"/>
       <c r="J884" s="11"/>
       <c r="K884" s="11"/>
@@ -12321,7 +12262,7 @@
       <c r="E885" s="9"/>
       <c r="F885" s="9"/>
       <c r="G885" s="11"/>
-      <c r="H885" s="13"/>
+      <c r="H885" s="16"/>
       <c r="I885" s="11"/>
       <c r="J885" s="11"/>
       <c r="K885" s="11"/>
@@ -12334,7 +12275,7 @@
       <c r="E886" s="9"/>
       <c r="F886" s="9"/>
       <c r="G886" s="11"/>
-      <c r="H886" s="13"/>
+      <c r="H886" s="16"/>
       <c r="I886" s="11"/>
       <c r="J886" s="11"/>
       <c r="K886" s="11"/>
@@ -12347,7 +12288,7 @@
       <c r="E887" s="9"/>
       <c r="F887" s="9"/>
       <c r="G887" s="11"/>
-      <c r="H887" s="13"/>
+      <c r="H887" s="16"/>
       <c r="I887" s="11"/>
       <c r="J887" s="11"/>
       <c r="K887" s="11"/>
@@ -12360,7 +12301,7 @@
       <c r="E888" s="9"/>
       <c r="F888" s="9"/>
       <c r="G888" s="11"/>
-      <c r="H888" s="13"/>
+      <c r="H888" s="16"/>
       <c r="I888" s="11"/>
       <c r="J888" s="11"/>
       <c r="K888" s="11"/>
@@ -12373,7 +12314,7 @@
       <c r="E889" s="9"/>
       <c r="F889" s="9"/>
       <c r="G889" s="11"/>
-      <c r="H889" s="13"/>
+      <c r="H889" s="16"/>
       <c r="I889" s="11"/>
       <c r="J889" s="11"/>
       <c r="K889" s="11"/>
@@ -12386,7 +12327,7 @@
       <c r="E890" s="9"/>
       <c r="F890" s="9"/>
       <c r="G890" s="11"/>
-      <c r="H890" s="13"/>
+      <c r="H890" s="16"/>
       <c r="I890" s="11"/>
       <c r="J890" s="11"/>
       <c r="K890" s="11"/>
@@ -12399,7 +12340,7 @@
       <c r="E891" s="9"/>
       <c r="F891" s="9"/>
       <c r="G891" s="11"/>
-      <c r="H891" s="13"/>
+      <c r="H891" s="16"/>
       <c r="I891" s="11"/>
       <c r="J891" s="11"/>
       <c r="K891" s="11"/>
@@ -12412,7 +12353,7 @@
       <c r="E892" s="9"/>
       <c r="F892" s="9"/>
       <c r="G892" s="11"/>
-      <c r="H892" s="13"/>
+      <c r="H892" s="16"/>
       <c r="I892" s="11"/>
       <c r="J892" s="11"/>
       <c r="K892" s="11"/>
@@ -12425,7 +12366,7 @@
       <c r="E893" s="9"/>
       <c r="F893" s="9"/>
       <c r="G893" s="11"/>
-      <c r="H893" s="13"/>
+      <c r="H893" s="16"/>
       <c r="I893" s="11"/>
       <c r="J893" s="11"/>
       <c r="K893" s="11"/>
@@ -12438,7 +12379,7 @@
       <c r="E894" s="9"/>
       <c r="F894" s="9"/>
       <c r="G894" s="11"/>
-      <c r="H894" s="13"/>
+      <c r="H894" s="16"/>
       <c r="I894" s="11"/>
       <c r="J894" s="11"/>
       <c r="K894" s="11"/>
@@ -12451,7 +12392,7 @@
       <c r="E895" s="9"/>
       <c r="F895" s="9"/>
       <c r="G895" s="11"/>
-      <c r="H895" s="13"/>
+      <c r="H895" s="16"/>
       <c r="I895" s="11"/>
       <c r="J895" s="11"/>
       <c r="K895" s="11"/>
@@ -12464,7 +12405,7 @@
       <c r="E896" s="9"/>
       <c r="F896" s="9"/>
       <c r="G896" s="11"/>
-      <c r="H896" s="13"/>
+      <c r="H896" s="16"/>
       <c r="I896" s="11"/>
       <c r="J896" s="11"/>
       <c r="K896" s="11"/>
@@ -12477,7 +12418,7 @@
       <c r="E897" s="9"/>
       <c r="F897" s="9"/>
       <c r="G897" s="11"/>
-      <c r="H897" s="13"/>
+      <c r="H897" s="16"/>
       <c r="I897" s="11"/>
       <c r="J897" s="11"/>
       <c r="K897" s="11"/>
@@ -12490,7 +12431,7 @@
       <c r="E898" s="9"/>
       <c r="F898" s="9"/>
       <c r="G898" s="11"/>
-      <c r="H898" s="13"/>
+      <c r="H898" s="16"/>
       <c r="I898" s="11"/>
       <c r="J898" s="11"/>
       <c r="K898" s="11"/>
@@ -12503,7 +12444,7 @@
       <c r="E899" s="9"/>
       <c r="F899" s="9"/>
       <c r="G899" s="11"/>
-      <c r="H899" s="13"/>
+      <c r="H899" s="16"/>
       <c r="I899" s="11"/>
       <c r="J899" s="11"/>
       <c r="K899" s="11"/>
@@ -12516,7 +12457,7 @@
       <c r="E900" s="9"/>
       <c r="F900" s="9"/>
       <c r="G900" s="11"/>
-      <c r="H900" s="13"/>
+      <c r="H900" s="16"/>
       <c r="I900" s="11"/>
       <c r="J900" s="11"/>
       <c r="K900" s="11"/>
@@ -12529,7 +12470,7 @@
       <c r="E901" s="9"/>
       <c r="F901" s="9"/>
       <c r="G901" s="11"/>
-      <c r="H901" s="13"/>
+      <c r="H901" s="16"/>
       <c r="I901" s="11"/>
       <c r="J901" s="11"/>
       <c r="K901" s="11"/>
@@ -12542,7 +12483,7 @@
       <c r="E902" s="9"/>
       <c r="F902" s="9"/>
       <c r="G902" s="11"/>
-      <c r="H902" s="13"/>
+      <c r="H902" s="16"/>
       <c r="I902" s="11"/>
       <c r="J902" s="11"/>
       <c r="K902" s="11"/>
@@ -12555,7 +12496,7 @@
       <c r="E903" s="9"/>
       <c r="F903" s="9"/>
       <c r="G903" s="11"/>
-      <c r="H903" s="13"/>
+      <c r="H903" s="16"/>
       <c r="I903" s="11"/>
       <c r="J903" s="11"/>
       <c r="K903" s="11"/>
@@ -12568,7 +12509,7 @@
       <c r="E904" s="9"/>
       <c r="F904" s="9"/>
       <c r="G904" s="11"/>
-      <c r="H904" s="13"/>
+      <c r="H904" s="16"/>
       <c r="I904" s="11"/>
       <c r="J904" s="11"/>
       <c r="K904" s="11"/>
@@ -12581,7 +12522,7 @@
       <c r="E905" s="9"/>
       <c r="F905" s="9"/>
       <c r="G905" s="11"/>
-      <c r="H905" s="13"/>
+      <c r="H905" s="16"/>
       <c r="I905" s="11"/>
       <c r="J905" s="11"/>
       <c r="K905" s="11"/>
@@ -12594,7 +12535,7 @@
       <c r="E906" s="9"/>
       <c r="F906" s="9"/>
       <c r="G906" s="11"/>
-      <c r="H906" s="13"/>
+      <c r="H906" s="16"/>
       <c r="I906" s="11"/>
       <c r="J906" s="11"/>
       <c r="K906" s="11"/>
@@ -12607,7 +12548,7 @@
       <c r="E907" s="9"/>
       <c r="F907" s="9"/>
       <c r="G907" s="11"/>
-      <c r="H907" s="13"/>
+      <c r="H907" s="16"/>
       <c r="I907" s="11"/>
       <c r="J907" s="11"/>
       <c r="K907" s="11"/>
@@ -12620,7 +12561,7 @@
       <c r="E908" s="9"/>
       <c r="F908" s="9"/>
       <c r="G908" s="11"/>
-      <c r="H908" s="13"/>
+      <c r="H908" s="16"/>
       <c r="I908" s="11"/>
       <c r="J908" s="11"/>
       <c r="K908" s="11"/>
@@ -12633,7 +12574,7 @@
       <c r="E909" s="9"/>
       <c r="F909" s="9"/>
       <c r="G909" s="11"/>
-      <c r="H909" s="13"/>
+      <c r="H909" s="16"/>
       <c r="I909" s="11"/>
       <c r="J909" s="11"/>
       <c r="K909" s="11"/>
@@ -12646,7 +12587,7 @@
       <c r="E910" s="9"/>
       <c r="F910" s="9"/>
       <c r="G910" s="11"/>
-      <c r="H910" s="13"/>
+      <c r="H910" s="16"/>
       <c r="I910" s="11"/>
       <c r="J910" s="11"/>
       <c r="K910" s="11"/>
@@ -12659,7 +12600,7 @@
       <c r="E911" s="9"/>
       <c r="F911" s="9"/>
       <c r="G911" s="11"/>
-      <c r="H911" s="13"/>
+      <c r="H911" s="16"/>
       <c r="I911" s="11"/>
       <c r="J911" s="11"/>
       <c r="K911" s="11"/>
@@ -12672,7 +12613,7 @@
       <c r="E912" s="9"/>
       <c r="F912" s="9"/>
       <c r="G912" s="11"/>
-      <c r="H912" s="13"/>
+      <c r="H912" s="16"/>
       <c r="I912" s="11"/>
       <c r="J912" s="11"/>
       <c r="K912" s="11"/>
@@ -12685,7 +12626,7 @@
       <c r="E913" s="9"/>
       <c r="F913" s="9"/>
       <c r="G913" s="11"/>
-      <c r="H913" s="13"/>
+      <c r="H913" s="16"/>
       <c r="I913" s="11"/>
       <c r="J913" s="11"/>
       <c r="K913" s="11"/>
@@ -12698,7 +12639,7 @@
       <c r="E914" s="9"/>
       <c r="F914" s="9"/>
       <c r="G914" s="11"/>
-      <c r="H914" s="13"/>
+      <c r="H914" s="16"/>
       <c r="I914" s="11"/>
       <c r="J914" s="11"/>
       <c r="K914" s="11"/>
@@ -12711,7 +12652,7 @@
       <c r="E915" s="9"/>
       <c r="F915" s="9"/>
       <c r="G915" s="11"/>
-      <c r="H915" s="13"/>
+      <c r="H915" s="16"/>
       <c r="I915" s="11"/>
       <c r="J915" s="11"/>
       <c r="K915" s="11"/>
@@ -12724,7 +12665,7 @@
       <c r="E916" s="9"/>
       <c r="F916" s="9"/>
       <c r="G916" s="11"/>
-      <c r="H916" s="13"/>
+      <c r="H916" s="16"/>
       <c r="I916" s="11"/>
       <c r="J916" s="11"/>
       <c r="K916" s="11"/>
@@ -12737,7 +12678,7 @@
       <c r="E917" s="9"/>
       <c r="F917" s="9"/>
       <c r="G917" s="11"/>
-      <c r="H917" s="13"/>
+      <c r="H917" s="16"/>
       <c r="I917" s="11"/>
       <c r="J917" s="11"/>
       <c r="K917" s="11"/>
@@ -12750,7 +12691,7 @@
       <c r="E918" s="9"/>
       <c r="F918" s="9"/>
       <c r="G918" s="11"/>
-      <c r="H918" s="13"/>
+      <c r="H918" s="16"/>
       <c r="I918" s="11"/>
       <c r="J918" s="11"/>
       <c r="K918" s="11"/>
@@ -12763,7 +12704,7 @@
       <c r="E919" s="9"/>
       <c r="F919" s="9"/>
       <c r="G919" s="11"/>
-      <c r="H919" s="13"/>
+      <c r="H919" s="16"/>
       <c r="I919" s="11"/>
       <c r="J919" s="11"/>
       <c r="K919" s="11"/>
@@ -12776,7 +12717,7 @@
       <c r="E920" s="9"/>
       <c r="F920" s="9"/>
       <c r="G920" s="11"/>
-      <c r="H920" s="13"/>
+      <c r="H920" s="16"/>
       <c r="I920" s="11"/>
       <c r="J920" s="11"/>
       <c r="K920" s="11"/>
@@ -12789,7 +12730,7 @@
       <c r="E921" s="9"/>
       <c r="F921" s="9"/>
       <c r="G921" s="11"/>
-      <c r="H921" s="13"/>
+      <c r="H921" s="16"/>
       <c r="I921" s="11"/>
       <c r="J921" s="11"/>
       <c r="K921" s="11"/>
@@ -12802,7 +12743,7 @@
       <c r="E922" s="9"/>
       <c r="F922" s="9"/>
       <c r="G922" s="11"/>
-      <c r="H922" s="13"/>
+      <c r="H922" s="16"/>
       <c r="I922" s="11"/>
       <c r="J922" s="11"/>
       <c r="K922" s="11"/>
@@ -12815,7 +12756,7 @@
       <c r="E923" s="9"/>
       <c r="F923" s="9"/>
       <c r="G923" s="11"/>
-      <c r="H923" s="13"/>
+      <c r="H923" s="16"/>
       <c r="I923" s="11"/>
       <c r="J923" s="11"/>
       <c r="K923" s="11"/>
@@ -12828,7 +12769,7 @@
       <c r="E924" s="9"/>
       <c r="F924" s="9"/>
       <c r="G924" s="11"/>
-      <c r="H924" s="13"/>
+      <c r="H924" s="16"/>
       <c r="I924" s="11"/>
       <c r="J924" s="11"/>
       <c r="K924" s="11"/>
@@ -12841,7 +12782,7 @@
       <c r="E925" s="9"/>
       <c r="F925" s="9"/>
       <c r="G925" s="11"/>
-      <c r="H925" s="13"/>
+      <c r="H925" s="16"/>
       <c r="I925" s="11"/>
       <c r="J925" s="11"/>
       <c r="K925" s="11"/>
@@ -12854,7 +12795,7 @@
       <c r="E926" s="9"/>
       <c r="F926" s="9"/>
       <c r="G926" s="11"/>
-      <c r="H926" s="13"/>
+      <c r="H926" s="16"/>
       <c r="I926" s="11"/>
       <c r="J926" s="11"/>
       <c r="K926" s="11"/>
@@ -12867,7 +12808,7 @@
       <c r="E927" s="9"/>
       <c r="F927" s="9"/>
       <c r="G927" s="11"/>
-      <c r="H927" s="13"/>
+      <c r="H927" s="16"/>
       <c r="I927" s="11"/>
       <c r="J927" s="11"/>
       <c r="K927" s="11"/>
@@ -12880,7 +12821,7 @@
       <c r="E928" s="9"/>
       <c r="F928" s="9"/>
       <c r="G928" s="11"/>
-      <c r="H928" s="13"/>
+      <c r="H928" s="16"/>
       <c r="I928" s="11"/>
       <c r="J928" s="11"/>
       <c r="K928" s="11"/>
@@ -12893,7 +12834,7 @@
       <c r="E929" s="9"/>
       <c r="F929" s="9"/>
       <c r="G929" s="11"/>
-      <c r="H929" s="13"/>
+      <c r="H929" s="16"/>
       <c r="I929" s="11"/>
       <c r="J929" s="11"/>
       <c r="K929" s="11"/>
@@ -12906,7 +12847,7 @@
       <c r="E930" s="9"/>
       <c r="F930" s="9"/>
       <c r="G930" s="11"/>
-      <c r="H930" s="13"/>
+      <c r="H930" s="16"/>
       <c r="I930" s="11"/>
       <c r="J930" s="11"/>
       <c r="K930" s="11"/>
@@ -12919,7 +12860,7 @@
       <c r="E931" s="9"/>
       <c r="F931" s="9"/>
       <c r="G931" s="11"/>
-      <c r="H931" s="13"/>
+      <c r="H931" s="16"/>
       <c r="I931" s="11"/>
       <c r="J931" s="11"/>
       <c r="K931" s="11"/>
@@ -12932,7 +12873,7 @@
       <c r="E932" s="9"/>
       <c r="F932" s="9"/>
       <c r="G932" s="11"/>
-      <c r="H932" s="13"/>
+      <c r="H932" s="16"/>
       <c r="I932" s="11"/>
       <c r="J932" s="11"/>
       <c r="K932" s="11"/>
@@ -12945,7 +12886,7 @@
       <c r="E933" s="9"/>
       <c r="F933" s="9"/>
       <c r="G933" s="11"/>
-      <c r="H933" s="13"/>
+      <c r="H933" s="16"/>
       <c r="I933" s="11"/>
       <c r="J933" s="11"/>
       <c r="K933" s="11"/>
@@ -12958,7 +12899,7 @@
       <c r="E934" s="9"/>
       <c r="F934" s="9"/>
       <c r="G934" s="11"/>
-      <c r="H934" s="13"/>
+      <c r="H934" s="16"/>
       <c r="I934" s="11"/>
       <c r="J934" s="11"/>
       <c r="K934" s="11"/>
@@ -12971,7 +12912,7 @@
       <c r="E935" s="9"/>
       <c r="F935" s="9"/>
       <c r="G935" s="11"/>
-      <c r="H935" s="13"/>
+      <c r="H935" s="16"/>
       <c r="I935" s="11"/>
       <c r="J935" s="11"/>
       <c r="K935" s="11"/>
@@ -12984,7 +12925,7 @@
       <c r="E936" s="9"/>
       <c r="F936" s="9"/>
       <c r="G936" s="11"/>
-      <c r="H936" s="13"/>
+      <c r="H936" s="16"/>
       <c r="I936" s="11"/>
       <c r="J936" s="11"/>
       <c r="K936" s="11"/>
@@ -12997,7 +12938,7 @@
       <c r="E937" s="9"/>
       <c r="F937" s="9"/>
       <c r="G937" s="11"/>
-      <c r="H937" s="13"/>
+      <c r="H937" s="16"/>
       <c r="I937" s="11"/>
       <c r="J937" s="11"/>
       <c r="K937" s="11"/>
@@ -13010,7 +12951,7 @@
       <c r="E938" s="9"/>
       <c r="F938" s="9"/>
       <c r="G938" s="11"/>
-      <c r="H938" s="13"/>
+      <c r="H938" s="16"/>
       <c r="I938" s="11"/>
       <c r="J938" s="11"/>
       <c r="K938" s="11"/>
@@ -13023,7 +12964,7 @@
       <c r="E939" s="9"/>
       <c r="F939" s="9"/>
       <c r="G939" s="11"/>
-      <c r="H939" s="13"/>
+      <c r="H939" s="16"/>
       <c r="I939" s="11"/>
       <c r="J939" s="11"/>
       <c r="K939" s="11"/>
@@ -13036,7 +12977,7 @@
       <c r="E940" s="9"/>
       <c r="F940" s="9"/>
       <c r="G940" s="11"/>
-      <c r="H940" s="13"/>
+      <c r="H940" s="16"/>
       <c r="I940" s="11"/>
       <c r="J940" s="11"/>
       <c r="K940" s="11"/>
@@ -13049,7 +12990,7 @@
       <c r="E941" s="9"/>
       <c r="F941" s="9"/>
       <c r="G941" s="11"/>
-      <c r="H941" s="13"/>
+      <c r="H941" s="16"/>
       <c r="I941" s="11"/>
       <c r="J941" s="11"/>
       <c r="K941" s="11"/>
@@ -13062,7 +13003,7 @@
       <c r="E942" s="9"/>
       <c r="F942" s="9"/>
       <c r="G942" s="11"/>
-      <c r="H942" s="13"/>
+      <c r="H942" s="16"/>
       <c r="I942" s="11"/>
       <c r="J942" s="11"/>
       <c r="K942" s="11"/>
@@ -13075,7 +13016,7 @@
       <c r="E943" s="9"/>
       <c r="F943" s="9"/>
       <c r="G943" s="11"/>
-      <c r="H943" s="13"/>
+      <c r="H943" s="16"/>
       <c r="I943" s="11"/>
       <c r="J943" s="11"/>
       <c r="K943" s="11"/>
@@ -13088,7 +13029,7 @@
       <c r="E944" s="9"/>
       <c r="F944" s="9"/>
       <c r="G944" s="11"/>
-      <c r="H944" s="13"/>
+      <c r="H944" s="16"/>
       <c r="I944" s="11"/>
       <c r="J944" s="11"/>
       <c r="K944" s="11"/>
@@ -13101,7 +13042,7 @@
       <c r="E945" s="9"/>
       <c r="F945" s="9"/>
       <c r="G945" s="11"/>
-      <c r="H945" s="13"/>
+      <c r="H945" s="16"/>
       <c r="I945" s="11"/>
       <c r="J945" s="11"/>
       <c r="K945" s="11"/>
@@ -13114,7 +13055,7 @@
       <c r="E946" s="9"/>
       <c r="F946" s="9"/>
       <c r="G946" s="11"/>
-      <c r="H946" s="13"/>
+      <c r="H946" s="16"/>
       <c r="I946" s="11"/>
       <c r="J946" s="11"/>
       <c r="K946" s="11"/>
@@ -13127,7 +13068,7 @@
       <c r="E947" s="9"/>
       <c r="F947" s="9"/>
       <c r="G947" s="11"/>
-      <c r="H947" s="13"/>
+      <c r="H947" s="16"/>
       <c r="I947" s="11"/>
       <c r="J947" s="11"/>
       <c r="K947" s="11"/>
@@ -13140,7 +13081,7 @@
       <c r="E948" s="9"/>
       <c r="F948" s="9"/>
       <c r="G948" s="11"/>
-      <c r="H948" s="13"/>
+      <c r="H948" s="16"/>
       <c r="I948" s="11"/>
       <c r="J948" s="11"/>
       <c r="K948" s="11"/>
@@ -13153,7 +13094,7 @@
       <c r="E949" s="9"/>
       <c r="F949" s="9"/>
       <c r="G949" s="11"/>
-      <c r="H949" s="13"/>
+      <c r="H949" s="16"/>
       <c r="I949" s="11"/>
       <c r="J949" s="11"/>
       <c r="K949" s="11"/>
@@ -13166,7 +13107,7 @@
       <c r="E950" s="9"/>
       <c r="F950" s="9"/>
       <c r="G950" s="11"/>
-      <c r="H950" s="13"/>
+      <c r="H950" s="16"/>
       <c r="I950" s="11"/>
       <c r="J950" s="11"/>
       <c r="K950" s="11"/>
@@ -13179,7 +13120,7 @@
       <c r="E951" s="9"/>
       <c r="F951" s="9"/>
       <c r="G951" s="11"/>
-      <c r="H951" s="13"/>
+      <c r="H951" s="16"/>
       <c r="I951" s="11"/>
       <c r="J951" s="11"/>
       <c r="K951" s="11"/>
@@ -13192,7 +13133,7 @@
       <c r="E952" s="9"/>
       <c r="F952" s="9"/>
       <c r="G952" s="11"/>
-      <c r="H952" s="13"/>
+      <c r="H952" s="16"/>
       <c r="I952" s="11"/>
       <c r="J952" s="11"/>
       <c r="K952" s="11"/>
@@ -13205,7 +13146,7 @@
       <c r="E953" s="9"/>
       <c r="F953" s="9"/>
       <c r="G953" s="11"/>
-      <c r="H953" s="13"/>
+      <c r="H953" s="16"/>
       <c r="I953" s="11"/>
       <c r="J953" s="11"/>
       <c r="K953" s="11"/>
@@ -13218,7 +13159,7 @@
       <c r="E954" s="9"/>
       <c r="F954" s="9"/>
       <c r="G954" s="11"/>
-      <c r="H954" s="13"/>
+      <c r="H954" s="16"/>
       <c r="I954" s="11"/>
       <c r="J954" s="11"/>
       <c r="K954" s="11"/>
@@ -13231,7 +13172,7 @@
       <c r="E955" s="9"/>
       <c r="F955" s="9"/>
       <c r="G955" s="11"/>
-      <c r="H955" s="13"/>
+      <c r="H955" s="16"/>
       <c r="I955" s="11"/>
       <c r="J955" s="11"/>
       <c r="K955" s="11"/>
@@ -13244,7 +13185,7 @@
       <c r="E956" s="9"/>
       <c r="F956" s="9"/>
       <c r="G956" s="11"/>
-      <c r="H956" s="13"/>
+      <c r="H956" s="16"/>
       <c r="I956" s="11"/>
       <c r="J956" s="11"/>
       <c r="K956" s="11"/>
@@ -13257,7 +13198,7 @@
       <c r="E957" s="9"/>
       <c r="F957" s="9"/>
       <c r="G957" s="11"/>
-      <c r="H957" s="13"/>
+      <c r="H957" s="16"/>
       <c r="I957" s="11"/>
       <c r="J957" s="11"/>
       <c r="K957" s="11"/>
@@ -13270,7 +13211,7 @@
       <c r="E958" s="9"/>
       <c r="F958" s="9"/>
       <c r="G958" s="11"/>
-      <c r="H958" s="13"/>
+      <c r="H958" s="16"/>
       <c r="I958" s="11"/>
       <c r="J958" s="11"/>
       <c r="K958" s="11"/>
@@ -13283,7 +13224,7 @@
       <c r="E959" s="9"/>
       <c r="F959" s="9"/>
       <c r="G959" s="11"/>
-      <c r="H959" s="13"/>
+      <c r="H959" s="16"/>
       <c r="I959" s="11"/>
       <c r="J959" s="11"/>
       <c r="K959" s="11"/>
@@ -13296,7 +13237,7 @@
       <c r="E960" s="9"/>
       <c r="F960" s="9"/>
       <c r="G960" s="11"/>
-      <c r="H960" s="13"/>
+      <c r="H960" s="16"/>
       <c r="I960" s="11"/>
       <c r="J960" s="11"/>
       <c r="K960" s="11"/>
@@ -13309,7 +13250,7 @@
       <c r="E961" s="9"/>
       <c r="F961" s="9"/>
       <c r="G961" s="11"/>
-      <c r="H961" s="13"/>
+      <c r="H961" s="16"/>
       <c r="I961" s="11"/>
       <c r="J961" s="11"/>
       <c r="K961" s="11"/>
@@ -13322,7 +13263,7 @@
       <c r="E962" s="9"/>
       <c r="F962" s="9"/>
       <c r="G962" s="11"/>
-      <c r="H962" s="13"/>
+      <c r="H962" s="16"/>
       <c r="I962" s="11"/>
       <c r="J962" s="11"/>
       <c r="K962" s="11"/>
@@ -13335,7 +13276,7 @@
       <c r="E963" s="9"/>
       <c r="F963" s="9"/>
       <c r="G963" s="11"/>
-      <c r="H963" s="13"/>
+      <c r="H963" s="16"/>
       <c r="I963" s="11"/>
       <c r="J963" s="11"/>
       <c r="K963" s="11"/>
@@ -13348,7 +13289,7 @@
       <c r="E964" s="9"/>
       <c r="F964" s="9"/>
       <c r="G964" s="11"/>
-      <c r="H964" s="13"/>
+      <c r="H964" s="16"/>
       <c r="I964" s="11"/>
       <c r="J964" s="11"/>
       <c r="K964" s="11"/>
@@ -13361,7 +13302,7 @@
       <c r="E965" s="9"/>
       <c r="F965" s="9"/>
       <c r="G965" s="11"/>
-      <c r="H965" s="13"/>
+      <c r="H965" s="16"/>
       <c r="I965" s="11"/>
       <c r="J965" s="11"/>
       <c r="K965" s="11"/>
@@ -13374,7 +13315,7 @@
       <c r="E966" s="9"/>
       <c r="F966" s="9"/>
       <c r="G966" s="11"/>
-      <c r="H966" s="13"/>
+      <c r="H966" s="16"/>
       <c r="I966" s="11"/>
       <c r="J966" s="11"/>
       <c r="K966" s="11"/>
@@ -13387,7 +13328,7 @@
       <c r="E967" s="9"/>
       <c r="F967" s="9"/>
       <c r="G967" s="11"/>
-      <c r="H967" s="13"/>
+      <c r="H967" s="16"/>
       <c r="I967" s="11"/>
       <c r="J967" s="11"/>
       <c r="K967" s="11"/>
@@ -13400,7 +13341,7 @@
       <c r="E968" s="9"/>
       <c r="F968" s="9"/>
       <c r="G968" s="11"/>
-      <c r="H968" s="13"/>
+      <c r="H968" s="16"/>
       <c r="I968" s="11"/>
       <c r="J968" s="11"/>
       <c r="K968" s="11"/>
@@ -13413,7 +13354,7 @@
       <c r="E969" s="9"/>
       <c r="F969" s="9"/>
       <c r="G969" s="11"/>
-      <c r="H969" s="13"/>
+      <c r="H969" s="16"/>
       <c r="I969" s="11"/>
       <c r="J969" s="11"/>
       <c r="K969" s="11"/>
@@ -13426,7 +13367,7 @@
       <c r="E970" s="9"/>
       <c r="F970" s="9"/>
       <c r="G970" s="11"/>
-      <c r="H970" s="13"/>
+      <c r="H970" s="16"/>
       <c r="I970" s="11"/>
       <c r="J970" s="11"/>
       <c r="K970" s="11"/>
@@ -13439,7 +13380,7 @@
       <c r="E971" s="9"/>
       <c r="F971" s="9"/>
       <c r="G971" s="11"/>
-      <c r="H971" s="13"/>
+      <c r="H971" s="16"/>
       <c r="I971" s="11"/>
       <c r="J971" s="11"/>
       <c r="K971" s="11"/>
@@ -13452,7 +13393,7 @@
       <c r="E972" s="9"/>
       <c r="F972" s="9"/>
       <c r="G972" s="11"/>
-      <c r="H972" s="13"/>
+      <c r="H972" s="16"/>
       <c r="I972" s="11"/>
       <c r="J972" s="11"/>
       <c r="K972" s="11"/>
@@ -13465,7 +13406,7 @@
       <c r="E973" s="9"/>
       <c r="F973" s="9"/>
       <c r="G973" s="11"/>
-      <c r="H973" s="13"/>
+      <c r="H973" s="16"/>
       <c r="I973" s="11"/>
       <c r="J973" s="11"/>
       <c r="K973" s="11"/>
@@ -13478,7 +13419,7 @@
       <c r="E974" s="9"/>
       <c r="F974" s="9"/>
       <c r="G974" s="11"/>
-      <c r="H974" s="13"/>
+      <c r="H974" s="16"/>
       <c r="I974" s="11"/>
       <c r="J974" s="11"/>
       <c r="K974" s="11"/>
@@ -13491,7 +13432,7 @@
       <c r="E975" s="9"/>
       <c r="F975" s="9"/>
       <c r="G975" s="11"/>
-      <c r="H975" s="13"/>
+      <c r="H975" s="16"/>
       <c r="I975" s="11"/>
       <c r="J975" s="11"/>
       <c r="K975" s="11"/>
@@ -13504,7 +13445,7 @@
       <c r="E976" s="9"/>
       <c r="F976" s="9"/>
       <c r="G976" s="11"/>
-      <c r="H976" s="13"/>
+      <c r="H976" s="16"/>
       <c r="I976" s="11"/>
       <c r="J976" s="11"/>
       <c r="K976" s="11"/>
@@ -13517,7 +13458,7 @@
       <c r="E977" s="9"/>
       <c r="F977" s="9"/>
       <c r="G977" s="11"/>
-      <c r="H977" s="13"/>
+      <c r="H977" s="16"/>
       <c r="I977" s="11"/>
       <c r="J977" s="11"/>
       <c r="K977" s="11"/>
@@ -13530,7 +13471,7 @@
       <c r="E978" s="9"/>
       <c r="F978" s="9"/>
       <c r="G978" s="11"/>
-      <c r="H978" s="13"/>
+      <c r="H978" s="16"/>
       <c r="I978" s="11"/>
       <c r="J978" s="11"/>
       <c r="K978" s="11"/>
@@ -13543,7 +13484,7 @@
       <c r="E979" s="9"/>
       <c r="F979" s="9"/>
       <c r="G979" s="11"/>
-      <c r="H979" s="13"/>
+      <c r="H979" s="16"/>
       <c r="I979" s="11"/>
       <c r="J979" s="11"/>
       <c r="K979" s="11"/>
@@ -13556,7 +13497,7 @@
       <c r="E980" s="9"/>
       <c r="F980" s="9"/>
       <c r="G980" s="11"/>
-      <c r="H980" s="13"/>
+      <c r="H980" s="16"/>
       <c r="I980" s="11"/>
       <c r="J980" s="11"/>
       <c r="K980" s="11"/>
@@ -13569,7 +13510,7 @@
       <c r="E981" s="9"/>
       <c r="F981" s="9"/>
       <c r="G981" s="11"/>
-      <c r="H981" s="13"/>
+      <c r="H981" s="16"/>
       <c r="I981" s="11"/>
       <c r="J981" s="11"/>
       <c r="K981" s="11"/>
@@ -13582,7 +13523,7 @@
       <c r="E982" s="9"/>
       <c r="F982" s="9"/>
       <c r="G982" s="11"/>
-      <c r="H982" s="13"/>
+      <c r="H982" s="16"/>
       <c r="I982" s="11"/>
       <c r="J982" s="11"/>
       <c r="K982" s="11"/>
@@ -13595,7 +13536,7 @@
       <c r="E983" s="9"/>
       <c r="F983" s="9"/>
       <c r="G983" s="11"/>
-      <c r="H983" s="13"/>
+      <c r="H983" s="16"/>
       <c r="I983" s="11"/>
       <c r="J983" s="11"/>
       <c r="K983" s="11"/>
@@ -13608,7 +13549,7 @@
       <c r="E984" s="9"/>
       <c r="F984" s="9"/>
       <c r="G984" s="11"/>
-      <c r="H984" s="13"/>
+      <c r="H984" s="16"/>
       <c r="I984" s="11"/>
       <c r="J984" s="11"/>
       <c r="K984" s="11"/>
@@ -13621,7 +13562,7 @@
       <c r="E985" s="9"/>
       <c r="F985" s="9"/>
       <c r="G985" s="11"/>
-      <c r="H985" s="13"/>
+      <c r="H985" s="16"/>
       <c r="I985" s="11"/>
       <c r="J985" s="11"/>
       <c r="K985" s="11"/>
@@ -13634,7 +13575,7 @@
       <c r="E986" s="9"/>
       <c r="F986" s="9"/>
       <c r="G986" s="11"/>
-      <c r="H986" s="13"/>
+      <c r="H986" s="16"/>
       <c r="I986" s="11"/>
       <c r="J986" s="11"/>
       <c r="K986" s="11"/>
@@ -13647,7 +13588,7 @@
       <c r="E987" s="9"/>
       <c r="F987" s="9"/>
       <c r="G987" s="11"/>
-      <c r="H987" s="13"/>
+      <c r="H987" s="16"/>
       <c r="I987" s="11"/>
       <c r="J987" s="11"/>
       <c r="K987" s="11"/>
@@ -13660,7 +13601,7 @@
       <c r="E988" s="9"/>
       <c r="F988" s="9"/>
       <c r="G988" s="11"/>
-      <c r="H988" s="13"/>
+      <c r="H988" s="16"/>
       <c r="I988" s="11"/>
       <c r="J988" s="11"/>
       <c r="K988" s="11"/>
@@ -13673,7 +13614,7 @@
       <c r="E989" s="9"/>
       <c r="F989" s="9"/>
       <c r="G989" s="11"/>
-      <c r="H989" s="13"/>
+      <c r="H989" s="16"/>
       <c r="I989" s="11"/>
       <c r="J989" s="11"/>
       <c r="K989" s="11"/>
@@ -13686,7 +13627,7 @@
       <c r="E990" s="9"/>
       <c r="F990" s="9"/>
       <c r="G990" s="11"/>
-      <c r="H990" s="13"/>
+      <c r="H990" s="16"/>
       <c r="I990" s="11"/>
       <c r="J990" s="11"/>
       <c r="K990" s="11"/>
@@ -13699,7 +13640,7 @@
       <c r="E991" s="9"/>
       <c r="F991" s="9"/>
       <c r="G991" s="11"/>
-      <c r="H991" s="13"/>
+      <c r="H991" s="16"/>
       <c r="I991" s="11"/>
       <c r="J991" s="11"/>
       <c r="K991" s="11"/>
@@ -13712,7 +13653,7 @@
       <c r="E992" s="9"/>
       <c r="F992" s="9"/>
       <c r="G992" s="11"/>
-      <c r="H992" s="13"/>
+      <c r="H992" s="16"/>
       <c r="I992" s="11"/>
       <c r="J992" s="11"/>
       <c r="K992" s="11"/>
@@ -13725,7 +13666,7 @@
       <c r="E993" s="9"/>
       <c r="F993" s="9"/>
       <c r="G993" s="11"/>
-      <c r="H993" s="13"/>
+      <c r="H993" s="16"/>
       <c r="I993" s="11"/>
       <c r="J993" s="11"/>
       <c r="K993" s="11"/>
@@ -13738,7 +13679,7 @@
       <c r="E994" s="9"/>
       <c r="F994" s="9"/>
       <c r="G994" s="11"/>
-      <c r="H994" s="13"/>
+      <c r="H994" s="16"/>
       <c r="I994" s="11"/>
       <c r="J994" s="11"/>
       <c r="K994" s="11"/>
@@ -13751,7 +13692,7 @@
       <c r="E995" s="9"/>
       <c r="F995" s="9"/>
       <c r="G995" s="11"/>
-      <c r="H995" s="13"/>
+      <c r="H995" s="16"/>
       <c r="I995" s="11"/>
       <c r="J995" s="11"/>
       <c r="K995" s="11"/>
@@ -13764,7 +13705,7 @@
       <c r="E996" s="9"/>
       <c r="F996" s="9"/>
       <c r="G996" s="11"/>
-      <c r="H996" s="13"/>
+      <c r="H996" s="16"/>
       <c r="I996" s="11"/>
       <c r="J996" s="11"/>
       <c r="K996" s="11"/>
@@ -13777,7 +13718,7 @@
       <c r="E997" s="9"/>
       <c r="F997" s="9"/>
       <c r="G997" s="11"/>
-      <c r="H997" s="13"/>
+      <c r="H997" s="16"/>
       <c r="I997" s="11"/>
       <c r="J997" s="11"/>
       <c r="K997" s="11"/>
@@ -13790,7 +13731,7 @@
       <c r="E998" s="9"/>
       <c r="F998" s="9"/>
       <c r="G998" s="11"/>
-      <c r="H998" s="13"/>
+      <c r="H998" s="16"/>
       <c r="I998" s="11"/>
       <c r="J998" s="11"/>
       <c r="K998" s="11"/>
@@ -13803,7 +13744,7 @@
       <c r="E999" s="9"/>
       <c r="F999" s="9"/>
       <c r="G999" s="11"/>
-      <c r="H999" s="13"/>
+      <c r="H999" s="16"/>
       <c r="I999" s="11"/>
       <c r="J999" s="11"/>
       <c r="K999" s="11"/>
@@ -13816,17 +13757,16 @@
       <c r="E1000" s="9"/>
       <c r="F1000" s="9"/>
       <c r="G1000" s="11"/>
-      <c r="H1000" s="13"/>
+      <c r="H1000" s="16"/>
       <c r="I1000" s="11"/>
       <c r="J1000" s="11"/>
       <c r="K1000" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>